--- a/Coordenadoria/02_Dados_Tratados/base_vencimentos_tratada.xlsx
+++ b/Coordenadoria/02_Dados_Tratados/base_vencimentos_tratada.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1236" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1085" uniqueCount="310">
   <si>
     <t>matricula</t>
   </si>
@@ -64,405 +64,351 @@
     <t>PCE-PC2360</t>
   </si>
   <si>
+    <t>A00260B2</t>
+  </si>
+  <si>
     <t>18B464</t>
   </si>
   <si>
+    <t>PCE-PC2055</t>
+  </si>
+  <si>
     <t>PZL/12/085</t>
   </si>
   <si>
-    <t>A00260B2</t>
-  </si>
-  <si>
-    <t>RWA11F115</t>
-  </si>
-  <si>
-    <t>CRAZAEYU119</t>
-  </si>
-  <si>
-    <t>A0040MHL</t>
-  </si>
-  <si>
-    <t>A004166F</t>
-  </si>
-  <si>
-    <t>YUAB001H725</t>
-  </si>
-  <si>
-    <t>PCE-PC2232</t>
-  </si>
-  <si>
-    <t>PCE-PC2055</t>
+    <t>PC-E17377</t>
   </si>
   <si>
     <t>PC-EPC0431</t>
   </si>
   <si>
+    <t>PCE-PC2050</t>
+  </si>
+  <si>
+    <t>5X499</t>
+  </si>
+  <si>
+    <t>6X312</t>
+  </si>
+  <si>
+    <t>A000CT12</t>
+  </si>
+  <si>
+    <t>5H725</t>
+  </si>
+  <si>
     <t>PCE-PC0797</t>
   </si>
   <si>
-    <t>5X424</t>
-  </si>
-  <si>
-    <t>5H725</t>
-  </si>
-  <si>
-    <t>A000CT12</t>
-  </si>
-  <si>
-    <t>6X312</t>
-  </si>
-  <si>
-    <t>5X499</t>
-  </si>
-  <si>
-    <t>PCE-PC2050</t>
-  </si>
-  <si>
-    <t>090520002930A9</t>
-  </si>
-  <si>
-    <t>98053601.0</t>
+    <t>CRAZAFLZ243</t>
   </si>
   <si>
     <t>PCE-PC2358</t>
   </si>
   <si>
-    <t>PCE-PC2223</t>
-  </si>
-  <si>
-    <t>CRAZAFLZ243</t>
+    <t>5784241.0</t>
+  </si>
+  <si>
+    <t>PCE-PC0743</t>
+  </si>
+  <si>
+    <t>090520028327B</t>
+  </si>
+  <si>
+    <t>PCE-PC1666</t>
+  </si>
+  <si>
+    <t>090520028EC43</t>
+  </si>
+  <si>
+    <t>PCE-PC1211</t>
+  </si>
+  <si>
+    <t>PCE-PC1570</t>
+  </si>
+  <si>
+    <t>16829339.0</t>
+  </si>
+  <si>
+    <t>26.0</t>
+  </si>
+  <si>
+    <t>2223.0</t>
+  </si>
+  <si>
+    <t>905200298400.0</t>
+  </si>
+  <si>
+    <t>PCE-PC2261</t>
+  </si>
+  <si>
+    <t>17176905.0</t>
+  </si>
+  <si>
+    <t>4572.0</t>
+  </si>
+  <si>
+    <t>338.0</t>
+  </si>
+  <si>
+    <t>9757.0</t>
+  </si>
+  <si>
+    <t>10000618.0</t>
+  </si>
+  <si>
+    <t>11100371.0</t>
+  </si>
+  <si>
+    <t>PZLL010SB</t>
+  </si>
+  <si>
+    <t>9038.0</t>
+  </si>
+  <si>
+    <t>A0037CAC</t>
+  </si>
+  <si>
+    <t>9601404.0</t>
+  </si>
+  <si>
+    <t>9802842.0</t>
+  </si>
+  <si>
+    <t>16A856</t>
+  </si>
+  <si>
+    <t>16799705.0</t>
+  </si>
+  <si>
+    <t>9804953.0</t>
+  </si>
+  <si>
+    <t>862.0</t>
+  </si>
+  <si>
+    <t>9804951.0</t>
+  </si>
+  <si>
+    <t>11200478.0</t>
+  </si>
+  <si>
+    <t>11402681.0</t>
+  </si>
+  <si>
+    <t>7475.0</t>
+  </si>
+  <si>
+    <t>11A</t>
+  </si>
+  <si>
+    <t>1705.0</t>
+  </si>
+  <si>
+    <t>PZL/12/060</t>
+  </si>
+  <si>
+    <t>JHZ-16-047</t>
+  </si>
+  <si>
+    <t>2K221</t>
+  </si>
+  <si>
+    <t>D-0397408</t>
+  </si>
+  <si>
+    <t>391730-020</t>
+  </si>
+  <si>
+    <t>110076.0</t>
+  </si>
+  <si>
+    <t>170-07437</t>
+  </si>
+  <si>
+    <t>B10811395</t>
+  </si>
+  <si>
+    <t>10603746.0</t>
+  </si>
+  <si>
+    <t>10BC80</t>
+  </si>
+  <si>
+    <t>100A</t>
+  </si>
+  <si>
+    <t>1779.0</t>
+  </si>
+  <si>
+    <t>929.0</t>
+  </si>
+  <si>
+    <t>D58293653</t>
+  </si>
+  <si>
+    <t>A-24022576</t>
+  </si>
+  <si>
+    <t>70.0</t>
   </si>
   <si>
     <t>PCE-PC2257</t>
   </si>
   <si>
-    <t>PCE-PC1211</t>
+    <t>PCE-PC0776</t>
+  </si>
+  <si>
+    <t>157.0</t>
+  </si>
+  <si>
+    <t>44.0</t>
+  </si>
+  <si>
+    <t>61.0</t>
+  </si>
+  <si>
+    <t>71.0</t>
+  </si>
+  <si>
+    <t>393069-038</t>
+  </si>
+  <si>
+    <t>G-45677217</t>
+  </si>
+  <si>
+    <t>7869.0</t>
+  </si>
+  <si>
+    <t>D-00397388</t>
+  </si>
+  <si>
+    <t>73.0</t>
+  </si>
+  <si>
+    <t>240.0</t>
+  </si>
+  <si>
+    <t>D00398015</t>
+  </si>
+  <si>
+    <t>248.0</t>
+  </si>
+  <si>
+    <t>8.0</t>
+  </si>
+  <si>
+    <t>E09393184</t>
+  </si>
+  <si>
+    <t>210-10043</t>
+  </si>
+  <si>
+    <t>D00398016</t>
+  </si>
+  <si>
+    <t>D00397796</t>
+  </si>
+  <si>
+    <t>9600123.0</t>
+  </si>
+  <si>
+    <t>B10811720</t>
+  </si>
+  <si>
+    <t>D-00397408</t>
+  </si>
+  <si>
+    <t>7044.0</t>
+  </si>
+  <si>
+    <t>210-10039</t>
+  </si>
+  <si>
+    <t>2986900100469.0</t>
+  </si>
+  <si>
+    <t>3726.0</t>
+  </si>
+  <si>
+    <t>I-01810674</t>
+  </si>
+  <si>
+    <t>210-13181</t>
+  </si>
+  <si>
+    <t>11100370.0</t>
+  </si>
+  <si>
+    <t>912962.0</t>
+  </si>
+  <si>
+    <t>7911.0</t>
+  </si>
+  <si>
+    <t>10000617.0</t>
+  </si>
+  <si>
+    <t>D00398018</t>
+  </si>
+  <si>
+    <t>2986900100392.0</t>
+  </si>
+  <si>
+    <t>2986900100467.0</t>
+  </si>
+  <si>
+    <t>2986900100513.0</t>
+  </si>
+  <si>
+    <t>960707.0</t>
+  </si>
+  <si>
+    <t>210-10042</t>
+  </si>
+  <si>
+    <t>5784239.0</t>
+  </si>
+  <si>
+    <t>T-24634412</t>
+  </si>
+  <si>
+    <t>396315-038</t>
+  </si>
+  <si>
+    <t>D00397793</t>
+  </si>
+  <si>
+    <t>399910-010</t>
+  </si>
+  <si>
+    <t>1000186-001</t>
+  </si>
+  <si>
+    <t>399407-032</t>
+  </si>
+  <si>
+    <t>397401-005</t>
+  </si>
+  <si>
+    <t>D58293589</t>
+  </si>
+  <si>
+    <t>F66943</t>
+  </si>
+  <si>
+    <t>392140-009</t>
   </si>
   <si>
     <t>PCE-PC1002</t>
   </si>
   <si>
-    <t>PZL/10/027</t>
-  </si>
-  <si>
-    <t>26.0</t>
-  </si>
-  <si>
-    <t>PCE-PC0776</t>
-  </si>
-  <si>
-    <t>905200298400.0</t>
-  </si>
-  <si>
-    <t>2223.0</t>
-  </si>
-  <si>
-    <t>PCE-PC2261</t>
-  </si>
-  <si>
-    <t>090520028327B</t>
-  </si>
-  <si>
-    <t>16829339.0</t>
-  </si>
-  <si>
-    <t>9T787</t>
-  </si>
-  <si>
-    <t>PZL/07/088</t>
-  </si>
-  <si>
-    <t>PCE-PC1570</t>
-  </si>
-  <si>
-    <t>17176905.0</t>
-  </si>
-  <si>
-    <t>PZL/09/072</t>
-  </si>
-  <si>
-    <t>JHZ-17-026</t>
-  </si>
-  <si>
-    <t>PCE-PC0743</t>
-  </si>
-  <si>
-    <t>5784241.0</t>
-  </si>
-  <si>
-    <t>090520028EC43</t>
-  </si>
-  <si>
-    <t>4572.0</t>
-  </si>
-  <si>
-    <t>PCE-PC2115</t>
-  </si>
-  <si>
-    <t>338.0</t>
-  </si>
-  <si>
-    <t>9802842.0</t>
-  </si>
-  <si>
-    <t>SM2702</t>
-  </si>
-  <si>
-    <t>A0039K1D</t>
-  </si>
-  <si>
-    <t>A003H05Y</t>
-  </si>
-  <si>
-    <t>RWA29E680</t>
-  </si>
-  <si>
-    <t>A003FFF9</t>
-  </si>
-  <si>
-    <t>CRAZAEOM091</t>
-  </si>
-  <si>
-    <t>1905XL</t>
-  </si>
-  <si>
-    <t>9757.0</t>
-  </si>
-  <si>
-    <t>11200478.0</t>
-  </si>
-  <si>
-    <t>9038.0</t>
-  </si>
-  <si>
-    <t>PZLL010SB</t>
-  </si>
-  <si>
-    <t>11100371.0</t>
-  </si>
-  <si>
-    <t>862.0</t>
-  </si>
-  <si>
-    <t>11402681.0</t>
-  </si>
-  <si>
-    <t>7475.0</t>
-  </si>
-  <si>
-    <t>16A856</t>
-  </si>
-  <si>
-    <t>A0037CAC</t>
-  </si>
-  <si>
-    <t>8890.0</t>
-  </si>
-  <si>
-    <t>1705.0</t>
-  </si>
-  <si>
-    <t>2K221</t>
-  </si>
-  <si>
-    <t>D-0397408</t>
-  </si>
-  <si>
-    <t>391730-020</t>
-  </si>
-  <si>
-    <t>110076.0</t>
-  </si>
-  <si>
-    <t>170-07437</t>
-  </si>
-  <si>
-    <t>B10811395</t>
-  </si>
-  <si>
-    <t>10603746.0</t>
-  </si>
-  <si>
-    <t>10BC80</t>
-  </si>
-  <si>
-    <t>392140-009</t>
+    <t>120677.0</t>
   </si>
   <si>
     <t>9803650.0</t>
   </si>
   <si>
-    <t>5784237.0</t>
-  </si>
-  <si>
-    <t>A87528</t>
-  </si>
-  <si>
-    <t>B10811727</t>
-  </si>
-  <si>
-    <t>7572.0</t>
-  </si>
-  <si>
-    <t>8737.0</t>
-  </si>
-  <si>
-    <t>1012821-019</t>
-  </si>
-  <si>
-    <t>929.0</t>
-  </si>
-  <si>
-    <t>D58293653</t>
-  </si>
-  <si>
-    <t>A-24022580</t>
-  </si>
-  <si>
-    <t>A-24022576</t>
-  </si>
-  <si>
-    <t>70.0</t>
-  </si>
-  <si>
-    <t>157.0</t>
-  </si>
-  <si>
-    <t>44.0</t>
-  </si>
-  <si>
-    <t>61.0</t>
-  </si>
-  <si>
-    <t>71.0</t>
-  </si>
-  <si>
-    <t>393069-038</t>
-  </si>
-  <si>
-    <t>G-45677217</t>
-  </si>
-  <si>
-    <t>7869.0</t>
-  </si>
-  <si>
-    <t>D-00397388</t>
-  </si>
-  <si>
-    <t>102.0</t>
-  </si>
-  <si>
-    <t>73.0</t>
-  </si>
-  <si>
-    <t>240.0</t>
-  </si>
-  <si>
-    <t>D00398015</t>
-  </si>
-  <si>
-    <t>E09393184</t>
-  </si>
-  <si>
-    <t>210-10043</t>
-  </si>
-  <si>
-    <t>D00398016</t>
-  </si>
-  <si>
-    <t>D00397796</t>
-  </si>
-  <si>
-    <t>9600123.0</t>
-  </si>
-  <si>
-    <t>B10811720</t>
-  </si>
-  <si>
-    <t>D-00397408</t>
-  </si>
-  <si>
-    <t>7044.0</t>
-  </si>
-  <si>
-    <t>210-10039</t>
-  </si>
-  <si>
-    <t>2986900100469.0</t>
-  </si>
-  <si>
-    <t>3726.0</t>
-  </si>
-  <si>
-    <t>C66369</t>
-  </si>
-  <si>
-    <t>I-01810674</t>
-  </si>
-  <si>
-    <t>210-13181</t>
-  </si>
-  <si>
-    <t>11100370.0</t>
-  </si>
-  <si>
-    <t>912962.0</t>
-  </si>
-  <si>
-    <t>7911.0</t>
-  </si>
-  <si>
-    <t>10000617.0</t>
-  </si>
-  <si>
-    <t>D00398018</t>
-  </si>
-  <si>
-    <t>2986900100392.0</t>
-  </si>
-  <si>
-    <t>2986900100467.0</t>
-  </si>
-  <si>
-    <t>2986900100513.0</t>
-  </si>
-  <si>
-    <t>11A</t>
-  </si>
-  <si>
-    <t>960707.0</t>
-  </si>
-  <si>
-    <t>210-10042</t>
-  </si>
-  <si>
-    <t>399407-032</t>
-  </si>
-  <si>
-    <t>5784239.0</t>
-  </si>
-  <si>
-    <t>T-24634412</t>
-  </si>
-  <si>
-    <t>396315-038</t>
-  </si>
-  <si>
-    <t>D00397793</t>
-  </si>
-  <si>
-    <t>399910-010</t>
-  </si>
-  <si>
-    <t>1779.0</t>
-  </si>
-  <si>
-    <t>D00397933</t>
-  </si>
-  <si>
-    <t>9601404.0</t>
-  </si>
-  <si>
     <t>2395-05-01 00:00:00</t>
   </si>
   <si>
@@ -484,31 +430,28 @@
     <t>7.0</t>
   </si>
   <si>
-    <t>797.0</t>
-  </si>
-  <si>
-    <t>775.0</t>
+    <t>2002A</t>
+  </si>
+  <si>
+    <t>41.0</t>
+  </si>
+  <si>
+    <t>799.0</t>
   </si>
   <si>
     <t>38.0</t>
   </si>
   <si>
-    <t>2545-05-01 00:00:00</t>
-  </si>
-  <si>
-    <t>2514-05-01 00:00:00</t>
-  </si>
-  <si>
-    <t>246.0</t>
-  </si>
-  <si>
     <t>1435-5</t>
   </si>
   <si>
     <t>2913.0</t>
   </si>
   <si>
-    <t>4041-05-01 00:00:00</t>
+    <t>2004.0</t>
+  </si>
+  <si>
+    <t>B4H-038</t>
   </si>
   <si>
     <t>970.0</t>
@@ -517,72 +460,63 @@
     <t>08G</t>
   </si>
   <si>
-    <t>B4H-011</t>
-  </si>
-  <si>
-    <t>2004.0</t>
-  </si>
-  <si>
     <t>5351.0</t>
   </si>
   <si>
-    <t>32.0</t>
-  </si>
-  <si>
-    <t>B4H-038</t>
-  </si>
-  <si>
     <t>796.0</t>
   </si>
   <si>
     <t>47.0</t>
   </si>
   <si>
-    <t>480.0</t>
-  </si>
-  <si>
-    <t>B4H-051</t>
-  </si>
-  <si>
-    <t>25.0</t>
-  </si>
-  <si>
     <t>82.0</t>
   </si>
   <si>
+    <t>16.0</t>
+  </si>
+  <si>
     <t>2890.0</t>
   </si>
   <si>
+    <t>2305-05-01 00:00:00</t>
+  </si>
+  <si>
+    <t>822-5</t>
+  </si>
+  <si>
+    <t>3481-05-01 00:00:00</t>
+  </si>
+  <si>
     <t>278.0</t>
   </si>
   <si>
-    <t>2305-05-01 00:00:00</t>
+    <t>272.0</t>
   </si>
   <si>
     <t>B4H-040</t>
   </si>
   <si>
-    <t>272.0</t>
-  </si>
-  <si>
-    <t>822-5</t>
-  </si>
-  <si>
-    <t>3481-05-01 00:00:00</t>
+    <t>AS41538</t>
   </si>
   <si>
     <t>687.0</t>
   </si>
   <si>
-    <t>AS41538</t>
+    <t>11.0</t>
+  </si>
+  <si>
+    <t>295.0</t>
+  </si>
+  <si>
+    <t>UNK-01</t>
+  </si>
+  <si>
+    <t>3124-05-01 00:00:00</t>
   </si>
   <si>
     <t>4609-05-01 00:00:00</t>
   </si>
   <si>
-    <t>3124-05-01 00:00:00</t>
-  </si>
-  <si>
     <t>Z28L22A</t>
   </si>
   <si>
@@ -595,9 +529,6 @@
     <t>29.0</t>
   </si>
   <si>
-    <t>UNK-01</t>
-  </si>
-  <si>
     <t>9004.0</t>
   </si>
   <si>
@@ -625,19 +556,22 @@
     <t>HSI PT6A-114A</t>
   </si>
   <si>
+    <t>3104100-01</t>
+  </si>
+  <si>
     <t>3013111.0</t>
   </si>
   <si>
     <t>3027798.0</t>
   </si>
   <si>
-    <t>3013712.0</t>
+    <t>30994-001</t>
   </si>
   <si>
     <t>023694-000</t>
   </si>
   <si>
-    <t>30994-001</t>
+    <t>8210-002-01</t>
   </si>
   <si>
     <t>2651023-19</t>
@@ -646,27 +580,30 @@
     <t>702801-5</t>
   </si>
   <si>
-    <t>8210-002-01</t>
+    <t>3049038-03</t>
+  </si>
+  <si>
+    <t>2651022-15</t>
+  </si>
+  <si>
+    <t>540-1407-4</t>
   </si>
   <si>
     <t>2651022-20-1</t>
   </si>
   <si>
-    <t>3049038-03</t>
-  </si>
-  <si>
-    <t>2651022-15</t>
+    <t>3121248-03</t>
+  </si>
+  <si>
+    <t>D210507</t>
+  </si>
+  <si>
+    <t>C482001-0402</t>
   </si>
   <si>
     <t>200SGL119Q</t>
   </si>
   <si>
-    <t>540-1407-4</t>
-  </si>
-  <si>
-    <t>3121248-03</t>
-  </si>
-  <si>
     <t>5934PAM-3</t>
   </si>
   <si>
@@ -682,12 +619,6 @@
     <t>453-5000-710</t>
   </si>
   <si>
-    <t>C482001-0402</t>
-  </si>
-  <si>
-    <t>3244809-4</t>
-  </si>
-  <si>
     <t>P7036368-01</t>
   </si>
   <si>
@@ -718,24 +649,24 @@
     <t>162-11800</t>
   </si>
   <si>
+    <t>161-12800</t>
+  </si>
+  <si>
+    <t>162-10700</t>
+  </si>
+  <si>
     <t>161-11700</t>
   </si>
   <si>
-    <t>162-10700</t>
-  </si>
-  <si>
-    <t>161-12800</t>
-  </si>
-  <si>
     <t>2622311-16</t>
   </si>
   <si>
+    <t>2613440-1</t>
+  </si>
+  <si>
     <t>2641011-1</t>
   </si>
   <si>
-    <t>2613440-1</t>
-  </si>
-  <si>
     <t>2643062-1</t>
   </si>
   <si>
@@ -751,24 +682,24 @@
     <t>7EK50</t>
   </si>
   <si>
+    <t>74025.0</t>
+  </si>
+  <si>
     <t>F6177</t>
   </si>
   <si>
-    <t>74025.0</t>
+    <t>66503.0</t>
   </si>
   <si>
     <t>59875.0</t>
   </si>
   <si>
-    <t>66503.0</t>
+    <t>077L2</t>
   </si>
   <si>
     <t>95270.0</t>
   </si>
   <si>
-    <t>077L2</t>
-  </si>
-  <si>
     <t>16455.0</t>
   </si>
   <si>
@@ -784,27 +715,27 @@
     <t>18560.0</t>
   </si>
   <si>
+    <t>1LGE7</t>
+  </si>
+  <si>
+    <t>002FK</t>
+  </si>
+  <si>
+    <t>80049.0</t>
+  </si>
+  <si>
+    <t>81205.0</t>
+  </si>
+  <si>
+    <t>K0068</t>
+  </si>
+  <si>
+    <t>U1601</t>
+  </si>
+  <si>
     <t>7213.0</t>
   </si>
   <si>
-    <t>1LGE7</t>
-  </si>
-  <si>
-    <t>002FK</t>
-  </si>
-  <si>
-    <t>80049.0</t>
-  </si>
-  <si>
-    <t>81205.0</t>
-  </si>
-  <si>
-    <t>K0068</t>
-  </si>
-  <si>
-    <t>U1601</t>
-  </si>
-  <si>
     <t>33269.0</t>
   </si>
   <si>
@@ -823,24 +754,21 @@
     <t>2 ETA</t>
   </si>
   <si>
+    <t>1 ETA</t>
+  </si>
+  <si>
+    <t>6 ETA</t>
+  </si>
+  <si>
     <t>5 ETA</t>
   </si>
   <si>
-    <t>1 ETA</t>
+    <t>1/15 GAV</t>
   </si>
   <si>
     <t>CLA</t>
   </si>
   <si>
-    <t>6 ETA</t>
-  </si>
-  <si>
-    <t>1/15 GAV</t>
-  </si>
-  <si>
-    <t>DACTA II</t>
-  </si>
-  <si>
     <t>TBO</t>
   </si>
   <si>
@@ -856,84 +784,84 @@
     <t>REV. GERAL</t>
   </si>
   <si>
+    <t>MOT1M12</t>
+  </si>
+  <si>
+    <t>200H</t>
+  </si>
+  <si>
     <t>REVG</t>
   </si>
   <si>
+    <t>1500H HSI</t>
+  </si>
+  <si>
     <t>RG</t>
   </si>
   <si>
-    <t>MOT1M12</t>
-  </si>
-  <si>
-    <t>200H</t>
-  </si>
-  <si>
-    <t>3000H</t>
-  </si>
-  <si>
-    <t>2800H</t>
+    <t>MOT2M6</t>
+  </si>
+  <si>
+    <t>400H</t>
+  </si>
+  <si>
+    <t>500H</t>
   </si>
   <si>
     <t>3400H</t>
   </si>
   <si>
-    <t>3300H</t>
+    <t>INSPC</t>
+  </si>
+  <si>
+    <t>CRI.</t>
   </si>
   <si>
     <t>HSI</t>
   </si>
   <si>
-    <t>400H</t>
-  </si>
-  <si>
-    <t>MOT2M6</t>
-  </si>
-  <si>
-    <t>INSPC</t>
-  </si>
-  <si>
-    <t>CRI.</t>
-  </si>
-  <si>
     <t>REV 5000</t>
   </si>
   <si>
+    <t>TROCA FILT</t>
+  </si>
+  <si>
+    <t>1-REV10000</t>
+  </si>
+  <si>
+    <t>TEC</t>
+  </si>
+  <si>
+    <t>TLV</t>
+  </si>
+  <si>
+    <t>CRI 12M</t>
+  </si>
+  <si>
     <t>CRI</t>
   </si>
   <si>
-    <t>TEC</t>
-  </si>
-  <si>
-    <t>TLV</t>
-  </si>
-  <si>
-    <t>CRI 12M</t>
-  </si>
-  <si>
     <t>1.0</t>
   </si>
   <si>
     <t>12M</t>
   </si>
   <si>
-    <t>TROCA FILT</t>
+    <t>MONT</t>
+  </si>
+  <si>
+    <t>INSP CRIT</t>
+  </si>
+  <si>
+    <t>PESAGEM</t>
+  </si>
+  <si>
+    <t>BATERIA</t>
   </si>
   <si>
     <t>CRI (12M)</t>
   </si>
   <si>
-    <t>MONT</t>
-  </si>
-  <si>
-    <t>INSP CRIT</t>
-  </si>
-  <si>
-    <t>PESAGEM</t>
-  </si>
-  <si>
-    <t>BATERIA</t>
-  </si>
-  <si>
     <t>IC5000</t>
   </si>
   <si>
@@ -949,10 +877,13 @@
     <t>Pouso</t>
   </si>
   <si>
-    <t>-318 m</t>
-  </si>
-  <si>
-    <t>-165 m</t>
+    <t>-319 m</t>
+  </si>
+  <si>
+    <t>-166 m</t>
+  </si>
+  <si>
+    <t>-29 m</t>
   </si>
   <si>
     <t>-28 m</t>
@@ -961,16 +892,13 @@
     <t>-26 m</t>
   </si>
   <si>
-    <t>-24 m</t>
-  </si>
-  <si>
-    <t>-22 m</t>
-  </si>
-  <si>
-    <t>-8 m</t>
-  </si>
-  <si>
-    <t>1 m</t>
+    <t>-23 m</t>
+  </si>
+  <si>
+    <t>-9 m</t>
+  </si>
+  <si>
+    <t>-2 m</t>
   </si>
   <si>
     <t>2 m</t>
@@ -1003,13 +931,19 @@
     <t>11 m</t>
   </si>
   <si>
-    <t>-27 d</t>
-  </si>
-  <si>
-    <t>-14 d</t>
-  </si>
-  <si>
-    <t>24 d</t>
+    <t>-26 d</t>
+  </si>
+  <si>
+    <t>2 d</t>
+  </si>
+  <si>
+    <t>12 d</t>
+  </si>
+  <si>
+    <t>13 d</t>
+  </si>
+  <si>
+    <t>23 d</t>
   </si>
 </sst>
 </file>
@@ -1019,16 +953,8 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1044,7 +970,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1052,30 +978,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1371,41 +1279,41 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K194"/>
+  <dimension ref="A1:K169"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1417,24 +1325,24 @@
         <v>2740</v>
       </c>
       <c r="C2" t="s">
-        <v>197</v>
+        <v>174</v>
       </c>
       <c r="D2" t="s">
-        <v>243</v>
+        <v>220</v>
       </c>
       <c r="E2" t="s">
-        <v>265</v>
+        <v>242</v>
       </c>
       <c r="F2" t="s">
-        <v>275</v>
+        <v>251</v>
       </c>
       <c r="G2" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="H2">
-        <v>-4300.3</v>
-      </c>
-      <c r="J2" s="2">
+        <v>-4349.4</v>
+      </c>
+      <c r="J2" s="1">
         <v>39285</v>
       </c>
       <c r="K2" t="b">
@@ -1449,24 +1357,24 @@
         <v>2730</v>
       </c>
       <c r="C3" t="s">
-        <v>198</v>
+        <v>175</v>
       </c>
       <c r="D3" t="s">
-        <v>244</v>
+        <v>221</v>
       </c>
       <c r="E3" t="s">
-        <v>266</v>
+        <v>243</v>
       </c>
       <c r="F3" t="s">
-        <v>276</v>
+        <v>252</v>
       </c>
       <c r="G3" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="H3">
         <v>-2354.2</v>
       </c>
-      <c r="J3" s="2">
+      <c r="J3" s="1">
         <v>40669</v>
       </c>
       <c r="K3" t="b">
@@ -1481,24 +1389,24 @@
         <v>2704</v>
       </c>
       <c r="C4" t="s">
-        <v>199</v>
+        <v>176</v>
       </c>
       <c r="D4" t="s">
+        <v>220</v>
+      </c>
+      <c r="E4" t="s">
         <v>243</v>
       </c>
-      <c r="E4" t="s">
-        <v>266</v>
-      </c>
       <c r="F4" t="s">
-        <v>277</v>
+        <v>253</v>
       </c>
       <c r="G4" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="H4">
-        <v>-910.7</v>
-      </c>
-      <c r="J4" s="2">
+        <v>-922.4</v>
+      </c>
+      <c r="J4" s="1">
         <v>40669</v>
       </c>
       <c r="K4" t="b">
@@ -1513,24 +1421,24 @@
         <v>2704</v>
       </c>
       <c r="C5" t="s">
-        <v>200</v>
+        <v>177</v>
       </c>
       <c r="D5" t="s">
+        <v>220</v>
+      </c>
+      <c r="E5" t="s">
         <v>243</v>
       </c>
-      <c r="E5" t="s">
-        <v>266</v>
-      </c>
       <c r="F5" t="s">
-        <v>275</v>
+        <v>251</v>
       </c>
       <c r="G5" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="H5">
-        <v>-868</v>
-      </c>
-      <c r="J5" s="2">
+        <v>-879.8</v>
+      </c>
+      <c r="J5" s="1">
         <v>44884</v>
       </c>
       <c r="K5" t="b">
@@ -1545,24 +1453,24 @@
         <v>2708</v>
       </c>
       <c r="C6" t="s">
-        <v>199</v>
+        <v>176</v>
       </c>
       <c r="D6" t="s">
-        <v>243</v>
+        <v>220</v>
       </c>
       <c r="E6" t="s">
-        <v>267</v>
+        <v>244</v>
       </c>
       <c r="F6" t="s">
-        <v>278</v>
+        <v>254</v>
       </c>
       <c r="G6" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="H6">
-        <v>-483.8</v>
-      </c>
-      <c r="J6" s="2">
+        <v>-536.4</v>
+      </c>
+      <c r="J6" s="1">
         <v>43855</v>
       </c>
       <c r="K6" t="b">
@@ -1574,28 +1482,28 @@
         <v>16</v>
       </c>
       <c r="B7">
-        <v>2740</v>
+        <v>2719</v>
       </c>
       <c r="C7" t="s">
-        <v>201</v>
+        <v>178</v>
       </c>
       <c r="D7" t="s">
-        <v>243</v>
+        <v>220</v>
       </c>
       <c r="E7" t="s">
-        <v>265</v>
+        <v>245</v>
       </c>
       <c r="F7" t="s">
-        <v>279</v>
+        <v>255</v>
       </c>
       <c r="G7" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="H7">
-        <v>-417</v>
-      </c>
-      <c r="J7" s="2">
-        <v>46014</v>
+        <v>-484.3</v>
+      </c>
+      <c r="J7" s="1">
+        <v>45804</v>
       </c>
       <c r="K7" t="b">
         <v>1</v>
@@ -1606,28 +1514,28 @@
         <v>16</v>
       </c>
       <c r="B8">
-        <v>2740</v>
+        <v>2719</v>
       </c>
       <c r="C8" t="s">
-        <v>202</v>
+        <v>179</v>
       </c>
       <c r="D8" t="s">
-        <v>243</v>
+        <v>220</v>
       </c>
       <c r="E8" t="s">
-        <v>265</v>
+        <v>245</v>
       </c>
       <c r="F8" t="s">
-        <v>275</v>
+        <v>251</v>
       </c>
       <c r="G8" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="H8">
-        <v>-414.2</v>
-      </c>
-      <c r="J8" s="2">
-        <v>46014</v>
+        <v>-482.8</v>
+      </c>
+      <c r="J8" s="1">
+        <v>45804</v>
       </c>
       <c r="K8" t="b">
         <v>1</v>
@@ -1638,28 +1546,28 @@
         <v>17</v>
       </c>
       <c r="B9">
-        <v>2732</v>
+        <v>2740</v>
       </c>
       <c r="C9" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="D9" t="s">
-        <v>244</v>
+        <v>220</v>
       </c>
       <c r="E9" t="s">
-        <v>266</v>
+        <v>242</v>
       </c>
       <c r="F9" t="s">
-        <v>276</v>
+        <v>255</v>
       </c>
       <c r="G9" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="H9">
-        <v>-391.8</v>
-      </c>
-      <c r="J9" s="2">
-        <v>42769</v>
+        <v>-466.1</v>
+      </c>
+      <c r="J9" s="1">
+        <v>46014</v>
       </c>
       <c r="K9" t="b">
         <v>1</v>
@@ -1670,28 +1578,28 @@
         <v>18</v>
       </c>
       <c r="B10">
-        <v>2719</v>
+        <v>2722</v>
       </c>
       <c r="C10" t="s">
-        <v>201</v>
+        <v>176</v>
       </c>
       <c r="D10" t="s">
-        <v>243</v>
+        <v>220</v>
       </c>
       <c r="E10" t="s">
-        <v>268</v>
+        <v>245</v>
       </c>
       <c r="F10" t="s">
-        <v>279</v>
+        <v>256</v>
       </c>
       <c r="G10" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="H10">
-        <v>-391.6</v>
-      </c>
-      <c r="J10" s="2">
-        <v>45804</v>
+        <v>-463.8</v>
+      </c>
+      <c r="J10" s="1">
+        <v>40979</v>
       </c>
       <c r="K10" t="b">
         <v>1</v>
@@ -1699,31 +1607,31 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11">
-        <v>2719</v>
+        <v>2740</v>
       </c>
       <c r="C11" t="s">
-        <v>202</v>
+        <v>179</v>
       </c>
       <c r="D11" t="s">
-        <v>243</v>
+        <v>220</v>
       </c>
       <c r="E11" t="s">
-        <v>268</v>
+        <v>242</v>
       </c>
       <c r="F11" t="s">
-        <v>275</v>
+        <v>251</v>
       </c>
       <c r="G11" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="H11">
-        <v>-391.6</v>
-      </c>
-      <c r="J11" s="2">
-        <v>45804</v>
+        <v>-463.3</v>
+      </c>
+      <c r="J11" s="1">
+        <v>46014</v>
       </c>
       <c r="K11" t="b">
         <v>1</v>
@@ -1734,28 +1642,28 @@
         <v>19</v>
       </c>
       <c r="B12">
-        <v>2743</v>
+        <v>2732</v>
       </c>
       <c r="C12" t="s">
-        <v>203</v>
+        <v>175</v>
       </c>
       <c r="D12" t="s">
-        <v>243</v>
+        <v>221</v>
       </c>
       <c r="E12" t="s">
-        <v>269</v>
+        <v>242</v>
       </c>
       <c r="F12" t="s">
-        <v>280</v>
+        <v>252</v>
       </c>
       <c r="G12" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="H12">
-        <v>-372.9</v>
-      </c>
-      <c r="J12" s="2">
-        <v>42821</v>
+        <v>-391.8</v>
+      </c>
+      <c r="J12" s="1">
+        <v>42769</v>
       </c>
       <c r="K12" t="b">
         <v>1</v>
@@ -1766,28 +1674,28 @@
         <v>20</v>
       </c>
       <c r="B13">
-        <v>2743</v>
+        <v>2703</v>
       </c>
       <c r="C13" t="s">
-        <v>204</v>
+        <v>180</v>
       </c>
       <c r="D13" t="s">
-        <v>243</v>
+        <v>220</v>
       </c>
       <c r="E13" t="s">
-        <v>269</v>
+        <v>244</v>
       </c>
       <c r="F13" t="s">
-        <v>275</v>
+        <v>253</v>
       </c>
       <c r="G13" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="H13">
-        <v>-372.9</v>
-      </c>
-      <c r="J13" s="2">
-        <v>46014</v>
+        <v>-390</v>
+      </c>
+      <c r="J13" s="1">
+        <v>32786</v>
       </c>
       <c r="K13" t="b">
         <v>1</v>
@@ -1798,28 +1706,28 @@
         <v>21</v>
       </c>
       <c r="B14">
-        <v>2743</v>
+        <v>2719</v>
       </c>
       <c r="C14" t="s">
-        <v>197</v>
+        <v>176</v>
       </c>
       <c r="D14" t="s">
-        <v>243</v>
+        <v>220</v>
       </c>
       <c r="E14" t="s">
-        <v>269</v>
+        <v>245</v>
       </c>
       <c r="F14" t="s">
-        <v>275</v>
+        <v>257</v>
       </c>
       <c r="G14" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="H14">
-        <v>-372.9</v>
-      </c>
-      <c r="J14" s="2">
-        <v>46014</v>
+        <v>-211.2</v>
+      </c>
+      <c r="J14" s="1">
+        <v>34700</v>
       </c>
       <c r="K14" t="b">
         <v>1</v>
@@ -1830,28 +1738,28 @@
         <v>22</v>
       </c>
       <c r="B15">
-        <v>2743</v>
+        <v>2702</v>
       </c>
       <c r="C15" t="s">
-        <v>205</v>
+        <v>176</v>
       </c>
       <c r="D15" t="s">
-        <v>243</v>
+        <v>220</v>
       </c>
       <c r="E15" t="s">
-        <v>269</v>
+        <v>244</v>
       </c>
       <c r="F15" t="s">
-        <v>275</v>
+        <v>256</v>
       </c>
       <c r="G15" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="H15">
-        <v>-372.9</v>
-      </c>
-      <c r="J15" s="2">
-        <v>46014</v>
+        <v>-176</v>
+      </c>
+      <c r="J15" s="1">
+        <v>41204</v>
       </c>
       <c r="K15" t="b">
         <v>1</v>
@@ -1862,28 +1770,28 @@
         <v>23</v>
       </c>
       <c r="B16">
-        <v>2743</v>
+        <v>2733</v>
       </c>
       <c r="C16" t="s">
-        <v>200</v>
+        <v>174</v>
       </c>
       <c r="D16" t="s">
-        <v>243</v>
+        <v>220</v>
       </c>
       <c r="E16" t="s">
-        <v>269</v>
+        <v>246</v>
       </c>
       <c r="F16" t="s">
-        <v>275</v>
+        <v>251</v>
       </c>
       <c r="G16" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="H16">
-        <v>-367.8</v>
-      </c>
-      <c r="J16" s="2">
-        <v>46017</v>
+        <v>-159.2</v>
+      </c>
+      <c r="J16" s="1">
+        <v>46111</v>
       </c>
       <c r="K16" t="b">
         <v>1</v>
@@ -1894,28 +1802,28 @@
         <v>24</v>
       </c>
       <c r="B17">
-        <v>2743</v>
+        <v>2733</v>
       </c>
       <c r="C17" t="s">
-        <v>199</v>
+        <v>181</v>
       </c>
       <c r="D17" t="s">
-        <v>243</v>
+        <v>220</v>
       </c>
       <c r="E17" t="s">
-        <v>269</v>
+        <v>246</v>
       </c>
       <c r="F17" t="s">
-        <v>281</v>
+        <v>258</v>
       </c>
       <c r="G17" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="H17">
-        <v>-367.8</v>
-      </c>
-      <c r="J17" s="2">
-        <v>46017</v>
+        <v>-159.2</v>
+      </c>
+      <c r="J17" s="1">
+        <v>46111</v>
       </c>
       <c r="K17" t="b">
         <v>1</v>
@@ -1926,28 +1834,28 @@
         <v>25</v>
       </c>
       <c r="B18">
-        <v>2722</v>
+        <v>2733</v>
       </c>
       <c r="C18" t="s">
-        <v>199</v>
+        <v>177</v>
       </c>
       <c r="D18" t="s">
-        <v>243</v>
+        <v>220</v>
       </c>
       <c r="E18" t="s">
-        <v>268</v>
+        <v>246</v>
       </c>
       <c r="F18" t="s">
-        <v>282</v>
+        <v>251</v>
       </c>
       <c r="G18" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="H18">
-        <v>-347.2</v>
-      </c>
-      <c r="J18" s="2">
-        <v>40979</v>
+        <v>-159.2</v>
+      </c>
+      <c r="J18" s="1">
+        <v>46111</v>
       </c>
       <c r="K18" t="b">
         <v>1</v>
@@ -1958,28 +1866,28 @@
         <v>26</v>
       </c>
       <c r="B19">
-        <v>2719</v>
+        <v>2733</v>
       </c>
       <c r="C19" t="s">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="D19" t="s">
-        <v>243</v>
+        <v>220</v>
       </c>
       <c r="E19" t="s">
-        <v>268</v>
+        <v>246</v>
       </c>
       <c r="F19" t="s">
-        <v>281</v>
+        <v>251</v>
       </c>
       <c r="G19" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="H19">
-        <v>-293.8</v>
-      </c>
-      <c r="J19" s="2">
-        <v>45846</v>
+        <v>-159.2</v>
+      </c>
+      <c r="J19" s="1">
+        <v>46111</v>
       </c>
       <c r="K19" t="b">
         <v>1</v>
@@ -1993,25 +1901,25 @@
         <v>2733</v>
       </c>
       <c r="C20" t="s">
-        <v>199</v>
+        <v>176</v>
       </c>
       <c r="D20" t="s">
-        <v>243</v>
+        <v>220</v>
       </c>
       <c r="E20" t="s">
-        <v>270</v>
+        <v>246</v>
       </c>
       <c r="F20" t="s">
-        <v>277</v>
+        <v>259</v>
       </c>
       <c r="G20" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="H20">
-        <v>-206.4</v>
-      </c>
-      <c r="J20" s="2">
-        <v>36669</v>
+        <v>-101.6</v>
+      </c>
+      <c r="J20" s="1">
+        <v>46161</v>
       </c>
       <c r="K20" t="b">
         <v>1</v>
@@ -2022,28 +1930,28 @@
         <v>28</v>
       </c>
       <c r="B21">
-        <v>2733</v>
+        <v>2736</v>
       </c>
       <c r="C21" t="s">
-        <v>205</v>
+        <v>178</v>
       </c>
       <c r="D21" t="s">
-        <v>243</v>
+        <v>220</v>
       </c>
       <c r="E21" t="s">
-        <v>270</v>
+        <v>242</v>
       </c>
       <c r="F21" t="s">
-        <v>275</v>
+        <v>255</v>
       </c>
       <c r="G21" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="H21">
-        <v>-131.6</v>
-      </c>
-      <c r="J21" s="2">
-        <v>46111</v>
+        <v>-69.7</v>
+      </c>
+      <c r="J21" s="1">
+        <v>46241</v>
       </c>
       <c r="K21" t="b">
         <v>1</v>
@@ -2051,31 +1959,31 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B22">
-        <v>2733</v>
+        <v>2736</v>
       </c>
       <c r="C22" t="s">
-        <v>204</v>
+        <v>179</v>
       </c>
       <c r="D22" t="s">
-        <v>243</v>
+        <v>220</v>
       </c>
       <c r="E22" t="s">
-        <v>270</v>
+        <v>242</v>
       </c>
       <c r="F22" t="s">
-        <v>275</v>
+        <v>251</v>
       </c>
       <c r="G22" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="H22">
-        <v>-131.6</v>
-      </c>
-      <c r="J22" s="2">
-        <v>46111</v>
+        <v>-61.8</v>
+      </c>
+      <c r="J22" s="1">
+        <v>46242</v>
       </c>
       <c r="K22" t="b">
         <v>1</v>
@@ -2083,31 +1991,31 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B23">
-        <v>2733</v>
+        <v>2736</v>
       </c>
       <c r="C23" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D23" t="s">
-        <v>243</v>
+        <v>220</v>
       </c>
       <c r="E23" t="s">
-        <v>270</v>
+        <v>242</v>
       </c>
       <c r="F23" t="s">
-        <v>275</v>
+        <v>260</v>
       </c>
       <c r="G23" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="H23">
-        <v>-131.6</v>
-      </c>
-      <c r="J23" s="2">
-        <v>46111</v>
+        <v>-53.5</v>
+      </c>
+      <c r="J23" s="1">
+        <v>46255</v>
       </c>
       <c r="K23" t="b">
         <v>1</v>
@@ -2115,31 +2023,31 @@
     </row>
     <row r="24" spans="1:11">
       <c r="A24" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B24">
-        <v>2733</v>
+        <v>2742</v>
       </c>
       <c r="C24" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="D24" t="s">
+        <v>222</v>
+      </c>
+      <c r="E24" t="s">
         <v>243</v>
       </c>
-      <c r="E24" t="s">
-        <v>270</v>
-      </c>
       <c r="F24" t="s">
-        <v>280</v>
+        <v>257</v>
       </c>
       <c r="G24" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="H24">
-        <v>-131.6</v>
-      </c>
-      <c r="J24" s="2">
-        <v>46111</v>
+        <v>-10</v>
+      </c>
+      <c r="J24" s="1">
+        <v>46276</v>
       </c>
       <c r="K24" t="b">
         <v>1</v>
@@ -2147,31 +2055,31 @@
     </row>
     <row r="25" spans="1:11">
       <c r="A25" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B25">
-        <v>2733</v>
+        <v>2742</v>
       </c>
       <c r="C25" t="s">
-        <v>197</v>
+        <v>176</v>
       </c>
       <c r="D25" t="s">
+        <v>220</v>
+      </c>
+      <c r="E25" t="s">
         <v>243</v>
       </c>
-      <c r="E25" t="s">
-        <v>270</v>
-      </c>
       <c r="F25" t="s">
-        <v>275</v>
+        <v>261</v>
       </c>
       <c r="G25" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="H25">
-        <v>-131.6</v>
-      </c>
-      <c r="J25" s="2">
-        <v>46111</v>
+        <v>-10</v>
+      </c>
+      <c r="J25" s="1">
+        <v>46276</v>
       </c>
       <c r="K25" t="b">
         <v>1</v>
@@ -2179,31 +2087,31 @@
     </row>
     <row r="26" spans="1:11">
       <c r="A26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B26">
-        <v>2702</v>
+        <v>2720</v>
       </c>
       <c r="C26" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="D26" t="s">
-        <v>243</v>
+        <v>223</v>
       </c>
       <c r="E26" t="s">
-        <v>267</v>
+        <v>247</v>
       </c>
       <c r="F26" t="s">
-        <v>282</v>
+        <v>253</v>
       </c>
       <c r="G26" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="H26">
-        <v>-98.3</v>
-      </c>
-      <c r="J26" s="2">
-        <v>41204</v>
+        <v>-7.4</v>
+      </c>
+      <c r="J26" s="1">
+        <v>46269</v>
       </c>
       <c r="K26" t="b">
         <v>1</v>
@@ -2211,31 +2119,31 @@
     </row>
     <row r="27" spans="1:11">
       <c r="A27" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B27">
-        <v>2739</v>
+        <v>2731</v>
       </c>
       <c r="C27" t="s">
-        <v>206</v>
+        <v>176</v>
       </c>
       <c r="D27" t="s">
-        <v>245</v>
+        <v>220</v>
       </c>
       <c r="E27" t="s">
-        <v>270</v>
+        <v>246</v>
       </c>
       <c r="F27" t="s">
-        <v>277</v>
+        <v>262</v>
       </c>
       <c r="G27" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="H27">
-        <v>-47.2</v>
-      </c>
-      <c r="J27" s="2">
-        <v>44011</v>
+        <v>-6.3</v>
+      </c>
+      <c r="J27" s="1">
+        <v>46236</v>
       </c>
       <c r="K27" t="b">
         <v>1</v>
@@ -2243,63 +2151,63 @@
     </row>
     <row r="28" spans="1:11">
       <c r="A28" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B28">
-        <v>2702</v>
+        <v>2743</v>
       </c>
       <c r="C28" t="s">
-        <v>207</v>
+        <v>184</v>
       </c>
       <c r="D28" t="s">
-        <v>246</v>
+        <v>223</v>
       </c>
       <c r="E28" t="s">
-        <v>267</v>
+        <v>248</v>
       </c>
       <c r="F28" t="s">
-        <v>283</v>
+        <v>253</v>
       </c>
       <c r="G28" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="H28">
-        <v>-22.3</v>
-      </c>
-      <c r="J28" s="2">
-        <v>46226</v>
+        <v>0</v>
+      </c>
+      <c r="J28" s="1">
+        <v>46282</v>
       </c>
       <c r="K28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:11">
       <c r="A29" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B29">
-        <v>2736</v>
+        <v>2738</v>
       </c>
       <c r="C29" t="s">
-        <v>199</v>
+        <v>176</v>
       </c>
       <c r="D29" t="s">
-        <v>243</v>
+        <v>220</v>
       </c>
       <c r="E29" t="s">
-        <v>265</v>
+        <v>242</v>
       </c>
       <c r="F29" t="s">
-        <v>277</v>
+        <v>257</v>
       </c>
       <c r="G29" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="H29">
-        <v>4.7</v>
-      </c>
-      <c r="J29" s="2">
-        <v>46265</v>
+        <v>7.7</v>
+      </c>
+      <c r="J29" s="1">
+        <v>46295</v>
       </c>
       <c r="K29" t="b">
         <v>0</v>
@@ -2307,31 +2215,31 @@
     </row>
     <row r="30" spans="1:11">
       <c r="A30" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B30">
-        <v>2723</v>
+        <v>2737</v>
       </c>
       <c r="C30" t="s">
-        <v>199</v>
+        <v>176</v>
       </c>
       <c r="D30" t="s">
-        <v>243</v>
+        <v>220</v>
       </c>
       <c r="E30" t="s">
-        <v>271</v>
+        <v>242</v>
       </c>
       <c r="F30" t="s">
+        <v>263</v>
+      </c>
+      <c r="G30" t="s">
         <v>284</v>
       </c>
-      <c r="G30" t="s">
-        <v>308</v>
-      </c>
       <c r="H30">
-        <v>7.5</v>
-      </c>
-      <c r="J30" s="2">
-        <v>46265</v>
+        <v>9.800000000000001</v>
+      </c>
+      <c r="J30" s="1">
+        <v>46295</v>
       </c>
       <c r="K30" t="b">
         <v>0</v>
@@ -2339,31 +2247,31 @@
     </row>
     <row r="31" spans="1:11">
       <c r="A31" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B31">
-        <v>2736</v>
+        <v>2740</v>
       </c>
       <c r="C31" t="s">
-        <v>201</v>
+        <v>185</v>
       </c>
       <c r="D31" t="s">
-        <v>243</v>
+        <v>224</v>
       </c>
       <c r="E31" t="s">
-        <v>265</v>
+        <v>242</v>
       </c>
       <c r="F31" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
       <c r="G31" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="H31">
-        <v>10</v>
-      </c>
-      <c r="J31" s="2">
-        <v>46265</v>
+        <v>10.9</v>
+      </c>
+      <c r="J31" s="1">
+        <v>46295</v>
       </c>
       <c r="K31" t="b">
         <v>0</v>
@@ -2371,31 +2279,31 @@
     </row>
     <row r="32" spans="1:11">
       <c r="A32" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B32">
-        <v>2709</v>
+        <v>2704</v>
       </c>
       <c r="C32" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
       <c r="D32" t="s">
+        <v>221</v>
+      </c>
+      <c r="E32" t="s">
         <v>243</v>
       </c>
-      <c r="E32" t="s">
-        <v>272</v>
-      </c>
       <c r="F32" t="s">
-        <v>285</v>
+        <v>252</v>
       </c>
       <c r="G32" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="H32">
-        <v>12.8</v>
-      </c>
-      <c r="J32" s="2">
-        <v>46265</v>
+        <v>21.8</v>
+      </c>
+      <c r="J32" s="1">
+        <v>46404</v>
       </c>
       <c r="K32" t="b">
         <v>0</v>
@@ -2403,31 +2311,31 @@
     </row>
     <row r="33" spans="1:11">
       <c r="A33" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B33">
-        <v>2738</v>
+        <v>2704</v>
       </c>
       <c r="C33" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D33" t="s">
+        <v>225</v>
+      </c>
+      <c r="E33" t="s">
         <v>243</v>
       </c>
-      <c r="E33" t="s">
-        <v>265</v>
-      </c>
       <c r="F33" t="s">
-        <v>277</v>
+        <v>255</v>
       </c>
       <c r="G33" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="H33">
-        <v>14</v>
-      </c>
-      <c r="J33" s="2">
-        <v>46265</v>
+        <v>33.9</v>
+      </c>
+      <c r="J33" s="1">
+        <v>46434</v>
       </c>
       <c r="K33" t="b">
         <v>0</v>
@@ -2435,31 +2343,31 @@
     </row>
     <row r="34" spans="1:11">
       <c r="A34" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B34">
-        <v>2736</v>
+        <v>2721</v>
       </c>
       <c r="C34" t="s">
-        <v>202</v>
+        <v>184</v>
       </c>
       <c r="D34" t="s">
-        <v>243</v>
+        <v>223</v>
       </c>
       <c r="E34" t="s">
-        <v>265</v>
+        <v>247</v>
       </c>
       <c r="F34" t="s">
-        <v>275</v>
+        <v>253</v>
       </c>
       <c r="G34" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="H34">
-        <v>17.8</v>
-      </c>
-      <c r="J34" s="2">
-        <v>46265</v>
+        <v>42.8</v>
+      </c>
+      <c r="J34" s="1">
+        <v>46385</v>
       </c>
       <c r="K34" t="b">
         <v>0</v>
@@ -2470,28 +2378,28 @@
         <v>41</v>
       </c>
       <c r="B35">
-        <v>2727</v>
+        <v>2720</v>
       </c>
       <c r="C35" t="s">
-        <v>199</v>
+        <v>176</v>
       </c>
       <c r="D35" t="s">
-        <v>243</v>
+        <v>220</v>
       </c>
       <c r="E35" t="s">
-        <v>273</v>
+        <v>247</v>
       </c>
       <c r="F35" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="G35" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="H35">
-        <v>20.4</v>
-      </c>
-      <c r="J35" s="2">
-        <v>46265</v>
+        <v>52.7</v>
+      </c>
+      <c r="J35" s="1">
+        <v>46337</v>
       </c>
       <c r="K35" t="b">
         <v>0</v>
@@ -2502,28 +2410,28 @@
         <v>42</v>
       </c>
       <c r="B36">
-        <v>2738</v>
+        <v>2704</v>
       </c>
       <c r="C36" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="D36" t="s">
-        <v>244</v>
+        <v>224</v>
       </c>
       <c r="E36" t="s">
-        <v>265</v>
+        <v>243</v>
       </c>
       <c r="F36" t="s">
-        <v>276</v>
+        <v>251</v>
       </c>
       <c r="G36" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="H36">
-        <v>21.2</v>
-      </c>
-      <c r="J36" s="2">
-        <v>46265</v>
+        <v>57.5</v>
+      </c>
+      <c r="J36" s="1">
+        <v>46493</v>
       </c>
       <c r="K36" t="b">
         <v>0</v>
@@ -2531,31 +2439,31 @@
     </row>
     <row r="37" spans="1:11">
       <c r="A37" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B37">
-        <v>2736</v>
+        <v>2704</v>
       </c>
       <c r="C37" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="D37" t="s">
+        <v>220</v>
+      </c>
+      <c r="E37" t="s">
         <v>243</v>
       </c>
-      <c r="E37" t="s">
+      <c r="F37" t="s">
         <v>265</v>
       </c>
-      <c r="F37" t="s">
-        <v>281</v>
-      </c>
       <c r="G37" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="H37">
-        <v>26.2</v>
-      </c>
-      <c r="J37" s="2">
-        <v>46265</v>
+        <v>71</v>
+      </c>
+      <c r="J37" s="1">
+        <v>46527</v>
       </c>
       <c r="K37" t="b">
         <v>0</v>
@@ -2563,31 +2471,31 @@
     </row>
     <row r="38" spans="1:11">
       <c r="A38" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B38">
         <v>2704</v>
       </c>
       <c r="C38" t="s">
-        <v>208</v>
+        <v>189</v>
       </c>
       <c r="D38" t="s">
-        <v>244</v>
+        <v>221</v>
       </c>
       <c r="E38" t="s">
-        <v>266</v>
+        <v>243</v>
       </c>
       <c r="F38" t="s">
-        <v>276</v>
+        <v>252</v>
       </c>
       <c r="G38" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="H38">
-        <v>33.6</v>
-      </c>
-      <c r="J38" s="2">
-        <v>46364</v>
+        <v>73</v>
+      </c>
+      <c r="J38" s="1">
+        <v>46532</v>
       </c>
       <c r="K38" t="b">
         <v>0</v>
@@ -2595,31 +2503,31 @@
     </row>
     <row r="39" spans="1:11">
       <c r="A39" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B39">
         <v>2740</v>
       </c>
       <c r="C39" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="D39" t="s">
-        <v>243</v>
+        <v>226</v>
       </c>
       <c r="E39" t="s">
-        <v>265</v>
+        <v>242</v>
       </c>
       <c r="F39" t="s">
-        <v>286</v>
+        <v>266</v>
       </c>
       <c r="G39" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="H39">
-        <v>42.2</v>
-      </c>
-      <c r="J39" s="2">
-        <v>46269</v>
+        <v>82</v>
+      </c>
+      <c r="J39" s="1">
+        <v>46389</v>
       </c>
       <c r="K39" t="b">
         <v>0</v>
@@ -2627,31 +2535,31 @@
     </row>
     <row r="40" spans="1:11">
       <c r="A40" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B40">
-        <v>2721</v>
+        <v>2738</v>
       </c>
       <c r="C40" t="s">
-        <v>206</v>
+        <v>183</v>
       </c>
       <c r="D40" t="s">
-        <v>245</v>
+        <v>222</v>
       </c>
       <c r="E40" t="s">
-        <v>272</v>
+        <v>242</v>
       </c>
       <c r="F40" t="s">
-        <v>277</v>
+        <v>257</v>
       </c>
       <c r="G40" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="H40">
-        <v>42.8</v>
-      </c>
-      <c r="J40" s="2">
-        <v>46291</v>
+        <v>107.1</v>
+      </c>
+      <c r="J40" s="1">
+        <v>46338</v>
       </c>
       <c r="K40" t="b">
         <v>0</v>
@@ -2659,31 +2567,31 @@
     </row>
     <row r="41" spans="1:11">
       <c r="A41" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B41">
-        <v>2704</v>
+        <v>2737</v>
       </c>
       <c r="C41" t="s">
-        <v>209</v>
+        <v>183</v>
       </c>
       <c r="D41" t="s">
-        <v>247</v>
+        <v>222</v>
       </c>
       <c r="E41" t="s">
-        <v>266</v>
+        <v>242</v>
       </c>
       <c r="F41" t="s">
-        <v>279</v>
+        <v>257</v>
       </c>
       <c r="G41" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="H41">
-        <v>45.7</v>
-      </c>
-      <c r="J41" s="2">
-        <v>46395</v>
+        <v>109.8</v>
+      </c>
+      <c r="J41" s="1">
+        <v>46337</v>
       </c>
       <c r="K41" t="b">
         <v>0</v>
@@ -2691,31 +2599,31 @@
     </row>
     <row r="42" spans="1:11">
       <c r="A42" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B42">
-        <v>2720</v>
+        <v>2740</v>
       </c>
       <c r="C42" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="D42" t="s">
-        <v>243</v>
+        <v>221</v>
       </c>
       <c r="E42" t="s">
-        <v>272</v>
+        <v>242</v>
       </c>
       <c r="F42" t="s">
-        <v>287</v>
+        <v>252</v>
       </c>
       <c r="G42" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="H42">
-        <v>47.2</v>
-      </c>
-      <c r="J42" s="2">
-        <v>46280</v>
+        <v>112.9</v>
+      </c>
+      <c r="J42" s="1">
+        <v>46401</v>
       </c>
       <c r="K42" t="b">
         <v>0</v>
@@ -2723,31 +2631,31 @@
     </row>
     <row r="43" spans="1:11">
       <c r="A43" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B43">
-        <v>2720</v>
+        <v>2709</v>
       </c>
       <c r="C43" t="s">
-        <v>206</v>
+        <v>190</v>
       </c>
       <c r="D43" t="s">
-        <v>245</v>
+        <v>226</v>
       </c>
       <c r="E43" t="s">
-        <v>272</v>
+        <v>247</v>
       </c>
       <c r="F43" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="G43" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="H43">
-        <v>48.7</v>
-      </c>
-      <c r="J43" s="2">
-        <v>46281</v>
+        <v>121.9</v>
+      </c>
+      <c r="J43" s="1">
+        <v>46412</v>
       </c>
       <c r="K43" t="b">
         <v>0</v>
@@ -2755,31 +2663,31 @@
     </row>
     <row r="44" spans="1:11">
       <c r="A44" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B44">
-        <v>2740</v>
+        <v>2739</v>
       </c>
       <c r="C44" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="D44" t="s">
-        <v>248</v>
+        <v>220</v>
       </c>
       <c r="E44" t="s">
-        <v>265</v>
+        <v>246</v>
       </c>
       <c r="F44" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="G44" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="H44">
-        <v>60</v>
-      </c>
-      <c r="J44" s="2">
-        <v>46281</v>
+        <v>135.1</v>
+      </c>
+      <c r="J44" s="1">
+        <v>46353</v>
       </c>
       <c r="K44" t="b">
         <v>0</v>
@@ -2787,31 +2695,31 @@
     </row>
     <row r="45" spans="1:11">
       <c r="A45" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B45">
-        <v>2743</v>
+        <v>2727</v>
       </c>
       <c r="C45" t="s">
-        <v>201</v>
+        <v>183</v>
       </c>
       <c r="D45" t="s">
-        <v>243</v>
+        <v>222</v>
       </c>
       <c r="E45" t="s">
-        <v>269</v>
+        <v>249</v>
       </c>
       <c r="F45" t="s">
-        <v>288</v>
+        <v>257</v>
       </c>
       <c r="G45" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="H45">
-        <v>62.6</v>
-      </c>
-      <c r="J45" s="2">
-        <v>46265</v>
+        <v>136.2</v>
+      </c>
+      <c r="J45" s="1">
+        <v>46419</v>
       </c>
       <c r="K45" t="b">
         <v>0</v>
@@ -2819,31 +2727,31 @@
     </row>
     <row r="46" spans="1:11">
       <c r="A46" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B46">
-        <v>2743</v>
+        <v>2736</v>
       </c>
       <c r="C46" t="s">
-        <v>202</v>
+        <v>183</v>
       </c>
       <c r="D46" t="s">
-        <v>243</v>
+        <v>222</v>
       </c>
       <c r="E46" t="s">
-        <v>269</v>
+        <v>242</v>
       </c>
       <c r="F46" t="s">
-        <v>288</v>
+        <v>257</v>
       </c>
       <c r="G46" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="H46">
-        <v>64.59999999999999</v>
-      </c>
-      <c r="J46" s="2">
-        <v>46265</v>
+        <v>138.8</v>
+      </c>
+      <c r="J46" s="1">
+        <v>46353</v>
       </c>
       <c r="K46" t="b">
         <v>0</v>
@@ -2851,31 +2759,31 @@
     </row>
     <row r="47" spans="1:11">
       <c r="A47" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B47">
-        <v>2722</v>
+        <v>2739</v>
       </c>
       <c r="C47" t="s">
-        <v>198</v>
+        <v>179</v>
       </c>
       <c r="D47" t="s">
-        <v>244</v>
+        <v>220</v>
       </c>
       <c r="E47" t="s">
-        <v>268</v>
+        <v>246</v>
       </c>
       <c r="F47" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="G47" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="H47">
-        <v>67.59999999999999</v>
-      </c>
-      <c r="J47" s="2">
-        <v>46267</v>
+        <v>140.1</v>
+      </c>
+      <c r="J47" s="1">
+        <v>46355</v>
       </c>
       <c r="K47" t="b">
         <v>0</v>
@@ -2883,31 +2791,31 @@
     </row>
     <row r="48" spans="1:11">
       <c r="A48" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B48">
-        <v>2737</v>
+        <v>2736</v>
       </c>
       <c r="C48" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="D48" t="s">
-        <v>243</v>
+        <v>220</v>
       </c>
       <c r="E48" t="s">
-        <v>265</v>
+        <v>242</v>
       </c>
       <c r="F48" t="s">
-        <v>289</v>
+        <v>252</v>
       </c>
       <c r="G48" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="H48">
-        <v>68.3</v>
-      </c>
-      <c r="J48" s="2">
-        <v>46278</v>
+        <v>141.6</v>
+      </c>
+      <c r="J48" s="1">
+        <v>46355</v>
       </c>
       <c r="K48" t="b">
         <v>0</v>
@@ -2915,31 +2823,31 @@
     </row>
     <row r="49" spans="1:11">
       <c r="A49" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B49">
-        <v>2704</v>
+        <v>2736</v>
       </c>
       <c r="C49" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="D49" t="s">
-        <v>248</v>
+        <v>224</v>
       </c>
       <c r="E49" t="s">
-        <v>266</v>
+        <v>242</v>
       </c>
       <c r="F49" t="s">
-        <v>275</v>
+        <v>255</v>
       </c>
       <c r="G49" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="H49">
-        <v>69.2</v>
-      </c>
-      <c r="J49" s="2">
-        <v>46453</v>
+        <v>161.2</v>
+      </c>
+      <c r="J49" s="1">
+        <v>46394</v>
       </c>
       <c r="K49" t="b">
         <v>0</v>
@@ -2947,31 +2855,31 @@
     </row>
     <row r="50" spans="1:11">
       <c r="A50" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B50">
-        <v>2743</v>
+        <v>2739</v>
       </c>
       <c r="C50" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="D50" t="s">
-        <v>244</v>
+        <v>222</v>
       </c>
       <c r="E50" t="s">
-        <v>269</v>
+        <v>246</v>
       </c>
       <c r="F50" t="s">
-        <v>276</v>
+        <v>257</v>
       </c>
       <c r="G50" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="H50">
-        <v>69.8</v>
-      </c>
-      <c r="J50" s="2">
-        <v>46265</v>
+        <v>170.3</v>
+      </c>
+      <c r="J50" s="1">
+        <v>46370</v>
       </c>
       <c r="K50" t="b">
         <v>0</v>
@@ -2979,31 +2887,31 @@
     </row>
     <row r="51" spans="1:11">
       <c r="A51" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B51">
-        <v>2743</v>
+        <v>2721</v>
       </c>
       <c r="C51" t="s">
-        <v>211</v>
+        <v>189</v>
       </c>
       <c r="D51" t="s">
-        <v>244</v>
+        <v>221</v>
       </c>
       <c r="E51" t="s">
-        <v>269</v>
+        <v>247</v>
       </c>
       <c r="F51" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="G51" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="H51">
-        <v>69.8</v>
-      </c>
-      <c r="J51" s="2">
-        <v>46265</v>
+        <v>177.4</v>
+      </c>
+      <c r="J51" s="1">
+        <v>46487</v>
       </c>
       <c r="K51" t="b">
         <v>0</v>
@@ -3011,31 +2919,31 @@
     </row>
     <row r="52" spans="1:11">
       <c r="A52" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B52">
-        <v>2742</v>
+        <v>2719</v>
       </c>
       <c r="C52" t="s">
-        <v>199</v>
+        <v>183</v>
       </c>
       <c r="D52" t="s">
-        <v>243</v>
+        <v>222</v>
       </c>
       <c r="E52" t="s">
-        <v>274</v>
+        <v>245</v>
       </c>
       <c r="F52" t="s">
-        <v>290</v>
+        <v>257</v>
       </c>
       <c r="G52" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="H52">
-        <v>72.2</v>
-      </c>
-      <c r="J52" s="2">
-        <v>46275</v>
+        <v>184.1</v>
+      </c>
+      <c r="J52" s="1">
+        <v>46358</v>
       </c>
       <c r="K52" t="b">
         <v>0</v>
@@ -3043,31 +2951,31 @@
     </row>
     <row r="53" spans="1:11">
       <c r="A53" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B53">
-        <v>2742</v>
+        <v>2740</v>
       </c>
       <c r="C53" t="s">
-        <v>207</v>
+        <v>183</v>
       </c>
       <c r="D53" t="s">
-        <v>246</v>
+        <v>222</v>
       </c>
       <c r="E53" t="s">
-        <v>274</v>
+        <v>242</v>
       </c>
       <c r="F53" t="s">
-        <v>283</v>
+        <v>257</v>
       </c>
       <c r="G53" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="H53">
-        <v>72.2</v>
-      </c>
-      <c r="J53" s="2">
-        <v>46275</v>
+        <v>199.3</v>
+      </c>
+      <c r="J53" s="1">
+        <v>46433</v>
       </c>
       <c r="K53" t="b">
         <v>0</v>
@@ -3075,31 +2983,31 @@
     </row>
     <row r="54" spans="1:11">
       <c r="A54" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B54">
-        <v>2743</v>
+        <v>2723</v>
       </c>
       <c r="C54" t="s">
-        <v>206</v>
+        <v>183</v>
       </c>
       <c r="D54" t="s">
-        <v>245</v>
+        <v>222</v>
       </c>
       <c r="E54" t="s">
-        <v>269</v>
+        <v>250</v>
       </c>
       <c r="F54" t="s">
-        <v>277</v>
+        <v>257</v>
       </c>
       <c r="G54" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="H54">
-        <v>78.09999999999999</v>
-      </c>
-      <c r="J54" s="2">
-        <v>46265</v>
+        <v>200</v>
+      </c>
+      <c r="J54" s="1">
+        <v>46367</v>
       </c>
       <c r="K54" t="b">
         <v>0</v>
@@ -3107,31 +3015,31 @@
     </row>
     <row r="55" spans="1:11">
       <c r="A55" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B55">
-        <v>2704</v>
+        <v>2731</v>
       </c>
       <c r="C55" t="s">
-        <v>212</v>
+        <v>188</v>
       </c>
       <c r="D55" t="s">
-        <v>243</v>
+        <v>220</v>
       </c>
       <c r="E55" t="s">
-        <v>266</v>
+        <v>246</v>
       </c>
       <c r="F55" t="s">
-        <v>291</v>
+        <v>265</v>
       </c>
       <c r="G55" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="H55">
-        <v>82.8</v>
-      </c>
-      <c r="J55" s="2">
-        <v>46487</v>
+        <v>203.6</v>
+      </c>
+      <c r="J55" s="1">
+        <v>46388</v>
       </c>
       <c r="K55" t="b">
         <v>0</v>
@@ -3139,31 +3047,31 @@
     </row>
     <row r="56" spans="1:11">
       <c r="A56" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B56">
-        <v>2741</v>
+        <v>2738</v>
       </c>
       <c r="C56" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="D56" t="s">
-        <v>243</v>
+        <v>221</v>
       </c>
       <c r="E56" t="s">
-        <v>265</v>
+        <v>242</v>
       </c>
       <c r="F56" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="G56" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="H56">
-        <v>83.09999999999999</v>
-      </c>
-      <c r="J56" s="2">
-        <v>46285</v>
+        <v>207.6</v>
+      </c>
+      <c r="J56" s="1">
+        <v>46391</v>
       </c>
       <c r="K56" t="b">
         <v>0</v>
@@ -3171,31 +3079,31 @@
     </row>
     <row r="57" spans="1:11">
       <c r="A57" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B57">
-        <v>2704</v>
+        <v>2740</v>
       </c>
       <c r="C57" t="s">
-        <v>213</v>
+        <v>195</v>
       </c>
       <c r="D57" t="s">
-        <v>244</v>
+        <v>227</v>
       </c>
       <c r="E57" t="s">
-        <v>266</v>
+        <v>242</v>
       </c>
       <c r="F57" t="s">
-        <v>276</v>
+        <v>255</v>
       </c>
       <c r="G57" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="H57">
-        <v>84.8</v>
-      </c>
-      <c r="J57" s="2">
-        <v>46492</v>
+        <v>226.1</v>
+      </c>
+      <c r="J57" s="1">
+        <v>46442</v>
       </c>
       <c r="K57" t="b">
         <v>0</v>
@@ -3203,31 +3111,31 @@
     </row>
     <row r="58" spans="1:11">
       <c r="A58" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B58">
-        <v>2741</v>
+        <v>2740</v>
       </c>
       <c r="C58" t="s">
-        <v>207</v>
+        <v>175</v>
       </c>
       <c r="D58" t="s">
-        <v>246</v>
+        <v>221</v>
       </c>
       <c r="E58" t="s">
-        <v>265</v>
+        <v>242</v>
       </c>
       <c r="F58" t="s">
-        <v>283</v>
+        <v>270</v>
       </c>
       <c r="G58" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="H58">
-        <v>104.9</v>
-      </c>
-      <c r="J58" s="2">
-        <v>46297</v>
+        <v>277</v>
+      </c>
+      <c r="J58" s="1">
+        <v>46461</v>
       </c>
       <c r="K58" t="b">
         <v>0</v>
@@ -3235,31 +3143,31 @@
     </row>
     <row r="59" spans="1:11">
       <c r="A59" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B59">
         <v>2719</v>
       </c>
       <c r="C59" t="s">
-        <v>207</v>
+        <v>191</v>
       </c>
       <c r="D59" t="s">
-        <v>246</v>
+        <v>221</v>
       </c>
       <c r="E59" t="s">
-        <v>268</v>
+        <v>245</v>
       </c>
       <c r="F59" t="s">
-        <v>283</v>
+        <v>252</v>
       </c>
       <c r="G59" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="H59">
-        <v>107.6</v>
-      </c>
-      <c r="J59" s="2">
-        <v>46283</v>
+        <v>280.6</v>
+      </c>
+      <c r="J59" s="1">
+        <v>46409</v>
       </c>
       <c r="K59" t="b">
         <v>0</v>
@@ -3267,351 +3175,384 @@
     </row>
     <row r="60" spans="1:11">
       <c r="A60" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B60">
-        <v>2741</v>
+        <v>2706</v>
       </c>
       <c r="C60" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="D60" t="s">
+        <v>228</v>
+      </c>
+      <c r="E60" t="s">
         <v>243</v>
       </c>
-      <c r="E60" t="s">
-        <v>265</v>
-      </c>
       <c r="F60" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="G60" t="s">
-        <v>308</v>
+        <v>285</v>
       </c>
       <c r="H60">
-        <v>111.9</v>
-      </c>
-      <c r="J60" s="2">
-        <v>46300</v>
+        <v>-9570</v>
+      </c>
+      <c r="I60" t="s">
+        <v>287</v>
+      </c>
+      <c r="J60" s="1">
+        <v>36557</v>
       </c>
       <c r="K60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:11">
       <c r="A61" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B61">
-        <v>2741</v>
+        <v>2740</v>
       </c>
       <c r="C61" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="D61" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="E61" t="s">
-        <v>265</v>
+        <v>242</v>
       </c>
       <c r="F61" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="G61" t="s">
-        <v>308</v>
+        <v>285</v>
       </c>
       <c r="H61">
-        <v>111.9</v>
-      </c>
-      <c r="J61" s="2">
-        <v>46300</v>
+        <v>-4980</v>
+      </c>
+      <c r="I61" t="s">
+        <v>288</v>
+      </c>
+      <c r="J61" s="1">
+        <v>41275</v>
       </c>
       <c r="K61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:11">
       <c r="A62" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B62">
-        <v>2741</v>
+        <v>2724</v>
       </c>
       <c r="C62" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="D62" t="s">
+        <v>230</v>
+      </c>
+      <c r="E62" t="s">
         <v>243</v>
       </c>
-      <c r="E62" t="s">
-        <v>265</v>
-      </c>
       <c r="F62" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="G62" t="s">
-        <v>308</v>
+        <v>285</v>
       </c>
       <c r="H62">
-        <v>111.9</v>
-      </c>
-      <c r="J62" s="2">
-        <v>46300</v>
+        <v>-870</v>
+      </c>
+      <c r="I62" t="s">
+        <v>289</v>
+      </c>
+      <c r="J62" s="1">
+        <v>45380</v>
       </c>
       <c r="K62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:11">
       <c r="A63" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B63">
-        <v>2741</v>
+        <v>2724</v>
       </c>
       <c r="C63" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D63" t="s">
+        <v>231</v>
+      </c>
+      <c r="E63" t="s">
         <v>243</v>
       </c>
-      <c r="E63" t="s">
-        <v>265</v>
-      </c>
       <c r="F63" t="s">
-        <v>275</v>
+        <v>251</v>
       </c>
       <c r="G63" t="s">
-        <v>308</v>
+        <v>285</v>
       </c>
       <c r="H63">
-        <v>111.9</v>
-      </c>
-      <c r="J63" s="2">
-        <v>46300</v>
+        <v>-840</v>
+      </c>
+      <c r="I63" t="s">
+        <v>290</v>
+      </c>
+      <c r="J63" s="1">
+        <v>45421</v>
       </c>
       <c r="K63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:11">
       <c r="A64" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B64">
-        <v>2741</v>
+        <v>2724</v>
       </c>
       <c r="C64" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="D64" t="s">
+        <v>232</v>
+      </c>
+      <c r="E64" t="s">
         <v>243</v>
       </c>
-      <c r="E64" t="s">
-        <v>265</v>
-      </c>
       <c r="F64" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G64" t="s">
-        <v>308</v>
+        <v>285</v>
       </c>
       <c r="H64">
-        <v>111.9</v>
-      </c>
-      <c r="J64" s="2">
-        <v>46300</v>
+        <v>-840</v>
+      </c>
+      <c r="I64" t="s">
+        <v>290</v>
+      </c>
+      <c r="J64" s="1">
+        <v>45428</v>
       </c>
       <c r="K64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:11">
       <c r="A65" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B65">
-        <v>2738</v>
+        <v>2724</v>
       </c>
       <c r="C65" t="s">
-        <v>214</v>
+        <v>197</v>
       </c>
       <c r="D65" t="s">
-        <v>249</v>
+        <v>229</v>
       </c>
       <c r="E65" t="s">
-        <v>265</v>
+        <v>243</v>
       </c>
       <c r="F65" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="G65" t="s">
-        <v>308</v>
+        <v>285</v>
       </c>
       <c r="H65">
-        <v>128.8</v>
-      </c>
-      <c r="J65" s="2">
-        <v>46308</v>
+        <v>-780</v>
+      </c>
+      <c r="I65" t="s">
+        <v>291</v>
+      </c>
+      <c r="J65" s="1">
+        <v>45490</v>
       </c>
       <c r="K65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:11">
       <c r="A66" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B66">
-        <v>2740</v>
+        <v>2724</v>
       </c>
       <c r="C66" t="s">
-        <v>215</v>
+        <v>183</v>
       </c>
       <c r="D66" t="s">
-        <v>250</v>
+        <v>222</v>
       </c>
       <c r="E66" t="s">
-        <v>265</v>
+        <v>243</v>
       </c>
       <c r="F66" t="s">
+        <v>276</v>
+      </c>
+      <c r="G66" t="s">
+        <v>285</v>
+      </c>
+      <c r="H66">
+        <v>-690</v>
+      </c>
+      <c r="I66" t="s">
         <v>292</v>
       </c>
-      <c r="G66" t="s">
-        <v>308</v>
-      </c>
-      <c r="H66">
-        <v>131.1</v>
-      </c>
-      <c r="J66" s="2">
-        <v>46336</v>
+      <c r="J66" s="1">
+        <v>45566</v>
       </c>
       <c r="K66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:11">
       <c r="A67" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B67">
-        <v>2740</v>
+        <v>2730</v>
       </c>
       <c r="C67" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="D67" t="s">
-        <v>246</v>
+        <v>221</v>
       </c>
       <c r="E67" t="s">
-        <v>265</v>
+        <v>243</v>
       </c>
       <c r="F67" t="s">
-        <v>283</v>
+        <v>269</v>
       </c>
       <c r="G67" t="s">
-        <v>308</v>
+        <v>285</v>
       </c>
       <c r="H67">
-        <v>138.4</v>
-      </c>
-      <c r="J67" s="2">
-        <v>46343</v>
+        <v>-270</v>
+      </c>
+      <c r="I67" t="s">
+        <v>293</v>
+      </c>
+      <c r="J67" s="1">
+        <v>45986</v>
       </c>
       <c r="K67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:11">
       <c r="A68" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B68">
-        <v>2709</v>
+        <v>2733</v>
       </c>
       <c r="C68" t="s">
-        <v>215</v>
+        <v>194</v>
       </c>
       <c r="D68" t="s">
-        <v>250</v>
+        <v>221</v>
       </c>
       <c r="E68" t="s">
-        <v>272</v>
+        <v>246</v>
       </c>
       <c r="F68" t="s">
-        <v>292</v>
+        <v>269</v>
       </c>
       <c r="G68" t="s">
-        <v>308</v>
+        <v>285</v>
       </c>
       <c r="H68">
-        <v>141</v>
-      </c>
-      <c r="J68" s="2">
-        <v>46350</v>
+        <v>-60</v>
+      </c>
+      <c r="I68" t="s">
+        <v>294</v>
+      </c>
+      <c r="J68" s="1">
+        <v>46197</v>
       </c>
       <c r="K68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:11">
       <c r="A69" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B69">
-        <v>2740</v>
+        <v>2729</v>
       </c>
       <c r="C69" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="D69" t="s">
+        <v>232</v>
+      </c>
+      <c r="E69" t="s">
         <v>244</v>
       </c>
-      <c r="E69" t="s">
-        <v>265</v>
-      </c>
       <c r="F69" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="G69" t="s">
-        <v>308</v>
+        <v>285</v>
       </c>
       <c r="H69">
-        <v>162</v>
-      </c>
-      <c r="J69" s="2">
-        <v>46391</v>
+        <v>-60</v>
+      </c>
+      <c r="I69" t="s">
+        <v>294</v>
+      </c>
+      <c r="J69" s="1">
+        <v>46212</v>
       </c>
       <c r="K69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:11">
       <c r="A70" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B70">
-        <v>2737</v>
+        <v>2722</v>
       </c>
       <c r="C70" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="D70" t="s">
-        <v>246</v>
+        <v>231</v>
       </c>
       <c r="E70" t="s">
-        <v>265</v>
+        <v>245</v>
       </c>
       <c r="F70" t="s">
-        <v>283</v>
+        <v>255</v>
       </c>
       <c r="G70" t="s">
-        <v>308</v>
+        <v>285</v>
       </c>
       <c r="H70">
-        <v>167.2</v>
-      </c>
-      <c r="J70" s="2">
-        <v>46330</v>
+        <v>60</v>
+      </c>
+      <c r="I70" t="s">
+        <v>295</v>
+      </c>
+      <c r="J70" s="1">
+        <v>46341</v>
       </c>
       <c r="K70" t="b">
         <v>0</v>
@@ -3619,31 +3560,34 @@
     </row>
     <row r="71" spans="1:11">
       <c r="A71" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B71">
-        <v>2721</v>
+        <v>2703</v>
       </c>
       <c r="C71" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="D71" t="s">
+        <v>233</v>
+      </c>
+      <c r="E71" t="s">
         <v>244</v>
       </c>
-      <c r="E71" t="s">
-        <v>272</v>
-      </c>
       <c r="F71" t="s">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="G71" t="s">
-        <v>308</v>
+        <v>285</v>
       </c>
       <c r="H71">
-        <v>177.4</v>
-      </c>
-      <c r="J71" s="2">
-        <v>46418</v>
+        <v>60</v>
+      </c>
+      <c r="I71" t="s">
+        <v>295</v>
+      </c>
+      <c r="J71" s="1">
+        <v>46344</v>
       </c>
       <c r="K71" t="b">
         <v>0</v>
@@ -3651,31 +3595,34 @@
     </row>
     <row r="72" spans="1:11">
       <c r="A72" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B72">
-        <v>2723</v>
+        <v>2728</v>
       </c>
       <c r="C72" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="D72" t="s">
-        <v>246</v>
+        <v>229</v>
       </c>
       <c r="E72" t="s">
-        <v>271</v>
+        <v>243</v>
       </c>
       <c r="F72" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="G72" t="s">
-        <v>308</v>
+        <v>285</v>
       </c>
       <c r="H72">
-        <v>200</v>
-      </c>
-      <c r="J72" s="2">
-        <v>46356</v>
+        <v>60</v>
+      </c>
+      <c r="I72" t="s">
+        <v>295</v>
+      </c>
+      <c r="J72" s="1">
+        <v>46360</v>
       </c>
       <c r="K72" t="b">
         <v>0</v>
@@ -3683,31 +3630,34 @@
     </row>
     <row r="73" spans="1:11">
       <c r="A73" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B73">
-        <v>2731</v>
+        <v>2734</v>
       </c>
       <c r="C73" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="D73" t="s">
+        <v>234</v>
+      </c>
+      <c r="E73" t="s">
         <v>243</v>
       </c>
-      <c r="E73" t="s">
-        <v>270</v>
-      </c>
       <c r="F73" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="G73" t="s">
-        <v>308</v>
+        <v>285</v>
       </c>
       <c r="H73">
-        <v>203.6</v>
-      </c>
-      <c r="J73" s="2">
-        <v>46436</v>
+        <v>60</v>
+      </c>
+      <c r="I73" t="s">
+        <v>295</v>
+      </c>
+      <c r="J73" s="1">
+        <v>46367</v>
       </c>
       <c r="K73" t="b">
         <v>0</v>
@@ -3715,31 +3665,34 @@
     </row>
     <row r="74" spans="1:11">
       <c r="A74" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B74">
-        <v>2736</v>
+        <v>2709</v>
       </c>
       <c r="C74" t="s">
-        <v>216</v>
+        <v>176</v>
       </c>
       <c r="D74" t="s">
-        <v>243</v>
+        <v>220</v>
       </c>
       <c r="E74" t="s">
-        <v>265</v>
+        <v>247</v>
       </c>
       <c r="F74" t="s">
-        <v>276</v>
+        <v>261</v>
       </c>
       <c r="G74" t="s">
-        <v>308</v>
+        <v>285</v>
       </c>
       <c r="H74">
-        <v>221.2</v>
-      </c>
-      <c r="J74" s="2">
-        <v>46426</v>
+        <v>60</v>
+      </c>
+      <c r="I74" t="s">
+        <v>295</v>
+      </c>
+      <c r="J74" s="1">
+        <v>46368</v>
       </c>
       <c r="K74" t="b">
         <v>0</v>
@@ -3747,31 +3700,34 @@
     </row>
     <row r="75" spans="1:11">
       <c r="A75" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B75">
-        <v>2739</v>
+        <v>2740</v>
       </c>
       <c r="C75" t="s">
-        <v>201</v>
+        <v>176</v>
       </c>
       <c r="D75" t="s">
-        <v>243</v>
+        <v>220</v>
       </c>
       <c r="E75" t="s">
-        <v>270</v>
+        <v>242</v>
       </c>
       <c r="F75" t="s">
-        <v>288</v>
+        <v>261</v>
       </c>
       <c r="G75" t="s">
-        <v>308</v>
+        <v>285</v>
       </c>
       <c r="H75">
-        <v>240.8</v>
-      </c>
-      <c r="J75" s="2">
-        <v>46450</v>
+        <v>60</v>
+      </c>
+      <c r="I75" t="s">
+        <v>295</v>
+      </c>
+      <c r="J75" s="1">
+        <v>46374</v>
       </c>
       <c r="K75" t="b">
         <v>0</v>
@@ -3779,31 +3735,34 @@
     </row>
     <row r="76" spans="1:11">
       <c r="A76" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B76">
-        <v>2739</v>
+        <v>2732</v>
       </c>
       <c r="C76" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D76" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="E76" t="s">
-        <v>270</v>
+        <v>242</v>
       </c>
       <c r="F76" t="s">
-        <v>288</v>
+        <v>258</v>
       </c>
       <c r="G76" t="s">
-        <v>308</v>
+        <v>285</v>
       </c>
       <c r="H76">
-        <v>245.8</v>
-      </c>
-      <c r="J76" s="2">
-        <v>46452</v>
+        <v>90</v>
+      </c>
+      <c r="I76" t="s">
+        <v>296</v>
+      </c>
+      <c r="J76" s="1">
+        <v>46375</v>
       </c>
       <c r="K76" t="b">
         <v>0</v>
@@ -3811,31 +3770,34 @@
     </row>
     <row r="77" spans="1:11">
       <c r="A77" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B77">
-        <v>2743</v>
+        <v>2730</v>
       </c>
       <c r="C77" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="D77" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="E77" t="s">
-        <v>269</v>
+        <v>243</v>
       </c>
       <c r="F77" t="s">
-        <v>294</v>
+        <v>277</v>
       </c>
       <c r="G77" t="s">
-        <v>308</v>
+        <v>285</v>
       </c>
       <c r="H77">
-        <v>263.4</v>
-      </c>
-      <c r="J77" s="2">
-        <v>46322</v>
+        <v>90</v>
+      </c>
+      <c r="I77" t="s">
+        <v>296</v>
+      </c>
+      <c r="J77" s="1">
+        <v>46387</v>
       </c>
       <c r="K77" t="b">
         <v>0</v>
@@ -3843,31 +3805,34 @@
     </row>
     <row r="78" spans="1:11">
       <c r="A78" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B78">
-        <v>2740</v>
+        <v>2732</v>
       </c>
       <c r="C78" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="D78" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
       <c r="E78" t="s">
-        <v>265</v>
+        <v>242</v>
       </c>
       <c r="F78" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="G78" t="s">
-        <v>308</v>
+        <v>285</v>
       </c>
       <c r="H78">
-        <v>275.2</v>
-      </c>
-      <c r="J78" s="2">
-        <v>46433</v>
+        <v>90</v>
+      </c>
+      <c r="I78" t="s">
+        <v>296</v>
+      </c>
+      <c r="J78" s="1">
+        <v>46387</v>
       </c>
       <c r="K78" t="b">
         <v>0</v>
@@ -3875,314 +3840,314 @@
     </row>
     <row r="79" spans="1:11">
       <c r="A79" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B79">
-        <v>2706</v>
+        <v>2736</v>
       </c>
       <c r="C79" t="s">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="D79" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
       <c r="E79" t="s">
-        <v>266</v>
+        <v>242</v>
       </c>
       <c r="F79" t="s">
-        <v>295</v>
+        <v>277</v>
       </c>
       <c r="G79" t="s">
-        <v>309</v>
+        <v>285</v>
       </c>
       <c r="H79">
-        <v>-9540</v>
+        <v>90</v>
       </c>
       <c r="I79" t="s">
-        <v>311</v>
-      </c>
-      <c r="J79" s="2">
-        <v>36557</v>
+        <v>296</v>
+      </c>
+      <c r="J79" s="1">
+        <v>46387</v>
       </c>
       <c r="K79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:11">
       <c r="A80" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B80">
-        <v>2740</v>
+        <v>2728</v>
       </c>
       <c r="C80" t="s">
-        <v>218</v>
+        <v>198</v>
       </c>
       <c r="D80" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="E80" t="s">
-        <v>265</v>
+        <v>243</v>
       </c>
       <c r="F80" t="s">
+        <v>272</v>
+      </c>
+      <c r="G80" t="s">
+        <v>285</v>
+      </c>
+      <c r="H80">
+        <v>90</v>
+      </c>
+      <c r="I80" t="s">
         <v>296</v>
       </c>
-      <c r="G80" t="s">
-        <v>309</v>
-      </c>
-      <c r="H80">
-        <v>-4950</v>
-      </c>
-      <c r="I80" t="s">
-        <v>312</v>
-      </c>
-      <c r="J80" s="2">
-        <v>41275</v>
+      <c r="J80" s="1">
+        <v>46388</v>
       </c>
       <c r="K80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:11">
       <c r="A81" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B81">
-        <v>2724</v>
+        <v>2704</v>
       </c>
       <c r="C81" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="D81" t="s">
-        <v>253</v>
+        <v>236</v>
       </c>
       <c r="E81" t="s">
-        <v>266</v>
+        <v>243</v>
       </c>
       <c r="F81" t="s">
-        <v>297</v>
+        <v>278</v>
       </c>
       <c r="G81" t="s">
-        <v>309</v>
+        <v>285</v>
       </c>
       <c r="H81">
-        <v>-840</v>
+        <v>90</v>
       </c>
       <c r="I81" t="s">
-        <v>313</v>
-      </c>
-      <c r="J81" s="2">
-        <v>45380</v>
+        <v>296</v>
+      </c>
+      <c r="J81" s="1">
+        <v>46401</v>
       </c>
       <c r="K81" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:11">
       <c r="A82" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B82">
-        <v>2724</v>
+        <v>2704</v>
       </c>
       <c r="C82" t="s">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="D82" t="s">
-        <v>254</v>
+        <v>232</v>
       </c>
       <c r="E82" t="s">
-        <v>266</v>
+        <v>243</v>
       </c>
       <c r="F82" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G82" t="s">
-        <v>309</v>
+        <v>285</v>
       </c>
       <c r="H82">
-        <v>-780</v>
+        <v>90</v>
       </c>
       <c r="I82" t="s">
-        <v>314</v>
-      </c>
-      <c r="J82" s="2">
-        <v>45421</v>
+        <v>296</v>
+      </c>
+      <c r="J82" s="1">
+        <v>46401</v>
       </c>
       <c r="K82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:11">
       <c r="A83" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B83">
-        <v>2724</v>
+        <v>2709</v>
       </c>
       <c r="C83" t="s">
-        <v>221</v>
+        <v>197</v>
       </c>
       <c r="D83" t="s">
-        <v>255</v>
+        <v>229</v>
       </c>
       <c r="E83" t="s">
-        <v>266</v>
+        <v>247</v>
       </c>
       <c r="F83" t="s">
-        <v>294</v>
+        <v>275</v>
       </c>
       <c r="G83" t="s">
-        <v>309</v>
+        <v>285</v>
       </c>
       <c r="H83">
-        <v>-780</v>
+        <v>90</v>
       </c>
       <c r="I83" t="s">
-        <v>314</v>
-      </c>
-      <c r="J83" s="2">
-        <v>45428</v>
+        <v>296</v>
+      </c>
+      <c r="J83" s="1">
+        <v>46401</v>
       </c>
       <c r="K83" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:11">
       <c r="A84" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B84">
-        <v>2724</v>
+        <v>2737</v>
       </c>
       <c r="C84" t="s">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="D84" t="s">
-        <v>252</v>
+        <v>234</v>
       </c>
       <c r="E84" t="s">
-        <v>266</v>
+        <v>242</v>
       </c>
       <c r="F84" t="s">
-        <v>298</v>
+        <v>277</v>
       </c>
       <c r="G84" t="s">
-        <v>309</v>
+        <v>285</v>
       </c>
       <c r="H84">
-        <v>-720</v>
+        <v>120</v>
       </c>
       <c r="I84" t="s">
-        <v>315</v>
-      </c>
-      <c r="J84" s="2">
-        <v>45490</v>
+        <v>297</v>
+      </c>
+      <c r="J84" s="1">
+        <v>46412</v>
       </c>
       <c r="K84" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:11">
       <c r="A85" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B85">
-        <v>2724</v>
+        <v>2740</v>
       </c>
       <c r="C85" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D85" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="E85" t="s">
-        <v>266</v>
+        <v>242</v>
       </c>
       <c r="F85" t="s">
-        <v>299</v>
+        <v>277</v>
       </c>
       <c r="G85" t="s">
-        <v>309</v>
+        <v>285</v>
       </c>
       <c r="H85">
-        <v>-660</v>
+        <v>120</v>
       </c>
       <c r="I85" t="s">
-        <v>316</v>
-      </c>
-      <c r="J85" s="2">
-        <v>45566</v>
+        <v>297</v>
+      </c>
+      <c r="J85" s="1">
+        <v>46412</v>
       </c>
       <c r="K85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:11">
       <c r="A86" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B86">
-        <v>2730</v>
+        <v>2733</v>
       </c>
       <c r="C86" t="s">
-        <v>222</v>
+        <v>197</v>
       </c>
       <c r="D86" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="E86" t="s">
-        <v>266</v>
+        <v>246</v>
       </c>
       <c r="F86" t="s">
-        <v>300</v>
+        <v>275</v>
       </c>
       <c r="G86" t="s">
-        <v>309</v>
+        <v>285</v>
       </c>
       <c r="H86">
-        <v>-240</v>
+        <v>120</v>
       </c>
       <c r="I86" t="s">
-        <v>317</v>
-      </c>
-      <c r="J86" s="2">
-        <v>45986</v>
+        <v>297</v>
+      </c>
+      <c r="J86" s="1">
+        <v>46424</v>
       </c>
       <c r="K86" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:11">
       <c r="A87" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B87">
-        <v>2740</v>
+        <v>2738</v>
       </c>
       <c r="C87" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="D87" t="s">
-        <v>253</v>
+        <v>234</v>
       </c>
       <c r="E87" t="s">
-        <v>265</v>
+        <v>242</v>
       </c>
       <c r="F87" t="s">
-        <v>296</v>
+        <v>277</v>
       </c>
       <c r="G87" t="s">
-        <v>309</v>
+        <v>285</v>
       </c>
       <c r="H87">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="I87" t="s">
-        <v>318</v>
-      </c>
-      <c r="J87" s="2">
-        <v>46284</v>
+        <v>297</v>
+      </c>
+      <c r="J87" s="1">
+        <v>46427</v>
       </c>
       <c r="K87" t="b">
         <v>0</v>
@@ -4190,34 +4155,34 @@
     </row>
     <row r="88" spans="1:11">
       <c r="A88" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B88">
-        <v>2733</v>
+        <v>2741</v>
       </c>
       <c r="C88" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D88" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="E88" t="s">
-        <v>270</v>
+        <v>242</v>
       </c>
       <c r="F88" t="s">
-        <v>299</v>
+        <v>277</v>
       </c>
       <c r="G88" t="s">
-        <v>309</v>
+        <v>285</v>
       </c>
       <c r="H88">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I88" t="s">
-        <v>319</v>
-      </c>
-      <c r="J88" s="2">
-        <v>46305</v>
+        <v>297</v>
+      </c>
+      <c r="J88" s="1">
+        <v>46427</v>
       </c>
       <c r="K88" t="b">
         <v>0</v>
@@ -4225,34 +4190,34 @@
     </row>
     <row r="89" spans="1:11">
       <c r="A89" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B89">
-        <v>2736</v>
+        <v>2739</v>
       </c>
       <c r="C89" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="D89" t="s">
+        <v>229</v>
+      </c>
+      <c r="E89" t="s">
         <v>246</v>
       </c>
-      <c r="E89" t="s">
-        <v>265</v>
-      </c>
       <c r="F89" t="s">
-        <v>299</v>
+        <v>275</v>
       </c>
       <c r="G89" t="s">
-        <v>309</v>
+        <v>285</v>
       </c>
       <c r="H89">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="I89" t="s">
-        <v>319</v>
-      </c>
-      <c r="J89" s="2">
-        <v>46310</v>
+        <v>298</v>
+      </c>
+      <c r="J89" s="1">
+        <v>46437</v>
       </c>
       <c r="K89" t="b">
         <v>0</v>
@@ -4260,34 +4225,34 @@
     </row>
     <row r="90" spans="1:11">
       <c r="A90" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B90">
-        <v>2739</v>
+        <v>2719</v>
       </c>
       <c r="C90" t="s">
-        <v>223</v>
+        <v>200</v>
       </c>
       <c r="D90" t="s">
-        <v>256</v>
+        <v>232</v>
       </c>
       <c r="E90" t="s">
-        <v>270</v>
+        <v>245</v>
       </c>
       <c r="F90" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G90" t="s">
-        <v>309</v>
+        <v>285</v>
       </c>
       <c r="H90">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="I90" t="s">
-        <v>319</v>
-      </c>
-      <c r="J90" s="2">
-        <v>46317</v>
+        <v>298</v>
+      </c>
+      <c r="J90" s="1">
+        <v>46451</v>
       </c>
       <c r="K90" t="b">
         <v>0</v>
@@ -4295,34 +4260,34 @@
     </row>
     <row r="91" spans="1:11">
       <c r="A91" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B91">
-        <v>2731</v>
+        <v>2741</v>
       </c>
       <c r="C91" t="s">
-        <v>218</v>
+        <v>197</v>
       </c>
       <c r="D91" t="s">
-        <v>252</v>
+        <v>229</v>
       </c>
       <c r="E91" t="s">
-        <v>270</v>
+        <v>242</v>
       </c>
       <c r="F91" t="s">
+        <v>275</v>
+      </c>
+      <c r="G91" t="s">
+        <v>285</v>
+      </c>
+      <c r="H91">
+        <v>150</v>
+      </c>
+      <c r="I91" t="s">
         <v>298</v>
       </c>
-      <c r="G91" t="s">
-        <v>309</v>
-      </c>
-      <c r="H91">
-        <v>60</v>
-      </c>
-      <c r="I91" t="s">
-        <v>319</v>
-      </c>
-      <c r="J91" s="2">
-        <v>46319</v>
+      <c r="J91" s="1">
+        <v>46451</v>
       </c>
       <c r="K91" t="b">
         <v>0</v>
@@ -4330,34 +4295,34 @@
     </row>
     <row r="92" spans="1:11">
       <c r="A92" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B92">
-        <v>2727</v>
+        <v>2738</v>
       </c>
       <c r="C92" t="s">
-        <v>221</v>
+        <v>197</v>
       </c>
       <c r="D92" t="s">
-        <v>255</v>
+        <v>229</v>
       </c>
       <c r="E92" t="s">
-        <v>273</v>
+        <v>242</v>
       </c>
       <c r="F92" t="s">
-        <v>294</v>
+        <v>275</v>
       </c>
       <c r="G92" t="s">
-        <v>309</v>
+        <v>285</v>
       </c>
       <c r="H92">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="I92" t="s">
-        <v>320</v>
-      </c>
-      <c r="J92" s="2">
-        <v>46333</v>
+        <v>298</v>
+      </c>
+      <c r="J92" s="1">
+        <v>46455</v>
       </c>
       <c r="K92" t="b">
         <v>0</v>
@@ -4365,34 +4330,34 @@
     </row>
     <row r="93" spans="1:11">
       <c r="A93" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B93">
-        <v>2721</v>
+        <v>2708</v>
       </c>
       <c r="C93" t="s">
-        <v>221</v>
+        <v>183</v>
       </c>
       <c r="D93" t="s">
-        <v>255</v>
+        <v>222</v>
       </c>
       <c r="E93" t="s">
-        <v>272</v>
+        <v>244</v>
       </c>
       <c r="F93" t="s">
-        <v>294</v>
+        <v>276</v>
       </c>
       <c r="G93" t="s">
-        <v>309</v>
+        <v>285</v>
       </c>
       <c r="H93">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="I93" t="s">
-        <v>320</v>
-      </c>
-      <c r="J93" s="2">
-        <v>46338</v>
+        <v>298</v>
+      </c>
+      <c r="J93" s="1">
+        <v>46456</v>
       </c>
       <c r="K93" t="b">
         <v>0</v>
@@ -4400,34 +4365,34 @@
     </row>
     <row r="94" spans="1:11">
       <c r="A94" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B94">
-        <v>2721</v>
+        <v>2720</v>
       </c>
       <c r="C94" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="D94" t="s">
-        <v>255</v>
+        <v>229</v>
       </c>
       <c r="E94" t="s">
-        <v>272</v>
+        <v>247</v>
       </c>
       <c r="F94" t="s">
-        <v>301</v>
+        <v>275</v>
       </c>
       <c r="G94" t="s">
-        <v>309</v>
+        <v>285</v>
       </c>
       <c r="H94">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="I94" t="s">
-        <v>320</v>
-      </c>
-      <c r="J94" s="2">
-        <v>46338</v>
+        <v>298</v>
+      </c>
+      <c r="J94" s="1">
+        <v>46457</v>
       </c>
       <c r="K94" t="b">
         <v>0</v>
@@ -4435,34 +4400,34 @@
     </row>
     <row r="95" spans="1:11">
       <c r="A95" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B95">
-        <v>2722</v>
+        <v>2734</v>
       </c>
       <c r="C95" t="s">
-        <v>224</v>
+        <v>197</v>
       </c>
       <c r="D95" t="s">
-        <v>254</v>
+        <v>229</v>
       </c>
       <c r="E95" t="s">
-        <v>268</v>
+        <v>243</v>
       </c>
       <c r="F95" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="G95" t="s">
-        <v>309</v>
+        <v>285</v>
       </c>
       <c r="H95">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="I95" t="s">
-        <v>320</v>
-      </c>
-      <c r="J95" s="2">
-        <v>46341</v>
+        <v>298</v>
+      </c>
+      <c r="J95" s="1">
+        <v>46464</v>
       </c>
       <c r="K95" t="b">
         <v>0</v>
@@ -4470,34 +4435,34 @@
     </row>
     <row r="96" spans="1:11">
       <c r="A96" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B96">
-        <v>2703</v>
+        <v>2723</v>
       </c>
       <c r="C96" t="s">
-        <v>225</v>
+        <v>206</v>
       </c>
       <c r="D96" t="s">
-        <v>257</v>
+        <v>232</v>
       </c>
       <c r="E96" t="s">
-        <v>267</v>
+        <v>250</v>
       </c>
       <c r="F96" t="s">
-        <v>294</v>
+        <v>271</v>
       </c>
       <c r="G96" t="s">
-        <v>309</v>
+        <v>285</v>
       </c>
       <c r="H96">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="I96" t="s">
-        <v>320</v>
-      </c>
-      <c r="J96" s="2">
-        <v>46344</v>
+        <v>299</v>
+      </c>
+      <c r="J96" s="1">
+        <v>46470</v>
       </c>
       <c r="K96" t="b">
         <v>0</v>
@@ -4505,34 +4470,34 @@
     </row>
     <row r="97" spans="1:11">
       <c r="A97" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B97">
-        <v>2721</v>
+        <v>2728</v>
       </c>
       <c r="C97" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
       <c r="D97" t="s">
-        <v>252</v>
+        <v>232</v>
       </c>
       <c r="E97" t="s">
-        <v>272</v>
+        <v>243</v>
       </c>
       <c r="F97" t="s">
-        <v>296</v>
+        <v>274</v>
       </c>
       <c r="G97" t="s">
-        <v>309</v>
+        <v>285</v>
       </c>
       <c r="H97">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="I97" t="s">
-        <v>321</v>
-      </c>
-      <c r="J97" s="2">
-        <v>46360</v>
+        <v>299</v>
+      </c>
+      <c r="J97" s="1">
+        <v>46485</v>
       </c>
       <c r="K97" t="b">
         <v>0</v>
@@ -4540,34 +4505,34 @@
     </row>
     <row r="98" spans="1:11">
       <c r="A98" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B98">
-        <v>2728</v>
+        <v>2741</v>
       </c>
       <c r="C98" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="D98" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="E98" t="s">
-        <v>266</v>
+        <v>242</v>
       </c>
       <c r="F98" t="s">
-        <v>296</v>
+        <v>258</v>
       </c>
       <c r="G98" t="s">
-        <v>309</v>
+        <v>285</v>
       </c>
       <c r="H98">
-        <v>120</v>
+        <v>210</v>
       </c>
       <c r="I98" t="s">
-        <v>321</v>
-      </c>
-      <c r="J98" s="2">
-        <v>46360</v>
+        <v>300</v>
+      </c>
+      <c r="J98" s="1">
+        <v>46499</v>
       </c>
       <c r="K98" t="b">
         <v>0</v>
@@ -4575,34 +4540,34 @@
     </row>
     <row r="99" spans="1:11">
       <c r="A99" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B99">
-        <v>2734</v>
+        <v>2722</v>
       </c>
       <c r="C99" t="s">
-        <v>226</v>
+        <v>200</v>
       </c>
       <c r="D99" t="s">
-        <v>258</v>
+        <v>232</v>
       </c>
       <c r="E99" t="s">
-        <v>266</v>
+        <v>245</v>
       </c>
       <c r="F99" t="s">
-        <v>302</v>
+        <v>274</v>
       </c>
       <c r="G99" t="s">
-        <v>309</v>
+        <v>285</v>
       </c>
       <c r="H99">
-        <v>120</v>
+        <v>210</v>
       </c>
       <c r="I99" t="s">
-        <v>321</v>
-      </c>
-      <c r="J99" s="2">
-        <v>46367</v>
+        <v>300</v>
+      </c>
+      <c r="J99" s="1">
+        <v>46504</v>
       </c>
       <c r="K99" t="b">
         <v>0</v>
@@ -4610,34 +4575,34 @@
     </row>
     <row r="100" spans="1:11">
       <c r="A100" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B100">
-        <v>2732</v>
+        <v>2743</v>
       </c>
       <c r="C100" t="s">
-        <v>227</v>
+        <v>197</v>
       </c>
       <c r="D100" t="s">
-        <v>259</v>
+        <v>229</v>
       </c>
       <c r="E100" t="s">
-        <v>266</v>
+        <v>248</v>
       </c>
       <c r="F100" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G100" t="s">
-        <v>309</v>
+        <v>285</v>
       </c>
       <c r="H100">
-        <v>120</v>
+        <v>210</v>
       </c>
       <c r="I100" t="s">
-        <v>321</v>
-      </c>
-      <c r="J100" s="2">
-        <v>46375</v>
+        <v>300</v>
+      </c>
+      <c r="J100" s="1">
+        <v>46507</v>
       </c>
       <c r="K100" t="b">
         <v>0</v>
@@ -4645,34 +4610,34 @@
     </row>
     <row r="101" spans="1:11">
       <c r="A101" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B101">
-        <v>2730</v>
+        <v>2702</v>
       </c>
       <c r="C101" t="s">
-        <v>226</v>
+        <v>200</v>
       </c>
       <c r="D101" t="s">
-        <v>258</v>
+        <v>232</v>
       </c>
       <c r="E101" t="s">
-        <v>266</v>
+        <v>244</v>
       </c>
       <c r="F101" t="s">
-        <v>302</v>
+        <v>280</v>
       </c>
       <c r="G101" t="s">
-        <v>309</v>
+        <v>285</v>
       </c>
       <c r="H101">
-        <v>120</v>
+        <v>210</v>
       </c>
       <c r="I101" t="s">
-        <v>321</v>
-      </c>
-      <c r="J101" s="2">
-        <v>46387</v>
+        <v>300</v>
+      </c>
+      <c r="J101" s="1">
+        <v>46508</v>
       </c>
       <c r="K101" t="b">
         <v>0</v>
@@ -4680,34 +4645,34 @@
     </row>
     <row r="102" spans="1:11">
       <c r="A102" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B102">
-        <v>2732</v>
+        <v>2728</v>
       </c>
       <c r="C102" t="s">
-        <v>226</v>
+        <v>183</v>
       </c>
       <c r="D102" t="s">
-        <v>258</v>
+        <v>222</v>
       </c>
       <c r="E102" t="s">
-        <v>266</v>
+        <v>243</v>
       </c>
       <c r="F102" t="s">
-        <v>302</v>
+        <v>276</v>
       </c>
       <c r="G102" t="s">
-        <v>309</v>
+        <v>285</v>
       </c>
       <c r="H102">
-        <v>120</v>
+        <v>210</v>
       </c>
       <c r="I102" t="s">
-        <v>321</v>
-      </c>
-      <c r="J102" s="2">
-        <v>46387</v>
+        <v>300</v>
+      </c>
+      <c r="J102" s="1">
+        <v>46512</v>
       </c>
       <c r="K102" t="b">
         <v>0</v>
@@ -4715,34 +4680,34 @@
     </row>
     <row r="103" spans="1:11">
       <c r="A103" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B103">
-        <v>2736</v>
+        <v>2733</v>
       </c>
       <c r="C103" t="s">
-        <v>226</v>
+        <v>201</v>
       </c>
       <c r="D103" t="s">
-        <v>258</v>
+        <v>231</v>
       </c>
       <c r="E103" t="s">
-        <v>265</v>
+        <v>246</v>
       </c>
       <c r="F103" t="s">
-        <v>302</v>
+        <v>255</v>
       </c>
       <c r="G103" t="s">
-        <v>309</v>
+        <v>285</v>
       </c>
       <c r="H103">
-        <v>120</v>
+        <v>210</v>
       </c>
       <c r="I103" t="s">
-        <v>321</v>
-      </c>
-      <c r="J103" s="2">
-        <v>46387</v>
+        <v>300</v>
+      </c>
+      <c r="J103" s="1">
+        <v>46512</v>
       </c>
       <c r="K103" t="b">
         <v>0</v>
@@ -4750,34 +4715,34 @@
     </row>
     <row r="104" spans="1:11">
       <c r="A104" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B104">
-        <v>2728</v>
+        <v>2703</v>
       </c>
       <c r="C104" t="s">
-        <v>219</v>
+        <v>200</v>
       </c>
       <c r="D104" t="s">
-        <v>253</v>
+        <v>232</v>
       </c>
       <c r="E104" t="s">
-        <v>266</v>
+        <v>244</v>
       </c>
       <c r="F104" t="s">
-        <v>296</v>
+        <v>274</v>
       </c>
       <c r="G104" t="s">
-        <v>309</v>
+        <v>285</v>
       </c>
       <c r="H104">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="I104" t="s">
-        <v>321</v>
-      </c>
-      <c r="J104" s="2">
-        <v>46388</v>
+        <v>301</v>
+      </c>
+      <c r="J104" s="1">
+        <v>46528</v>
       </c>
       <c r="K104" t="b">
         <v>0</v>
@@ -4785,34 +4750,34 @@
     </row>
     <row r="105" spans="1:11">
       <c r="A105" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B105">
         <v>2704</v>
       </c>
       <c r="C105" t="s">
-        <v>228</v>
+        <v>183</v>
       </c>
       <c r="D105" t="s">
-        <v>260</v>
+        <v>222</v>
       </c>
       <c r="E105" t="s">
-        <v>266</v>
+        <v>243</v>
       </c>
       <c r="F105" t="s">
-        <v>303</v>
+        <v>276</v>
       </c>
       <c r="G105" t="s">
-        <v>309</v>
+        <v>285</v>
       </c>
       <c r="H105">
-        <v>150</v>
+        <v>240</v>
       </c>
       <c r="I105" t="s">
-        <v>322</v>
-      </c>
-      <c r="J105" s="2">
-        <v>46401</v>
+        <v>301</v>
+      </c>
+      <c r="J105" s="1">
+        <v>46529</v>
       </c>
       <c r="K105" t="b">
         <v>0</v>
@@ -4820,34 +4785,34 @@
     </row>
     <row r="106" spans="1:11">
       <c r="A106" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B106">
-        <v>2704</v>
+        <v>2736</v>
       </c>
       <c r="C106" t="s">
-        <v>221</v>
+        <v>197</v>
       </c>
       <c r="D106" t="s">
-        <v>255</v>
+        <v>229</v>
       </c>
       <c r="E106" t="s">
-        <v>266</v>
+        <v>242</v>
       </c>
       <c r="F106" t="s">
-        <v>294</v>
+        <v>275</v>
       </c>
       <c r="G106" t="s">
-        <v>309</v>
+        <v>285</v>
       </c>
       <c r="H106">
-        <v>150</v>
+        <v>240</v>
       </c>
       <c r="I106" t="s">
-        <v>322</v>
-      </c>
-      <c r="J106" s="2">
-        <v>46401</v>
+        <v>301</v>
+      </c>
+      <c r="J106" s="1">
+        <v>46537</v>
       </c>
       <c r="K106" t="b">
         <v>0</v>
@@ -4855,34 +4820,34 @@
     </row>
     <row r="107" spans="1:11">
       <c r="A107" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B107">
-        <v>2709</v>
+        <v>2737</v>
       </c>
       <c r="C107" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="D107" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="E107" t="s">
-        <v>272</v>
+        <v>242</v>
       </c>
       <c r="F107" t="s">
-        <v>298</v>
+        <v>258</v>
       </c>
       <c r="G107" t="s">
-        <v>309</v>
+        <v>285</v>
       </c>
       <c r="H107">
-        <v>150</v>
+        <v>240</v>
       </c>
       <c r="I107" t="s">
-        <v>322</v>
-      </c>
-      <c r="J107" s="2">
-        <v>46401</v>
+        <v>301</v>
+      </c>
+      <c r="J107" s="1">
+        <v>46546</v>
       </c>
       <c r="K107" t="b">
         <v>0</v>
@@ -4890,34 +4855,34 @@
     </row>
     <row r="108" spans="1:11">
       <c r="A108" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B108">
-        <v>2741</v>
+        <v>2740</v>
       </c>
       <c r="C108" t="s">
-        <v>226</v>
+        <v>207</v>
       </c>
       <c r="D108" t="s">
+        <v>237</v>
+      </c>
+      <c r="E108" t="s">
+        <v>242</v>
+      </c>
+      <c r="F108" t="s">
         <v>258</v>
       </c>
-      <c r="E108" t="s">
-        <v>265</v>
-      </c>
-      <c r="F108" t="s">
-        <v>302</v>
-      </c>
       <c r="G108" t="s">
-        <v>309</v>
+        <v>285</v>
       </c>
       <c r="H108">
-        <v>150</v>
+        <v>240</v>
       </c>
       <c r="I108" t="s">
-        <v>322</v>
-      </c>
-      <c r="J108" s="2">
-        <v>46412</v>
+        <v>301</v>
+      </c>
+      <c r="J108" s="1">
+        <v>46547</v>
       </c>
       <c r="K108" t="b">
         <v>0</v>
@@ -4925,34 +4890,34 @@
     </row>
     <row r="109" spans="1:11">
       <c r="A109" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B109">
-        <v>2737</v>
+        <v>2736</v>
       </c>
       <c r="C109" t="s">
-        <v>226</v>
+        <v>207</v>
       </c>
       <c r="D109" t="s">
+        <v>237</v>
+      </c>
+      <c r="E109" t="s">
+        <v>242</v>
+      </c>
+      <c r="F109" t="s">
         <v>258</v>
       </c>
-      <c r="E109" t="s">
-        <v>265</v>
-      </c>
-      <c r="F109" t="s">
-        <v>302</v>
-      </c>
       <c r="G109" t="s">
-        <v>309</v>
+        <v>285</v>
       </c>
       <c r="H109">
-        <v>150</v>
+        <v>240</v>
       </c>
       <c r="I109" t="s">
-        <v>322</v>
-      </c>
-      <c r="J109" s="2">
-        <v>46412</v>
+        <v>301</v>
+      </c>
+      <c r="J109" s="1">
+        <v>46547</v>
       </c>
       <c r="K109" t="b">
         <v>0</v>
@@ -4960,34 +4925,34 @@
     </row>
     <row r="110" spans="1:11">
       <c r="A110" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B110">
-        <v>2740</v>
+        <v>2708</v>
       </c>
       <c r="C110" t="s">
-        <v>226</v>
+        <v>201</v>
       </c>
       <c r="D110" t="s">
-        <v>258</v>
+        <v>231</v>
       </c>
       <c r="E110" t="s">
-        <v>265</v>
+        <v>244</v>
       </c>
       <c r="F110" t="s">
-        <v>302</v>
+        <v>255</v>
       </c>
       <c r="G110" t="s">
-        <v>309</v>
+        <v>285</v>
       </c>
       <c r="H110">
-        <v>150</v>
+        <v>240</v>
       </c>
       <c r="I110" t="s">
-        <v>322</v>
-      </c>
-      <c r="J110" s="2">
-        <v>46412</v>
+        <v>301</v>
+      </c>
+      <c r="J110" s="1">
+        <v>46551</v>
       </c>
       <c r="K110" t="b">
         <v>0</v>
@@ -4995,34 +4960,34 @@
     </row>
     <row r="111" spans="1:11">
       <c r="A111" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B111">
-        <v>2733</v>
+        <v>2708</v>
       </c>
       <c r="C111" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
       <c r="D111" t="s">
-        <v>252</v>
+        <v>232</v>
       </c>
       <c r="E111" t="s">
+        <v>244</v>
+      </c>
+      <c r="F111" t="s">
+        <v>274</v>
+      </c>
+      <c r="G111" t="s">
+        <v>285</v>
+      </c>
+      <c r="H111">
         <v>270</v>
       </c>
-      <c r="F111" t="s">
-        <v>298</v>
-      </c>
-      <c r="G111" t="s">
-        <v>309</v>
-      </c>
-      <c r="H111">
-        <v>180</v>
-      </c>
       <c r="I111" t="s">
-        <v>323</v>
-      </c>
-      <c r="J111" s="2">
-        <v>46424</v>
+        <v>302</v>
+      </c>
+      <c r="J111" s="1">
+        <v>46560</v>
       </c>
       <c r="K111" t="b">
         <v>0</v>
@@ -5030,34 +4995,34 @@
     </row>
     <row r="112" spans="1:11">
       <c r="A112" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B112">
-        <v>2739</v>
+        <v>2703</v>
       </c>
       <c r="C112" t="s">
-        <v>218</v>
+        <v>183</v>
       </c>
       <c r="D112" t="s">
-        <v>252</v>
+        <v>222</v>
       </c>
       <c r="E112" t="s">
+        <v>244</v>
+      </c>
+      <c r="F112" t="s">
+        <v>276</v>
+      </c>
+      <c r="G112" t="s">
+        <v>285</v>
+      </c>
+      <c r="H112">
         <v>270</v>
       </c>
-      <c r="F112" t="s">
-        <v>298</v>
-      </c>
-      <c r="G112" t="s">
-        <v>309</v>
-      </c>
-      <c r="H112">
-        <v>180</v>
-      </c>
       <c r="I112" t="s">
-        <v>323</v>
-      </c>
-      <c r="J112" s="2">
-        <v>46437</v>
+        <v>302</v>
+      </c>
+      <c r="J112" s="1">
+        <v>46567</v>
       </c>
       <c r="K112" t="b">
         <v>0</v>
@@ -5065,34 +5030,34 @@
     </row>
     <row r="113" spans="1:11">
       <c r="A113" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B113">
-        <v>2719</v>
+        <v>2742</v>
       </c>
       <c r="C113" t="s">
-        <v>221</v>
+        <v>197</v>
       </c>
       <c r="D113" t="s">
-        <v>255</v>
+        <v>229</v>
       </c>
       <c r="E113" t="s">
-        <v>268</v>
+        <v>243</v>
       </c>
       <c r="F113" t="s">
-        <v>294</v>
+        <v>275</v>
       </c>
       <c r="G113" t="s">
-        <v>309</v>
+        <v>285</v>
       </c>
       <c r="H113">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="I113" t="s">
-        <v>323</v>
-      </c>
-      <c r="J113" s="2">
-        <v>46451</v>
+        <v>302</v>
+      </c>
+      <c r="J113" s="1">
+        <v>46568</v>
       </c>
       <c r="K113" t="b">
         <v>0</v>
@@ -5100,34 +5065,34 @@
     </row>
     <row r="114" spans="1:11">
       <c r="A114" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B114">
-        <v>2741</v>
+        <v>2736</v>
       </c>
       <c r="C114" t="s">
-        <v>218</v>
+        <v>198</v>
       </c>
       <c r="D114" t="s">
-        <v>252</v>
+        <v>232</v>
       </c>
       <c r="E114" t="s">
-        <v>265</v>
+        <v>242</v>
       </c>
       <c r="F114" t="s">
-        <v>298</v>
+        <v>281</v>
       </c>
       <c r="G114" t="s">
-        <v>309</v>
+        <v>285</v>
       </c>
       <c r="H114">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="I114" t="s">
-        <v>323</v>
-      </c>
-      <c r="J114" s="2">
-        <v>46451</v>
+        <v>302</v>
+      </c>
+      <c r="J114" s="1">
+        <v>46578</v>
       </c>
       <c r="K114" t="b">
         <v>0</v>
@@ -5135,34 +5100,34 @@
     </row>
     <row r="115" spans="1:11">
       <c r="A115" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B115">
-        <v>2738</v>
+        <v>2737</v>
       </c>
       <c r="C115" t="s">
-        <v>218</v>
+        <v>197</v>
       </c>
       <c r="D115" t="s">
-        <v>252</v>
+        <v>229</v>
       </c>
       <c r="E115" t="s">
-        <v>265</v>
+        <v>242</v>
       </c>
       <c r="F115" t="s">
-        <v>298</v>
+        <v>275</v>
       </c>
       <c r="G115" t="s">
-        <v>309</v>
+        <v>285</v>
       </c>
       <c r="H115">
-        <v>210</v>
+        <v>300</v>
       </c>
       <c r="I115" t="s">
-        <v>324</v>
-      </c>
-      <c r="J115" s="2">
-        <v>46455</v>
+        <v>303</v>
+      </c>
+      <c r="J115" s="1">
+        <v>46592</v>
       </c>
       <c r="K115" t="b">
         <v>0</v>
@@ -5170,34 +5135,34 @@
     </row>
     <row r="116" spans="1:11">
       <c r="A116" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B116">
-        <v>2708</v>
+        <v>2737</v>
       </c>
       <c r="C116" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="D116" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="E116" t="s">
-        <v>267</v>
+        <v>242</v>
       </c>
       <c r="F116" t="s">
-        <v>299</v>
+        <v>281</v>
       </c>
       <c r="G116" t="s">
-        <v>309</v>
+        <v>285</v>
       </c>
       <c r="H116">
-        <v>210</v>
+        <v>300</v>
       </c>
       <c r="I116" t="s">
-        <v>324</v>
-      </c>
-      <c r="J116" s="2">
-        <v>46456</v>
+        <v>303</v>
+      </c>
+      <c r="J116" s="1">
+        <v>46592</v>
       </c>
       <c r="K116" t="b">
         <v>0</v>
@@ -5205,34 +5170,34 @@
     </row>
     <row r="117" spans="1:11">
       <c r="A117" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B117">
-        <v>2720</v>
+        <v>2731</v>
       </c>
       <c r="C117" t="s">
-        <v>218</v>
+        <v>198</v>
       </c>
       <c r="D117" t="s">
-        <v>252</v>
+        <v>232</v>
       </c>
       <c r="E117" t="s">
-        <v>272</v>
+        <v>246</v>
       </c>
       <c r="F117" t="s">
-        <v>298</v>
+        <v>281</v>
       </c>
       <c r="G117" t="s">
-        <v>309</v>
+        <v>285</v>
       </c>
       <c r="H117">
-        <v>210</v>
+        <v>300</v>
       </c>
       <c r="I117" t="s">
-        <v>324</v>
-      </c>
-      <c r="J117" s="2">
-        <v>46457</v>
+        <v>303</v>
+      </c>
+      <c r="J117" s="1">
+        <v>46603</v>
       </c>
       <c r="K117" t="b">
         <v>0</v>
@@ -5240,34 +5205,34 @@
     </row>
     <row r="118" spans="1:11">
       <c r="A118" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B118">
-        <v>2734</v>
+        <v>2738</v>
       </c>
       <c r="C118" t="s">
-        <v>218</v>
+        <v>198</v>
       </c>
       <c r="D118" t="s">
-        <v>252</v>
+        <v>232</v>
       </c>
       <c r="E118" t="s">
-        <v>266</v>
+        <v>242</v>
       </c>
       <c r="F118" t="s">
-        <v>298</v>
+        <v>281</v>
       </c>
       <c r="G118" t="s">
-        <v>309</v>
+        <v>285</v>
       </c>
       <c r="H118">
-        <v>210</v>
+        <v>300</v>
       </c>
       <c r="I118" t="s">
-        <v>324</v>
-      </c>
-      <c r="J118" s="2">
-        <v>46464</v>
+        <v>303</v>
+      </c>
+      <c r="J118" s="1">
+        <v>46611</v>
       </c>
       <c r="K118" t="b">
         <v>0</v>
@@ -5275,34 +5240,34 @@
     </row>
     <row r="119" spans="1:11">
       <c r="A119" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B119">
-        <v>2723</v>
+        <v>2742</v>
       </c>
       <c r="C119" t="s">
-        <v>229</v>
+        <v>198</v>
       </c>
       <c r="D119" t="s">
-        <v>255</v>
+        <v>230</v>
       </c>
       <c r="E119" t="s">
-        <v>271</v>
+        <v>243</v>
       </c>
       <c r="F119" t="s">
-        <v>295</v>
+        <v>272</v>
       </c>
       <c r="G119" t="s">
-        <v>309</v>
+        <v>285</v>
       </c>
       <c r="H119">
-        <v>210</v>
+        <v>330</v>
       </c>
       <c r="I119" t="s">
-        <v>324</v>
-      </c>
-      <c r="J119" s="2">
-        <v>46470</v>
+        <v>304</v>
+      </c>
+      <c r="J119" s="1">
+        <v>46631</v>
       </c>
       <c r="K119" t="b">
         <v>0</v>
@@ -5310,34 +5275,34 @@
     </row>
     <row r="120" spans="1:11">
       <c r="A120" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B120">
-        <v>2728</v>
+        <v>2727</v>
       </c>
       <c r="C120" t="s">
-        <v>221</v>
+        <v>202</v>
       </c>
       <c r="D120" t="s">
-        <v>255</v>
+        <v>233</v>
       </c>
       <c r="E120" t="s">
-        <v>266</v>
+        <v>249</v>
       </c>
       <c r="F120" t="s">
-        <v>294</v>
+        <v>274</v>
       </c>
       <c r="G120" t="s">
-        <v>309</v>
+        <v>285</v>
       </c>
       <c r="H120">
-        <v>240</v>
+        <v>330</v>
       </c>
       <c r="I120" t="s">
-        <v>325</v>
-      </c>
-      <c r="J120" s="2">
-        <v>46485</v>
+        <v>304</v>
+      </c>
+      <c r="J120" s="1">
+        <v>46645</v>
       </c>
       <c r="K120" t="b">
         <v>0</v>
@@ -5345,69 +5310,69 @@
     </row>
     <row r="121" spans="1:11">
       <c r="A121" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B121">
-        <v>2741</v>
+        <v>2723</v>
       </c>
       <c r="C121" t="s">
-        <v>230</v>
+        <v>208</v>
       </c>
       <c r="D121" t="s">
-        <v>261</v>
+        <v>239</v>
       </c>
       <c r="E121" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
       <c r="F121" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G121" t="s">
-        <v>309</v>
+        <v>285</v>
       </c>
       <c r="H121">
-        <v>240</v>
+        <v>-26</v>
       </c>
       <c r="I121" t="s">
-        <v>325</v>
-      </c>
-      <c r="J121" s="2">
-        <v>46499</v>
+        <v>305</v>
+      </c>
+      <c r="J121" s="1">
+        <v>46254</v>
       </c>
       <c r="K121" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122" spans="1:11">
       <c r="A122" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B122">
-        <v>2722</v>
+        <v>2740</v>
       </c>
       <c r="C122" t="s">
-        <v>221</v>
+        <v>198</v>
       </c>
       <c r="D122" t="s">
-        <v>255</v>
+        <v>230</v>
       </c>
       <c r="E122" t="s">
-        <v>268</v>
+        <v>242</v>
       </c>
       <c r="F122" t="s">
-        <v>294</v>
+        <v>272</v>
       </c>
       <c r="G122" t="s">
-        <v>309</v>
+        <v>285</v>
       </c>
       <c r="H122">
-        <v>240</v>
+        <v>2</v>
       </c>
       <c r="I122" t="s">
-        <v>325</v>
-      </c>
-      <c r="J122" s="2">
-        <v>46504</v>
+        <v>306</v>
+      </c>
+      <c r="J122" s="1">
+        <v>46284</v>
       </c>
       <c r="K122" t="b">
         <v>0</v>
@@ -5415,34 +5380,34 @@
     </row>
     <row r="123" spans="1:11">
       <c r="A123" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B123">
-        <v>2737</v>
+        <v>2727</v>
       </c>
       <c r="C123" t="s">
-        <v>231</v>
+        <v>176</v>
       </c>
       <c r="D123" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="E123" t="s">
-        <v>265</v>
+        <v>249</v>
       </c>
       <c r="F123" t="s">
-        <v>303</v>
+        <v>261</v>
       </c>
       <c r="G123" t="s">
-        <v>309</v>
+        <v>285</v>
       </c>
       <c r="H123">
-        <v>240</v>
+        <v>12</v>
       </c>
       <c r="I123" t="s">
-        <v>325</v>
-      </c>
-      <c r="J123" s="2">
-        <v>46504</v>
+        <v>307</v>
+      </c>
+      <c r="J123" s="1">
+        <v>46296</v>
       </c>
       <c r="K123" t="b">
         <v>0</v>
@@ -5450,34 +5415,34 @@
     </row>
     <row r="124" spans="1:11">
       <c r="A124" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B124">
-        <v>2743</v>
+        <v>2704</v>
       </c>
       <c r="C124" t="s">
-        <v>218</v>
+        <v>199</v>
       </c>
       <c r="D124" t="s">
-        <v>252</v>
+        <v>231</v>
       </c>
       <c r="E124" t="s">
-        <v>269</v>
+        <v>243</v>
       </c>
       <c r="F124" t="s">
-        <v>304</v>
+        <v>251</v>
       </c>
       <c r="G124" t="s">
-        <v>309</v>
+        <v>285</v>
       </c>
       <c r="H124">
-        <v>240</v>
+        <v>13</v>
       </c>
       <c r="I124" t="s">
-        <v>325</v>
-      </c>
-      <c r="J124" s="2">
-        <v>46507</v>
+        <v>308</v>
+      </c>
+      <c r="J124" s="1">
+        <v>46293</v>
       </c>
       <c r="K124" t="b">
         <v>0</v>
@@ -5485,34 +5450,34 @@
     </row>
     <row r="125" spans="1:11">
       <c r="A125" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B125">
-        <v>2702</v>
+        <v>2733</v>
       </c>
       <c r="C125" t="s">
-        <v>221</v>
+        <v>183</v>
       </c>
       <c r="D125" t="s">
-        <v>255</v>
+        <v>222</v>
       </c>
       <c r="E125" t="s">
-        <v>267</v>
+        <v>246</v>
       </c>
       <c r="F125" t="s">
-        <v>305</v>
+        <v>276</v>
       </c>
       <c r="G125" t="s">
+        <v>285</v>
+      </c>
+      <c r="H125">
+        <v>23</v>
+      </c>
+      <c r="I125" t="s">
         <v>309</v>
       </c>
-      <c r="H125">
-        <v>240</v>
-      </c>
-      <c r="I125" t="s">
-        <v>325</v>
-      </c>
-      <c r="J125" s="2">
-        <v>46508</v>
+      <c r="J125" s="1">
+        <v>46305</v>
       </c>
       <c r="K125" t="b">
         <v>0</v>
@@ -5520,384 +5485,351 @@
     </row>
     <row r="126" spans="1:11">
       <c r="A126" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B126">
-        <v>2728</v>
+        <v>2724</v>
       </c>
       <c r="C126" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D126" t="s">
-        <v>246</v>
+        <v>221</v>
       </c>
       <c r="E126" t="s">
-        <v>266</v>
+        <v>243</v>
       </c>
       <c r="F126" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="G126" t="s">
-        <v>309</v>
+        <v>286</v>
       </c>
       <c r="H126">
-        <v>240</v>
-      </c>
-      <c r="I126" t="s">
-        <v>325</v>
-      </c>
-      <c r="J126" s="2">
-        <v>46512</v>
+        <v>-1476</v>
+      </c>
+      <c r="J126" s="1">
+        <v>43773</v>
       </c>
       <c r="K126" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127" spans="1:11">
       <c r="A127" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B127">
-        <v>2733</v>
+        <v>2724</v>
       </c>
       <c r="C127" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="D127" t="s">
-        <v>254</v>
+        <v>221</v>
       </c>
       <c r="E127" t="s">
-        <v>270</v>
+        <v>243</v>
       </c>
       <c r="F127" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="G127" t="s">
-        <v>309</v>
+        <v>286</v>
       </c>
       <c r="H127">
-        <v>270</v>
-      </c>
-      <c r="I127" t="s">
-        <v>326</v>
-      </c>
-      <c r="J127" s="2">
-        <v>46512</v>
+        <v>-1469</v>
+      </c>
+      <c r="J127" s="1">
+        <v>43773</v>
       </c>
       <c r="K127" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128" spans="1:11">
       <c r="A128" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B128">
-        <v>2703</v>
+        <v>2736</v>
       </c>
       <c r="C128" t="s">
+        <v>209</v>
+      </c>
+      <c r="D128" t="s">
         <v>221</v>
       </c>
-      <c r="D128" t="s">
-        <v>255</v>
-      </c>
       <c r="E128" t="s">
-        <v>267</v>
+        <v>242</v>
       </c>
       <c r="F128" t="s">
-        <v>294</v>
+        <v>283</v>
       </c>
       <c r="G128" t="s">
-        <v>309</v>
+        <v>286</v>
       </c>
       <c r="H128">
-        <v>270</v>
-      </c>
-      <c r="I128" t="s">
-        <v>326</v>
-      </c>
-      <c r="J128" s="2">
-        <v>46528</v>
+        <v>-1250</v>
+      </c>
+      <c r="J128" s="1">
+        <v>45295</v>
       </c>
       <c r="K128" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129" spans="1:11">
       <c r="A129" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B129">
-        <v>2704</v>
+        <v>2740</v>
       </c>
       <c r="C129" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D129" t="s">
-        <v>246</v>
+        <v>221</v>
       </c>
       <c r="E129" t="s">
-        <v>266</v>
+        <v>242</v>
       </c>
       <c r="F129" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="G129" t="s">
-        <v>309</v>
+        <v>286</v>
       </c>
       <c r="H129">
-        <v>270</v>
-      </c>
-      <c r="I129" t="s">
-        <v>326</v>
-      </c>
-      <c r="J129" s="2">
-        <v>46529</v>
+        <v>-1089</v>
+      </c>
+      <c r="J129" s="1">
+        <v>45617</v>
       </c>
       <c r="K129" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130" spans="1:11">
       <c r="A130" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B130">
-        <v>2736</v>
+        <v>2740</v>
       </c>
       <c r="C130" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="D130" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="E130" t="s">
-        <v>265</v>
+        <v>242</v>
       </c>
       <c r="F130" t="s">
-        <v>298</v>
+        <v>282</v>
       </c>
       <c r="G130" t="s">
-        <v>309</v>
+        <v>286</v>
       </c>
       <c r="H130">
-        <v>270</v>
-      </c>
-      <c r="I130" t="s">
-        <v>326</v>
-      </c>
-      <c r="J130" s="2">
-        <v>46537</v>
+        <v>-1021</v>
+      </c>
+      <c r="J130" s="1">
+        <v>45677</v>
       </c>
       <c r="K130" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131" spans="1:11">
       <c r="A131" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B131">
-        <v>2737</v>
+        <v>2720</v>
       </c>
       <c r="C131" t="s">
-        <v>230</v>
+        <v>209</v>
       </c>
       <c r="D131" t="s">
-        <v>262</v>
+        <v>221</v>
       </c>
       <c r="E131" t="s">
-        <v>265</v>
+        <v>247</v>
       </c>
       <c r="F131" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="G131" t="s">
-        <v>309</v>
+        <v>286</v>
       </c>
       <c r="H131">
-        <v>300</v>
-      </c>
-      <c r="I131" t="s">
-        <v>327</v>
-      </c>
-      <c r="J131" s="2">
-        <v>46546</v>
+        <v>-1000</v>
+      </c>
+      <c r="J131" s="1">
+        <v>44944</v>
       </c>
       <c r="K131" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132" spans="1:11">
       <c r="A132" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B132">
-        <v>2740</v>
+        <v>2703</v>
       </c>
       <c r="C132" t="s">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="D132" t="s">
-        <v>261</v>
+        <v>240</v>
       </c>
       <c r="E132" t="s">
-        <v>265</v>
+        <v>244</v>
       </c>
       <c r="F132" t="s">
-        <v>280</v>
+        <v>258</v>
       </c>
       <c r="G132" t="s">
-        <v>309</v>
+        <v>286</v>
       </c>
       <c r="H132">
-        <v>300</v>
-      </c>
-      <c r="I132" t="s">
-        <v>327</v>
-      </c>
-      <c r="J132" s="2">
-        <v>46547</v>
+        <v>-296</v>
+      </c>
+      <c r="J132" s="1">
+        <v>46092</v>
       </c>
       <c r="K132" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133" spans="1:11">
       <c r="A133" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B133">
-        <v>2736</v>
+        <v>2703</v>
       </c>
       <c r="C133" t="s">
-        <v>230</v>
+        <v>211</v>
       </c>
       <c r="D133" t="s">
-        <v>261</v>
+        <v>241</v>
       </c>
       <c r="E133" t="s">
-        <v>265</v>
+        <v>244</v>
       </c>
       <c r="F133" t="s">
-        <v>280</v>
+        <v>258</v>
       </c>
       <c r="G133" t="s">
-        <v>309</v>
+        <v>286</v>
       </c>
       <c r="H133">
-        <v>300</v>
-      </c>
-      <c r="I133" t="s">
-        <v>327</v>
-      </c>
-      <c r="J133" s="2">
-        <v>46547</v>
+        <v>-51</v>
+      </c>
+      <c r="J133" s="1">
+        <v>46258</v>
       </c>
       <c r="K133" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134" spans="1:11">
       <c r="A134" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B134">
-        <v>2738</v>
+        <v>2702</v>
       </c>
       <c r="C134" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="D134" t="s">
+        <v>241</v>
+      </c>
+      <c r="E134" t="s">
         <v>244</v>
       </c>
-      <c r="E134" t="s">
-        <v>265</v>
-      </c>
       <c r="F134" t="s">
-        <v>300</v>
+        <v>258</v>
       </c>
       <c r="G134" t="s">
-        <v>309</v>
+        <v>286</v>
       </c>
       <c r="H134">
-        <v>300</v>
-      </c>
-      <c r="I134" t="s">
-        <v>327</v>
-      </c>
-      <c r="J134" s="2">
-        <v>46547</v>
+        <v>-49</v>
+      </c>
+      <c r="J134" s="1">
+        <v>46254</v>
       </c>
       <c r="K134" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135" spans="1:11">
       <c r="A135" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B135">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="C135" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="D135" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="E135" t="s">
-        <v>267</v>
+        <v>244</v>
       </c>
       <c r="F135" t="s">
-        <v>279</v>
+        <v>258</v>
       </c>
       <c r="G135" t="s">
-        <v>309</v>
+        <v>286</v>
       </c>
       <c r="H135">
-        <v>300</v>
-      </c>
-      <c r="I135" t="s">
-        <v>327</v>
-      </c>
-      <c r="J135" s="2">
-        <v>46551</v>
+        <v>-49</v>
+      </c>
+      <c r="J135" s="1">
+        <v>46254</v>
       </c>
       <c r="K135" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136" spans="1:11">
       <c r="A136" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B136">
-        <v>2708</v>
+        <v>2728</v>
       </c>
       <c r="C136" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="D136" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="E136" t="s">
-        <v>267</v>
+        <v>243</v>
       </c>
       <c r="F136" t="s">
-        <v>294</v>
+        <v>258</v>
       </c>
       <c r="G136" t="s">
-        <v>309</v>
+        <v>286</v>
       </c>
       <c r="H136">
-        <v>300</v>
-      </c>
-      <c r="I136" t="s">
-        <v>327</v>
-      </c>
-      <c r="J136" s="2">
-        <v>46560</v>
+        <v>43</v>
+      </c>
+      <c r="J136" s="1">
+        <v>46440</v>
       </c>
       <c r="K136" t="b">
         <v>0</v>
@@ -5905,34 +5837,31 @@
     </row>
     <row r="137" spans="1:11">
       <c r="A137" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B137">
-        <v>2738</v>
+        <v>2728</v>
       </c>
       <c r="C137" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="D137" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="E137" t="s">
-        <v>265</v>
+        <v>243</v>
       </c>
       <c r="F137" t="s">
-        <v>301</v>
+        <v>258</v>
       </c>
       <c r="G137" t="s">
-        <v>309</v>
+        <v>286</v>
       </c>
       <c r="H137">
-        <v>300</v>
-      </c>
-      <c r="I137" t="s">
-        <v>327</v>
-      </c>
-      <c r="J137" s="2">
-        <v>46564</v>
+        <v>43</v>
+      </c>
+      <c r="J137" s="1">
+        <v>46440</v>
       </c>
       <c r="K137" t="b">
         <v>0</v>
@@ -5940,34 +5869,31 @@
     </row>
     <row r="138" spans="1:11">
       <c r="A138" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B138">
-        <v>2703</v>
+        <v>2732</v>
       </c>
       <c r="C138" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D138" t="s">
-        <v>246</v>
+        <v>221</v>
       </c>
       <c r="E138" t="s">
-        <v>267</v>
+        <v>242</v>
       </c>
       <c r="F138" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="G138" t="s">
-        <v>309</v>
+        <v>286</v>
       </c>
       <c r="H138">
-        <v>300</v>
-      </c>
-      <c r="I138" t="s">
-        <v>327</v>
-      </c>
-      <c r="J138" s="2">
-        <v>46567</v>
+        <v>102</v>
+      </c>
+      <c r="J138" s="1">
+        <v>46463</v>
       </c>
       <c r="K138" t="b">
         <v>0</v>
@@ -5975,34 +5901,31 @@
     </row>
     <row r="139" spans="1:11">
       <c r="A139" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B139">
-        <v>2742</v>
+        <v>2741</v>
       </c>
       <c r="C139" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="D139" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="E139" t="s">
-        <v>274</v>
+        <v>242</v>
       </c>
       <c r="F139" t="s">
-        <v>298</v>
+        <v>282</v>
       </c>
       <c r="G139" t="s">
-        <v>309</v>
+        <v>286</v>
       </c>
       <c r="H139">
-        <v>300</v>
-      </c>
-      <c r="I139" t="s">
-        <v>327</v>
-      </c>
-      <c r="J139" s="2">
-        <v>46568</v>
+        <v>106</v>
+      </c>
+      <c r="J139" s="1">
+        <v>46424</v>
       </c>
       <c r="K139" t="b">
         <v>0</v>
@@ -6010,34 +5933,31 @@
     </row>
     <row r="140" spans="1:11">
       <c r="A140" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B140">
-        <v>2736</v>
+        <v>2720</v>
       </c>
       <c r="C140" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="D140" t="s">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="E140" t="s">
-        <v>265</v>
+        <v>247</v>
       </c>
       <c r="F140" t="s">
-        <v>301</v>
+        <v>258</v>
       </c>
       <c r="G140" t="s">
-        <v>309</v>
+        <v>286</v>
       </c>
       <c r="H140">
-        <v>330</v>
-      </c>
-      <c r="I140" t="s">
-        <v>328</v>
-      </c>
-      <c r="J140" s="2">
-        <v>46578</v>
+        <v>119</v>
+      </c>
+      <c r="J140" s="1">
+        <v>46407</v>
       </c>
       <c r="K140" t="b">
         <v>0</v>
@@ -6045,34 +5965,31 @@
     </row>
     <row r="141" spans="1:11">
       <c r="A141" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B141">
-        <v>2737</v>
+        <v>2720</v>
       </c>
       <c r="C141" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="D141" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="E141" t="s">
-        <v>265</v>
+        <v>247</v>
       </c>
       <c r="F141" t="s">
-        <v>298</v>
+        <v>258</v>
       </c>
       <c r="G141" t="s">
-        <v>309</v>
+        <v>286</v>
       </c>
       <c r="H141">
-        <v>330</v>
-      </c>
-      <c r="I141" t="s">
-        <v>328</v>
-      </c>
-      <c r="J141" s="2">
-        <v>46592</v>
+        <v>130</v>
+      </c>
+      <c r="J141" s="1">
+        <v>46416</v>
       </c>
       <c r="K141" t="b">
         <v>0</v>
@@ -6080,34 +5997,31 @@
     </row>
     <row r="142" spans="1:11">
       <c r="A142" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B142">
-        <v>2737</v>
+        <v>2723</v>
       </c>
       <c r="C142" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="D142" t="s">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="E142" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
       <c r="F142" t="s">
-        <v>301</v>
+        <v>258</v>
       </c>
       <c r="G142" t="s">
-        <v>309</v>
+        <v>286</v>
       </c>
       <c r="H142">
-        <v>330</v>
-      </c>
-      <c r="I142" t="s">
-        <v>328</v>
-      </c>
-      <c r="J142" s="2">
-        <v>46592</v>
+        <v>152</v>
+      </c>
+      <c r="J142" s="1">
+        <v>46295</v>
       </c>
       <c r="K142" t="b">
         <v>0</v>
@@ -6115,104 +6029,95 @@
     </row>
     <row r="143" spans="1:11">
       <c r="A143" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B143">
-        <v>2729</v>
+        <v>2723</v>
       </c>
       <c r="C143" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="D143" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="E143" t="s">
-        <v>267</v>
+        <v>250</v>
       </c>
       <c r="F143" t="s">
-        <v>294</v>
+        <v>258</v>
       </c>
       <c r="G143" t="s">
-        <v>309</v>
+        <v>286</v>
       </c>
       <c r="H143">
-        <v>-27</v>
-      </c>
-      <c r="I143" t="s">
-        <v>329</v>
-      </c>
-      <c r="J143" s="2">
-        <v>46212</v>
+        <v>152</v>
+      </c>
+      <c r="J143" s="1">
+        <v>46295</v>
       </c>
       <c r="K143" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144" spans="1:11">
       <c r="A144" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B144">
-        <v>2730</v>
+        <v>2728</v>
       </c>
       <c r="C144" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="D144" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="E144" t="s">
-        <v>266</v>
+        <v>243</v>
       </c>
       <c r="F144" t="s">
-        <v>298</v>
+        <v>282</v>
       </c>
       <c r="G144" t="s">
-        <v>309</v>
+        <v>286</v>
       </c>
       <c r="H144">
-        <v>-14</v>
-      </c>
-      <c r="I144" t="s">
-        <v>330</v>
-      </c>
-      <c r="J144" s="2">
-        <v>46225</v>
+        <v>163</v>
+      </c>
+      <c r="J144" s="1">
+        <v>46592</v>
       </c>
       <c r="K144" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145" spans="1:11">
       <c r="A145" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B145">
-        <v>2727</v>
+        <v>2709</v>
       </c>
       <c r="C145" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="D145" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E145" t="s">
-        <v>273</v>
+        <v>247</v>
       </c>
       <c r="F145" t="s">
-        <v>299</v>
+        <v>258</v>
       </c>
       <c r="G145" t="s">
-        <v>309</v>
+        <v>286</v>
       </c>
       <c r="H145">
-        <v>24</v>
-      </c>
-      <c r="I145" t="s">
-        <v>331</v>
-      </c>
-      <c r="J145" s="2">
-        <v>46263</v>
+        <v>172</v>
+      </c>
+      <c r="J145" s="1">
+        <v>46448</v>
       </c>
       <c r="K145" t="b">
         <v>0</v>
@@ -6220,255 +6125,255 @@
     </row>
     <row r="146" spans="1:11">
       <c r="A146" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B146">
-        <v>2724</v>
+        <v>2709</v>
       </c>
       <c r="C146" t="s">
-        <v>232</v>
+        <v>212</v>
       </c>
       <c r="D146" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="E146" t="s">
-        <v>266</v>
+        <v>247</v>
       </c>
       <c r="F146" t="s">
-        <v>306</v>
+        <v>258</v>
       </c>
       <c r="G146" t="s">
-        <v>310</v>
+        <v>286</v>
       </c>
       <c r="H146">
-        <v>-1476</v>
-      </c>
-      <c r="J146" s="2">
-        <v>43773</v>
+        <v>174</v>
+      </c>
+      <c r="J146" s="1">
+        <v>46450</v>
       </c>
       <c r="K146" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147" spans="1:11">
       <c r="A147" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B147">
-        <v>2724</v>
+        <v>2706</v>
       </c>
       <c r="C147" t="s">
-        <v>232</v>
+        <v>214</v>
       </c>
       <c r="D147" t="s">
-        <v>244</v>
+        <v>221</v>
       </c>
       <c r="E147" t="s">
-        <v>266</v>
+        <v>243</v>
       </c>
       <c r="F147" t="s">
-        <v>306</v>
+        <v>252</v>
       </c>
       <c r="G147" t="s">
-        <v>310</v>
+        <v>286</v>
       </c>
       <c r="H147">
-        <v>-1469</v>
-      </c>
-      <c r="J147" s="2">
-        <v>43773</v>
+        <v>248</v>
+      </c>
+      <c r="J147" s="1">
+        <v>46571</v>
       </c>
       <c r="K147" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148" spans="1:11">
       <c r="A148" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B148">
-        <v>2736</v>
+        <v>2742</v>
       </c>
       <c r="C148" t="s">
-        <v>232</v>
+        <v>211</v>
       </c>
       <c r="D148" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="E148" t="s">
-        <v>265</v>
+        <v>243</v>
       </c>
       <c r="F148" t="s">
-        <v>307</v>
+        <v>258</v>
       </c>
       <c r="G148" t="s">
-        <v>310</v>
+        <v>286</v>
       </c>
       <c r="H148">
-        <v>-1186</v>
-      </c>
-      <c r="J148" s="2">
-        <v>45295</v>
+        <v>270</v>
+      </c>
+      <c r="J148" s="1">
+        <v>46524</v>
       </c>
       <c r="K148" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149" spans="1:11">
       <c r="A149" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B149">
-        <v>2740</v>
+        <v>2733</v>
       </c>
       <c r="C149" t="s">
-        <v>232</v>
+        <v>209</v>
       </c>
       <c r="D149" t="s">
-        <v>244</v>
+        <v>221</v>
       </c>
       <c r="E149" t="s">
-        <v>265</v>
+        <v>246</v>
       </c>
       <c r="F149" t="s">
-        <v>306</v>
+        <v>283</v>
       </c>
       <c r="G149" t="s">
-        <v>310</v>
+        <v>286</v>
       </c>
       <c r="H149">
-        <v>-1048</v>
-      </c>
-      <c r="J149" s="2">
-        <v>45617</v>
+        <v>281</v>
+      </c>
+      <c r="J149" s="1">
+        <v>46459</v>
       </c>
       <c r="K149" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150" spans="1:11">
       <c r="A150" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B150">
-        <v>2740</v>
+        <v>2738</v>
       </c>
       <c r="C150" t="s">
-        <v>232</v>
+        <v>209</v>
       </c>
       <c r="D150" t="s">
-        <v>244</v>
+        <v>221</v>
       </c>
       <c r="E150" t="s">
-        <v>265</v>
+        <v>242</v>
       </c>
       <c r="F150" t="s">
-        <v>306</v>
+        <v>283</v>
       </c>
       <c r="G150" t="s">
-        <v>310</v>
+        <v>286</v>
       </c>
       <c r="H150">
-        <v>-980</v>
-      </c>
-      <c r="J150" s="2">
-        <v>45677</v>
+        <v>288</v>
+      </c>
+      <c r="J150" s="1">
+        <v>46531</v>
       </c>
       <c r="K150" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151" spans="1:11">
       <c r="A151" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B151">
-        <v>2720</v>
+        <v>2738</v>
       </c>
       <c r="C151" t="s">
-        <v>232</v>
+        <v>209</v>
       </c>
       <c r="D151" t="s">
-        <v>244</v>
+        <v>221</v>
       </c>
       <c r="E151" t="s">
-        <v>272</v>
+        <v>242</v>
       </c>
       <c r="F151" t="s">
-        <v>307</v>
+        <v>283</v>
       </c>
       <c r="G151" t="s">
-        <v>310</v>
+        <v>286</v>
       </c>
       <c r="H151">
-        <v>-961</v>
-      </c>
-      <c r="J151" s="2">
-        <v>44944</v>
+        <v>294</v>
+      </c>
+      <c r="J151" s="1">
+        <v>46535</v>
       </c>
       <c r="K151" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152" spans="1:11">
       <c r="A152" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B152">
-        <v>2703</v>
+        <v>2739</v>
       </c>
       <c r="C152" t="s">
-        <v>233</v>
+        <v>209</v>
       </c>
       <c r="D152" t="s">
-        <v>263</v>
+        <v>221</v>
       </c>
       <c r="E152" t="s">
-        <v>267</v>
+        <v>246</v>
       </c>
       <c r="F152" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="G152" t="s">
-        <v>310</v>
+        <v>286</v>
       </c>
       <c r="H152">
-        <v>-252</v>
-      </c>
-      <c r="J152" s="2">
-        <v>46092</v>
+        <v>295</v>
+      </c>
+      <c r="J152" s="1">
+        <v>46468</v>
       </c>
       <c r="K152" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153" spans="1:11">
       <c r="A153" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B153">
-        <v>2719</v>
+        <v>2739</v>
       </c>
       <c r="C153" t="s">
-        <v>234</v>
+        <v>210</v>
       </c>
       <c r="D153" t="s">
-        <v>264</v>
+        <v>240</v>
       </c>
       <c r="E153" t="s">
-        <v>268</v>
+        <v>246</v>
       </c>
       <c r="F153" t="s">
-        <v>280</v>
+        <v>258</v>
       </c>
       <c r="G153" t="s">
-        <v>310</v>
+        <v>286</v>
       </c>
       <c r="H153">
-        <v>3</v>
-      </c>
-      <c r="J153" s="2">
-        <v>46265</v>
+        <v>318</v>
+      </c>
+      <c r="J153" s="1">
+        <v>46482</v>
       </c>
       <c r="K153" t="b">
         <v>0</v>
@@ -6476,31 +6381,31 @@
     </row>
     <row r="154" spans="1:11">
       <c r="A154" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B154">
-        <v>2719</v>
+        <v>2733</v>
       </c>
       <c r="C154" t="s">
-        <v>235</v>
+        <v>210</v>
       </c>
       <c r="D154" t="s">
-        <v>264</v>
+        <v>240</v>
       </c>
       <c r="E154" t="s">
-        <v>268</v>
+        <v>246</v>
       </c>
       <c r="F154" t="s">
-        <v>280</v>
+        <v>258</v>
       </c>
       <c r="G154" t="s">
-        <v>310</v>
+        <v>286</v>
       </c>
       <c r="H154">
-        <v>3</v>
-      </c>
-      <c r="J154" s="2">
-        <v>46265</v>
+        <v>332</v>
+      </c>
+      <c r="J154" s="1">
+        <v>46490</v>
       </c>
       <c r="K154" t="b">
         <v>0</v>
@@ -6508,31 +6413,31 @@
     </row>
     <row r="155" spans="1:11">
       <c r="A155" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B155">
-        <v>2728</v>
+        <v>2733</v>
       </c>
       <c r="C155" t="s">
-        <v>234</v>
+        <v>211</v>
       </c>
       <c r="D155" t="s">
-        <v>264</v>
+        <v>241</v>
       </c>
       <c r="E155" t="s">
-        <v>266</v>
+        <v>246</v>
       </c>
       <c r="F155" t="s">
-        <v>280</v>
+        <v>258</v>
       </c>
       <c r="G155" t="s">
-        <v>310</v>
+        <v>286</v>
       </c>
       <c r="H155">
-        <v>43</v>
-      </c>
-      <c r="J155" s="2">
-        <v>46440</v>
+        <v>332</v>
+      </c>
+      <c r="J155" s="1">
+        <v>46490</v>
       </c>
       <c r="K155" t="b">
         <v>0</v>
@@ -6540,31 +6445,31 @@
     </row>
     <row r="156" spans="1:11">
       <c r="A156" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B156">
-        <v>2728</v>
+        <v>2720</v>
       </c>
       <c r="C156" t="s">
-        <v>235</v>
+        <v>215</v>
       </c>
       <c r="D156" t="s">
-        <v>264</v>
+        <v>221</v>
       </c>
       <c r="E156" t="s">
-        <v>266</v>
+        <v>247</v>
       </c>
       <c r="F156" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="G156" t="s">
-        <v>310</v>
+        <v>286</v>
       </c>
       <c r="H156">
-        <v>43</v>
-      </c>
-      <c r="J156" s="2">
-        <v>46440</v>
+        <v>378</v>
+      </c>
+      <c r="J156" s="1">
+        <v>46603</v>
       </c>
       <c r="K156" t="b">
         <v>0</v>
@@ -6572,31 +6477,31 @@
     </row>
     <row r="157" spans="1:11">
       <c r="A157" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B157">
-        <v>2722</v>
+        <v>2731</v>
       </c>
       <c r="C157" t="s">
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="D157" t="s">
-        <v>244</v>
+        <v>221</v>
       </c>
       <c r="E157" t="s">
-        <v>268</v>
+        <v>246</v>
       </c>
       <c r="F157" t="s">
-        <v>306</v>
+        <v>252</v>
       </c>
       <c r="G157" t="s">
-        <v>310</v>
+        <v>286</v>
       </c>
       <c r="H157">
-        <v>72</v>
-      </c>
-      <c r="J157" s="2">
-        <v>46289</v>
+        <v>385</v>
+      </c>
+      <c r="J157" s="1">
+        <v>46526</v>
       </c>
       <c r="K157" t="b">
         <v>0</v>
@@ -6604,31 +6509,31 @@
     </row>
     <row r="158" spans="1:11">
       <c r="A158" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B158">
-        <v>2722</v>
+        <v>2719</v>
       </c>
       <c r="C158" t="s">
-        <v>232</v>
+        <v>210</v>
       </c>
       <c r="D158" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="E158" t="s">
-        <v>268</v>
+        <v>245</v>
       </c>
       <c r="F158" t="s">
-        <v>306</v>
+        <v>258</v>
       </c>
       <c r="G158" t="s">
-        <v>310</v>
+        <v>286</v>
       </c>
       <c r="H158">
-        <v>72</v>
-      </c>
-      <c r="J158" s="2">
-        <v>46289</v>
+        <v>400</v>
+      </c>
+      <c r="J158" s="1">
+        <v>46643</v>
       </c>
       <c r="K158" t="b">
         <v>0</v>
@@ -6636,31 +6541,31 @@
     </row>
     <row r="159" spans="1:11">
       <c r="A159" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B159">
-        <v>2736</v>
+        <v>2739</v>
       </c>
       <c r="C159" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
       <c r="D159" t="s">
-        <v>264</v>
+        <v>240</v>
       </c>
       <c r="E159" t="s">
-        <v>265</v>
+        <v>246</v>
       </c>
       <c r="F159" t="s">
-        <v>280</v>
+        <v>258</v>
       </c>
       <c r="G159" t="s">
-        <v>310</v>
+        <v>286</v>
       </c>
       <c r="H159">
-        <v>81</v>
-      </c>
-      <c r="J159" s="2">
-        <v>46405</v>
+        <v>459</v>
+      </c>
+      <c r="J159" s="1">
+        <v>46568</v>
       </c>
       <c r="K159" t="b">
         <v>0</v>
@@ -6668,31 +6573,31 @@
     </row>
     <row r="160" spans="1:11">
       <c r="A160" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B160">
-        <v>2732</v>
+        <v>2724</v>
       </c>
       <c r="C160" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="D160" t="s">
-        <v>244</v>
+        <v>221</v>
       </c>
       <c r="E160" t="s">
-        <v>266</v>
+        <v>243</v>
       </c>
       <c r="F160" t="s">
-        <v>306</v>
+        <v>272</v>
       </c>
       <c r="G160" t="s">
-        <v>310</v>
+        <v>286</v>
       </c>
       <c r="H160">
-        <v>102</v>
-      </c>
-      <c r="J160" s="2">
-        <v>46463</v>
+        <v>488</v>
+      </c>
+      <c r="J160" s="1">
+        <v>46190</v>
       </c>
       <c r="K160" t="b">
         <v>0</v>
@@ -6700,31 +6605,31 @@
     </row>
     <row r="161" spans="1:11">
       <c r="A161" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B161">
-        <v>2741</v>
+        <v>2723</v>
       </c>
       <c r="C161" t="s">
-        <v>232</v>
+        <v>209</v>
       </c>
       <c r="D161" t="s">
-        <v>244</v>
+        <v>221</v>
       </c>
       <c r="E161" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
       <c r="F161" t="s">
-        <v>306</v>
+        <v>283</v>
       </c>
       <c r="G161" t="s">
-        <v>310</v>
+        <v>286</v>
       </c>
       <c r="H161">
-        <v>109</v>
-      </c>
-      <c r="J161" s="2">
-        <v>46353</v>
+        <v>721</v>
+      </c>
+      <c r="J161" s="1">
+        <v>46358</v>
       </c>
       <c r="K161" t="b">
         <v>0</v>
@@ -6732,31 +6637,31 @@
     </row>
     <row r="162" spans="1:11">
       <c r="A162" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B162">
-        <v>2739</v>
+        <v>2723</v>
       </c>
       <c r="C162" t="s">
-        <v>232</v>
+        <v>209</v>
       </c>
       <c r="D162" t="s">
-        <v>244</v>
+        <v>221</v>
       </c>
       <c r="E162" t="s">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="F162" t="s">
-        <v>307</v>
+        <v>283</v>
       </c>
       <c r="G162" t="s">
-        <v>310</v>
+        <v>286</v>
       </c>
       <c r="H162">
-        <v>127</v>
-      </c>
-      <c r="J162" s="2">
-        <v>46417</v>
+        <v>721</v>
+      </c>
+      <c r="J162" s="1">
+        <v>46358</v>
       </c>
       <c r="K162" t="b">
         <v>0</v>
@@ -6764,31 +6669,31 @@
     </row>
     <row r="163" spans="1:11">
       <c r="A163" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B163">
         <v>2723</v>
       </c>
       <c r="C163" t="s">
-        <v>233</v>
+        <v>212</v>
       </c>
       <c r="D163" t="s">
-        <v>263</v>
+        <v>241</v>
       </c>
       <c r="E163" t="s">
-        <v>271</v>
+        <v>250</v>
       </c>
       <c r="F163" t="s">
-        <v>280</v>
+        <v>258</v>
       </c>
       <c r="G163" t="s">
-        <v>310</v>
+        <v>286</v>
       </c>
       <c r="H163">
-        <v>152</v>
-      </c>
-      <c r="J163" s="2">
-        <v>46271</v>
+        <v>850</v>
+      </c>
+      <c r="J163" s="1">
+        <v>46374</v>
       </c>
       <c r="K163" t="b">
         <v>0</v>
@@ -6796,31 +6701,31 @@
     </row>
     <row r="164" spans="1:11">
       <c r="A164" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B164">
         <v>2723</v>
       </c>
       <c r="C164" t="s">
-        <v>236</v>
+        <v>213</v>
       </c>
       <c r="D164" t="s">
-        <v>264</v>
+        <v>241</v>
       </c>
       <c r="E164" t="s">
-        <v>271</v>
+        <v>250</v>
       </c>
       <c r="F164" t="s">
-        <v>280</v>
+        <v>258</v>
       </c>
       <c r="G164" t="s">
-        <v>310</v>
+        <v>286</v>
       </c>
       <c r="H164">
-        <v>152</v>
-      </c>
-      <c r="J164" s="2">
-        <v>46271</v>
+        <v>850</v>
+      </c>
+      <c r="J164" s="1">
+        <v>46374</v>
       </c>
       <c r="K164" t="b">
         <v>0</v>
@@ -6828,31 +6733,31 @@
     </row>
     <row r="165" spans="1:11">
       <c r="A165" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B165">
-        <v>2736</v>
+        <v>2723</v>
       </c>
       <c r="C165" t="s">
-        <v>233</v>
+        <v>210</v>
       </c>
       <c r="D165" t="s">
-        <v>263</v>
+        <v>240</v>
       </c>
       <c r="E165" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
       <c r="F165" t="s">
-        <v>280</v>
+        <v>258</v>
       </c>
       <c r="G165" t="s">
-        <v>310</v>
+        <v>286</v>
       </c>
       <c r="H165">
-        <v>153</v>
-      </c>
-      <c r="J165" s="2">
-        <v>46458</v>
+        <v>1661</v>
+      </c>
+      <c r="J165" s="1">
+        <v>46529</v>
       </c>
       <c r="K165" t="b">
         <v>0</v>
@@ -6860,31 +6765,31 @@
     </row>
     <row r="166" spans="1:11">
       <c r="A166" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B166">
-        <v>2720</v>
+        <v>2723</v>
       </c>
       <c r="C166" t="s">
-        <v>233</v>
+        <v>211</v>
       </c>
       <c r="D166" t="s">
-        <v>263</v>
+        <v>241</v>
       </c>
       <c r="E166" t="s">
-        <v>272</v>
+        <v>250</v>
       </c>
       <c r="F166" t="s">
-        <v>280</v>
+        <v>258</v>
       </c>
       <c r="G166" t="s">
-        <v>310</v>
+        <v>286</v>
       </c>
       <c r="H166">
-        <v>158</v>
-      </c>
-      <c r="J166" s="2">
-        <v>46381</v>
+        <v>1661</v>
+      </c>
+      <c r="J166" s="1">
+        <v>46529</v>
       </c>
       <c r="K166" t="b">
         <v>0</v>
@@ -6892,31 +6797,31 @@
     </row>
     <row r="167" spans="1:11">
       <c r="A167" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B167">
-        <v>2728</v>
+        <v>2724</v>
       </c>
       <c r="C167" t="s">
-        <v>232</v>
+        <v>214</v>
       </c>
       <c r="D167" t="s">
-        <v>244</v>
+        <v>221</v>
       </c>
       <c r="E167" t="s">
-        <v>266</v>
+        <v>243</v>
       </c>
       <c r="F167" t="s">
-        <v>306</v>
+        <v>272</v>
       </c>
       <c r="G167" t="s">
-        <v>310</v>
+        <v>286</v>
       </c>
       <c r="H167">
-        <v>163</v>
-      </c>
-      <c r="J167" s="2">
-        <v>46592</v>
+        <v>25565</v>
+      </c>
+      <c r="J167" s="1">
+        <v>46190</v>
       </c>
       <c r="K167" t="b">
         <v>0</v>
@@ -6924,31 +6829,31 @@
     </row>
     <row r="168" spans="1:11">
       <c r="A168" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B168">
-        <v>2731</v>
+        <v>2724</v>
       </c>
       <c r="C168" t="s">
-        <v>236</v>
+        <v>218</v>
       </c>
       <c r="D168" t="s">
-        <v>264</v>
+        <v>221</v>
       </c>
       <c r="E168" t="s">
-        <v>270</v>
+        <v>243</v>
       </c>
       <c r="F168" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="G168" t="s">
-        <v>310</v>
+        <v>286</v>
       </c>
       <c r="H168">
-        <v>167</v>
-      </c>
-      <c r="J168" s="2">
-        <v>46441</v>
+        <v>25567</v>
+      </c>
+      <c r="J168" s="1">
+        <v>46190</v>
       </c>
       <c r="K168" t="b">
         <v>0</v>
@@ -6956,833 +6861,33 @@
     </row>
     <row r="169" spans="1:11">
       <c r="A169" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B169">
-        <v>2720</v>
+        <v>2724</v>
       </c>
       <c r="C169" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="D169" t="s">
-        <v>264</v>
+        <v>221</v>
       </c>
       <c r="E169" t="s">
+        <v>243</v>
+      </c>
+      <c r="F169" t="s">
         <v>272</v>
       </c>
-      <c r="F169" t="s">
-        <v>280</v>
-      </c>
       <c r="G169" t="s">
-        <v>310</v>
+        <v>286</v>
       </c>
       <c r="H169">
-        <v>169</v>
-      </c>
-      <c r="J169" s="2">
-        <v>46391</v>
+        <v>31293</v>
+      </c>
+      <c r="J169" s="1">
+        <v>46190</v>
       </c>
       <c r="K169" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="170" spans="1:11">
-      <c r="A170" t="s">
-        <v>172</v>
-      </c>
-      <c r="B170">
-        <v>2709</v>
-      </c>
-      <c r="C170" t="s">
-        <v>234</v>
-      </c>
-      <c r="D170" t="s">
-        <v>264</v>
-      </c>
-      <c r="E170" t="s">
-        <v>272</v>
-      </c>
-      <c r="F170" t="s">
-        <v>280</v>
-      </c>
-      <c r="G170" t="s">
-        <v>310</v>
-      </c>
-      <c r="H170">
-        <v>184</v>
-      </c>
-      <c r="J170" s="2">
-        <v>46385</v>
-      </c>
-      <c r="K170" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="171" spans="1:11">
-      <c r="A171" t="s">
-        <v>173</v>
-      </c>
-      <c r="B171">
-        <v>2709</v>
-      </c>
-      <c r="C171" t="s">
-        <v>235</v>
-      </c>
-      <c r="D171" t="s">
-        <v>264</v>
-      </c>
-      <c r="E171" t="s">
-        <v>272</v>
-      </c>
-      <c r="F171" t="s">
-        <v>280</v>
-      </c>
-      <c r="G171" t="s">
-        <v>310</v>
-      </c>
-      <c r="H171">
-        <v>186</v>
-      </c>
-      <c r="J171" s="2">
-        <v>46387</v>
-      </c>
-      <c r="K171" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="172" spans="1:11">
-      <c r="A172" t="s">
-        <v>174</v>
-      </c>
-      <c r="B172">
-        <v>2719</v>
-      </c>
-      <c r="C172" t="s">
-        <v>236</v>
-      </c>
-      <c r="D172" t="s">
-        <v>264</v>
-      </c>
-      <c r="E172" t="s">
-        <v>268</v>
-      </c>
-      <c r="F172" t="s">
-        <v>280</v>
-      </c>
-      <c r="G172" t="s">
-        <v>310</v>
-      </c>
-      <c r="H172">
-        <v>206</v>
-      </c>
-      <c r="J172" s="2">
-        <v>46399</v>
-      </c>
-      <c r="K172" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="173" spans="1:11">
-      <c r="A173" t="s">
-        <v>175</v>
-      </c>
-      <c r="B173">
-        <v>2719</v>
-      </c>
-      <c r="C173" t="s">
-        <v>233</v>
-      </c>
-      <c r="D173" t="s">
-        <v>263</v>
-      </c>
-      <c r="E173" t="s">
-        <v>268</v>
-      </c>
-      <c r="F173" t="s">
-        <v>280</v>
-      </c>
-      <c r="G173" t="s">
-        <v>310</v>
-      </c>
-      <c r="H173">
-        <v>206</v>
-      </c>
-      <c r="J173" s="2">
-        <v>46399</v>
-      </c>
-      <c r="K173" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="174" spans="1:11">
-      <c r="A174" t="s">
-        <v>176</v>
-      </c>
-      <c r="B174">
-        <v>2738</v>
-      </c>
-      <c r="C174" t="s">
-        <v>233</v>
-      </c>
-      <c r="D174" t="s">
-        <v>263</v>
-      </c>
-      <c r="E174" t="s">
-        <v>265</v>
-      </c>
-      <c r="F174" t="s">
-        <v>280</v>
-      </c>
-      <c r="G174" t="s">
-        <v>310</v>
-      </c>
-      <c r="H174">
-        <v>234</v>
-      </c>
-      <c r="J174" s="2">
-        <v>46458</v>
-      </c>
-      <c r="K174" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="175" spans="1:11">
-      <c r="A175" t="s">
-        <v>177</v>
-      </c>
-      <c r="B175">
-        <v>2706</v>
-      </c>
-      <c r="C175" t="s">
-        <v>237</v>
-      </c>
-      <c r="D175" t="s">
-        <v>244</v>
-      </c>
-      <c r="E175" t="s">
-        <v>266</v>
-      </c>
-      <c r="F175" t="s">
-        <v>276</v>
-      </c>
-      <c r="G175" t="s">
-        <v>310</v>
-      </c>
-      <c r="H175">
-        <v>248</v>
-      </c>
-      <c r="J175" s="2">
-        <v>46528</v>
-      </c>
-      <c r="K175" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="176" spans="1:11">
-      <c r="A176" t="s">
-        <v>178</v>
-      </c>
-      <c r="B176">
-        <v>2733</v>
-      </c>
-      <c r="C176" t="s">
-        <v>232</v>
-      </c>
-      <c r="D176" t="s">
-        <v>244</v>
-      </c>
-      <c r="E176" t="s">
-        <v>270</v>
-      </c>
-      <c r="F176" t="s">
-        <v>307</v>
-      </c>
-      <c r="G176" t="s">
-        <v>310</v>
-      </c>
-      <c r="H176">
-        <v>317</v>
-      </c>
-      <c r="J176" s="2">
-        <v>46540</v>
-      </c>
-      <c r="K176" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="177" spans="1:11">
-      <c r="A177" t="s">
-        <v>179</v>
-      </c>
-      <c r="B177">
-        <v>2731</v>
-      </c>
-      <c r="C177" t="s">
-        <v>233</v>
-      </c>
-      <c r="D177" t="s">
-        <v>263</v>
-      </c>
-      <c r="E177" t="s">
-        <v>270</v>
-      </c>
-      <c r="F177" t="s">
-        <v>280</v>
-      </c>
-      <c r="G177" t="s">
-        <v>310</v>
-      </c>
-      <c r="H177">
-        <v>340</v>
-      </c>
-      <c r="J177" s="2">
-        <v>46547</v>
-      </c>
-      <c r="K177" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="178" spans="1:11">
-      <c r="A178" t="s">
-        <v>180</v>
-      </c>
-      <c r="B178">
-        <v>2738</v>
-      </c>
-      <c r="C178" t="s">
-        <v>232</v>
-      </c>
-      <c r="D178" t="s">
-        <v>244</v>
-      </c>
-      <c r="E178" t="s">
-        <v>265</v>
-      </c>
-      <c r="F178" t="s">
-        <v>307</v>
-      </c>
-      <c r="G178" t="s">
-        <v>310</v>
-      </c>
-      <c r="H178">
-        <v>364</v>
-      </c>
-      <c r="J178" s="2">
-        <v>46557</v>
-      </c>
-      <c r="K178" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="179" spans="1:11">
-      <c r="A179" t="s">
-        <v>181</v>
-      </c>
-      <c r="B179">
-        <v>2733</v>
-      </c>
-      <c r="C179" t="s">
-        <v>236</v>
-      </c>
-      <c r="D179" t="s">
-        <v>264</v>
-      </c>
-      <c r="E179" t="s">
-        <v>270</v>
-      </c>
-      <c r="F179" t="s">
-        <v>280</v>
-      </c>
-      <c r="G179" t="s">
-        <v>310</v>
-      </c>
-      <c r="H179">
-        <v>368</v>
-      </c>
-      <c r="J179" s="2">
-        <v>46571</v>
-      </c>
-      <c r="K179" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="180" spans="1:11">
-      <c r="A180" t="s">
-        <v>182</v>
-      </c>
-      <c r="B180">
-        <v>2733</v>
-      </c>
-      <c r="C180" t="s">
-        <v>233</v>
-      </c>
-      <c r="D180" t="s">
-        <v>263</v>
-      </c>
-      <c r="E180" t="s">
-        <v>270</v>
-      </c>
-      <c r="F180" t="s">
-        <v>280</v>
-      </c>
-      <c r="G180" t="s">
-        <v>310</v>
-      </c>
-      <c r="H180">
-        <v>368</v>
-      </c>
-      <c r="J180" s="2">
-        <v>46571</v>
-      </c>
-      <c r="K180" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="181" spans="1:11">
-      <c r="A181" t="s">
-        <v>183</v>
-      </c>
-      <c r="B181">
-        <v>2738</v>
-      </c>
-      <c r="C181" t="s">
-        <v>232</v>
-      </c>
-      <c r="D181" t="s">
-        <v>244</v>
-      </c>
-      <c r="E181" t="s">
-        <v>265</v>
-      </c>
-      <c r="F181" t="s">
-        <v>307</v>
-      </c>
-      <c r="G181" t="s">
-        <v>310</v>
-      </c>
-      <c r="H181">
-        <v>370</v>
-      </c>
-      <c r="J181" s="2">
-        <v>46562</v>
-      </c>
-      <c r="K181" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="182" spans="1:11">
-      <c r="A182" t="s">
-        <v>184</v>
-      </c>
-      <c r="B182">
-        <v>2731</v>
-      </c>
-      <c r="C182" t="s">
-        <v>232</v>
-      </c>
-      <c r="D182" t="s">
-        <v>244</v>
-      </c>
-      <c r="E182" t="s">
-        <v>270</v>
-      </c>
-      <c r="F182" t="s">
-        <v>307</v>
-      </c>
-      <c r="G182" t="s">
-        <v>310</v>
-      </c>
-      <c r="H182">
-        <v>385</v>
-      </c>
-      <c r="J182" s="2">
-        <v>46574</v>
-      </c>
-      <c r="K182" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="183" spans="1:11">
-      <c r="A183" t="s">
-        <v>185</v>
-      </c>
-      <c r="B183">
-        <v>2731</v>
-      </c>
-      <c r="C183" t="s">
-        <v>238</v>
-      </c>
-      <c r="D183" t="s">
-        <v>244</v>
-      </c>
-      <c r="E183" t="s">
-        <v>270</v>
-      </c>
-      <c r="F183" t="s">
-        <v>276</v>
-      </c>
-      <c r="G183" t="s">
-        <v>310</v>
-      </c>
-      <c r="H183">
-        <v>385</v>
-      </c>
-      <c r="J183" s="2">
-        <v>46574</v>
-      </c>
-      <c r="K183" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="184" spans="1:11">
-      <c r="A184" t="s">
-        <v>186</v>
-      </c>
-      <c r="B184">
-        <v>2720</v>
-      </c>
-      <c r="C184" t="s">
-        <v>239</v>
-      </c>
-      <c r="D184" t="s">
-        <v>244</v>
-      </c>
-      <c r="E184" t="s">
-        <v>272</v>
-      </c>
-      <c r="F184" t="s">
-        <v>296</v>
-      </c>
-      <c r="G184" t="s">
-        <v>310</v>
-      </c>
-      <c r="H184">
-        <v>417</v>
-      </c>
-      <c r="J184" s="2">
-        <v>46578</v>
-      </c>
-      <c r="K184" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="185" spans="1:11">
-      <c r="A185" t="s">
-        <v>187</v>
-      </c>
-      <c r="B185">
-        <v>2723</v>
-      </c>
-      <c r="C185" t="s">
-        <v>232</v>
-      </c>
-      <c r="D185" t="s">
-        <v>244</v>
-      </c>
-      <c r="E185" t="s">
-        <v>271</v>
-      </c>
-      <c r="F185" t="s">
-        <v>307</v>
-      </c>
-      <c r="G185" t="s">
-        <v>310</v>
-      </c>
-      <c r="H185">
-        <v>721</v>
-      </c>
-      <c r="J185" s="2">
-        <v>46345</v>
-      </c>
-      <c r="K185" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="186" spans="1:11">
-      <c r="A186" t="s">
-        <v>188</v>
-      </c>
-      <c r="B186">
-        <v>2723</v>
-      </c>
-      <c r="C186" t="s">
-        <v>232</v>
-      </c>
-      <c r="D186" t="s">
-        <v>244</v>
-      </c>
-      <c r="E186" t="s">
-        <v>271</v>
-      </c>
-      <c r="F186" t="s">
-        <v>307</v>
-      </c>
-      <c r="G186" t="s">
-        <v>310</v>
-      </c>
-      <c r="H186">
-        <v>721</v>
-      </c>
-      <c r="J186" s="2">
-        <v>46345</v>
-      </c>
-      <c r="K186" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="187" spans="1:11">
-      <c r="A187" t="s">
-        <v>189</v>
-      </c>
-      <c r="B187">
-        <v>2723</v>
-      </c>
-      <c r="C187" t="s">
-        <v>235</v>
-      </c>
-      <c r="D187" t="s">
-        <v>264</v>
-      </c>
-      <c r="E187" t="s">
-        <v>271</v>
-      </c>
-      <c r="F187" t="s">
-        <v>280</v>
-      </c>
-      <c r="G187" t="s">
-        <v>310</v>
-      </c>
-      <c r="H187">
-        <v>850</v>
-      </c>
-      <c r="J187" s="2">
-        <v>46366</v>
-      </c>
-      <c r="K187" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="188" spans="1:11">
-      <c r="A188" t="s">
-        <v>190</v>
-      </c>
-      <c r="B188">
-        <v>2723</v>
-      </c>
-      <c r="C188" t="s">
-        <v>234</v>
-      </c>
-      <c r="D188" t="s">
-        <v>264</v>
-      </c>
-      <c r="E188" t="s">
-        <v>271</v>
-      </c>
-      <c r="F188" t="s">
-        <v>280</v>
-      </c>
-      <c r="G188" t="s">
-        <v>310</v>
-      </c>
-      <c r="H188">
-        <v>850</v>
-      </c>
-      <c r="J188" s="2">
-        <v>46366</v>
-      </c>
-      <c r="K188" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="189" spans="1:11">
-      <c r="A189" t="s">
-        <v>191</v>
-      </c>
-      <c r="B189">
-        <v>2723</v>
-      </c>
-      <c r="C189" t="s">
-        <v>233</v>
-      </c>
-      <c r="D189" t="s">
-        <v>263</v>
-      </c>
-      <c r="E189" t="s">
-        <v>271</v>
-      </c>
-      <c r="F189" t="s">
-        <v>280</v>
-      </c>
-      <c r="G189" t="s">
-        <v>310</v>
-      </c>
-      <c r="H189">
-        <v>1661</v>
-      </c>
-      <c r="J189" s="2">
-        <v>46524</v>
-      </c>
-      <c r="K189" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="190" spans="1:11">
-      <c r="A190" t="s">
-        <v>192</v>
-      </c>
-      <c r="B190">
-        <v>2723</v>
-      </c>
-      <c r="C190" t="s">
-        <v>236</v>
-      </c>
-      <c r="D190" t="s">
-        <v>264</v>
-      </c>
-      <c r="E190" t="s">
-        <v>271</v>
-      </c>
-      <c r="F190" t="s">
-        <v>280</v>
-      </c>
-      <c r="G190" t="s">
-        <v>310</v>
-      </c>
-      <c r="H190">
-        <v>1661</v>
-      </c>
-      <c r="J190" s="2">
-        <v>46524</v>
-      </c>
-      <c r="K190" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="191" spans="1:11">
-      <c r="A191" t="s">
-        <v>193</v>
-      </c>
-      <c r="B191">
-        <v>2724</v>
-      </c>
-      <c r="C191" t="s">
-        <v>240</v>
-      </c>
-      <c r="D191" t="s">
-        <v>244</v>
-      </c>
-      <c r="E191" t="s">
-        <v>266</v>
-      </c>
-      <c r="F191" t="s">
-        <v>296</v>
-      </c>
-      <c r="G191" t="s">
-        <v>310</v>
-      </c>
-      <c r="H191">
-        <v>488</v>
-      </c>
-      <c r="J191" s="2">
-        <v>46190</v>
-      </c>
-      <c r="K191" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="192" spans="1:11">
-      <c r="A192" t="s">
-        <v>194</v>
-      </c>
-      <c r="B192">
-        <v>2724</v>
-      </c>
-      <c r="C192" t="s">
-        <v>237</v>
-      </c>
-      <c r="D192" t="s">
-        <v>244</v>
-      </c>
-      <c r="E192" t="s">
-        <v>266</v>
-      </c>
-      <c r="F192" t="s">
-        <v>296</v>
-      </c>
-      <c r="G192" t="s">
-        <v>310</v>
-      </c>
-      <c r="H192">
-        <v>25565</v>
-      </c>
-      <c r="J192" s="2">
-        <v>46190</v>
-      </c>
-      <c r="K192" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="193" spans="1:11">
-      <c r="A193" t="s">
-        <v>195</v>
-      </c>
-      <c r="B193">
-        <v>2724</v>
-      </c>
-      <c r="C193" t="s">
-        <v>241</v>
-      </c>
-      <c r="D193" t="s">
-        <v>244</v>
-      </c>
-      <c r="E193" t="s">
-        <v>266</v>
-      </c>
-      <c r="F193" t="s">
-        <v>296</v>
-      </c>
-      <c r="G193" t="s">
-        <v>310</v>
-      </c>
-      <c r="H193">
-        <v>25567</v>
-      </c>
-      <c r="J193" s="2">
-        <v>46190</v>
-      </c>
-      <c r="K193" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="194" spans="1:11">
-      <c r="A194" t="s">
-        <v>196</v>
-      </c>
-      <c r="B194">
-        <v>2724</v>
-      </c>
-      <c r="C194" t="s">
-        <v>242</v>
-      </c>
-      <c r="D194" t="s">
-        <v>244</v>
-      </c>
-      <c r="E194" t="s">
-        <v>266</v>
-      </c>
-      <c r="F194" t="s">
-        <v>296</v>
-      </c>
-      <c r="G194" t="s">
-        <v>310</v>
-      </c>
-      <c r="H194">
-        <v>31293</v>
-      </c>
-      <c r="J194" s="2">
-        <v>46190</v>
-      </c>
-      <c r="K194" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Coordenadoria/02_Dados_Tratados/base_vencimentos_tratada.xlsx
+++ b/Coordenadoria/02_Dados_Tratados/base_vencimentos_tratada.xlsx
@@ -953,8 +953,16 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -970,7 +978,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -978,12 +986,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1283,37 +1309,37 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1342,7 +1368,7 @@
       <c r="H2">
         <v>-4349.4</v>
       </c>
-      <c r="J2" s="1">
+      <c r="J2" s="2">
         <v>39285</v>
       </c>
       <c r="K2" t="b">
@@ -1374,7 +1400,7 @@
       <c r="H3">
         <v>-2354.2</v>
       </c>
-      <c r="J3" s="1">
+      <c r="J3" s="2">
         <v>40669</v>
       </c>
       <c r="K3" t="b">
@@ -1406,7 +1432,7 @@
       <c r="H4">
         <v>-922.4</v>
       </c>
-      <c r="J4" s="1">
+      <c r="J4" s="2">
         <v>40669</v>
       </c>
       <c r="K4" t="b">
@@ -1438,7 +1464,7 @@
       <c r="H5">
         <v>-879.8</v>
       </c>
-      <c r="J5" s="1">
+      <c r="J5" s="2">
         <v>44884</v>
       </c>
       <c r="K5" t="b">
@@ -1470,7 +1496,7 @@
       <c r="H6">
         <v>-536.4</v>
       </c>
-      <c r="J6" s="1">
+      <c r="J6" s="2">
         <v>43855</v>
       </c>
       <c r="K6" t="b">
@@ -1502,7 +1528,7 @@
       <c r="H7">
         <v>-484.3</v>
       </c>
-      <c r="J7" s="1">
+      <c r="J7" s="2">
         <v>45804</v>
       </c>
       <c r="K7" t="b">
@@ -1534,7 +1560,7 @@
       <c r="H8">
         <v>-482.8</v>
       </c>
-      <c r="J8" s="1">
+      <c r="J8" s="2">
         <v>45804</v>
       </c>
       <c r="K8" t="b">
@@ -1566,7 +1592,7 @@
       <c r="H9">
         <v>-466.1</v>
       </c>
-      <c r="J9" s="1">
+      <c r="J9" s="2">
         <v>46014</v>
       </c>
       <c r="K9" t="b">
@@ -1598,7 +1624,7 @@
       <c r="H10">
         <v>-463.8</v>
       </c>
-      <c r="J10" s="1">
+      <c r="J10" s="2">
         <v>40979</v>
       </c>
       <c r="K10" t="b">
@@ -1630,7 +1656,7 @@
       <c r="H11">
         <v>-463.3</v>
       </c>
-      <c r="J11" s="1">
+      <c r="J11" s="2">
         <v>46014</v>
       </c>
       <c r="K11" t="b">
@@ -1662,7 +1688,7 @@
       <c r="H12">
         <v>-391.8</v>
       </c>
-      <c r="J12" s="1">
+      <c r="J12" s="2">
         <v>42769</v>
       </c>
       <c r="K12" t="b">
@@ -1694,7 +1720,7 @@
       <c r="H13">
         <v>-390</v>
       </c>
-      <c r="J13" s="1">
+      <c r="J13" s="2">
         <v>32786</v>
       </c>
       <c r="K13" t="b">
@@ -1726,7 +1752,7 @@
       <c r="H14">
         <v>-211.2</v>
       </c>
-      <c r="J14" s="1">
+      <c r="J14" s="2">
         <v>34700</v>
       </c>
       <c r="K14" t="b">
@@ -1758,7 +1784,7 @@
       <c r="H15">
         <v>-176</v>
       </c>
-      <c r="J15" s="1">
+      <c r="J15" s="2">
         <v>41204</v>
       </c>
       <c r="K15" t="b">
@@ -1790,7 +1816,7 @@
       <c r="H16">
         <v>-159.2</v>
       </c>
-      <c r="J16" s="1">
+      <c r="J16" s="2">
         <v>46111</v>
       </c>
       <c r="K16" t="b">
@@ -1822,7 +1848,7 @@
       <c r="H17">
         <v>-159.2</v>
       </c>
-      <c r="J17" s="1">
+      <c r="J17" s="2">
         <v>46111</v>
       </c>
       <c r="K17" t="b">
@@ -1854,7 +1880,7 @@
       <c r="H18">
         <v>-159.2</v>
       </c>
-      <c r="J18" s="1">
+      <c r="J18" s="2">
         <v>46111</v>
       </c>
       <c r="K18" t="b">
@@ -1886,7 +1912,7 @@
       <c r="H19">
         <v>-159.2</v>
       </c>
-      <c r="J19" s="1">
+      <c r="J19" s="2">
         <v>46111</v>
       </c>
       <c r="K19" t="b">
@@ -1918,7 +1944,7 @@
       <c r="H20">
         <v>-101.6</v>
       </c>
-      <c r="J20" s="1">
+      <c r="J20" s="2">
         <v>46161</v>
       </c>
       <c r="K20" t="b">
@@ -1950,7 +1976,7 @@
       <c r="H21">
         <v>-69.7</v>
       </c>
-      <c r="J21" s="1">
+      <c r="J21" s="2">
         <v>46241</v>
       </c>
       <c r="K21" t="b">
@@ -1982,7 +2008,7 @@
       <c r="H22">
         <v>-61.8</v>
       </c>
-      <c r="J22" s="1">
+      <c r="J22" s="2">
         <v>46242</v>
       </c>
       <c r="K22" t="b">
@@ -2014,7 +2040,7 @@
       <c r="H23">
         <v>-53.5</v>
       </c>
-      <c r="J23" s="1">
+      <c r="J23" s="2">
         <v>46255</v>
       </c>
       <c r="K23" t="b">
@@ -2046,7 +2072,7 @@
       <c r="H24">
         <v>-10</v>
       </c>
-      <c r="J24" s="1">
+      <c r="J24" s="2">
         <v>46276</v>
       </c>
       <c r="K24" t="b">
@@ -2078,7 +2104,7 @@
       <c r="H25">
         <v>-10</v>
       </c>
-      <c r="J25" s="1">
+      <c r="J25" s="2">
         <v>46276</v>
       </c>
       <c r="K25" t="b">
@@ -2110,7 +2136,7 @@
       <c r="H26">
         <v>-7.4</v>
       </c>
-      <c r="J26" s="1">
+      <c r="J26" s="2">
         <v>46269</v>
       </c>
       <c r="K26" t="b">
@@ -2142,7 +2168,7 @@
       <c r="H27">
         <v>-6.3</v>
       </c>
-      <c r="J27" s="1">
+      <c r="J27" s="2">
         <v>46236</v>
       </c>
       <c r="K27" t="b">
@@ -2174,7 +2200,7 @@
       <c r="H28">
         <v>0</v>
       </c>
-      <c r="J28" s="1">
+      <c r="J28" s="2">
         <v>46282</v>
       </c>
       <c r="K28" t="b">
@@ -2206,7 +2232,7 @@
       <c r="H29">
         <v>7.7</v>
       </c>
-      <c r="J29" s="1">
+      <c r="J29" s="2">
         <v>46295</v>
       </c>
       <c r="K29" t="b">
@@ -2238,7 +2264,7 @@
       <c r="H30">
         <v>9.800000000000001</v>
       </c>
-      <c r="J30" s="1">
+      <c r="J30" s="2">
         <v>46295</v>
       </c>
       <c r="K30" t="b">
@@ -2270,7 +2296,7 @@
       <c r="H31">
         <v>10.9</v>
       </c>
-      <c r="J31" s="1">
+      <c r="J31" s="2">
         <v>46295</v>
       </c>
       <c r="K31" t="b">
@@ -2302,7 +2328,7 @@
       <c r="H32">
         <v>21.8</v>
       </c>
-      <c r="J32" s="1">
+      <c r="J32" s="2">
         <v>46404</v>
       </c>
       <c r="K32" t="b">
@@ -2334,7 +2360,7 @@
       <c r="H33">
         <v>33.9</v>
       </c>
-      <c r="J33" s="1">
+      <c r="J33" s="2">
         <v>46434</v>
       </c>
       <c r="K33" t="b">
@@ -2366,7 +2392,7 @@
       <c r="H34">
         <v>42.8</v>
       </c>
-      <c r="J34" s="1">
+      <c r="J34" s="2">
         <v>46385</v>
       </c>
       <c r="K34" t="b">
@@ -2398,7 +2424,7 @@
       <c r="H35">
         <v>52.7</v>
       </c>
-      <c r="J35" s="1">
+      <c r="J35" s="2">
         <v>46337</v>
       </c>
       <c r="K35" t="b">
@@ -2430,7 +2456,7 @@
       <c r="H36">
         <v>57.5</v>
       </c>
-      <c r="J36" s="1">
+      <c r="J36" s="2">
         <v>46493</v>
       </c>
       <c r="K36" t="b">
@@ -2462,7 +2488,7 @@
       <c r="H37">
         <v>71</v>
       </c>
-      <c r="J37" s="1">
+      <c r="J37" s="2">
         <v>46527</v>
       </c>
       <c r="K37" t="b">
@@ -2494,7 +2520,7 @@
       <c r="H38">
         <v>73</v>
       </c>
-      <c r="J38" s="1">
+      <c r="J38" s="2">
         <v>46532</v>
       </c>
       <c r="K38" t="b">
@@ -2526,7 +2552,7 @@
       <c r="H39">
         <v>82</v>
       </c>
-      <c r="J39" s="1">
+      <c r="J39" s="2">
         <v>46389</v>
       </c>
       <c r="K39" t="b">
@@ -2558,7 +2584,7 @@
       <c r="H40">
         <v>107.1</v>
       </c>
-      <c r="J40" s="1">
+      <c r="J40" s="2">
         <v>46338</v>
       </c>
       <c r="K40" t="b">
@@ -2590,7 +2616,7 @@
       <c r="H41">
         <v>109.8</v>
       </c>
-      <c r="J41" s="1">
+      <c r="J41" s="2">
         <v>46337</v>
       </c>
       <c r="K41" t="b">
@@ -2622,7 +2648,7 @@
       <c r="H42">
         <v>112.9</v>
       </c>
-      <c r="J42" s="1">
+      <c r="J42" s="2">
         <v>46401</v>
       </c>
       <c r="K42" t="b">
@@ -2654,7 +2680,7 @@
       <c r="H43">
         <v>121.9</v>
       </c>
-      <c r="J43" s="1">
+      <c r="J43" s="2">
         <v>46412</v>
       </c>
       <c r="K43" t="b">
@@ -2686,7 +2712,7 @@
       <c r="H44">
         <v>135.1</v>
       </c>
-      <c r="J44" s="1">
+      <c r="J44" s="2">
         <v>46353</v>
       </c>
       <c r="K44" t="b">
@@ -2718,7 +2744,7 @@
       <c r="H45">
         <v>136.2</v>
       </c>
-      <c r="J45" s="1">
+      <c r="J45" s="2">
         <v>46419</v>
       </c>
       <c r="K45" t="b">
@@ -2750,7 +2776,7 @@
       <c r="H46">
         <v>138.8</v>
       </c>
-      <c r="J46" s="1">
+      <c r="J46" s="2">
         <v>46353</v>
       </c>
       <c r="K46" t="b">
@@ -2782,7 +2808,7 @@
       <c r="H47">
         <v>140.1</v>
       </c>
-      <c r="J47" s="1">
+      <c r="J47" s="2">
         <v>46355</v>
       </c>
       <c r="K47" t="b">
@@ -2814,7 +2840,7 @@
       <c r="H48">
         <v>141.6</v>
       </c>
-      <c r="J48" s="1">
+      <c r="J48" s="2">
         <v>46355</v>
       </c>
       <c r="K48" t="b">
@@ -2846,7 +2872,7 @@
       <c r="H49">
         <v>161.2</v>
       </c>
-      <c r="J49" s="1">
+      <c r="J49" s="2">
         <v>46394</v>
       </c>
       <c r="K49" t="b">
@@ -2878,7 +2904,7 @@
       <c r="H50">
         <v>170.3</v>
       </c>
-      <c r="J50" s="1">
+      <c r="J50" s="2">
         <v>46370</v>
       </c>
       <c r="K50" t="b">
@@ -2910,7 +2936,7 @@
       <c r="H51">
         <v>177.4</v>
       </c>
-      <c r="J51" s="1">
+      <c r="J51" s="2">
         <v>46487</v>
       </c>
       <c r="K51" t="b">
@@ -2942,7 +2968,7 @@
       <c r="H52">
         <v>184.1</v>
       </c>
-      <c r="J52" s="1">
+      <c r="J52" s="2">
         <v>46358</v>
       </c>
       <c r="K52" t="b">
@@ -2974,7 +3000,7 @@
       <c r="H53">
         <v>199.3</v>
       </c>
-      <c r="J53" s="1">
+      <c r="J53" s="2">
         <v>46433</v>
       </c>
       <c r="K53" t="b">
@@ -3006,7 +3032,7 @@
       <c r="H54">
         <v>200</v>
       </c>
-      <c r="J54" s="1">
+      <c r="J54" s="2">
         <v>46367</v>
       </c>
       <c r="K54" t="b">
@@ -3038,7 +3064,7 @@
       <c r="H55">
         <v>203.6</v>
       </c>
-      <c r="J55" s="1">
+      <c r="J55" s="2">
         <v>46388</v>
       </c>
       <c r="K55" t="b">
@@ -3070,7 +3096,7 @@
       <c r="H56">
         <v>207.6</v>
       </c>
-      <c r="J56" s="1">
+      <c r="J56" s="2">
         <v>46391</v>
       </c>
       <c r="K56" t="b">
@@ -3102,7 +3128,7 @@
       <c r="H57">
         <v>226.1</v>
       </c>
-      <c r="J57" s="1">
+      <c r="J57" s="2">
         <v>46442</v>
       </c>
       <c r="K57" t="b">
@@ -3134,7 +3160,7 @@
       <c r="H58">
         <v>277</v>
       </c>
-      <c r="J58" s="1">
+      <c r="J58" s="2">
         <v>46461</v>
       </c>
       <c r="K58" t="b">
@@ -3166,7 +3192,7 @@
       <c r="H59">
         <v>280.6</v>
       </c>
-      <c r="J59" s="1">
+      <c r="J59" s="2">
         <v>46409</v>
       </c>
       <c r="K59" t="b">
@@ -3201,7 +3227,7 @@
       <c r="I60" t="s">
         <v>287</v>
       </c>
-      <c r="J60" s="1">
+      <c r="J60" s="2">
         <v>36557</v>
       </c>
       <c r="K60" t="b">
@@ -3236,7 +3262,7 @@
       <c r="I61" t="s">
         <v>288</v>
       </c>
-      <c r="J61" s="1">
+      <c r="J61" s="2">
         <v>41275</v>
       </c>
       <c r="K61" t="b">
@@ -3271,7 +3297,7 @@
       <c r="I62" t="s">
         <v>289</v>
       </c>
-      <c r="J62" s="1">
+      <c r="J62" s="2">
         <v>45380</v>
       </c>
       <c r="K62" t="b">
@@ -3306,7 +3332,7 @@
       <c r="I63" t="s">
         <v>290</v>
       </c>
-      <c r="J63" s="1">
+      <c r="J63" s="2">
         <v>45421</v>
       </c>
       <c r="K63" t="b">
@@ -3341,7 +3367,7 @@
       <c r="I64" t="s">
         <v>290</v>
       </c>
-      <c r="J64" s="1">
+      <c r="J64" s="2">
         <v>45428</v>
       </c>
       <c r="K64" t="b">
@@ -3376,7 +3402,7 @@
       <c r="I65" t="s">
         <v>291</v>
       </c>
-      <c r="J65" s="1">
+      <c r="J65" s="2">
         <v>45490</v>
       </c>
       <c r="K65" t="b">
@@ -3411,7 +3437,7 @@
       <c r="I66" t="s">
         <v>292</v>
       </c>
-      <c r="J66" s="1">
+      <c r="J66" s="2">
         <v>45566</v>
       </c>
       <c r="K66" t="b">
@@ -3446,7 +3472,7 @@
       <c r="I67" t="s">
         <v>293</v>
       </c>
-      <c r="J67" s="1">
+      <c r="J67" s="2">
         <v>45986</v>
       </c>
       <c r="K67" t="b">
@@ -3481,7 +3507,7 @@
       <c r="I68" t="s">
         <v>294</v>
       </c>
-      <c r="J68" s="1">
+      <c r="J68" s="2">
         <v>46197</v>
       </c>
       <c r="K68" t="b">
@@ -3516,7 +3542,7 @@
       <c r="I69" t="s">
         <v>294</v>
       </c>
-      <c r="J69" s="1">
+      <c r="J69" s="2">
         <v>46212</v>
       </c>
       <c r="K69" t="b">
@@ -3551,7 +3577,7 @@
       <c r="I70" t="s">
         <v>295</v>
       </c>
-      <c r="J70" s="1">
+      <c r="J70" s="2">
         <v>46341</v>
       </c>
       <c r="K70" t="b">
@@ -3586,7 +3612,7 @@
       <c r="I71" t="s">
         <v>295</v>
       </c>
-      <c r="J71" s="1">
+      <c r="J71" s="2">
         <v>46344</v>
       </c>
       <c r="K71" t="b">
@@ -3621,7 +3647,7 @@
       <c r="I72" t="s">
         <v>295</v>
       </c>
-      <c r="J72" s="1">
+      <c r="J72" s="2">
         <v>46360</v>
       </c>
       <c r="K72" t="b">
@@ -3656,7 +3682,7 @@
       <c r="I73" t="s">
         <v>295</v>
       </c>
-      <c r="J73" s="1">
+      <c r="J73" s="2">
         <v>46367</v>
       </c>
       <c r="K73" t="b">
@@ -3691,7 +3717,7 @@
       <c r="I74" t="s">
         <v>295</v>
       </c>
-      <c r="J74" s="1">
+      <c r="J74" s="2">
         <v>46368</v>
       </c>
       <c r="K74" t="b">
@@ -3726,7 +3752,7 @@
       <c r="I75" t="s">
         <v>295</v>
       </c>
-      <c r="J75" s="1">
+      <c r="J75" s="2">
         <v>46374</v>
       </c>
       <c r="K75" t="b">
@@ -3761,7 +3787,7 @@
       <c r="I76" t="s">
         <v>296</v>
       </c>
-      <c r="J76" s="1">
+      <c r="J76" s="2">
         <v>46375</v>
       </c>
       <c r="K76" t="b">
@@ -3796,7 +3822,7 @@
       <c r="I77" t="s">
         <v>296</v>
       </c>
-      <c r="J77" s="1">
+      <c r="J77" s="2">
         <v>46387</v>
       </c>
       <c r="K77" t="b">
@@ -3831,7 +3857,7 @@
       <c r="I78" t="s">
         <v>296</v>
       </c>
-      <c r="J78" s="1">
+      <c r="J78" s="2">
         <v>46387</v>
       </c>
       <c r="K78" t="b">
@@ -3866,7 +3892,7 @@
       <c r="I79" t="s">
         <v>296</v>
       </c>
-      <c r="J79" s="1">
+      <c r="J79" s="2">
         <v>46387</v>
       </c>
       <c r="K79" t="b">
@@ -3901,7 +3927,7 @@
       <c r="I80" t="s">
         <v>296</v>
       </c>
-      <c r="J80" s="1">
+      <c r="J80" s="2">
         <v>46388</v>
       </c>
       <c r="K80" t="b">
@@ -3936,7 +3962,7 @@
       <c r="I81" t="s">
         <v>296</v>
       </c>
-      <c r="J81" s="1">
+      <c r="J81" s="2">
         <v>46401</v>
       </c>
       <c r="K81" t="b">
@@ -3971,7 +3997,7 @@
       <c r="I82" t="s">
         <v>296</v>
       </c>
-      <c r="J82" s="1">
+      <c r="J82" s="2">
         <v>46401</v>
       </c>
       <c r="K82" t="b">
@@ -4006,7 +4032,7 @@
       <c r="I83" t="s">
         <v>296</v>
       </c>
-      <c r="J83" s="1">
+      <c r="J83" s="2">
         <v>46401</v>
       </c>
       <c r="K83" t="b">
@@ -4041,7 +4067,7 @@
       <c r="I84" t="s">
         <v>297</v>
       </c>
-      <c r="J84" s="1">
+      <c r="J84" s="2">
         <v>46412</v>
       </c>
       <c r="K84" t="b">
@@ -4076,7 +4102,7 @@
       <c r="I85" t="s">
         <v>297</v>
       </c>
-      <c r="J85" s="1">
+      <c r="J85" s="2">
         <v>46412</v>
       </c>
       <c r="K85" t="b">
@@ -4111,7 +4137,7 @@
       <c r="I86" t="s">
         <v>297</v>
       </c>
-      <c r="J86" s="1">
+      <c r="J86" s="2">
         <v>46424</v>
       </c>
       <c r="K86" t="b">
@@ -4146,7 +4172,7 @@
       <c r="I87" t="s">
         <v>297</v>
       </c>
-      <c r="J87" s="1">
+      <c r="J87" s="2">
         <v>46427</v>
       </c>
       <c r="K87" t="b">
@@ -4181,7 +4207,7 @@
       <c r="I88" t="s">
         <v>297</v>
       </c>
-      <c r="J88" s="1">
+      <c r="J88" s="2">
         <v>46427</v>
       </c>
       <c r="K88" t="b">
@@ -4216,7 +4242,7 @@
       <c r="I89" t="s">
         <v>298</v>
       </c>
-      <c r="J89" s="1">
+      <c r="J89" s="2">
         <v>46437</v>
       </c>
       <c r="K89" t="b">
@@ -4251,7 +4277,7 @@
       <c r="I90" t="s">
         <v>298</v>
       </c>
-      <c r="J90" s="1">
+      <c r="J90" s="2">
         <v>46451</v>
       </c>
       <c r="K90" t="b">
@@ -4286,7 +4312,7 @@
       <c r="I91" t="s">
         <v>298</v>
       </c>
-      <c r="J91" s="1">
+      <c r="J91" s="2">
         <v>46451</v>
       </c>
       <c r="K91" t="b">
@@ -4321,7 +4347,7 @@
       <c r="I92" t="s">
         <v>298</v>
       </c>
-      <c r="J92" s="1">
+      <c r="J92" s="2">
         <v>46455</v>
       </c>
       <c r="K92" t="b">
@@ -4356,7 +4382,7 @@
       <c r="I93" t="s">
         <v>298</v>
       </c>
-      <c r="J93" s="1">
+      <c r="J93" s="2">
         <v>46456</v>
       </c>
       <c r="K93" t="b">
@@ -4391,7 +4417,7 @@
       <c r="I94" t="s">
         <v>298</v>
       </c>
-      <c r="J94" s="1">
+      <c r="J94" s="2">
         <v>46457</v>
       </c>
       <c r="K94" t="b">
@@ -4426,7 +4452,7 @@
       <c r="I95" t="s">
         <v>298</v>
       </c>
-      <c r="J95" s="1">
+      <c r="J95" s="2">
         <v>46464</v>
       </c>
       <c r="K95" t="b">
@@ -4461,7 +4487,7 @@
       <c r="I96" t="s">
         <v>299</v>
       </c>
-      <c r="J96" s="1">
+      <c r="J96" s="2">
         <v>46470</v>
       </c>
       <c r="K96" t="b">
@@ -4496,7 +4522,7 @@
       <c r="I97" t="s">
         <v>299</v>
       </c>
-      <c r="J97" s="1">
+      <c r="J97" s="2">
         <v>46485</v>
       </c>
       <c r="K97" t="b">
@@ -4531,7 +4557,7 @@
       <c r="I98" t="s">
         <v>300</v>
       </c>
-      <c r="J98" s="1">
+      <c r="J98" s="2">
         <v>46499</v>
       </c>
       <c r="K98" t="b">
@@ -4566,7 +4592,7 @@
       <c r="I99" t="s">
         <v>300</v>
       </c>
-      <c r="J99" s="1">
+      <c r="J99" s="2">
         <v>46504</v>
       </c>
       <c r="K99" t="b">
@@ -4601,7 +4627,7 @@
       <c r="I100" t="s">
         <v>300</v>
       </c>
-      <c r="J100" s="1">
+      <c r="J100" s="2">
         <v>46507</v>
       </c>
       <c r="K100" t="b">
@@ -4636,7 +4662,7 @@
       <c r="I101" t="s">
         <v>300</v>
       </c>
-      <c r="J101" s="1">
+      <c r="J101" s="2">
         <v>46508</v>
       </c>
       <c r="K101" t="b">
@@ -4671,7 +4697,7 @@
       <c r="I102" t="s">
         <v>300</v>
       </c>
-      <c r="J102" s="1">
+      <c r="J102" s="2">
         <v>46512</v>
       </c>
       <c r="K102" t="b">
@@ -4706,7 +4732,7 @@
       <c r="I103" t="s">
         <v>300</v>
       </c>
-      <c r="J103" s="1">
+      <c r="J103" s="2">
         <v>46512</v>
       </c>
       <c r="K103" t="b">
@@ -4741,7 +4767,7 @@
       <c r="I104" t="s">
         <v>301</v>
       </c>
-      <c r="J104" s="1">
+      <c r="J104" s="2">
         <v>46528</v>
       </c>
       <c r="K104" t="b">
@@ -4776,7 +4802,7 @@
       <c r="I105" t="s">
         <v>301</v>
       </c>
-      <c r="J105" s="1">
+      <c r="J105" s="2">
         <v>46529</v>
       </c>
       <c r="K105" t="b">
@@ -4811,7 +4837,7 @@
       <c r="I106" t="s">
         <v>301</v>
       </c>
-      <c r="J106" s="1">
+      <c r="J106" s="2">
         <v>46537</v>
       </c>
       <c r="K106" t="b">
@@ -4846,7 +4872,7 @@
       <c r="I107" t="s">
         <v>301</v>
       </c>
-      <c r="J107" s="1">
+      <c r="J107" s="2">
         <v>46546</v>
       </c>
       <c r="K107" t="b">
@@ -4881,7 +4907,7 @@
       <c r="I108" t="s">
         <v>301</v>
       </c>
-      <c r="J108" s="1">
+      <c r="J108" s="2">
         <v>46547</v>
       </c>
       <c r="K108" t="b">
@@ -4916,7 +4942,7 @@
       <c r="I109" t="s">
         <v>301</v>
       </c>
-      <c r="J109" s="1">
+      <c r="J109" s="2">
         <v>46547</v>
       </c>
       <c r="K109" t="b">
@@ -4951,7 +4977,7 @@
       <c r="I110" t="s">
         <v>301</v>
       </c>
-      <c r="J110" s="1">
+      <c r="J110" s="2">
         <v>46551</v>
       </c>
       <c r="K110" t="b">
@@ -4986,7 +5012,7 @@
       <c r="I111" t="s">
         <v>302</v>
       </c>
-      <c r="J111" s="1">
+      <c r="J111" s="2">
         <v>46560</v>
       </c>
       <c r="K111" t="b">
@@ -5021,7 +5047,7 @@
       <c r="I112" t="s">
         <v>302</v>
       </c>
-      <c r="J112" s="1">
+      <c r="J112" s="2">
         <v>46567</v>
       </c>
       <c r="K112" t="b">
@@ -5056,7 +5082,7 @@
       <c r="I113" t="s">
         <v>302</v>
       </c>
-      <c r="J113" s="1">
+      <c r="J113" s="2">
         <v>46568</v>
       </c>
       <c r="K113" t="b">
@@ -5091,7 +5117,7 @@
       <c r="I114" t="s">
         <v>302</v>
       </c>
-      <c r="J114" s="1">
+      <c r="J114" s="2">
         <v>46578</v>
       </c>
       <c r="K114" t="b">
@@ -5126,7 +5152,7 @@
       <c r="I115" t="s">
         <v>303</v>
       </c>
-      <c r="J115" s="1">
+      <c r="J115" s="2">
         <v>46592</v>
       </c>
       <c r="K115" t="b">
@@ -5161,7 +5187,7 @@
       <c r="I116" t="s">
         <v>303</v>
       </c>
-      <c r="J116" s="1">
+      <c r="J116" s="2">
         <v>46592</v>
       </c>
       <c r="K116" t="b">
@@ -5196,7 +5222,7 @@
       <c r="I117" t="s">
         <v>303</v>
       </c>
-      <c r="J117" s="1">
+      <c r="J117" s="2">
         <v>46603</v>
       </c>
       <c r="K117" t="b">
@@ -5231,7 +5257,7 @@
       <c r="I118" t="s">
         <v>303</v>
       </c>
-      <c r="J118" s="1">
+      <c r="J118" s="2">
         <v>46611</v>
       </c>
       <c r="K118" t="b">
@@ -5266,7 +5292,7 @@
       <c r="I119" t="s">
         <v>304</v>
       </c>
-      <c r="J119" s="1">
+      <c r="J119" s="2">
         <v>46631</v>
       </c>
       <c r="K119" t="b">
@@ -5301,7 +5327,7 @@
       <c r="I120" t="s">
         <v>304</v>
       </c>
-      <c r="J120" s="1">
+      <c r="J120" s="2">
         <v>46645</v>
       </c>
       <c r="K120" t="b">
@@ -5336,7 +5362,7 @@
       <c r="I121" t="s">
         <v>305</v>
       </c>
-      <c r="J121" s="1">
+      <c r="J121" s="2">
         <v>46254</v>
       </c>
       <c r="K121" t="b">
@@ -5371,7 +5397,7 @@
       <c r="I122" t="s">
         <v>306</v>
       </c>
-      <c r="J122" s="1">
+      <c r="J122" s="2">
         <v>46284</v>
       </c>
       <c r="K122" t="b">
@@ -5406,7 +5432,7 @@
       <c r="I123" t="s">
         <v>307</v>
       </c>
-      <c r="J123" s="1">
+      <c r="J123" s="2">
         <v>46296</v>
       </c>
       <c r="K123" t="b">
@@ -5441,7 +5467,7 @@
       <c r="I124" t="s">
         <v>308</v>
       </c>
-      <c r="J124" s="1">
+      <c r="J124" s="2">
         <v>46293</v>
       </c>
       <c r="K124" t="b">
@@ -5476,7 +5502,7 @@
       <c r="I125" t="s">
         <v>309</v>
       </c>
-      <c r="J125" s="1">
+      <c r="J125" s="2">
         <v>46305</v>
       </c>
       <c r="K125" t="b">
@@ -5508,7 +5534,7 @@
       <c r="H126">
         <v>-1476</v>
       </c>
-      <c r="J126" s="1">
+      <c r="J126" s="2">
         <v>43773</v>
       </c>
       <c r="K126" t="b">
@@ -5540,7 +5566,7 @@
       <c r="H127">
         <v>-1469</v>
       </c>
-      <c r="J127" s="1">
+      <c r="J127" s="2">
         <v>43773</v>
       </c>
       <c r="K127" t="b">
@@ -5572,7 +5598,7 @@
       <c r="H128">
         <v>-1250</v>
       </c>
-      <c r="J128" s="1">
+      <c r="J128" s="2">
         <v>45295</v>
       </c>
       <c r="K128" t="b">
@@ -5604,7 +5630,7 @@
       <c r="H129">
         <v>-1089</v>
       </c>
-      <c r="J129" s="1">
+      <c r="J129" s="2">
         <v>45617</v>
       </c>
       <c r="K129" t="b">
@@ -5636,7 +5662,7 @@
       <c r="H130">
         <v>-1021</v>
       </c>
-      <c r="J130" s="1">
+      <c r="J130" s="2">
         <v>45677</v>
       </c>
       <c r="K130" t="b">
@@ -5668,7 +5694,7 @@
       <c r="H131">
         <v>-1000</v>
       </c>
-      <c r="J131" s="1">
+      <c r="J131" s="2">
         <v>44944</v>
       </c>
       <c r="K131" t="b">
@@ -5700,7 +5726,7 @@
       <c r="H132">
         <v>-296</v>
       </c>
-      <c r="J132" s="1">
+      <c r="J132" s="2">
         <v>46092</v>
       </c>
       <c r="K132" t="b">
@@ -5732,7 +5758,7 @@
       <c r="H133">
         <v>-51</v>
       </c>
-      <c r="J133" s="1">
+      <c r="J133" s="2">
         <v>46258</v>
       </c>
       <c r="K133" t="b">
@@ -5764,7 +5790,7 @@
       <c r="H134">
         <v>-49</v>
       </c>
-      <c r="J134" s="1">
+      <c r="J134" s="2">
         <v>46254</v>
       </c>
       <c r="K134" t="b">
@@ -5796,7 +5822,7 @@
       <c r="H135">
         <v>-49</v>
       </c>
-      <c r="J135" s="1">
+      <c r="J135" s="2">
         <v>46254</v>
       </c>
       <c r="K135" t="b">
@@ -5828,7 +5854,7 @@
       <c r="H136">
         <v>43</v>
       </c>
-      <c r="J136" s="1">
+      <c r="J136" s="2">
         <v>46440</v>
       </c>
       <c r="K136" t="b">
@@ -5860,7 +5886,7 @@
       <c r="H137">
         <v>43</v>
       </c>
-      <c r="J137" s="1">
+      <c r="J137" s="2">
         <v>46440</v>
       </c>
       <c r="K137" t="b">
@@ -5892,7 +5918,7 @@
       <c r="H138">
         <v>102</v>
       </c>
-      <c r="J138" s="1">
+      <c r="J138" s="2">
         <v>46463</v>
       </c>
       <c r="K138" t="b">
@@ -5924,7 +5950,7 @@
       <c r="H139">
         <v>106</v>
       </c>
-      <c r="J139" s="1">
+      <c r="J139" s="2">
         <v>46424</v>
       </c>
       <c r="K139" t="b">
@@ -5956,7 +5982,7 @@
       <c r="H140">
         <v>119</v>
       </c>
-      <c r="J140" s="1">
+      <c r="J140" s="2">
         <v>46407</v>
       </c>
       <c r="K140" t="b">
@@ -5988,7 +6014,7 @@
       <c r="H141">
         <v>130</v>
       </c>
-      <c r="J141" s="1">
+      <c r="J141" s="2">
         <v>46416</v>
       </c>
       <c r="K141" t="b">
@@ -6020,7 +6046,7 @@
       <c r="H142">
         <v>152</v>
       </c>
-      <c r="J142" s="1">
+      <c r="J142" s="2">
         <v>46295</v>
       </c>
       <c r="K142" t="b">
@@ -6052,7 +6078,7 @@
       <c r="H143">
         <v>152</v>
       </c>
-      <c r="J143" s="1">
+      <c r="J143" s="2">
         <v>46295</v>
       </c>
       <c r="K143" t="b">
@@ -6084,7 +6110,7 @@
       <c r="H144">
         <v>163</v>
       </c>
-      <c r="J144" s="1">
+      <c r="J144" s="2">
         <v>46592</v>
       </c>
       <c r="K144" t="b">
@@ -6116,7 +6142,7 @@
       <c r="H145">
         <v>172</v>
       </c>
-      <c r="J145" s="1">
+      <c r="J145" s="2">
         <v>46448</v>
       </c>
       <c r="K145" t="b">
@@ -6148,7 +6174,7 @@
       <c r="H146">
         <v>174</v>
       </c>
-      <c r="J146" s="1">
+      <c r="J146" s="2">
         <v>46450</v>
       </c>
       <c r="K146" t="b">
@@ -6180,7 +6206,7 @@
       <c r="H147">
         <v>248</v>
       </c>
-      <c r="J147" s="1">
+      <c r="J147" s="2">
         <v>46571</v>
       </c>
       <c r="K147" t="b">
@@ -6212,7 +6238,7 @@
       <c r="H148">
         <v>270</v>
       </c>
-      <c r="J148" s="1">
+      <c r="J148" s="2">
         <v>46524</v>
       </c>
       <c r="K148" t="b">
@@ -6244,7 +6270,7 @@
       <c r="H149">
         <v>281</v>
       </c>
-      <c r="J149" s="1">
+      <c r="J149" s="2">
         <v>46459</v>
       </c>
       <c r="K149" t="b">
@@ -6276,7 +6302,7 @@
       <c r="H150">
         <v>288</v>
       </c>
-      <c r="J150" s="1">
+      <c r="J150" s="2">
         <v>46531</v>
       </c>
       <c r="K150" t="b">
@@ -6308,7 +6334,7 @@
       <c r="H151">
         <v>294</v>
       </c>
-      <c r="J151" s="1">
+      <c r="J151" s="2">
         <v>46535</v>
       </c>
       <c r="K151" t="b">
@@ -6340,7 +6366,7 @@
       <c r="H152">
         <v>295</v>
       </c>
-      <c r="J152" s="1">
+      <c r="J152" s="2">
         <v>46468</v>
       </c>
       <c r="K152" t="b">
@@ -6372,7 +6398,7 @@
       <c r="H153">
         <v>318</v>
       </c>
-      <c r="J153" s="1">
+      <c r="J153" s="2">
         <v>46482</v>
       </c>
       <c r="K153" t="b">
@@ -6404,7 +6430,7 @@
       <c r="H154">
         <v>332</v>
       </c>
-      <c r="J154" s="1">
+      <c r="J154" s="2">
         <v>46490</v>
       </c>
       <c r="K154" t="b">
@@ -6436,7 +6462,7 @@
       <c r="H155">
         <v>332</v>
       </c>
-      <c r="J155" s="1">
+      <c r="J155" s="2">
         <v>46490</v>
       </c>
       <c r="K155" t="b">
@@ -6468,7 +6494,7 @@
       <c r="H156">
         <v>378</v>
       </c>
-      <c r="J156" s="1">
+      <c r="J156" s="2">
         <v>46603</v>
       </c>
       <c r="K156" t="b">
@@ -6500,7 +6526,7 @@
       <c r="H157">
         <v>385</v>
       </c>
-      <c r="J157" s="1">
+      <c r="J157" s="2">
         <v>46526</v>
       </c>
       <c r="K157" t="b">
@@ -6532,7 +6558,7 @@
       <c r="H158">
         <v>400</v>
       </c>
-      <c r="J158" s="1">
+      <c r="J158" s="2">
         <v>46643</v>
       </c>
       <c r="K158" t="b">
@@ -6564,7 +6590,7 @@
       <c r="H159">
         <v>459</v>
       </c>
-      <c r="J159" s="1">
+      <c r="J159" s="2">
         <v>46568</v>
       </c>
       <c r="K159" t="b">
@@ -6596,7 +6622,7 @@
       <c r="H160">
         <v>488</v>
       </c>
-      <c r="J160" s="1">
+      <c r="J160" s="2">
         <v>46190</v>
       </c>
       <c r="K160" t="b">
@@ -6628,7 +6654,7 @@
       <c r="H161">
         <v>721</v>
       </c>
-      <c r="J161" s="1">
+      <c r="J161" s="2">
         <v>46358</v>
       </c>
       <c r="K161" t="b">
@@ -6660,7 +6686,7 @@
       <c r="H162">
         <v>721</v>
       </c>
-      <c r="J162" s="1">
+      <c r="J162" s="2">
         <v>46358</v>
       </c>
       <c r="K162" t="b">
@@ -6692,7 +6718,7 @@
       <c r="H163">
         <v>850</v>
       </c>
-      <c r="J163" s="1">
+      <c r="J163" s="2">
         <v>46374</v>
       </c>
       <c r="K163" t="b">
@@ -6724,7 +6750,7 @@
       <c r="H164">
         <v>850</v>
       </c>
-      <c r="J164" s="1">
+      <c r="J164" s="2">
         <v>46374</v>
       </c>
       <c r="K164" t="b">
@@ -6756,7 +6782,7 @@
       <c r="H165">
         <v>1661</v>
       </c>
-      <c r="J165" s="1">
+      <c r="J165" s="2">
         <v>46529</v>
       </c>
       <c r="K165" t="b">
@@ -6788,7 +6814,7 @@
       <c r="H166">
         <v>1661</v>
       </c>
-      <c r="J166" s="1">
+      <c r="J166" s="2">
         <v>46529</v>
       </c>
       <c r="K166" t="b">
@@ -6820,7 +6846,7 @@
       <c r="H167">
         <v>25565</v>
       </c>
-      <c r="J167" s="1">
+      <c r="J167" s="2">
         <v>46190</v>
       </c>
       <c r="K167" t="b">
@@ -6852,7 +6878,7 @@
       <c r="H168">
         <v>25567</v>
       </c>
-      <c r="J168" s="1">
+      <c r="J168" s="2">
         <v>46190</v>
       </c>
       <c r="K168" t="b">
@@ -6884,7 +6910,7 @@
       <c r="H169">
         <v>31293</v>
       </c>
-      <c r="J169" s="1">
+      <c r="J169" s="2">
         <v>46190</v>
       </c>
       <c r="K169" t="b">

--- a/Coordenadoria/02_Dados_Tratados/base_vencimentos_tratada.xlsx
+++ b/Coordenadoria/02_Dados_Tratados/base_vencimentos_tratada.xlsx
@@ -953,16 +953,8 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -978,7 +970,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -986,30 +978,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1309,37 +1283,37 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1368,7 +1342,7 @@
       <c r="H2">
         <v>-4349.4</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J2" s="1">
         <v>39285</v>
       </c>
       <c r="K2" t="b">
@@ -1400,7 +1374,7 @@
       <c r="H3">
         <v>-2354.2</v>
       </c>
-      <c r="J3" s="2">
+      <c r="J3" s="1">
         <v>40669</v>
       </c>
       <c r="K3" t="b">
@@ -1432,7 +1406,7 @@
       <c r="H4">
         <v>-922.4</v>
       </c>
-      <c r="J4" s="2">
+      <c r="J4" s="1">
         <v>40669</v>
       </c>
       <c r="K4" t="b">
@@ -1464,7 +1438,7 @@
       <c r="H5">
         <v>-879.8</v>
       </c>
-      <c r="J5" s="2">
+      <c r="J5" s="1">
         <v>44884</v>
       </c>
       <c r="K5" t="b">
@@ -1496,7 +1470,7 @@
       <c r="H6">
         <v>-536.4</v>
       </c>
-      <c r="J6" s="2">
+      <c r="J6" s="1">
         <v>43855</v>
       </c>
       <c r="K6" t="b">
@@ -1528,7 +1502,7 @@
       <c r="H7">
         <v>-484.3</v>
       </c>
-      <c r="J7" s="2">
+      <c r="J7" s="1">
         <v>45804</v>
       </c>
       <c r="K7" t="b">
@@ -1560,7 +1534,7 @@
       <c r="H8">
         <v>-482.8</v>
       </c>
-      <c r="J8" s="2">
+      <c r="J8" s="1">
         <v>45804</v>
       </c>
       <c r="K8" t="b">
@@ -1592,7 +1566,7 @@
       <c r="H9">
         <v>-466.1</v>
       </c>
-      <c r="J9" s="2">
+      <c r="J9" s="1">
         <v>46014</v>
       </c>
       <c r="K9" t="b">
@@ -1624,7 +1598,7 @@
       <c r="H10">
         <v>-463.8</v>
       </c>
-      <c r="J10" s="2">
+      <c r="J10" s="1">
         <v>40979</v>
       </c>
       <c r="K10" t="b">
@@ -1656,7 +1630,7 @@
       <c r="H11">
         <v>-463.3</v>
       </c>
-      <c r="J11" s="2">
+      <c r="J11" s="1">
         <v>46014</v>
       </c>
       <c r="K11" t="b">
@@ -1688,7 +1662,7 @@
       <c r="H12">
         <v>-391.8</v>
       </c>
-      <c r="J12" s="2">
+      <c r="J12" s="1">
         <v>42769</v>
       </c>
       <c r="K12" t="b">
@@ -1720,7 +1694,7 @@
       <c r="H13">
         <v>-390</v>
       </c>
-      <c r="J13" s="2">
+      <c r="J13" s="1">
         <v>32786</v>
       </c>
       <c r="K13" t="b">
@@ -1752,7 +1726,7 @@
       <c r="H14">
         <v>-211.2</v>
       </c>
-      <c r="J14" s="2">
+      <c r="J14" s="1">
         <v>34700</v>
       </c>
       <c r="K14" t="b">
@@ -1784,7 +1758,7 @@
       <c r="H15">
         <v>-176</v>
       </c>
-      <c r="J15" s="2">
+      <c r="J15" s="1">
         <v>41204</v>
       </c>
       <c r="K15" t="b">
@@ -1816,7 +1790,7 @@
       <c r="H16">
         <v>-159.2</v>
       </c>
-      <c r="J16" s="2">
+      <c r="J16" s="1">
         <v>46111</v>
       </c>
       <c r="K16" t="b">
@@ -1848,7 +1822,7 @@
       <c r="H17">
         <v>-159.2</v>
       </c>
-      <c r="J17" s="2">
+      <c r="J17" s="1">
         <v>46111</v>
       </c>
       <c r="K17" t="b">
@@ -1880,7 +1854,7 @@
       <c r="H18">
         <v>-159.2</v>
       </c>
-      <c r="J18" s="2">
+      <c r="J18" s="1">
         <v>46111</v>
       </c>
       <c r="K18" t="b">
@@ -1912,7 +1886,7 @@
       <c r="H19">
         <v>-159.2</v>
       </c>
-      <c r="J19" s="2">
+      <c r="J19" s="1">
         <v>46111</v>
       </c>
       <c r="K19" t="b">
@@ -1944,7 +1918,7 @@
       <c r="H20">
         <v>-101.6</v>
       </c>
-      <c r="J20" s="2">
+      <c r="J20" s="1">
         <v>46161</v>
       </c>
       <c r="K20" t="b">
@@ -1976,7 +1950,7 @@
       <c r="H21">
         <v>-69.7</v>
       </c>
-      <c r="J21" s="2">
+      <c r="J21" s="1">
         <v>46241</v>
       </c>
       <c r="K21" t="b">
@@ -2008,7 +1982,7 @@
       <c r="H22">
         <v>-61.8</v>
       </c>
-      <c r="J22" s="2">
+      <c r="J22" s="1">
         <v>46242</v>
       </c>
       <c r="K22" t="b">
@@ -2040,7 +2014,7 @@
       <c r="H23">
         <v>-53.5</v>
       </c>
-      <c r="J23" s="2">
+      <c r="J23" s="1">
         <v>46255</v>
       </c>
       <c r="K23" t="b">
@@ -2072,7 +2046,7 @@
       <c r="H24">
         <v>-10</v>
       </c>
-      <c r="J24" s="2">
+      <c r="J24" s="1">
         <v>46276</v>
       </c>
       <c r="K24" t="b">
@@ -2104,7 +2078,7 @@
       <c r="H25">
         <v>-10</v>
       </c>
-      <c r="J25" s="2">
+      <c r="J25" s="1">
         <v>46276</v>
       </c>
       <c r="K25" t="b">
@@ -2136,7 +2110,7 @@
       <c r="H26">
         <v>-7.4</v>
       </c>
-      <c r="J26" s="2">
+      <c r="J26" s="1">
         <v>46269</v>
       </c>
       <c r="K26" t="b">
@@ -2168,7 +2142,7 @@
       <c r="H27">
         <v>-6.3</v>
       </c>
-      <c r="J27" s="2">
+      <c r="J27" s="1">
         <v>46236</v>
       </c>
       <c r="K27" t="b">
@@ -2200,7 +2174,7 @@
       <c r="H28">
         <v>0</v>
       </c>
-      <c r="J28" s="2">
+      <c r="J28" s="1">
         <v>46282</v>
       </c>
       <c r="K28" t="b">
@@ -2232,7 +2206,7 @@
       <c r="H29">
         <v>7.7</v>
       </c>
-      <c r="J29" s="2">
+      <c r="J29" s="1">
         <v>46295</v>
       </c>
       <c r="K29" t="b">
@@ -2264,7 +2238,7 @@
       <c r="H30">
         <v>9.800000000000001</v>
       </c>
-      <c r="J30" s="2">
+      <c r="J30" s="1">
         <v>46295</v>
       </c>
       <c r="K30" t="b">
@@ -2296,7 +2270,7 @@
       <c r="H31">
         <v>10.9</v>
       </c>
-      <c r="J31" s="2">
+      <c r="J31" s="1">
         <v>46295</v>
       </c>
       <c r="K31" t="b">
@@ -2328,7 +2302,7 @@
       <c r="H32">
         <v>21.8</v>
       </c>
-      <c r="J32" s="2">
+      <c r="J32" s="1">
         <v>46404</v>
       </c>
       <c r="K32" t="b">
@@ -2360,7 +2334,7 @@
       <c r="H33">
         <v>33.9</v>
       </c>
-      <c r="J33" s="2">
+      <c r="J33" s="1">
         <v>46434</v>
       </c>
       <c r="K33" t="b">
@@ -2392,7 +2366,7 @@
       <c r="H34">
         <v>42.8</v>
       </c>
-      <c r="J34" s="2">
+      <c r="J34" s="1">
         <v>46385</v>
       </c>
       <c r="K34" t="b">
@@ -2424,7 +2398,7 @@
       <c r="H35">
         <v>52.7</v>
       </c>
-      <c r="J35" s="2">
+      <c r="J35" s="1">
         <v>46337</v>
       </c>
       <c r="K35" t="b">
@@ -2456,7 +2430,7 @@
       <c r="H36">
         <v>57.5</v>
       </c>
-      <c r="J36" s="2">
+      <c r="J36" s="1">
         <v>46493</v>
       </c>
       <c r="K36" t="b">
@@ -2488,7 +2462,7 @@
       <c r="H37">
         <v>71</v>
       </c>
-      <c r="J37" s="2">
+      <c r="J37" s="1">
         <v>46527</v>
       </c>
       <c r="K37" t="b">
@@ -2520,7 +2494,7 @@
       <c r="H38">
         <v>73</v>
       </c>
-      <c r="J38" s="2">
+      <c r="J38" s="1">
         <v>46532</v>
       </c>
       <c r="K38" t="b">
@@ -2552,7 +2526,7 @@
       <c r="H39">
         <v>82</v>
       </c>
-      <c r="J39" s="2">
+      <c r="J39" s="1">
         <v>46389</v>
       </c>
       <c r="K39" t="b">
@@ -2584,7 +2558,7 @@
       <c r="H40">
         <v>107.1</v>
       </c>
-      <c r="J40" s="2">
+      <c r="J40" s="1">
         <v>46338</v>
       </c>
       <c r="K40" t="b">
@@ -2616,7 +2590,7 @@
       <c r="H41">
         <v>109.8</v>
       </c>
-      <c r="J41" s="2">
+      <c r="J41" s="1">
         <v>46337</v>
       </c>
       <c r="K41" t="b">
@@ -2648,7 +2622,7 @@
       <c r="H42">
         <v>112.9</v>
       </c>
-      <c r="J42" s="2">
+      <c r="J42" s="1">
         <v>46401</v>
       </c>
       <c r="K42" t="b">
@@ -2680,7 +2654,7 @@
       <c r="H43">
         <v>121.9</v>
       </c>
-      <c r="J43" s="2">
+      <c r="J43" s="1">
         <v>46412</v>
       </c>
       <c r="K43" t="b">
@@ -2712,7 +2686,7 @@
       <c r="H44">
         <v>135.1</v>
       </c>
-      <c r="J44" s="2">
+      <c r="J44" s="1">
         <v>46353</v>
       </c>
       <c r="K44" t="b">
@@ -2744,7 +2718,7 @@
       <c r="H45">
         <v>136.2</v>
       </c>
-      <c r="J45" s="2">
+      <c r="J45" s="1">
         <v>46419</v>
       </c>
       <c r="K45" t="b">
@@ -2776,7 +2750,7 @@
       <c r="H46">
         <v>138.8</v>
       </c>
-      <c r="J46" s="2">
+      <c r="J46" s="1">
         <v>46353</v>
       </c>
       <c r="K46" t="b">
@@ -2808,7 +2782,7 @@
       <c r="H47">
         <v>140.1</v>
       </c>
-      <c r="J47" s="2">
+      <c r="J47" s="1">
         <v>46355</v>
       </c>
       <c r="K47" t="b">
@@ -2840,7 +2814,7 @@
       <c r="H48">
         <v>141.6</v>
       </c>
-      <c r="J48" s="2">
+      <c r="J48" s="1">
         <v>46355</v>
       </c>
       <c r="K48" t="b">
@@ -2872,7 +2846,7 @@
       <c r="H49">
         <v>161.2</v>
       </c>
-      <c r="J49" s="2">
+      <c r="J49" s="1">
         <v>46394</v>
       </c>
       <c r="K49" t="b">
@@ -2904,7 +2878,7 @@
       <c r="H50">
         <v>170.3</v>
       </c>
-      <c r="J50" s="2">
+      <c r="J50" s="1">
         <v>46370</v>
       </c>
       <c r="K50" t="b">
@@ -2936,7 +2910,7 @@
       <c r="H51">
         <v>177.4</v>
       </c>
-      <c r="J51" s="2">
+      <c r="J51" s="1">
         <v>46487</v>
       </c>
       <c r="K51" t="b">
@@ -2968,7 +2942,7 @@
       <c r="H52">
         <v>184.1</v>
       </c>
-      <c r="J52" s="2">
+      <c r="J52" s="1">
         <v>46358</v>
       </c>
       <c r="K52" t="b">
@@ -3000,7 +2974,7 @@
       <c r="H53">
         <v>199.3</v>
       </c>
-      <c r="J53" s="2">
+      <c r="J53" s="1">
         <v>46433</v>
       </c>
       <c r="K53" t="b">
@@ -3032,7 +3006,7 @@
       <c r="H54">
         <v>200</v>
       </c>
-      <c r="J54" s="2">
+      <c r="J54" s="1">
         <v>46367</v>
       </c>
       <c r="K54" t="b">
@@ -3064,7 +3038,7 @@
       <c r="H55">
         <v>203.6</v>
       </c>
-      <c r="J55" s="2">
+      <c r="J55" s="1">
         <v>46388</v>
       </c>
       <c r="K55" t="b">
@@ -3096,7 +3070,7 @@
       <c r="H56">
         <v>207.6</v>
       </c>
-      <c r="J56" s="2">
+      <c r="J56" s="1">
         <v>46391</v>
       </c>
       <c r="K56" t="b">
@@ -3128,7 +3102,7 @@
       <c r="H57">
         <v>226.1</v>
       </c>
-      <c r="J57" s="2">
+      <c r="J57" s="1">
         <v>46442</v>
       </c>
       <c r="K57" t="b">
@@ -3160,7 +3134,7 @@
       <c r="H58">
         <v>277</v>
       </c>
-      <c r="J58" s="2">
+      <c r="J58" s="1">
         <v>46461</v>
       </c>
       <c r="K58" t="b">
@@ -3192,7 +3166,7 @@
       <c r="H59">
         <v>280.6</v>
       </c>
-      <c r="J59" s="2">
+      <c r="J59" s="1">
         <v>46409</v>
       </c>
       <c r="K59" t="b">
@@ -3227,7 +3201,7 @@
       <c r="I60" t="s">
         <v>287</v>
       </c>
-      <c r="J60" s="2">
+      <c r="J60" s="1">
         <v>36557</v>
       </c>
       <c r="K60" t="b">
@@ -3262,7 +3236,7 @@
       <c r="I61" t="s">
         <v>288</v>
       </c>
-      <c r="J61" s="2">
+      <c r="J61" s="1">
         <v>41275</v>
       </c>
       <c r="K61" t="b">
@@ -3297,7 +3271,7 @@
       <c r="I62" t="s">
         <v>289</v>
       </c>
-      <c r="J62" s="2">
+      <c r="J62" s="1">
         <v>45380</v>
       </c>
       <c r="K62" t="b">
@@ -3332,7 +3306,7 @@
       <c r="I63" t="s">
         <v>290</v>
       </c>
-      <c r="J63" s="2">
+      <c r="J63" s="1">
         <v>45421</v>
       </c>
       <c r="K63" t="b">
@@ -3367,7 +3341,7 @@
       <c r="I64" t="s">
         <v>290</v>
       </c>
-      <c r="J64" s="2">
+      <c r="J64" s="1">
         <v>45428</v>
       </c>
       <c r="K64" t="b">
@@ -3402,7 +3376,7 @@
       <c r="I65" t="s">
         <v>291</v>
       </c>
-      <c r="J65" s="2">
+      <c r="J65" s="1">
         <v>45490</v>
       </c>
       <c r="K65" t="b">
@@ -3437,7 +3411,7 @@
       <c r="I66" t="s">
         <v>292</v>
       </c>
-      <c r="J66" s="2">
+      <c r="J66" s="1">
         <v>45566</v>
       </c>
       <c r="K66" t="b">
@@ -3472,7 +3446,7 @@
       <c r="I67" t="s">
         <v>293</v>
       </c>
-      <c r="J67" s="2">
+      <c r="J67" s="1">
         <v>45986</v>
       </c>
       <c r="K67" t="b">
@@ -3507,7 +3481,7 @@
       <c r="I68" t="s">
         <v>294</v>
       </c>
-      <c r="J68" s="2">
+      <c r="J68" s="1">
         <v>46197</v>
       </c>
       <c r="K68" t="b">
@@ -3542,7 +3516,7 @@
       <c r="I69" t="s">
         <v>294</v>
       </c>
-      <c r="J69" s="2">
+      <c r="J69" s="1">
         <v>46212</v>
       </c>
       <c r="K69" t="b">
@@ -3577,7 +3551,7 @@
       <c r="I70" t="s">
         <v>295</v>
       </c>
-      <c r="J70" s="2">
+      <c r="J70" s="1">
         <v>46341</v>
       </c>
       <c r="K70" t="b">
@@ -3612,7 +3586,7 @@
       <c r="I71" t="s">
         <v>295</v>
       </c>
-      <c r="J71" s="2">
+      <c r="J71" s="1">
         <v>46344</v>
       </c>
       <c r="K71" t="b">
@@ -3647,7 +3621,7 @@
       <c r="I72" t="s">
         <v>295</v>
       </c>
-      <c r="J72" s="2">
+      <c r="J72" s="1">
         <v>46360</v>
       </c>
       <c r="K72" t="b">
@@ -3682,7 +3656,7 @@
       <c r="I73" t="s">
         <v>295</v>
       </c>
-      <c r="J73" s="2">
+      <c r="J73" s="1">
         <v>46367</v>
       </c>
       <c r="K73" t="b">
@@ -3717,7 +3691,7 @@
       <c r="I74" t="s">
         <v>295</v>
       </c>
-      <c r="J74" s="2">
+      <c r="J74" s="1">
         <v>46368</v>
       </c>
       <c r="K74" t="b">
@@ -3752,7 +3726,7 @@
       <c r="I75" t="s">
         <v>295</v>
       </c>
-      <c r="J75" s="2">
+      <c r="J75" s="1">
         <v>46374</v>
       </c>
       <c r="K75" t="b">
@@ -3787,7 +3761,7 @@
       <c r="I76" t="s">
         <v>296</v>
       </c>
-      <c r="J76" s="2">
+      <c r="J76" s="1">
         <v>46375</v>
       </c>
       <c r="K76" t="b">
@@ -3822,7 +3796,7 @@
       <c r="I77" t="s">
         <v>296</v>
       </c>
-      <c r="J77" s="2">
+      <c r="J77" s="1">
         <v>46387</v>
       </c>
       <c r="K77" t="b">
@@ -3857,7 +3831,7 @@
       <c r="I78" t="s">
         <v>296</v>
       </c>
-      <c r="J78" s="2">
+      <c r="J78" s="1">
         <v>46387</v>
       </c>
       <c r="K78" t="b">
@@ -3892,7 +3866,7 @@
       <c r="I79" t="s">
         <v>296</v>
       </c>
-      <c r="J79" s="2">
+      <c r="J79" s="1">
         <v>46387</v>
       </c>
       <c r="K79" t="b">
@@ -3927,7 +3901,7 @@
       <c r="I80" t="s">
         <v>296</v>
       </c>
-      <c r="J80" s="2">
+      <c r="J80" s="1">
         <v>46388</v>
       </c>
       <c r="K80" t="b">
@@ -3962,7 +3936,7 @@
       <c r="I81" t="s">
         <v>296</v>
       </c>
-      <c r="J81" s="2">
+      <c r="J81" s="1">
         <v>46401</v>
       </c>
       <c r="K81" t="b">
@@ -3997,7 +3971,7 @@
       <c r="I82" t="s">
         <v>296</v>
       </c>
-      <c r="J82" s="2">
+      <c r="J82" s="1">
         <v>46401</v>
       </c>
       <c r="K82" t="b">
@@ -4032,7 +4006,7 @@
       <c r="I83" t="s">
         <v>296</v>
       </c>
-      <c r="J83" s="2">
+      <c r="J83" s="1">
         <v>46401</v>
       </c>
       <c r="K83" t="b">
@@ -4067,7 +4041,7 @@
       <c r="I84" t="s">
         <v>297</v>
       </c>
-      <c r="J84" s="2">
+      <c r="J84" s="1">
         <v>46412</v>
       </c>
       <c r="K84" t="b">
@@ -4102,7 +4076,7 @@
       <c r="I85" t="s">
         <v>297</v>
       </c>
-      <c r="J85" s="2">
+      <c r="J85" s="1">
         <v>46412</v>
       </c>
       <c r="K85" t="b">
@@ -4137,7 +4111,7 @@
       <c r="I86" t="s">
         <v>297</v>
       </c>
-      <c r="J86" s="2">
+      <c r="J86" s="1">
         <v>46424</v>
       </c>
       <c r="K86" t="b">
@@ -4172,7 +4146,7 @@
       <c r="I87" t="s">
         <v>297</v>
       </c>
-      <c r="J87" s="2">
+      <c r="J87" s="1">
         <v>46427</v>
       </c>
       <c r="K87" t="b">
@@ -4207,7 +4181,7 @@
       <c r="I88" t="s">
         <v>297</v>
       </c>
-      <c r="J88" s="2">
+      <c r="J88" s="1">
         <v>46427</v>
       </c>
       <c r="K88" t="b">
@@ -4242,7 +4216,7 @@
       <c r="I89" t="s">
         <v>298</v>
       </c>
-      <c r="J89" s="2">
+      <c r="J89" s="1">
         <v>46437</v>
       </c>
       <c r="K89" t="b">
@@ -4277,7 +4251,7 @@
       <c r="I90" t="s">
         <v>298</v>
       </c>
-      <c r="J90" s="2">
+      <c r="J90" s="1">
         <v>46451</v>
       </c>
       <c r="K90" t="b">
@@ -4312,7 +4286,7 @@
       <c r="I91" t="s">
         <v>298</v>
       </c>
-      <c r="J91" s="2">
+      <c r="J91" s="1">
         <v>46451</v>
       </c>
       <c r="K91" t="b">
@@ -4347,7 +4321,7 @@
       <c r="I92" t="s">
         <v>298</v>
       </c>
-      <c r="J92" s="2">
+      <c r="J92" s="1">
         <v>46455</v>
       </c>
       <c r="K92" t="b">
@@ -4382,7 +4356,7 @@
       <c r="I93" t="s">
         <v>298</v>
       </c>
-      <c r="J93" s="2">
+      <c r="J93" s="1">
         <v>46456</v>
       </c>
       <c r="K93" t="b">
@@ -4417,7 +4391,7 @@
       <c r="I94" t="s">
         <v>298</v>
       </c>
-      <c r="J94" s="2">
+      <c r="J94" s="1">
         <v>46457</v>
       </c>
       <c r="K94" t="b">
@@ -4452,7 +4426,7 @@
       <c r="I95" t="s">
         <v>298</v>
       </c>
-      <c r="J95" s="2">
+      <c r="J95" s="1">
         <v>46464</v>
       </c>
       <c r="K95" t="b">
@@ -4487,7 +4461,7 @@
       <c r="I96" t="s">
         <v>299</v>
       </c>
-      <c r="J96" s="2">
+      <c r="J96" s="1">
         <v>46470</v>
       </c>
       <c r="K96" t="b">
@@ -4522,7 +4496,7 @@
       <c r="I97" t="s">
         <v>299</v>
       </c>
-      <c r="J97" s="2">
+      <c r="J97" s="1">
         <v>46485</v>
       </c>
       <c r="K97" t="b">
@@ -4557,7 +4531,7 @@
       <c r="I98" t="s">
         <v>300</v>
       </c>
-      <c r="J98" s="2">
+      <c r="J98" s="1">
         <v>46499</v>
       </c>
       <c r="K98" t="b">
@@ -4592,7 +4566,7 @@
       <c r="I99" t="s">
         <v>300</v>
       </c>
-      <c r="J99" s="2">
+      <c r="J99" s="1">
         <v>46504</v>
       </c>
       <c r="K99" t="b">
@@ -4627,7 +4601,7 @@
       <c r="I100" t="s">
         <v>300</v>
       </c>
-      <c r="J100" s="2">
+      <c r="J100" s="1">
         <v>46507</v>
       </c>
       <c r="K100" t="b">
@@ -4662,7 +4636,7 @@
       <c r="I101" t="s">
         <v>300</v>
       </c>
-      <c r="J101" s="2">
+      <c r="J101" s="1">
         <v>46508</v>
       </c>
       <c r="K101" t="b">
@@ -4697,7 +4671,7 @@
       <c r="I102" t="s">
         <v>300</v>
       </c>
-      <c r="J102" s="2">
+      <c r="J102" s="1">
         <v>46512</v>
       </c>
       <c r="K102" t="b">
@@ -4732,7 +4706,7 @@
       <c r="I103" t="s">
         <v>300</v>
       </c>
-      <c r="J103" s="2">
+      <c r="J103" s="1">
         <v>46512</v>
       </c>
       <c r="K103" t="b">
@@ -4767,7 +4741,7 @@
       <c r="I104" t="s">
         <v>301</v>
       </c>
-      <c r="J104" s="2">
+      <c r="J104" s="1">
         <v>46528</v>
       </c>
       <c r="K104" t="b">
@@ -4802,7 +4776,7 @@
       <c r="I105" t="s">
         <v>301</v>
       </c>
-      <c r="J105" s="2">
+      <c r="J105" s="1">
         <v>46529</v>
       </c>
       <c r="K105" t="b">
@@ -4837,7 +4811,7 @@
       <c r="I106" t="s">
         <v>301</v>
       </c>
-      <c r="J106" s="2">
+      <c r="J106" s="1">
         <v>46537</v>
       </c>
       <c r="K106" t="b">
@@ -4872,7 +4846,7 @@
       <c r="I107" t="s">
         <v>301</v>
       </c>
-      <c r="J107" s="2">
+      <c r="J107" s="1">
         <v>46546</v>
       </c>
       <c r="K107" t="b">
@@ -4907,7 +4881,7 @@
       <c r="I108" t="s">
         <v>301</v>
       </c>
-      <c r="J108" s="2">
+      <c r="J108" s="1">
         <v>46547</v>
       </c>
       <c r="K108" t="b">
@@ -4942,7 +4916,7 @@
       <c r="I109" t="s">
         <v>301</v>
       </c>
-      <c r="J109" s="2">
+      <c r="J109" s="1">
         <v>46547</v>
       </c>
       <c r="K109" t="b">
@@ -4977,7 +4951,7 @@
       <c r="I110" t="s">
         <v>301</v>
       </c>
-      <c r="J110" s="2">
+      <c r="J110" s="1">
         <v>46551</v>
       </c>
       <c r="K110" t="b">
@@ -5012,7 +4986,7 @@
       <c r="I111" t="s">
         <v>302</v>
       </c>
-      <c r="J111" s="2">
+      <c r="J111" s="1">
         <v>46560</v>
       </c>
       <c r="K111" t="b">
@@ -5047,7 +5021,7 @@
       <c r="I112" t="s">
         <v>302</v>
       </c>
-      <c r="J112" s="2">
+      <c r="J112" s="1">
         <v>46567</v>
       </c>
       <c r="K112" t="b">
@@ -5082,7 +5056,7 @@
       <c r="I113" t="s">
         <v>302</v>
       </c>
-      <c r="J113" s="2">
+      <c r="J113" s="1">
         <v>46568</v>
       </c>
       <c r="K113" t="b">
@@ -5117,7 +5091,7 @@
       <c r="I114" t="s">
         <v>302</v>
       </c>
-      <c r="J114" s="2">
+      <c r="J114" s="1">
         <v>46578</v>
       </c>
       <c r="K114" t="b">
@@ -5152,7 +5126,7 @@
       <c r="I115" t="s">
         <v>303</v>
       </c>
-      <c r="J115" s="2">
+      <c r="J115" s="1">
         <v>46592</v>
       </c>
       <c r="K115" t="b">
@@ -5187,7 +5161,7 @@
       <c r="I116" t="s">
         <v>303</v>
       </c>
-      <c r="J116" s="2">
+      <c r="J116" s="1">
         <v>46592</v>
       </c>
       <c r="K116" t="b">
@@ -5222,7 +5196,7 @@
       <c r="I117" t="s">
         <v>303</v>
       </c>
-      <c r="J117" s="2">
+      <c r="J117" s="1">
         <v>46603</v>
       </c>
       <c r="K117" t="b">
@@ -5257,7 +5231,7 @@
       <c r="I118" t="s">
         <v>303</v>
       </c>
-      <c r="J118" s="2">
+      <c r="J118" s="1">
         <v>46611</v>
       </c>
       <c r="K118" t="b">
@@ -5292,7 +5266,7 @@
       <c r="I119" t="s">
         <v>304</v>
       </c>
-      <c r="J119" s="2">
+      <c r="J119" s="1">
         <v>46631</v>
       </c>
       <c r="K119" t="b">
@@ -5327,7 +5301,7 @@
       <c r="I120" t="s">
         <v>304</v>
       </c>
-      <c r="J120" s="2">
+      <c r="J120" s="1">
         <v>46645</v>
       </c>
       <c r="K120" t="b">
@@ -5362,7 +5336,7 @@
       <c r="I121" t="s">
         <v>305</v>
       </c>
-      <c r="J121" s="2">
+      <c r="J121" s="1">
         <v>46254</v>
       </c>
       <c r="K121" t="b">
@@ -5397,7 +5371,7 @@
       <c r="I122" t="s">
         <v>306</v>
       </c>
-      <c r="J122" s="2">
+      <c r="J122" s="1">
         <v>46284</v>
       </c>
       <c r="K122" t="b">
@@ -5432,7 +5406,7 @@
       <c r="I123" t="s">
         <v>307</v>
       </c>
-      <c r="J123" s="2">
+      <c r="J123" s="1">
         <v>46296</v>
       </c>
       <c r="K123" t="b">
@@ -5467,7 +5441,7 @@
       <c r="I124" t="s">
         <v>308</v>
       </c>
-      <c r="J124" s="2">
+      <c r="J124" s="1">
         <v>46293</v>
       </c>
       <c r="K124" t="b">
@@ -5502,7 +5476,7 @@
       <c r="I125" t="s">
         <v>309</v>
       </c>
-      <c r="J125" s="2">
+      <c r="J125" s="1">
         <v>46305</v>
       </c>
       <c r="K125" t="b">
@@ -5534,7 +5508,7 @@
       <c r="H126">
         <v>-1476</v>
       </c>
-      <c r="J126" s="2">
+      <c r="J126" s="1">
         <v>43773</v>
       </c>
       <c r="K126" t="b">
@@ -5566,7 +5540,7 @@
       <c r="H127">
         <v>-1469</v>
       </c>
-      <c r="J127" s="2">
+      <c r="J127" s="1">
         <v>43773</v>
       </c>
       <c r="K127" t="b">
@@ -5598,7 +5572,7 @@
       <c r="H128">
         <v>-1250</v>
       </c>
-      <c r="J128" s="2">
+      <c r="J128" s="1">
         <v>45295</v>
       </c>
       <c r="K128" t="b">
@@ -5630,7 +5604,7 @@
       <c r="H129">
         <v>-1089</v>
       </c>
-      <c r="J129" s="2">
+      <c r="J129" s="1">
         <v>45617</v>
       </c>
       <c r="K129" t="b">
@@ -5662,7 +5636,7 @@
       <c r="H130">
         <v>-1021</v>
       </c>
-      <c r="J130" s="2">
+      <c r="J130" s="1">
         <v>45677</v>
       </c>
       <c r="K130" t="b">
@@ -5694,7 +5668,7 @@
       <c r="H131">
         <v>-1000</v>
       </c>
-      <c r="J131" s="2">
+      <c r="J131" s="1">
         <v>44944</v>
       </c>
       <c r="K131" t="b">
@@ -5726,7 +5700,7 @@
       <c r="H132">
         <v>-296</v>
       </c>
-      <c r="J132" s="2">
+      <c r="J132" s="1">
         <v>46092</v>
       </c>
       <c r="K132" t="b">
@@ -5758,7 +5732,7 @@
       <c r="H133">
         <v>-51</v>
       </c>
-      <c r="J133" s="2">
+      <c r="J133" s="1">
         <v>46258</v>
       </c>
       <c r="K133" t="b">
@@ -5790,7 +5764,7 @@
       <c r="H134">
         <v>-49</v>
       </c>
-      <c r="J134" s="2">
+      <c r="J134" s="1">
         <v>46254</v>
       </c>
       <c r="K134" t="b">
@@ -5822,7 +5796,7 @@
       <c r="H135">
         <v>-49</v>
       </c>
-      <c r="J135" s="2">
+      <c r="J135" s="1">
         <v>46254</v>
       </c>
       <c r="K135" t="b">
@@ -5854,7 +5828,7 @@
       <c r="H136">
         <v>43</v>
       </c>
-      <c r="J136" s="2">
+      <c r="J136" s="1">
         <v>46440</v>
       </c>
       <c r="K136" t="b">
@@ -5886,7 +5860,7 @@
       <c r="H137">
         <v>43</v>
       </c>
-      <c r="J137" s="2">
+      <c r="J137" s="1">
         <v>46440</v>
       </c>
       <c r="K137" t="b">
@@ -5918,7 +5892,7 @@
       <c r="H138">
         <v>102</v>
       </c>
-      <c r="J138" s="2">
+      <c r="J138" s="1">
         <v>46463</v>
       </c>
       <c r="K138" t="b">
@@ -5950,7 +5924,7 @@
       <c r="H139">
         <v>106</v>
       </c>
-      <c r="J139" s="2">
+      <c r="J139" s="1">
         <v>46424</v>
       </c>
       <c r="K139" t="b">
@@ -5982,7 +5956,7 @@
       <c r="H140">
         <v>119</v>
       </c>
-      <c r="J140" s="2">
+      <c r="J140" s="1">
         <v>46407</v>
       </c>
       <c r="K140" t="b">
@@ -6014,7 +5988,7 @@
       <c r="H141">
         <v>130</v>
       </c>
-      <c r="J141" s="2">
+      <c r="J141" s="1">
         <v>46416</v>
       </c>
       <c r="K141" t="b">
@@ -6046,7 +6020,7 @@
       <c r="H142">
         <v>152</v>
       </c>
-      <c r="J142" s="2">
+      <c r="J142" s="1">
         <v>46295</v>
       </c>
       <c r="K142" t="b">
@@ -6078,7 +6052,7 @@
       <c r="H143">
         <v>152</v>
       </c>
-      <c r="J143" s="2">
+      <c r="J143" s="1">
         <v>46295</v>
       </c>
       <c r="K143" t="b">
@@ -6110,7 +6084,7 @@
       <c r="H144">
         <v>163</v>
       </c>
-      <c r="J144" s="2">
+      <c r="J144" s="1">
         <v>46592</v>
       </c>
       <c r="K144" t="b">
@@ -6142,7 +6116,7 @@
       <c r="H145">
         <v>172</v>
       </c>
-      <c r="J145" s="2">
+      <c r="J145" s="1">
         <v>46448</v>
       </c>
       <c r="K145" t="b">
@@ -6174,7 +6148,7 @@
       <c r="H146">
         <v>174</v>
       </c>
-      <c r="J146" s="2">
+      <c r="J146" s="1">
         <v>46450</v>
       </c>
       <c r="K146" t="b">
@@ -6206,7 +6180,7 @@
       <c r="H147">
         <v>248</v>
       </c>
-      <c r="J147" s="2">
+      <c r="J147" s="1">
         <v>46571</v>
       </c>
       <c r="K147" t="b">
@@ -6238,7 +6212,7 @@
       <c r="H148">
         <v>270</v>
       </c>
-      <c r="J148" s="2">
+      <c r="J148" s="1">
         <v>46524</v>
       </c>
       <c r="K148" t="b">
@@ -6270,7 +6244,7 @@
       <c r="H149">
         <v>281</v>
       </c>
-      <c r="J149" s="2">
+      <c r="J149" s="1">
         <v>46459</v>
       </c>
       <c r="K149" t="b">
@@ -6302,7 +6276,7 @@
       <c r="H150">
         <v>288</v>
       </c>
-      <c r="J150" s="2">
+      <c r="J150" s="1">
         <v>46531</v>
       </c>
       <c r="K150" t="b">
@@ -6334,7 +6308,7 @@
       <c r="H151">
         <v>294</v>
       </c>
-      <c r="J151" s="2">
+      <c r="J151" s="1">
         <v>46535</v>
       </c>
       <c r="K151" t="b">
@@ -6366,7 +6340,7 @@
       <c r="H152">
         <v>295</v>
       </c>
-      <c r="J152" s="2">
+      <c r="J152" s="1">
         <v>46468</v>
       </c>
       <c r="K152" t="b">
@@ -6398,7 +6372,7 @@
       <c r="H153">
         <v>318</v>
       </c>
-      <c r="J153" s="2">
+      <c r="J153" s="1">
         <v>46482</v>
       </c>
       <c r="K153" t="b">
@@ -6430,7 +6404,7 @@
       <c r="H154">
         <v>332</v>
       </c>
-      <c r="J154" s="2">
+      <c r="J154" s="1">
         <v>46490</v>
       </c>
       <c r="K154" t="b">
@@ -6462,7 +6436,7 @@
       <c r="H155">
         <v>332</v>
       </c>
-      <c r="J155" s="2">
+      <c r="J155" s="1">
         <v>46490</v>
       </c>
       <c r="K155" t="b">
@@ -6494,7 +6468,7 @@
       <c r="H156">
         <v>378</v>
       </c>
-      <c r="J156" s="2">
+      <c r="J156" s="1">
         <v>46603</v>
       </c>
       <c r="K156" t="b">
@@ -6526,7 +6500,7 @@
       <c r="H157">
         <v>385</v>
       </c>
-      <c r="J157" s="2">
+      <c r="J157" s="1">
         <v>46526</v>
       </c>
       <c r="K157" t="b">
@@ -6558,7 +6532,7 @@
       <c r="H158">
         <v>400</v>
       </c>
-      <c r="J158" s="2">
+      <c r="J158" s="1">
         <v>46643</v>
       </c>
       <c r="K158" t="b">
@@ -6590,7 +6564,7 @@
       <c r="H159">
         <v>459</v>
       </c>
-      <c r="J159" s="2">
+      <c r="J159" s="1">
         <v>46568</v>
       </c>
       <c r="K159" t="b">
@@ -6622,7 +6596,7 @@
       <c r="H160">
         <v>488</v>
       </c>
-      <c r="J160" s="2">
+      <c r="J160" s="1">
         <v>46190</v>
       </c>
       <c r="K160" t="b">
@@ -6654,7 +6628,7 @@
       <c r="H161">
         <v>721</v>
       </c>
-      <c r="J161" s="2">
+      <c r="J161" s="1">
         <v>46358</v>
       </c>
       <c r="K161" t="b">
@@ -6686,7 +6660,7 @@
       <c r="H162">
         <v>721</v>
       </c>
-      <c r="J162" s="2">
+      <c r="J162" s="1">
         <v>46358</v>
       </c>
       <c r="K162" t="b">
@@ -6718,7 +6692,7 @@
       <c r="H163">
         <v>850</v>
       </c>
-      <c r="J163" s="2">
+      <c r="J163" s="1">
         <v>46374</v>
       </c>
       <c r="K163" t="b">
@@ -6750,7 +6724,7 @@
       <c r="H164">
         <v>850</v>
       </c>
-      <c r="J164" s="2">
+      <c r="J164" s="1">
         <v>46374</v>
       </c>
       <c r="K164" t="b">
@@ -6782,7 +6756,7 @@
       <c r="H165">
         <v>1661</v>
       </c>
-      <c r="J165" s="2">
+      <c r="J165" s="1">
         <v>46529</v>
       </c>
       <c r="K165" t="b">
@@ -6814,7 +6788,7 @@
       <c r="H166">
         <v>1661</v>
       </c>
-      <c r="J166" s="2">
+      <c r="J166" s="1">
         <v>46529</v>
       </c>
       <c r="K166" t="b">
@@ -6846,7 +6820,7 @@
       <c r="H167">
         <v>25565</v>
       </c>
-      <c r="J167" s="2">
+      <c r="J167" s="1">
         <v>46190</v>
       </c>
       <c r="K167" t="b">
@@ -6878,7 +6852,7 @@
       <c r="H168">
         <v>25567</v>
       </c>
-      <c r="J168" s="2">
+      <c r="J168" s="1">
         <v>46190</v>
       </c>
       <c r="K168" t="b">
@@ -6910,7 +6884,7 @@
       <c r="H169">
         <v>31293</v>
       </c>
-      <c r="J169" s="2">
+      <c r="J169" s="1">
         <v>46190</v>
       </c>
       <c r="K169" t="b">

--- a/Coordenadoria/02_Dados_Tratados/base_vencimentos_tratada.xlsx
+++ b/Coordenadoria/02_Dados_Tratados/base_vencimentos_tratada.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1085" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1182" uniqueCount="339">
   <si>
     <t>matricula</t>
   </si>
@@ -49,9 +49,6 @@
     <t>vencido</t>
   </si>
   <si>
-    <t>A000AH4R</t>
-  </si>
-  <si>
     <t>PZL/10/039</t>
   </si>
   <si>
@@ -70,175 +67,379 @@
     <t>18B464</t>
   </si>
   <si>
+    <t>PC-E17377</t>
+  </si>
+  <si>
+    <t>PZL/12/085</t>
+  </si>
+  <si>
+    <t>PC-EPC0431</t>
+  </si>
+  <si>
+    <t>PCE-PC2050</t>
+  </si>
+  <si>
+    <t>5H725</t>
+  </si>
+  <si>
+    <t>6X312</t>
+  </si>
+  <si>
+    <t>5X424</t>
+  </si>
+  <si>
+    <t>5X499</t>
+  </si>
+  <si>
+    <t>A000CT12</t>
+  </si>
+  <si>
+    <t>PCE-PC0797</t>
+  </si>
+  <si>
+    <t>CRAZAFLZ243</t>
+  </si>
+  <si>
     <t>PCE-PC2055</t>
   </si>
   <si>
-    <t>PZL/12/085</t>
-  </si>
-  <si>
-    <t>PC-E17377</t>
-  </si>
-  <si>
-    <t>PC-EPC0431</t>
-  </si>
-  <si>
-    <t>PCE-PC2050</t>
-  </si>
-  <si>
-    <t>5X499</t>
-  </si>
-  <si>
-    <t>6X312</t>
-  </si>
-  <si>
-    <t>A000CT12</t>
-  </si>
-  <si>
-    <t>5H725</t>
-  </si>
-  <si>
-    <t>PCE-PC0797</t>
-  </si>
-  <si>
-    <t>CRAZAFLZ243</t>
-  </si>
-  <si>
     <t>PCE-PC2358</t>
   </si>
   <si>
+    <t>16829339.0</t>
+  </si>
+  <si>
+    <t>090520028327B</t>
+  </si>
+  <si>
+    <t>PCE-PC2223</t>
+  </si>
+  <si>
+    <t>PCE-PC1666</t>
+  </si>
+  <si>
+    <t>26.0</t>
+  </si>
+  <si>
+    <t>9757.0</t>
+  </si>
+  <si>
+    <t>PCE-PC2261</t>
+  </si>
+  <si>
+    <t>PCE-PC0776</t>
+  </si>
+  <si>
+    <t>PCE-PC1211</t>
+  </si>
+  <si>
+    <t>PCE-PC1570</t>
+  </si>
+  <si>
+    <t>905200298400.0</t>
+  </si>
+  <si>
+    <t>17176905.0</t>
+  </si>
+  <si>
+    <t>PZLL010SB</t>
+  </si>
+  <si>
+    <t>4572.0</t>
+  </si>
+  <si>
+    <t>338.0</t>
+  </si>
+  <si>
+    <t>PCE-PC0743</t>
+  </si>
+  <si>
+    <t>A0037CAC</t>
+  </si>
+  <si>
+    <t>PCE-PC1850</t>
+  </si>
+  <si>
+    <t>090520028EC43</t>
+  </si>
+  <si>
+    <t>16A856</t>
+  </si>
+  <si>
+    <t>510086.0</t>
+  </si>
+  <si>
+    <t>PCE-PC1835</t>
+  </si>
+  <si>
+    <t>9804953.0</t>
+  </si>
+  <si>
+    <t>9601404.0</t>
+  </si>
+  <si>
+    <t>9804951.0</t>
+  </si>
+  <si>
+    <t>9038.0</t>
+  </si>
+  <si>
+    <t>16799705.0</t>
+  </si>
+  <si>
+    <t>11200478.0</t>
+  </si>
+  <si>
+    <t>5784237.0</t>
+  </si>
+  <si>
+    <t>11100371.0</t>
+  </si>
+  <si>
+    <t>11A</t>
+  </si>
+  <si>
+    <t>1705.0</t>
+  </si>
+  <si>
     <t>5784241.0</t>
   </si>
   <si>
-    <t>PCE-PC0743</t>
-  </si>
-  <si>
-    <t>090520028327B</t>
-  </si>
-  <si>
-    <t>PCE-PC1666</t>
-  </si>
-  <si>
-    <t>090520028EC43</t>
-  </si>
-  <si>
-    <t>PCE-PC1211</t>
-  </si>
-  <si>
-    <t>PCE-PC1570</t>
-  </si>
-  <si>
-    <t>16829339.0</t>
-  </si>
-  <si>
-    <t>26.0</t>
-  </si>
-  <si>
-    <t>2223.0</t>
-  </si>
-  <si>
-    <t>905200298400.0</t>
-  </si>
-  <si>
-    <t>PCE-PC2261</t>
-  </si>
-  <si>
-    <t>17176905.0</t>
-  </si>
-  <si>
-    <t>4572.0</t>
-  </si>
-  <si>
-    <t>338.0</t>
-  </si>
-  <si>
-    <t>9757.0</t>
-  </si>
-  <si>
-    <t>10000618.0</t>
-  </si>
-  <si>
-    <t>11100371.0</t>
-  </si>
-  <si>
-    <t>PZLL010SB</t>
-  </si>
-  <si>
-    <t>9038.0</t>
-  </si>
-  <si>
-    <t>A0037CAC</t>
-  </si>
-  <si>
-    <t>9601404.0</t>
-  </si>
-  <si>
     <t>9802842.0</t>
   </si>
   <si>
-    <t>16A856</t>
-  </si>
-  <si>
-    <t>16799705.0</t>
-  </si>
-  <si>
-    <t>9804953.0</t>
-  </si>
-  <si>
     <t>862.0</t>
   </si>
   <si>
-    <t>9804951.0</t>
-  </si>
-  <si>
-    <t>11200478.0</t>
-  </si>
-  <si>
     <t>11402681.0</t>
   </si>
   <si>
     <t>7475.0</t>
   </si>
   <si>
-    <t>11A</t>
-  </si>
-  <si>
-    <t>1705.0</t>
+    <t>JHZ-16-047</t>
   </si>
   <si>
     <t>PZL/12/060</t>
   </si>
   <si>
-    <t>JHZ-16-047</t>
+    <t>C65807</t>
+  </si>
+  <si>
+    <t>7458.0</t>
   </si>
   <si>
     <t>2K221</t>
   </si>
   <si>
+    <t>1001328-033</t>
+  </si>
+  <si>
+    <t>391730-020</t>
+  </si>
+  <si>
+    <t>110076.0</t>
+  </si>
+  <si>
+    <t>170-07437</t>
+  </si>
+  <si>
+    <t>B10811395</t>
+  </si>
+  <si>
+    <t>10603746.0</t>
+  </si>
+  <si>
+    <t>10BC80</t>
+  </si>
+  <si>
+    <t>100A</t>
+  </si>
+  <si>
+    <t>1779.0</t>
+  </si>
+  <si>
+    <t>D00397933</t>
+  </si>
+  <si>
+    <t>9704228.0</t>
+  </si>
+  <si>
+    <t>392140-009</t>
+  </si>
+  <si>
+    <t>A-24022576</t>
+  </si>
+  <si>
+    <t>70.0</t>
+  </si>
+  <si>
+    <t>PCE-PC2257</t>
+  </si>
+  <si>
+    <t>157.0</t>
+  </si>
+  <si>
+    <t>44.0</t>
+  </si>
+  <si>
+    <t>61.0</t>
+  </si>
+  <si>
+    <t>71.0</t>
+  </si>
+  <si>
+    <t>393069-038</t>
+  </si>
+  <si>
+    <t>G-45677217</t>
+  </si>
+  <si>
+    <t>7869.0</t>
+  </si>
+  <si>
+    <t>D-00397388</t>
+  </si>
+  <si>
+    <t>B10811727</t>
+  </si>
+  <si>
+    <t>73.0</t>
+  </si>
+  <si>
+    <t>240.0</t>
+  </si>
+  <si>
+    <t>D00398015</t>
+  </si>
+  <si>
+    <t>248.0</t>
+  </si>
+  <si>
+    <t>8.0</t>
+  </si>
+  <si>
+    <t>E09393184</t>
+  </si>
+  <si>
+    <t>210-10043</t>
+  </si>
+  <si>
+    <t>D00398016</t>
+  </si>
+  <si>
+    <t>D00397796</t>
+  </si>
+  <si>
+    <t>9600123.0</t>
+  </si>
+  <si>
+    <t>B10811720</t>
+  </si>
+  <si>
     <t>D-0397408</t>
   </si>
   <si>
-    <t>391730-020</t>
-  </si>
-  <si>
-    <t>110076.0</t>
-  </si>
-  <si>
-    <t>170-07437</t>
-  </si>
-  <si>
-    <t>B10811395</t>
-  </si>
-  <si>
-    <t>10603746.0</t>
-  </si>
-  <si>
-    <t>10BC80</t>
-  </si>
-  <si>
-    <t>100A</t>
-  </si>
-  <si>
-    <t>1779.0</t>
+    <t>D-00397408</t>
+  </si>
+  <si>
+    <t>7044.0</t>
+  </si>
+  <si>
+    <t>210-10039</t>
+  </si>
+  <si>
+    <t>2986900100469.0</t>
+  </si>
+  <si>
+    <t>3726.0</t>
+  </si>
+  <si>
+    <t>I-01810674</t>
+  </si>
+  <si>
+    <t>210-13181</t>
+  </si>
+  <si>
+    <t>11100370.0</t>
+  </si>
+  <si>
+    <t>7911.0</t>
+  </si>
+  <si>
+    <t>10000617.0</t>
+  </si>
+  <si>
+    <t>D00398018</t>
+  </si>
+  <si>
+    <t>2986900100392.0</t>
+  </si>
+  <si>
+    <t>2986900100467.0</t>
+  </si>
+  <si>
+    <t>2986900100513.0</t>
+  </si>
+  <si>
+    <t>960707.0</t>
+  </si>
+  <si>
+    <t>210-10042</t>
+  </si>
+  <si>
+    <t>T-24634412</t>
+  </si>
+  <si>
+    <t>D00397793</t>
+  </si>
+  <si>
+    <t>1000186-001</t>
+  </si>
+  <si>
+    <t>399407-032</t>
+  </si>
+  <si>
+    <t>397401-005</t>
+  </si>
+  <si>
+    <t>D58293589</t>
+  </si>
+  <si>
+    <t>98053601.0</t>
+  </si>
+  <si>
+    <t>399910-010</t>
+  </si>
+  <si>
+    <t>396315-038</t>
+  </si>
+  <si>
+    <t>1659.0</t>
+  </si>
+  <si>
+    <t>F66943</t>
+  </si>
+  <si>
+    <t>120677.0</t>
+  </si>
+  <si>
+    <t>PCE-PC1002</t>
+  </si>
+  <si>
+    <t>9803650.0</t>
+  </si>
+  <si>
+    <t>A87528</t>
+  </si>
+  <si>
+    <t>7572.0</t>
+  </si>
+  <si>
+    <t>8737.0</t>
+  </si>
+  <si>
+    <t>1012821-019</t>
   </si>
   <si>
     <t>929.0</t>
@@ -247,168 +448,6 @@
     <t>D58293653</t>
   </si>
   <si>
-    <t>A-24022576</t>
-  </si>
-  <si>
-    <t>70.0</t>
-  </si>
-  <si>
-    <t>PCE-PC2257</t>
-  </si>
-  <si>
-    <t>PCE-PC0776</t>
-  </si>
-  <si>
-    <t>157.0</t>
-  </si>
-  <si>
-    <t>44.0</t>
-  </si>
-  <si>
-    <t>61.0</t>
-  </si>
-  <si>
-    <t>71.0</t>
-  </si>
-  <si>
-    <t>393069-038</t>
-  </si>
-  <si>
-    <t>G-45677217</t>
-  </si>
-  <si>
-    <t>7869.0</t>
-  </si>
-  <si>
-    <t>D-00397388</t>
-  </si>
-  <si>
-    <t>73.0</t>
-  </si>
-  <si>
-    <t>240.0</t>
-  </si>
-  <si>
-    <t>D00398015</t>
-  </si>
-  <si>
-    <t>248.0</t>
-  </si>
-  <si>
-    <t>8.0</t>
-  </si>
-  <si>
-    <t>E09393184</t>
-  </si>
-  <si>
-    <t>210-10043</t>
-  </si>
-  <si>
-    <t>D00398016</t>
-  </si>
-  <si>
-    <t>D00397796</t>
-  </si>
-  <si>
-    <t>9600123.0</t>
-  </si>
-  <si>
-    <t>B10811720</t>
-  </si>
-  <si>
-    <t>D-00397408</t>
-  </si>
-  <si>
-    <t>7044.0</t>
-  </si>
-  <si>
-    <t>210-10039</t>
-  </si>
-  <si>
-    <t>2986900100469.0</t>
-  </si>
-  <si>
-    <t>3726.0</t>
-  </si>
-  <si>
-    <t>I-01810674</t>
-  </si>
-  <si>
-    <t>210-13181</t>
-  </si>
-  <si>
-    <t>11100370.0</t>
-  </si>
-  <si>
-    <t>912962.0</t>
-  </si>
-  <si>
-    <t>7911.0</t>
-  </si>
-  <si>
-    <t>10000617.0</t>
-  </si>
-  <si>
-    <t>D00398018</t>
-  </si>
-  <si>
-    <t>2986900100392.0</t>
-  </si>
-  <si>
-    <t>2986900100467.0</t>
-  </si>
-  <si>
-    <t>2986900100513.0</t>
-  </si>
-  <si>
-    <t>960707.0</t>
-  </si>
-  <si>
-    <t>210-10042</t>
-  </si>
-  <si>
-    <t>5784239.0</t>
-  </si>
-  <si>
-    <t>T-24634412</t>
-  </si>
-  <si>
-    <t>396315-038</t>
-  </si>
-  <si>
-    <t>D00397793</t>
-  </si>
-  <si>
-    <t>399910-010</t>
-  </si>
-  <si>
-    <t>1000186-001</t>
-  </si>
-  <si>
-    <t>399407-032</t>
-  </si>
-  <si>
-    <t>397401-005</t>
-  </si>
-  <si>
-    <t>D58293589</t>
-  </si>
-  <si>
-    <t>F66943</t>
-  </si>
-  <si>
-    <t>392140-009</t>
-  </si>
-  <si>
-    <t>PCE-PC1002</t>
-  </si>
-  <si>
-    <t>120677.0</t>
-  </si>
-  <si>
-    <t>9803650.0</t>
-  </si>
-  <si>
     <t>2395-05-01 00:00:00</t>
   </si>
   <si>
@@ -424,40 +463,40 @@
     <t>2850.0</t>
   </si>
   <si>
-    <t>488.0</t>
-  </si>
-  <si>
-    <t>7.0</t>
-  </si>
-  <si>
-    <t>2002A</t>
-  </si>
-  <si>
     <t>41.0</t>
   </si>
   <si>
     <t>799.0</t>
   </si>
   <si>
+    <t>2309-05-01 00:00:00</t>
+  </si>
+  <si>
+    <t>3275-05-01 00:00:00</t>
+  </si>
+  <si>
     <t>38.0</t>
   </si>
   <si>
+    <t>2004.0</t>
+  </si>
+  <si>
+    <t>970.0</t>
+  </si>
+  <si>
+    <t>08G</t>
+  </si>
+  <si>
+    <t>B4H-038</t>
+  </si>
+  <si>
     <t>1435-5</t>
   </si>
   <si>
     <t>2913.0</t>
   </si>
   <si>
-    <t>2004.0</t>
-  </si>
-  <si>
-    <t>B4H-038</t>
-  </si>
-  <si>
-    <t>970.0</t>
-  </si>
-  <si>
-    <t>08G</t>
+    <t>650.0</t>
   </si>
   <si>
     <t>5351.0</t>
@@ -469,66 +508,75 @@
     <t>47.0</t>
   </si>
   <si>
+    <t>2890.0</t>
+  </si>
+  <si>
+    <t>2305-05-01 00:00:00</t>
+  </si>
+  <si>
+    <t>822-5</t>
+  </si>
+  <si>
+    <t>272.0</t>
+  </si>
+  <si>
+    <t>B4H-040</t>
+  </si>
+  <si>
     <t>82.0</t>
   </si>
   <si>
+    <t>3481-05-01 00:00:00</t>
+  </si>
+  <si>
     <t>16.0</t>
   </si>
   <si>
-    <t>2890.0</t>
-  </si>
-  <si>
-    <t>2305-05-01 00:00:00</t>
-  </si>
-  <si>
-    <t>822-5</t>
-  </si>
-  <si>
-    <t>3481-05-01 00:00:00</t>
+    <t>AS41538</t>
+  </si>
+  <si>
+    <t>32.0</t>
+  </si>
+  <si>
+    <t>11.0</t>
+  </si>
+  <si>
+    <t>687.0</t>
+  </si>
+  <si>
+    <t>LSEAM3620</t>
+  </si>
+  <si>
+    <t>45.0</t>
+  </si>
+  <si>
+    <t>295.0</t>
+  </si>
+  <si>
+    <t>UNK-01</t>
   </si>
   <si>
     <t>278.0</t>
   </si>
   <si>
-    <t>272.0</t>
-  </si>
-  <si>
-    <t>B4H-040</t>
-  </si>
-  <si>
-    <t>AS41538</t>
-  </si>
-  <si>
-    <t>687.0</t>
-  </si>
-  <si>
-    <t>11.0</t>
-  </si>
-  <si>
-    <t>295.0</t>
-  </si>
-  <si>
-    <t>UNK-01</t>
+    <t>4609-05-01 00:00:00</t>
   </si>
   <si>
     <t>3124-05-01 00:00:00</t>
   </si>
   <si>
-    <t>4609-05-01 00:00:00</t>
-  </si>
-  <si>
     <t>Z28L22A</t>
   </si>
   <si>
     <t>39.0</t>
   </si>
   <si>
+    <t>29.0</t>
+  </si>
+  <si>
     <t>92E</t>
   </si>
   <si>
-    <t>29.0</t>
-  </si>
-  <si>
     <t>9004.0</t>
   </si>
   <si>
@@ -538,63 +586,66 @@
     <t>208-2724-2</t>
   </si>
   <si>
+    <t>2651023-23</t>
+  </si>
+  <si>
+    <t>3044000.0</t>
+  </si>
+  <si>
+    <t>3026812.0</t>
+  </si>
+  <si>
+    <t>3013411.0</t>
+  </si>
+  <si>
+    <t>HSIPT6A-114A</t>
+  </si>
+  <si>
+    <t>3104100-01</t>
+  </si>
+  <si>
+    <t>3027798.0</t>
+  </si>
+  <si>
+    <t>3013111.0</t>
+  </si>
+  <si>
+    <t>3013712.0</t>
+  </si>
+  <si>
     <t>3011713.0</t>
   </si>
   <si>
-    <t>2651023-23</t>
-  </si>
-  <si>
-    <t>3044000.0</t>
-  </si>
-  <si>
-    <t>3026812.0</t>
-  </si>
-  <si>
-    <t>3013411.0</t>
-  </si>
-  <si>
-    <t>HSI PT6A-114A</t>
-  </si>
-  <si>
-    <t>3104100-01</t>
-  </si>
-  <si>
-    <t>3013111.0</t>
-  </si>
-  <si>
-    <t>3027798.0</t>
+    <t>8210-002-01</t>
+  </si>
+  <si>
+    <t>023694-000</t>
+  </si>
+  <si>
+    <t>2651023-19</t>
+  </si>
+  <si>
+    <t>540-1407-4</t>
+  </si>
+  <si>
+    <t>2651022-20-1</t>
+  </si>
+  <si>
+    <t>3049038-03</t>
+  </si>
+  <si>
+    <t>2651022-15</t>
+  </si>
+  <si>
+    <t>3121248-03</t>
+  </si>
+  <si>
+    <t>AD-4078-19</t>
   </si>
   <si>
     <t>30994-001</t>
   </si>
   <si>
-    <t>023694-000</t>
-  </si>
-  <si>
-    <t>8210-002-01</t>
-  </si>
-  <si>
-    <t>2651023-19</t>
-  </si>
-  <si>
-    <t>702801-5</t>
-  </si>
-  <si>
-    <t>3049038-03</t>
-  </si>
-  <si>
-    <t>2651022-15</t>
-  </si>
-  <si>
-    <t>540-1407-4</t>
-  </si>
-  <si>
-    <t>2651022-20-1</t>
-  </si>
-  <si>
-    <t>3121248-03</t>
-  </si>
-  <si>
     <t>D210507</t>
   </si>
   <si>
@@ -604,19 +655,37 @@
     <t>200SGL119Q</t>
   </si>
   <si>
+    <t>3244897-4</t>
+  </si>
+  <si>
     <t>5934PAM-3</t>
   </si>
   <si>
+    <t>452-0133</t>
+  </si>
+  <si>
+    <t>P7036368-0154</t>
+  </si>
+  <si>
+    <t>453-5000-710</t>
+  </si>
+  <si>
     <t>C352TS</t>
   </si>
   <si>
-    <t>452-0133</t>
-  </si>
-  <si>
-    <t>P7036368-0154</t>
-  </si>
-  <si>
-    <t>453-5000-710</t>
+    <t>DCN3-4120</t>
+  </si>
+  <si>
+    <t>LRU-1/P</t>
+  </si>
+  <si>
+    <t>C352</t>
+  </si>
+  <si>
+    <t>453-5000</t>
+  </si>
+  <si>
+    <t>51001.0</t>
   </si>
   <si>
     <t>P7036368-01</t>
@@ -625,39 +694,27 @@
     <t>RT-A1200</t>
   </si>
   <si>
-    <t>DCN3-4120</t>
-  </si>
-  <si>
-    <t>LRU-1/P</t>
-  </si>
-  <si>
-    <t>C352</t>
-  </si>
-  <si>
-    <t>453-5000</t>
-  </si>
-  <si>
-    <t>51001.0</t>
-  </si>
-  <si>
     <t>3122678-04</t>
   </si>
   <si>
+    <t>3244809-4</t>
+  </si>
+  <si>
     <t>2641011-5</t>
   </si>
   <si>
+    <t>162-10700</t>
+  </si>
+  <si>
+    <t>161-11700</t>
+  </si>
+  <si>
     <t>162-11800</t>
   </si>
   <si>
     <t>161-12800</t>
   </si>
   <si>
-    <t>162-10700</t>
-  </si>
-  <si>
-    <t>161-11700</t>
-  </si>
-  <si>
     <t>2622311-16</t>
   </si>
   <si>
@@ -676,181 +733,199 @@
     <t>2634027-1</t>
   </si>
   <si>
+    <t>7EK50</t>
+  </si>
+  <si>
     <t>198.0</t>
   </si>
   <si>
-    <t>7EK50</t>
+    <t>66503.0</t>
+  </si>
+  <si>
+    <t>F6177</t>
+  </si>
+  <si>
+    <t>077L2</t>
+  </si>
+  <si>
+    <t>1Y369</t>
   </si>
   <si>
     <t>74025.0</t>
   </si>
   <si>
-    <t>F6177</t>
-  </si>
-  <si>
-    <t>66503.0</t>
-  </si>
-  <si>
-    <t>59875.0</t>
-  </si>
-  <si>
-    <t>077L2</t>
-  </si>
-  <si>
     <t>95270.0</t>
   </si>
   <si>
+    <t>7213.0</t>
+  </si>
+  <si>
     <t>16455.0</t>
   </si>
   <si>
+    <t>18560.0</t>
+  </si>
+  <si>
+    <t>74703.0</t>
+  </si>
+  <si>
+    <t>76275.0</t>
+  </si>
+  <si>
     <t>54905.0</t>
   </si>
   <si>
-    <t>74703.0</t>
-  </si>
-  <si>
-    <t>76275.0</t>
-  </si>
-  <si>
-    <t>18560.0</t>
+    <t>002FK</t>
+  </si>
+  <si>
+    <t>80049.0</t>
+  </si>
+  <si>
+    <t>81205.0</t>
+  </si>
+  <si>
+    <t>K0068</t>
+  </si>
+  <si>
+    <t>U1601</t>
   </si>
   <si>
     <t>1LGE7</t>
   </si>
   <si>
-    <t>002FK</t>
-  </si>
-  <si>
-    <t>80049.0</t>
-  </si>
-  <si>
-    <t>81205.0</t>
-  </si>
-  <si>
-    <t>K0068</t>
-  </si>
-  <si>
-    <t>U1601</t>
-  </si>
-  <si>
-    <t>7213.0</t>
+    <t>71513.0</t>
   </si>
   <si>
     <t>33269.0</t>
   </si>
   <si>
-    <t>71513.0</t>
-  </si>
-  <si>
-    <t>7 ETA</t>
-  </si>
-  <si>
     <t>PAMALS</t>
   </si>
   <si>
-    <t>1/5 GAV</t>
-  </si>
-  <si>
-    <t>2 ETA</t>
-  </si>
-  <si>
-    <t>1 ETA</t>
-  </si>
-  <si>
-    <t>6 ETA</t>
-  </si>
-  <si>
-    <t>5 ETA</t>
-  </si>
-  <si>
-    <t>1/15 GAV</t>
+    <t>1/5GAV</t>
+  </si>
+  <si>
+    <t>2ETA</t>
+  </si>
+  <si>
+    <t>7ETA</t>
+  </si>
+  <si>
+    <t>1ETA</t>
+  </si>
+  <si>
+    <t>6ETA</t>
   </si>
   <si>
     <t>CLA</t>
   </si>
   <si>
+    <t>DACTAII</t>
+  </si>
+  <si>
+    <t>5ETA</t>
+  </si>
+  <si>
+    <t>1/15GAV</t>
+  </si>
+  <si>
+    <t>IC</t>
+  </si>
+  <si>
+    <t>100H</t>
+  </si>
+  <si>
     <t>TBO</t>
   </si>
   <si>
-    <t>IC</t>
-  </si>
-  <si>
-    <t>100H</t>
-  </si>
-  <si>
     <t>MOT18A6</t>
   </si>
   <si>
-    <t>REV. GERAL</t>
+    <t>REV.GERAL</t>
+  </si>
+  <si>
+    <t>200H</t>
   </si>
   <si>
     <t>MOT1M12</t>
   </si>
   <si>
-    <t>200H</t>
-  </si>
-  <si>
     <t>REVG</t>
   </si>
   <si>
-    <t>1500H HSI</t>
+    <t>1500HHSI</t>
+  </si>
+  <si>
+    <t>1100H</t>
   </si>
   <si>
     <t>RG</t>
   </si>
   <si>
+    <t>3000H</t>
+  </si>
+  <si>
+    <t>CRI.</t>
+  </si>
+  <si>
+    <t>3400H</t>
+  </si>
+  <si>
+    <t>3500H</t>
+  </si>
+  <si>
+    <t>300H</t>
+  </si>
+  <si>
+    <t>600H</t>
+  </si>
+  <si>
+    <t>INSPC</t>
+  </si>
+  <si>
+    <t>900H</t>
+  </si>
+  <si>
+    <t>HSI</t>
+  </si>
+  <si>
+    <t>TROCAFILT</t>
+  </si>
+  <si>
+    <t>REV5000</t>
+  </si>
+  <si>
+    <t>1-REV10000</t>
+  </si>
+  <si>
+    <t>INSPCRI</t>
+  </si>
+  <si>
+    <t>TEC</t>
+  </si>
+  <si>
+    <t>TLV</t>
+  </si>
+  <si>
+    <t>CRI12M</t>
+  </si>
+  <si>
+    <t>CRI</t>
+  </si>
+  <si>
+    <t>1.0</t>
+  </si>
+  <si>
+    <t>12M</t>
+  </si>
+  <si>
+    <t>MONT</t>
+  </si>
+  <si>
     <t>MOT2M6</t>
   </si>
   <si>
-    <t>400H</t>
-  </si>
-  <si>
-    <t>500H</t>
-  </si>
-  <si>
-    <t>3400H</t>
-  </si>
-  <si>
-    <t>INSPC</t>
-  </si>
-  <si>
-    <t>CRI.</t>
-  </si>
-  <si>
-    <t>HSI</t>
-  </si>
-  <si>
-    <t>REV 5000</t>
-  </si>
-  <si>
-    <t>TROCA FILT</t>
-  </si>
-  <si>
-    <t>1-REV10000</t>
-  </si>
-  <si>
-    <t>TEC</t>
-  </si>
-  <si>
-    <t>TLV</t>
-  </si>
-  <si>
-    <t>CRI 12M</t>
-  </si>
-  <si>
-    <t>CRI</t>
-  </si>
-  <si>
-    <t>1.0</t>
-  </si>
-  <si>
-    <t>12M</t>
-  </si>
-  <si>
-    <t>MONT</t>
-  </si>
-  <si>
-    <t>INSP CRIT</t>
+    <t>INSPCRIT</t>
   </si>
   <si>
     <t>PESAGEM</t>
@@ -859,7 +934,7 @@
     <t>BATERIA</t>
   </si>
   <si>
-    <t>CRI (12M)</t>
+    <t>CRI(12M)</t>
   </si>
   <si>
     <t>IC5000</t>
@@ -877,73 +952,85 @@
     <t>Pouso</t>
   </si>
   <si>
-    <t>-319 m</t>
-  </si>
-  <si>
-    <t>-166 m</t>
-  </si>
-  <si>
-    <t>-29 m</t>
-  </si>
-  <si>
-    <t>-28 m</t>
-  </si>
-  <si>
-    <t>-26 m</t>
-  </si>
-  <si>
-    <t>-23 m</t>
-  </si>
-  <si>
-    <t>-9 m</t>
-  </si>
-  <si>
-    <t>-2 m</t>
-  </si>
-  <si>
-    <t>2 m</t>
-  </si>
-  <si>
-    <t>3 m</t>
-  </si>
-  <si>
-    <t>4 m</t>
-  </si>
-  <si>
-    <t>5 m</t>
-  </si>
-  <si>
-    <t>6 m</t>
-  </si>
-  <si>
-    <t>7 m</t>
-  </si>
-  <si>
-    <t>8 m</t>
-  </si>
-  <si>
-    <t>9 m</t>
-  </si>
-  <si>
-    <t>10 m</t>
-  </si>
-  <si>
-    <t>11 m</t>
-  </si>
-  <si>
-    <t>-26 d</t>
-  </si>
-  <si>
-    <t>2 d</t>
-  </si>
-  <si>
-    <t>12 d</t>
-  </si>
-  <si>
-    <t>13 d</t>
-  </si>
-  <si>
-    <t>23 d</t>
+    <t>-320m</t>
+  </si>
+  <si>
+    <t>-265m</t>
+  </si>
+  <si>
+    <t>-30m</t>
+  </si>
+  <si>
+    <t>-28m</t>
+  </si>
+  <si>
+    <t>-26m</t>
+  </si>
+  <si>
+    <t>-24m</t>
+  </si>
+  <si>
+    <t>-10m</t>
+  </si>
+  <si>
+    <t>-3m</t>
+  </si>
+  <si>
+    <t>-2m</t>
+  </si>
+  <si>
+    <t>1m</t>
+  </si>
+  <si>
+    <t>2m</t>
+  </si>
+  <si>
+    <t>3m</t>
+  </si>
+  <si>
+    <t>4m</t>
+  </si>
+  <si>
+    <t>5m</t>
+  </si>
+  <si>
+    <t>6m</t>
+  </si>
+  <si>
+    <t>7m</t>
+  </si>
+  <si>
+    <t>8m</t>
+  </si>
+  <si>
+    <t>9m</t>
+  </si>
+  <si>
+    <t>10m</t>
+  </si>
+  <si>
+    <t>11m</t>
+  </si>
+  <si>
+    <t>-1me17d</t>
+  </si>
+  <si>
+    <t>-8d</t>
+  </si>
+  <si>
+    <t>2d</t>
+  </si>
+  <si>
+    <t>18d</t>
+  </si>
+  <si>
+    <t>1me5d</t>
+  </si>
+  <si>
+    <t>1me10d</t>
+  </si>
+  <si>
+    <t>1me12d</t>
   </si>
 </sst>
 </file>
@@ -1279,7 +1366,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K169"/>
+  <dimension ref="A1:K184"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -1322,28 +1409,28 @@
         <v>11</v>
       </c>
       <c r="B2">
-        <v>2740</v>
+        <v>2730</v>
       </c>
       <c r="C2" t="s">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="D2" t="s">
-        <v>220</v>
+        <v>239</v>
       </c>
       <c r="E2" t="s">
-        <v>242</v>
+        <v>261</v>
       </c>
       <c r="F2" t="s">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="G2" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="H2">
-        <v>-4349.4</v>
+        <v>-2354.2</v>
       </c>
       <c r="J2" s="1">
-        <v>39285</v>
+        <v>40669</v>
       </c>
       <c r="K2" t="b">
         <v>1</v>
@@ -1354,25 +1441,25 @@
         <v>12</v>
       </c>
       <c r="B3">
-        <v>2730</v>
+        <v>2704</v>
       </c>
       <c r="C3" t="s">
-        <v>175</v>
+        <v>191</v>
       </c>
       <c r="D3" t="s">
-        <v>221</v>
+        <v>240</v>
       </c>
       <c r="E3" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="F3" t="s">
-        <v>252</v>
+        <v>272</v>
       </c>
       <c r="G3" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="H3">
-        <v>-2354.2</v>
+        <v>-934.3</v>
       </c>
       <c r="J3" s="1">
         <v>40669</v>
@@ -1389,25 +1476,25 @@
         <v>2704</v>
       </c>
       <c r="C4" t="s">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="D4" t="s">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="E4" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="F4" t="s">
-        <v>253</v>
+        <v>273</v>
       </c>
       <c r="G4" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="H4">
-        <v>-922.4</v>
+        <v>-891.7</v>
       </c>
       <c r="J4" s="1">
-        <v>40669</v>
+        <v>44884</v>
       </c>
       <c r="K4" t="b">
         <v>1</v>
@@ -1418,28 +1505,28 @@
         <v>14</v>
       </c>
       <c r="B5">
-        <v>2704</v>
+        <v>2708</v>
       </c>
       <c r="C5" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="D5" t="s">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="E5" t="s">
-        <v>243</v>
+        <v>262</v>
       </c>
       <c r="F5" t="s">
-        <v>251</v>
+        <v>274</v>
       </c>
       <c r="G5" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="H5">
-        <v>-879.8</v>
+        <v>-589.5</v>
       </c>
       <c r="J5" s="1">
-        <v>44884</v>
+        <v>43855</v>
       </c>
       <c r="K5" t="b">
         <v>1</v>
@@ -1450,28 +1537,28 @@
         <v>15</v>
       </c>
       <c r="B6">
-        <v>2708</v>
+        <v>2719</v>
       </c>
       <c r="C6" t="s">
-        <v>176</v>
+        <v>193</v>
       </c>
       <c r="D6" t="s">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="E6" t="s">
-        <v>244</v>
+        <v>263</v>
       </c>
       <c r="F6" t="s">
-        <v>254</v>
+        <v>275</v>
       </c>
       <c r="G6" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="H6">
-        <v>-536.4</v>
+        <v>-562</v>
       </c>
       <c r="J6" s="1">
-        <v>43855</v>
+        <v>45804</v>
       </c>
       <c r="K6" t="b">
         <v>1</v>
@@ -1479,28 +1566,28 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7">
         <v>2719</v>
       </c>
       <c r="C7" t="s">
-        <v>178</v>
+        <v>194</v>
       </c>
       <c r="D7" t="s">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="E7" t="s">
-        <v>245</v>
+        <v>263</v>
       </c>
       <c r="F7" t="s">
-        <v>255</v>
+        <v>273</v>
       </c>
       <c r="G7" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="H7">
-        <v>-484.3</v>
+        <v>-560.5</v>
       </c>
       <c r="J7" s="1">
         <v>45804</v>
@@ -1514,28 +1601,28 @@
         <v>16</v>
       </c>
       <c r="B8">
-        <v>2719</v>
+        <v>2740</v>
       </c>
       <c r="C8" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="D8" t="s">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="E8" t="s">
-        <v>245</v>
+        <v>264</v>
       </c>
       <c r="F8" t="s">
-        <v>251</v>
+        <v>275</v>
       </c>
       <c r="G8" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="H8">
-        <v>-482.8</v>
+        <v>-531.8</v>
       </c>
       <c r="J8" s="1">
-        <v>45804</v>
+        <v>46014</v>
       </c>
       <c r="K8" t="b">
         <v>1</v>
@@ -1543,28 +1630,28 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9">
         <v>2740</v>
       </c>
       <c r="C9" t="s">
-        <v>178</v>
+        <v>194</v>
       </c>
       <c r="D9" t="s">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="E9" t="s">
-        <v>242</v>
+        <v>264</v>
       </c>
       <c r="F9" t="s">
-        <v>255</v>
+        <v>273</v>
       </c>
       <c r="G9" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="H9">
-        <v>-466.1</v>
+        <v>-529.1</v>
       </c>
       <c r="J9" s="1">
         <v>46014</v>
@@ -1575,31 +1662,31 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10">
-        <v>2722</v>
+        <v>2703</v>
       </c>
       <c r="C10" t="s">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="D10" t="s">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="E10" t="s">
-        <v>245</v>
+        <v>262</v>
       </c>
       <c r="F10" t="s">
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="G10" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="H10">
-        <v>-463.8</v>
+        <v>-391.8</v>
       </c>
       <c r="J10" s="1">
-        <v>40979</v>
+        <v>32786</v>
       </c>
       <c r="K10" t="b">
         <v>1</v>
@@ -1607,31 +1694,31 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11">
-        <v>2740</v>
+        <v>2732</v>
       </c>
       <c r="C11" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="D11" t="s">
-        <v>220</v>
+        <v>239</v>
       </c>
       <c r="E11" t="s">
-        <v>242</v>
+        <v>264</v>
       </c>
       <c r="F11" t="s">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="G11" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="H11">
-        <v>-463.3</v>
+        <v>-391.8</v>
       </c>
       <c r="J11" s="1">
-        <v>46014</v>
+        <v>42769</v>
       </c>
       <c r="K11" t="b">
         <v>1</v>
@@ -1642,28 +1729,28 @@
         <v>19</v>
       </c>
       <c r="B12">
-        <v>2732</v>
+        <v>2719</v>
       </c>
       <c r="C12" t="s">
-        <v>175</v>
+        <v>191</v>
       </c>
       <c r="D12" t="s">
-        <v>221</v>
+        <v>240</v>
       </c>
       <c r="E12" t="s">
-        <v>242</v>
+        <v>263</v>
       </c>
       <c r="F12" t="s">
-        <v>252</v>
+        <v>276</v>
       </c>
       <c r="G12" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="H12">
-        <v>-391.8</v>
+        <v>-288.8</v>
       </c>
       <c r="J12" s="1">
-        <v>42769</v>
+        <v>34700</v>
       </c>
       <c r="K12" t="b">
         <v>1</v>
@@ -1674,28 +1761,28 @@
         <v>20</v>
       </c>
       <c r="B13">
-        <v>2703</v>
+        <v>2702</v>
       </c>
       <c r="C13" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="D13" t="s">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="E13" t="s">
-        <v>244</v>
+        <v>262</v>
       </c>
       <c r="F13" t="s">
-        <v>253</v>
+        <v>277</v>
       </c>
       <c r="G13" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="H13">
-        <v>-390</v>
+        <v>-206</v>
       </c>
       <c r="J13" s="1">
-        <v>32786</v>
+        <v>41204</v>
       </c>
       <c r="K13" t="b">
         <v>1</v>
@@ -1706,28 +1793,28 @@
         <v>21</v>
       </c>
       <c r="B14">
-        <v>2719</v>
+        <v>2733</v>
       </c>
       <c r="C14" t="s">
-        <v>176</v>
+        <v>196</v>
       </c>
       <c r="D14" t="s">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="E14" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="F14" t="s">
-        <v>257</v>
+        <v>273</v>
       </c>
       <c r="G14" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="H14">
-        <v>-211.2</v>
+        <v>-186.8</v>
       </c>
       <c r="J14" s="1">
-        <v>34700</v>
+        <v>46111</v>
       </c>
       <c r="K14" t="b">
         <v>1</v>
@@ -1738,28 +1825,28 @@
         <v>22</v>
       </c>
       <c r="B15">
-        <v>2702</v>
+        <v>2733</v>
       </c>
       <c r="C15" t="s">
-        <v>176</v>
+        <v>197</v>
       </c>
       <c r="D15" t="s">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="E15" t="s">
-        <v>244</v>
+        <v>265</v>
       </c>
       <c r="F15" t="s">
-        <v>256</v>
+        <v>278</v>
       </c>
       <c r="G15" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="H15">
-        <v>-176</v>
+        <v>-186.8</v>
       </c>
       <c r="J15" s="1">
-        <v>41204</v>
+        <v>46111</v>
       </c>
       <c r="K15" t="b">
         <v>1</v>
@@ -1773,22 +1860,22 @@
         <v>2733</v>
       </c>
       <c r="C16" t="s">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="D16" t="s">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="E16" t="s">
-        <v>246</v>
+        <v>265</v>
       </c>
       <c r="F16" t="s">
-        <v>251</v>
+        <v>273</v>
       </c>
       <c r="G16" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="H16">
-        <v>-159.2</v>
+        <v>-186.8</v>
       </c>
       <c r="J16" s="1">
         <v>46111</v>
@@ -1805,22 +1892,22 @@
         <v>2733</v>
       </c>
       <c r="C17" t="s">
-        <v>181</v>
+        <v>199</v>
       </c>
       <c r="D17" t="s">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="E17" t="s">
-        <v>246</v>
+        <v>265</v>
       </c>
       <c r="F17" t="s">
-        <v>258</v>
+        <v>273</v>
       </c>
       <c r="G17" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="H17">
-        <v>-159.2</v>
+        <v>-186.8</v>
       </c>
       <c r="J17" s="1">
         <v>46111</v>
@@ -1837,22 +1924,22 @@
         <v>2733</v>
       </c>
       <c r="C18" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="D18" t="s">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="E18" t="s">
-        <v>246</v>
+        <v>265</v>
       </c>
       <c r="F18" t="s">
-        <v>251</v>
+        <v>273</v>
       </c>
       <c r="G18" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="H18">
-        <v>-159.2</v>
+        <v>-186.8</v>
       </c>
       <c r="J18" s="1">
         <v>46111</v>
@@ -1869,25 +1956,25 @@
         <v>2733</v>
       </c>
       <c r="C19" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="D19" t="s">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="E19" t="s">
-        <v>246</v>
+        <v>265</v>
       </c>
       <c r="F19" t="s">
-        <v>251</v>
+        <v>279</v>
       </c>
       <c r="G19" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="H19">
-        <v>-159.2</v>
+        <v>-128.6</v>
       </c>
       <c r="J19" s="1">
-        <v>46111</v>
+        <v>46161</v>
       </c>
       <c r="K19" t="b">
         <v>1</v>
@@ -1898,28 +1985,28 @@
         <v>27</v>
       </c>
       <c r="B20">
-        <v>2733</v>
+        <v>2736</v>
       </c>
       <c r="C20" t="s">
-        <v>176</v>
+        <v>194</v>
       </c>
       <c r="D20" t="s">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="E20" t="s">
-        <v>246</v>
+        <v>264</v>
       </c>
       <c r="F20" t="s">
-        <v>259</v>
+        <v>273</v>
       </c>
       <c r="G20" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="H20">
-        <v>-101.6</v>
+        <v>-108.2</v>
       </c>
       <c r="J20" s="1">
-        <v>46161</v>
+        <v>46242</v>
       </c>
       <c r="K20" t="b">
         <v>1</v>
@@ -1930,28 +2017,28 @@
         <v>28</v>
       </c>
       <c r="B21">
-        <v>2736</v>
+        <v>2722</v>
       </c>
       <c r="C21" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="D21" t="s">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="E21" t="s">
-        <v>242</v>
+        <v>263</v>
       </c>
       <c r="F21" t="s">
-        <v>255</v>
+        <v>280</v>
       </c>
       <c r="G21" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="H21">
-        <v>-69.7</v>
+        <v>-107</v>
       </c>
       <c r="J21" s="1">
-        <v>46241</v>
+        <v>40979</v>
       </c>
       <c r="K21" t="b">
         <v>1</v>
@@ -1959,31 +2046,31 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B22">
         <v>2736</v>
       </c>
       <c r="C22" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="D22" t="s">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="E22" t="s">
-        <v>242</v>
+        <v>264</v>
       </c>
       <c r="F22" t="s">
-        <v>251</v>
+        <v>281</v>
       </c>
       <c r="G22" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="H22">
-        <v>-61.8</v>
+        <v>-99.8</v>
       </c>
       <c r="J22" s="1">
-        <v>46242</v>
+        <v>46255</v>
       </c>
       <c r="K22" t="b">
         <v>1</v>
@@ -1991,31 +2078,31 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B23">
-        <v>2736</v>
+        <v>2740</v>
       </c>
       <c r="C23" t="s">
-        <v>176</v>
+        <v>200</v>
       </c>
       <c r="D23" t="s">
-        <v>220</v>
+        <v>241</v>
       </c>
       <c r="E23" t="s">
-        <v>242</v>
+        <v>264</v>
       </c>
       <c r="F23" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="G23" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="H23">
-        <v>-53.5</v>
+        <v>-54.8</v>
       </c>
       <c r="J23" s="1">
-        <v>46255</v>
+        <v>46285</v>
       </c>
       <c r="K23" t="b">
         <v>1</v>
@@ -2023,31 +2110,31 @@
     </row>
     <row r="24" spans="1:11">
       <c r="A24" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B24">
-        <v>2742</v>
+        <v>2720</v>
       </c>
       <c r="C24" t="s">
-        <v>183</v>
+        <v>201</v>
       </c>
       <c r="D24" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="E24" t="s">
-        <v>243</v>
+        <v>266</v>
       </c>
       <c r="F24" t="s">
-        <v>257</v>
+        <v>272</v>
       </c>
       <c r="G24" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="H24">
-        <v>-10</v>
+        <v>-29.7</v>
       </c>
       <c r="J24" s="1">
-        <v>46276</v>
+        <v>46269</v>
       </c>
       <c r="K24" t="b">
         <v>1</v>
@@ -2055,31 +2142,31 @@
     </row>
     <row r="25" spans="1:11">
       <c r="A25" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B25">
-        <v>2742</v>
+        <v>2723</v>
       </c>
       <c r="C25" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="D25" t="s">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="E25" t="s">
-        <v>243</v>
+        <v>267</v>
       </c>
       <c r="F25" t="s">
-        <v>261</v>
+        <v>282</v>
       </c>
       <c r="G25" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="H25">
-        <v>-10</v>
+        <v>-25.6</v>
       </c>
       <c r="J25" s="1">
-        <v>46276</v>
+        <v>46282</v>
       </c>
       <c r="K25" t="b">
         <v>1</v>
@@ -2087,31 +2174,31 @@
     </row>
     <row r="26" spans="1:11">
       <c r="A26" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B26">
-        <v>2720</v>
+        <v>2731</v>
       </c>
       <c r="C26" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="D26" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="E26" t="s">
-        <v>247</v>
+        <v>265</v>
       </c>
       <c r="F26" t="s">
-        <v>253</v>
+        <v>277</v>
       </c>
       <c r="G26" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="H26">
-        <v>-7.4</v>
+        <v>-13.8</v>
       </c>
       <c r="J26" s="1">
-        <v>46269</v>
+        <v>46236</v>
       </c>
       <c r="K26" t="b">
         <v>1</v>
@@ -2119,63 +2206,63 @@
     </row>
     <row r="27" spans="1:11">
       <c r="A27" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B27">
-        <v>2731</v>
+        <v>2704</v>
       </c>
       <c r="C27" t="s">
-        <v>176</v>
+        <v>202</v>
       </c>
       <c r="D27" t="s">
-        <v>220</v>
+        <v>239</v>
       </c>
       <c r="E27" t="s">
-        <v>246</v>
+        <v>261</v>
       </c>
       <c r="F27" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="G27" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="H27">
-        <v>-6.3</v>
+        <v>9.9</v>
       </c>
       <c r="J27" s="1">
-        <v>46236</v>
+        <v>46354</v>
       </c>
       <c r="K27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B28">
-        <v>2743</v>
+        <v>2740</v>
       </c>
       <c r="C28" t="s">
-        <v>184</v>
+        <v>203</v>
       </c>
       <c r="D28" t="s">
-        <v>223</v>
+        <v>243</v>
       </c>
       <c r="E28" t="s">
-        <v>248</v>
+        <v>264</v>
       </c>
       <c r="F28" t="s">
-        <v>253</v>
+        <v>283</v>
       </c>
       <c r="G28" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>16.2</v>
       </c>
       <c r="J28" s="1">
-        <v>46282</v>
+        <v>46326</v>
       </c>
       <c r="K28" t="b">
         <v>0</v>
@@ -2183,31 +2270,31 @@
     </row>
     <row r="29" spans="1:11">
       <c r="A29" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B29">
-        <v>2738</v>
+        <v>2720</v>
       </c>
       <c r="C29" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="D29" t="s">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="E29" t="s">
-        <v>242</v>
+        <v>266</v>
       </c>
       <c r="F29" t="s">
-        <v>257</v>
+        <v>284</v>
       </c>
       <c r="G29" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="H29">
-        <v>7.7</v>
+        <v>30.4</v>
       </c>
       <c r="J29" s="1">
-        <v>46295</v>
+        <v>46335</v>
       </c>
       <c r="K29" t="b">
         <v>0</v>
@@ -2215,31 +2302,31 @@
     </row>
     <row r="30" spans="1:11">
       <c r="A30" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B30">
-        <v>2737</v>
+        <v>2740</v>
       </c>
       <c r="C30" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="D30" t="s">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="E30" t="s">
-        <v>242</v>
+        <v>264</v>
       </c>
       <c r="F30" t="s">
-        <v>263</v>
+        <v>285</v>
       </c>
       <c r="G30" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="H30">
-        <v>9.800000000000001</v>
+        <v>33.6</v>
       </c>
       <c r="J30" s="1">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="K30" t="b">
         <v>0</v>
@@ -2247,31 +2334,31 @@
     </row>
     <row r="31" spans="1:11">
       <c r="A31" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B31">
-        <v>2740</v>
+        <v>2738</v>
       </c>
       <c r="C31" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="D31" t="s">
-        <v>224</v>
+        <v>240</v>
       </c>
       <c r="E31" t="s">
-        <v>242</v>
+        <v>264</v>
       </c>
       <c r="F31" t="s">
-        <v>251</v>
+        <v>286</v>
       </c>
       <c r="G31" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="H31">
-        <v>10.9</v>
+        <v>36.7</v>
       </c>
       <c r="J31" s="1">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="K31" t="b">
         <v>0</v>
@@ -2279,31 +2366,31 @@
     </row>
     <row r="32" spans="1:11">
       <c r="A32" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B32">
-        <v>2704</v>
+        <v>2737</v>
       </c>
       <c r="C32" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="D32" t="s">
-        <v>221</v>
+        <v>240</v>
       </c>
       <c r="E32" t="s">
-        <v>243</v>
+        <v>264</v>
       </c>
       <c r="F32" t="s">
-        <v>252</v>
+        <v>287</v>
       </c>
       <c r="G32" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="H32">
-        <v>21.8</v>
+        <v>41.4</v>
       </c>
       <c r="J32" s="1">
-        <v>46404</v>
+        <v>46335</v>
       </c>
       <c r="K32" t="b">
         <v>0</v>
@@ -2311,31 +2398,31 @@
     </row>
     <row r="33" spans="1:11">
       <c r="A33" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B33">
-        <v>2704</v>
+        <v>2721</v>
       </c>
       <c r="C33" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="D33" t="s">
-        <v>225</v>
+        <v>242</v>
       </c>
       <c r="E33" t="s">
-        <v>243</v>
+        <v>266</v>
       </c>
       <c r="F33" t="s">
-        <v>255</v>
+        <v>272</v>
       </c>
       <c r="G33" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="H33">
-        <v>33.9</v>
+        <v>42.8</v>
       </c>
       <c r="J33" s="1">
-        <v>46434</v>
+        <v>46389</v>
       </c>
       <c r="K33" t="b">
         <v>0</v>
@@ -2343,31 +2430,31 @@
     </row>
     <row r="34" spans="1:11">
       <c r="A34" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B34">
-        <v>2721</v>
+        <v>2704</v>
       </c>
       <c r="C34" t="s">
-        <v>184</v>
+        <v>200</v>
       </c>
       <c r="D34" t="s">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="E34" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="F34" t="s">
-        <v>253</v>
+        <v>273</v>
       </c>
       <c r="G34" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="H34">
-        <v>42.8</v>
+        <v>45.6</v>
       </c>
       <c r="J34" s="1">
-        <v>46385</v>
+        <v>46475</v>
       </c>
       <c r="K34" t="b">
         <v>0</v>
@@ -2375,31 +2462,31 @@
     </row>
     <row r="35" spans="1:11">
       <c r="A35" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B35">
-        <v>2720</v>
+        <v>2740</v>
       </c>
       <c r="C35" t="s">
-        <v>176</v>
+        <v>204</v>
       </c>
       <c r="D35" t="s">
-        <v>220</v>
+        <v>239</v>
       </c>
       <c r="E35" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="F35" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="G35" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="H35">
-        <v>52.7</v>
+        <v>47.2</v>
       </c>
       <c r="J35" s="1">
-        <v>46337</v>
+        <v>46391</v>
       </c>
       <c r="K35" t="b">
         <v>0</v>
@@ -2407,31 +2494,31 @@
     </row>
     <row r="36" spans="1:11">
       <c r="A36" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B36">
         <v>2704</v>
       </c>
       <c r="C36" t="s">
-        <v>185</v>
+        <v>205</v>
       </c>
       <c r="D36" t="s">
-        <v>224</v>
+        <v>240</v>
       </c>
       <c r="E36" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="F36" t="s">
-        <v>251</v>
+        <v>288</v>
       </c>
       <c r="G36" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="H36">
-        <v>57.5</v>
+        <v>59.1</v>
       </c>
       <c r="J36" s="1">
-        <v>46493</v>
+        <v>46509</v>
       </c>
       <c r="K36" t="b">
         <v>0</v>
@@ -2439,31 +2526,31 @@
     </row>
     <row r="37" spans="1:11">
       <c r="A37" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B37">
         <v>2704</v>
       </c>
       <c r="C37" t="s">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="D37" t="s">
-        <v>220</v>
+        <v>239</v>
       </c>
       <c r="E37" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="F37" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="G37" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="H37">
-        <v>71</v>
+        <v>61.1</v>
       </c>
       <c r="J37" s="1">
-        <v>46527</v>
+        <v>46514</v>
       </c>
       <c r="K37" t="b">
         <v>0</v>
@@ -2471,31 +2558,31 @@
     </row>
     <row r="38" spans="1:11">
       <c r="A38" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B38">
-        <v>2704</v>
+        <v>2742</v>
       </c>
       <c r="C38" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D38" t="s">
-        <v>221</v>
+        <v>240</v>
       </c>
       <c r="E38" t="s">
-        <v>243</v>
+        <v>268</v>
       </c>
       <c r="F38" t="s">
-        <v>252</v>
+        <v>289</v>
       </c>
       <c r="G38" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="H38">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="J38" s="1">
-        <v>46532</v>
+        <v>46336</v>
       </c>
       <c r="K38" t="b">
         <v>0</v>
@@ -2503,31 +2590,31 @@
     </row>
     <row r="39" spans="1:11">
       <c r="A39" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B39">
-        <v>2740</v>
+        <v>2739</v>
       </c>
       <c r="C39" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="D39" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="E39" t="s">
-        <v>242</v>
+        <v>265</v>
       </c>
       <c r="F39" t="s">
-        <v>266</v>
+        <v>290</v>
       </c>
       <c r="G39" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="H39">
-        <v>82</v>
+        <v>72.5</v>
       </c>
       <c r="J39" s="1">
-        <v>46389</v>
+        <v>46343</v>
       </c>
       <c r="K39" t="b">
         <v>0</v>
@@ -2535,31 +2622,31 @@
     </row>
     <row r="40" spans="1:11">
       <c r="A40" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B40">
-        <v>2738</v>
+        <v>2743</v>
       </c>
       <c r="C40" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="D40" t="s">
-        <v>222</v>
+        <v>240</v>
       </c>
       <c r="E40" t="s">
-        <v>242</v>
+        <v>269</v>
       </c>
       <c r="F40" t="s">
-        <v>257</v>
+        <v>272</v>
       </c>
       <c r="G40" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="H40">
-        <v>107.1</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="J40" s="1">
-        <v>46338</v>
+        <v>46326</v>
       </c>
       <c r="K40" t="b">
         <v>0</v>
@@ -2567,31 +2654,31 @@
     </row>
     <row r="41" spans="1:11">
       <c r="A41" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B41">
-        <v>2737</v>
+        <v>2743</v>
       </c>
       <c r="C41" t="s">
-        <v>183</v>
+        <v>201</v>
       </c>
       <c r="D41" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="E41" t="s">
-        <v>242</v>
+        <v>269</v>
       </c>
       <c r="F41" t="s">
-        <v>257</v>
+        <v>272</v>
       </c>
       <c r="G41" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="H41">
-        <v>109.8</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="J41" s="1">
-        <v>46337</v>
+        <v>46326</v>
       </c>
       <c r="K41" t="b">
         <v>0</v>
@@ -2599,31 +2686,31 @@
     </row>
     <row r="42" spans="1:11">
       <c r="A42" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B42">
-        <v>2740</v>
+        <v>2739</v>
       </c>
       <c r="C42" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="D42" t="s">
-        <v>221</v>
+        <v>240</v>
       </c>
       <c r="E42" t="s">
-        <v>242</v>
+        <v>265</v>
       </c>
       <c r="F42" t="s">
-        <v>252</v>
+        <v>290</v>
       </c>
       <c r="G42" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="H42">
-        <v>112.9</v>
+        <v>77.5</v>
       </c>
       <c r="J42" s="1">
-        <v>46401</v>
+        <v>46346</v>
       </c>
       <c r="K42" t="b">
         <v>0</v>
@@ -2634,28 +2721,28 @@
         <v>49</v>
       </c>
       <c r="B43">
-        <v>2709</v>
+        <v>2736</v>
       </c>
       <c r="C43" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
       <c r="D43" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="E43" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="F43" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="G43" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="H43">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="J43" s="1">
-        <v>46412</v>
+        <v>46392</v>
       </c>
       <c r="K43" t="b">
         <v>0</v>
@@ -2666,28 +2753,28 @@
         <v>50</v>
       </c>
       <c r="B44">
-        <v>2739</v>
+        <v>2741</v>
       </c>
       <c r="C44" t="s">
-        <v>178</v>
+        <v>208</v>
       </c>
       <c r="D44" t="s">
-        <v>220</v>
+        <v>244</v>
       </c>
       <c r="E44" t="s">
-        <v>246</v>
+        <v>264</v>
       </c>
       <c r="F44" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="G44" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="H44">
-        <v>135.1</v>
+        <v>100</v>
       </c>
       <c r="J44" s="1">
-        <v>46353</v>
+        <v>46375</v>
       </c>
       <c r="K44" t="b">
         <v>0</v>
@@ -2698,28 +2785,28 @@
         <v>51</v>
       </c>
       <c r="B45">
-        <v>2727</v>
+        <v>2741</v>
       </c>
       <c r="C45" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="D45" t="s">
-        <v>222</v>
+        <v>240</v>
       </c>
       <c r="E45" t="s">
-        <v>249</v>
+        <v>264</v>
       </c>
       <c r="F45" t="s">
-        <v>257</v>
+        <v>272</v>
       </c>
       <c r="G45" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="H45">
-        <v>136.2</v>
+        <v>100</v>
       </c>
       <c r="J45" s="1">
-        <v>46419</v>
+        <v>46375</v>
       </c>
       <c r="K45" t="b">
         <v>0</v>
@@ -2730,28 +2817,28 @@
         <v>52</v>
       </c>
       <c r="B46">
-        <v>2736</v>
+        <v>2731</v>
       </c>
       <c r="C46" t="s">
-        <v>183</v>
+        <v>209</v>
       </c>
       <c r="D46" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E46" t="s">
-        <v>242</v>
+        <v>265</v>
       </c>
       <c r="F46" t="s">
-        <v>257</v>
+        <v>276</v>
       </c>
       <c r="G46" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="H46">
-        <v>138.8</v>
+        <v>100.3</v>
       </c>
       <c r="J46" s="1">
-        <v>46353</v>
+        <v>46345</v>
       </c>
       <c r="K46" t="b">
         <v>0</v>
@@ -2759,31 +2846,31 @@
     </row>
     <row r="47" spans="1:11">
       <c r="A47" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B47">
-        <v>2739</v>
+        <v>2727</v>
       </c>
       <c r="C47" t="s">
-        <v>179</v>
+        <v>209</v>
       </c>
       <c r="D47" t="s">
-        <v>220</v>
+        <v>245</v>
       </c>
       <c r="E47" t="s">
-        <v>246</v>
+        <v>270</v>
       </c>
       <c r="F47" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="G47" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="H47">
-        <v>140.1</v>
+        <v>104.1</v>
       </c>
       <c r="J47" s="1">
-        <v>46355</v>
+        <v>46418</v>
       </c>
       <c r="K47" t="b">
         <v>0</v>
@@ -2791,31 +2878,31 @@
     </row>
     <row r="48" spans="1:11">
       <c r="A48" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B48">
-        <v>2736</v>
+        <v>2719</v>
       </c>
       <c r="C48" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="D48" t="s">
-        <v>220</v>
+        <v>245</v>
       </c>
       <c r="E48" t="s">
-        <v>242</v>
+        <v>263</v>
       </c>
       <c r="F48" t="s">
-        <v>252</v>
+        <v>276</v>
       </c>
       <c r="G48" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="H48">
-        <v>141.6</v>
+        <v>106.4</v>
       </c>
       <c r="J48" s="1">
-        <v>46355</v>
+        <v>46347</v>
       </c>
       <c r="K48" t="b">
         <v>0</v>
@@ -2823,31 +2910,31 @@
     </row>
     <row r="49" spans="1:11">
       <c r="A49" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B49">
-        <v>2736</v>
+        <v>2709</v>
       </c>
       <c r="C49" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="D49" t="s">
-        <v>224</v>
+        <v>243</v>
       </c>
       <c r="E49" t="s">
-        <v>242</v>
+        <v>266</v>
       </c>
       <c r="F49" t="s">
-        <v>255</v>
+        <v>283</v>
       </c>
       <c r="G49" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="H49">
-        <v>161.2</v>
+        <v>114.3</v>
       </c>
       <c r="J49" s="1">
-        <v>46394</v>
+        <v>46418</v>
       </c>
       <c r="K49" t="b">
         <v>0</v>
@@ -2855,31 +2942,31 @@
     </row>
     <row r="50" spans="1:11">
       <c r="A50" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B50">
-        <v>2739</v>
+        <v>2736</v>
       </c>
       <c r="C50" t="s">
-        <v>183</v>
+        <v>210</v>
       </c>
       <c r="D50" t="s">
-        <v>222</v>
+        <v>241</v>
       </c>
       <c r="E50" t="s">
-        <v>246</v>
+        <v>264</v>
       </c>
       <c r="F50" t="s">
-        <v>257</v>
+        <v>275</v>
       </c>
       <c r="G50" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="H50">
-        <v>170.3</v>
+        <v>114.8</v>
       </c>
       <c r="J50" s="1">
-        <v>46370</v>
+        <v>46400</v>
       </c>
       <c r="K50" t="b">
         <v>0</v>
@@ -2887,31 +2974,31 @@
     </row>
     <row r="51" spans="1:11">
       <c r="A51" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B51">
-        <v>2721</v>
+        <v>2740</v>
       </c>
       <c r="C51" t="s">
-        <v>189</v>
+        <v>209</v>
       </c>
       <c r="D51" t="s">
-        <v>221</v>
+        <v>245</v>
       </c>
       <c r="E51" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="F51" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="G51" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="H51">
-        <v>177.4</v>
+        <v>133.6</v>
       </c>
       <c r="J51" s="1">
-        <v>46487</v>
+        <v>46424</v>
       </c>
       <c r="K51" t="b">
         <v>0</v>
@@ -2919,31 +3006,31 @@
     </row>
     <row r="52" spans="1:11">
       <c r="A52" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B52">
-        <v>2719</v>
+        <v>2738</v>
       </c>
       <c r="C52" t="s">
-        <v>183</v>
+        <v>209</v>
       </c>
       <c r="D52" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E52" t="s">
-        <v>245</v>
+        <v>264</v>
       </c>
       <c r="F52" t="s">
-        <v>257</v>
+        <v>276</v>
       </c>
       <c r="G52" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="H52">
-        <v>184.1</v>
+        <v>135.2</v>
       </c>
       <c r="J52" s="1">
-        <v>46358</v>
+        <v>46384</v>
       </c>
       <c r="K52" t="b">
         <v>0</v>
@@ -2951,31 +3038,31 @@
     </row>
     <row r="53" spans="1:11">
       <c r="A53" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B53">
-        <v>2740</v>
+        <v>2737</v>
       </c>
       <c r="C53" t="s">
-        <v>183</v>
+        <v>209</v>
       </c>
       <c r="D53" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E53" t="s">
-        <v>242</v>
+        <v>264</v>
       </c>
       <c r="F53" t="s">
-        <v>257</v>
+        <v>276</v>
       </c>
       <c r="G53" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="H53">
-        <v>199.3</v>
+        <v>141.4</v>
       </c>
       <c r="J53" s="1">
-        <v>46433</v>
+        <v>46395</v>
       </c>
       <c r="K53" t="b">
         <v>0</v>
@@ -2983,31 +3070,31 @@
     </row>
     <row r="54" spans="1:11">
       <c r="A54" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B54">
-        <v>2723</v>
+        <v>2738</v>
       </c>
       <c r="C54" t="s">
-        <v>183</v>
+        <v>211</v>
       </c>
       <c r="D54" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="E54" t="s">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="F54" t="s">
-        <v>257</v>
+        <v>291</v>
       </c>
       <c r="G54" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="H54">
-        <v>200</v>
+        <v>144.2</v>
       </c>
       <c r="J54" s="1">
-        <v>46367</v>
+        <v>46388</v>
       </c>
       <c r="K54" t="b">
         <v>0</v>
@@ -3015,31 +3102,31 @@
     </row>
     <row r="55" spans="1:11">
       <c r="A55" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B55">
-        <v>2731</v>
+        <v>2740</v>
       </c>
       <c r="C55" t="s">
-        <v>188</v>
+        <v>212</v>
       </c>
       <c r="D55" t="s">
-        <v>220</v>
+        <v>246</v>
       </c>
       <c r="E55" t="s">
-        <v>246</v>
+        <v>264</v>
       </c>
       <c r="F55" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="G55" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="H55">
-        <v>203.6</v>
+        <v>160.3</v>
       </c>
       <c r="J55" s="1">
-        <v>46388</v>
+        <v>46433</v>
       </c>
       <c r="K55" t="b">
         <v>0</v>
@@ -3047,31 +3134,31 @@
     </row>
     <row r="56" spans="1:11">
       <c r="A56" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B56">
-        <v>2738</v>
+        <v>2742</v>
       </c>
       <c r="C56" t="s">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="D56" t="s">
-        <v>221</v>
+        <v>245</v>
       </c>
       <c r="E56" t="s">
-        <v>242</v>
+        <v>268</v>
       </c>
       <c r="F56" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="G56" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="H56">
-        <v>207.6</v>
+        <v>177</v>
       </c>
       <c r="J56" s="1">
-        <v>46391</v>
+        <v>46397</v>
       </c>
       <c r="K56" t="b">
         <v>0</v>
@@ -3079,31 +3166,31 @@
     </row>
     <row r="57" spans="1:11">
       <c r="A57" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B57">
-        <v>2740</v>
+        <v>2736</v>
       </c>
       <c r="C57" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="D57" t="s">
-        <v>227</v>
+        <v>245</v>
       </c>
       <c r="E57" t="s">
-        <v>242</v>
+        <v>264</v>
       </c>
       <c r="F57" t="s">
-        <v>255</v>
+        <v>276</v>
       </c>
       <c r="G57" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="H57">
-        <v>226.1</v>
+        <v>177.2</v>
       </c>
       <c r="J57" s="1">
-        <v>46442</v>
+        <v>46423</v>
       </c>
       <c r="K57" t="b">
         <v>0</v>
@@ -3111,31 +3198,31 @@
     </row>
     <row r="58" spans="1:11">
       <c r="A58" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B58">
-        <v>2740</v>
+        <v>2721</v>
       </c>
       <c r="C58" t="s">
-        <v>175</v>
+        <v>206</v>
       </c>
       <c r="D58" t="s">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="E58" t="s">
-        <v>242</v>
+        <v>266</v>
       </c>
       <c r="F58" t="s">
-        <v>270</v>
+        <v>292</v>
       </c>
       <c r="G58" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="H58">
-        <v>277</v>
+        <v>177.4</v>
       </c>
       <c r="J58" s="1">
-        <v>46461</v>
+        <v>46490</v>
       </c>
       <c r="K58" t="b">
         <v>0</v>
@@ -3143,31 +3230,31 @@
     </row>
     <row r="59" spans="1:11">
       <c r="A59" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B59">
-        <v>2719</v>
+        <v>2723</v>
       </c>
       <c r="C59" t="s">
-        <v>191</v>
+        <v>209</v>
       </c>
       <c r="D59" t="s">
-        <v>221</v>
+        <v>245</v>
       </c>
       <c r="E59" t="s">
-        <v>245</v>
+        <v>267</v>
       </c>
       <c r="F59" t="s">
-        <v>252</v>
+        <v>276</v>
       </c>
       <c r="G59" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="H59">
-        <v>280.6</v>
+        <v>178.8</v>
       </c>
       <c r="J59" s="1">
-        <v>46409</v>
+        <v>46384</v>
       </c>
       <c r="K59" t="b">
         <v>0</v>
@@ -3175,209 +3262,194 @@
     </row>
     <row r="60" spans="1:11">
       <c r="A60" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B60">
-        <v>2706</v>
+        <v>2731</v>
       </c>
       <c r="C60" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="D60" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="E60" t="s">
-        <v>243</v>
+        <v>265</v>
       </c>
       <c r="F60" t="s">
-        <v>271</v>
+        <v>288</v>
       </c>
       <c r="G60" t="s">
-        <v>285</v>
+        <v>309</v>
       </c>
       <c r="H60">
-        <v>-9570</v>
-      </c>
-      <c r="I60" t="s">
-        <v>287</v>
+        <v>196.2</v>
       </c>
       <c r="J60" s="1">
-        <v>36557</v>
+        <v>46392</v>
       </c>
       <c r="K60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:11">
       <c r="A61" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B61">
-        <v>2740</v>
+        <v>2719</v>
       </c>
       <c r="C61" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="D61" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="E61" t="s">
-        <v>242</v>
+        <v>263</v>
       </c>
       <c r="F61" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G61" t="s">
-        <v>285</v>
+        <v>309</v>
       </c>
       <c r="H61">
-        <v>-4980</v>
-      </c>
-      <c r="I61" t="s">
-        <v>288</v>
+        <v>202.9</v>
       </c>
       <c r="J61" s="1">
-        <v>41275</v>
+        <v>46394</v>
       </c>
       <c r="K61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:11">
       <c r="A62" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B62">
-        <v>2724</v>
+        <v>2740</v>
       </c>
       <c r="C62" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="D62" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="E62" t="s">
-        <v>243</v>
+        <v>264</v>
       </c>
       <c r="F62" t="s">
-        <v>273</v>
+        <v>293</v>
       </c>
       <c r="G62" t="s">
-        <v>285</v>
+        <v>309</v>
       </c>
       <c r="H62">
-        <v>-870</v>
-      </c>
-      <c r="I62" t="s">
-        <v>289</v>
+        <v>211.2</v>
       </c>
       <c r="J62" s="1">
-        <v>45380</v>
+        <v>46451</v>
       </c>
       <c r="K62" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:11">
       <c r="A63" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B63">
-        <v>2724</v>
+        <v>2736</v>
       </c>
       <c r="C63" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="D63" t="s">
-        <v>231</v>
+        <v>247</v>
       </c>
       <c r="E63" t="s">
-        <v>243</v>
+        <v>264</v>
       </c>
       <c r="F63" t="s">
-        <v>251</v>
+        <v>294</v>
       </c>
       <c r="G63" t="s">
-        <v>285</v>
+        <v>309</v>
       </c>
       <c r="H63">
-        <v>-840</v>
-      </c>
-      <c r="I63" t="s">
-        <v>290</v>
+        <v>275.6</v>
       </c>
       <c r="J63" s="1">
-        <v>45421</v>
+        <v>46459</v>
       </c>
       <c r="K63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:11">
       <c r="A64" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B64">
-        <v>2724</v>
+        <v>2723</v>
       </c>
       <c r="C64" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="D64" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="E64" t="s">
-        <v>243</v>
+        <v>267</v>
       </c>
       <c r="F64" t="s">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="G64" t="s">
-        <v>285</v>
+        <v>309</v>
       </c>
       <c r="H64">
-        <v>-840</v>
-      </c>
-      <c r="I64" t="s">
-        <v>290</v>
+        <v>293.4</v>
       </c>
       <c r="J64" s="1">
-        <v>45428</v>
+        <v>46473</v>
       </c>
       <c r="K64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:11">
       <c r="A65" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B65">
-        <v>2724</v>
+        <v>2706</v>
       </c>
       <c r="C65" t="s">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="D65" t="s">
-        <v>229</v>
+        <v>248</v>
       </c>
       <c r="E65" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="F65" t="s">
-        <v>275</v>
+        <v>295</v>
       </c>
       <c r="G65" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="H65">
-        <v>-780</v>
+        <v>-9600</v>
       </c>
       <c r="I65" t="s">
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="J65" s="1">
-        <v>45490</v>
+        <v>36557</v>
       </c>
       <c r="K65" t="b">
         <v>1</v>
@@ -3385,34 +3457,34 @@
     </row>
     <row r="66" spans="1:11">
       <c r="A66" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B66">
-        <v>2724</v>
+        <v>2741</v>
       </c>
       <c r="C66" t="s">
-        <v>183</v>
+        <v>215</v>
       </c>
       <c r="D66" t="s">
-        <v>222</v>
+        <v>249</v>
       </c>
       <c r="E66" t="s">
-        <v>243</v>
+        <v>264</v>
       </c>
       <c r="F66" t="s">
-        <v>276</v>
+        <v>296</v>
       </c>
       <c r="G66" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="H66">
-        <v>-690</v>
+        <v>-7950</v>
       </c>
       <c r="I66" t="s">
-        <v>292</v>
+        <v>313</v>
       </c>
       <c r="J66" s="1">
-        <v>45566</v>
+        <v>38353</v>
       </c>
       <c r="K66" t="b">
         <v>1</v>
@@ -3420,34 +3492,34 @@
     </row>
     <row r="67" spans="1:11">
       <c r="A67" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B67">
-        <v>2730</v>
+        <v>2724</v>
       </c>
       <c r="C67" t="s">
-        <v>194</v>
+        <v>215</v>
       </c>
       <c r="D67" t="s">
-        <v>221</v>
+        <v>250</v>
       </c>
       <c r="E67" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="F67" t="s">
-        <v>269</v>
+        <v>297</v>
       </c>
       <c r="G67" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="H67">
-        <v>-270</v>
+        <v>-900</v>
       </c>
       <c r="I67" t="s">
-        <v>293</v>
+        <v>314</v>
       </c>
       <c r="J67" s="1">
-        <v>45986</v>
+        <v>45380</v>
       </c>
       <c r="K67" t="b">
         <v>1</v>
@@ -3455,34 +3527,34 @@
     </row>
     <row r="68" spans="1:11">
       <c r="A68" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B68">
-        <v>2733</v>
+        <v>2724</v>
       </c>
       <c r="C68" t="s">
-        <v>194</v>
+        <v>216</v>
       </c>
       <c r="D68" t="s">
-        <v>221</v>
+        <v>251</v>
       </c>
       <c r="E68" t="s">
-        <v>246</v>
+        <v>261</v>
       </c>
       <c r="F68" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="G68" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="H68">
-        <v>-60</v>
+        <v>-840</v>
       </c>
       <c r="I68" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="J68" s="1">
-        <v>46197</v>
+        <v>45421</v>
       </c>
       <c r="K68" t="b">
         <v>1</v>
@@ -3490,34 +3562,34 @@
     </row>
     <row r="69" spans="1:11">
       <c r="A69" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B69">
-        <v>2729</v>
+        <v>2724</v>
       </c>
       <c r="C69" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="D69" t="s">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="E69" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="F69" t="s">
-        <v>274</v>
+        <v>298</v>
       </c>
       <c r="G69" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="H69">
-        <v>-60</v>
+        <v>-840</v>
       </c>
       <c r="I69" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="J69" s="1">
-        <v>46212</v>
+        <v>45428</v>
       </c>
       <c r="K69" t="b">
         <v>1</v>
@@ -3525,279 +3597,279 @@
     </row>
     <row r="70" spans="1:11">
       <c r="A70" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B70">
-        <v>2722</v>
+        <v>2724</v>
       </c>
       <c r="C70" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="D70" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="E70" t="s">
-        <v>245</v>
+        <v>261</v>
       </c>
       <c r="F70" t="s">
-        <v>255</v>
+        <v>299</v>
       </c>
       <c r="G70" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="H70">
-        <v>60</v>
+        <v>-780</v>
       </c>
       <c r="I70" t="s">
-        <v>295</v>
+        <v>316</v>
       </c>
       <c r="J70" s="1">
-        <v>46341</v>
+        <v>45490</v>
       </c>
       <c r="K70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:11">
       <c r="A71" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B71">
-        <v>2703</v>
+        <v>2724</v>
       </c>
       <c r="C71" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="D71" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="E71" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="F71" t="s">
-        <v>274</v>
+        <v>300</v>
       </c>
       <c r="G71" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="H71">
-        <v>60</v>
+        <v>-720</v>
       </c>
       <c r="I71" t="s">
-        <v>295</v>
+        <v>317</v>
       </c>
       <c r="J71" s="1">
-        <v>46344</v>
+        <v>45566</v>
       </c>
       <c r="K71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:11">
       <c r="A72" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B72">
-        <v>2728</v>
+        <v>2730</v>
       </c>
       <c r="C72" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="D72" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="E72" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="F72" t="s">
-        <v>272</v>
+        <v>291</v>
       </c>
       <c r="G72" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="H72">
-        <v>60</v>
+        <v>-300</v>
       </c>
       <c r="I72" t="s">
-        <v>295</v>
+        <v>318</v>
       </c>
       <c r="J72" s="1">
-        <v>46360</v>
+        <v>45986</v>
       </c>
       <c r="K72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:11">
       <c r="A73" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B73">
-        <v>2734</v>
+        <v>2733</v>
       </c>
       <c r="C73" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="D73" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="E73" t="s">
-        <v>243</v>
+        <v>265</v>
       </c>
       <c r="F73" t="s">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="G73" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="H73">
-        <v>60</v>
+        <v>-90</v>
       </c>
       <c r="I73" t="s">
-        <v>295</v>
+        <v>319</v>
       </c>
       <c r="J73" s="1">
-        <v>46367</v>
+        <v>46197</v>
       </c>
       <c r="K73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:11">
       <c r="A74" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B74">
-        <v>2709</v>
+        <v>2729</v>
       </c>
       <c r="C74" t="s">
-        <v>176</v>
+        <v>217</v>
       </c>
       <c r="D74" t="s">
-        <v>220</v>
+        <v>249</v>
       </c>
       <c r="E74" t="s">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="F74" t="s">
-        <v>261</v>
+        <v>298</v>
       </c>
       <c r="G74" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="H74">
-        <v>60</v>
+        <v>-60</v>
       </c>
       <c r="I74" t="s">
-        <v>295</v>
+        <v>320</v>
       </c>
       <c r="J74" s="1">
-        <v>46368</v>
+        <v>46212</v>
       </c>
       <c r="K74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:11">
       <c r="A75" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B75">
-        <v>2740</v>
+        <v>2730</v>
       </c>
       <c r="C75" t="s">
-        <v>176</v>
+        <v>218</v>
       </c>
       <c r="D75" t="s">
-        <v>220</v>
+        <v>252</v>
       </c>
       <c r="E75" t="s">
-        <v>242</v>
+        <v>261</v>
       </c>
       <c r="F75" t="s">
-        <v>261</v>
+        <v>299</v>
       </c>
       <c r="G75" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="H75">
-        <v>60</v>
+        <v>-60</v>
       </c>
       <c r="I75" t="s">
-        <v>295</v>
+        <v>320</v>
       </c>
       <c r="J75" s="1">
-        <v>46374</v>
+        <v>46225</v>
       </c>
       <c r="K75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:11">
       <c r="A76" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B76">
-        <v>2732</v>
+        <v>2702</v>
       </c>
       <c r="C76" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="D76" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="E76" t="s">
-        <v>242</v>
+        <v>262</v>
       </c>
       <c r="F76" t="s">
-        <v>258</v>
+        <v>300</v>
       </c>
       <c r="G76" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="H76">
-        <v>90</v>
+        <v>-60</v>
       </c>
       <c r="I76" t="s">
-        <v>296</v>
+        <v>320</v>
       </c>
       <c r="J76" s="1">
-        <v>46375</v>
+        <v>46235</v>
       </c>
       <c r="K76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:11">
       <c r="A77" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B77">
-        <v>2730</v>
+        <v>2740</v>
       </c>
       <c r="C77" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="D77" t="s">
-        <v>234</v>
+        <v>250</v>
       </c>
       <c r="E77" t="s">
-        <v>243</v>
+        <v>264</v>
       </c>
       <c r="F77" t="s">
-        <v>277</v>
+        <v>296</v>
       </c>
       <c r="G77" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="H77">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="I77" t="s">
-        <v>296</v>
+        <v>321</v>
       </c>
       <c r="J77" s="1">
-        <v>46387</v>
+        <v>46345</v>
       </c>
       <c r="K77" t="b">
         <v>0</v>
@@ -3805,34 +3877,34 @@
     </row>
     <row r="78" spans="1:11">
       <c r="A78" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B78">
-        <v>2732</v>
+        <v>2728</v>
       </c>
       <c r="C78" t="s">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="D78" t="s">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="E78" t="s">
-        <v>242</v>
+        <v>261</v>
       </c>
       <c r="F78" t="s">
-        <v>277</v>
+        <v>296</v>
       </c>
       <c r="G78" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="H78">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="I78" t="s">
-        <v>296</v>
+        <v>321</v>
       </c>
       <c r="J78" s="1">
-        <v>46387</v>
+        <v>46360</v>
       </c>
       <c r="K78" t="b">
         <v>0</v>
@@ -3840,34 +3912,34 @@
     </row>
     <row r="79" spans="1:11">
       <c r="A79" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B79">
-        <v>2736</v>
+        <v>2734</v>
       </c>
       <c r="C79" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="D79" t="s">
-        <v>234</v>
+        <v>253</v>
       </c>
       <c r="E79" t="s">
-        <v>242</v>
+        <v>261</v>
       </c>
       <c r="F79" t="s">
-        <v>277</v>
+        <v>301</v>
       </c>
       <c r="G79" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="H79">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="I79" t="s">
-        <v>296</v>
+        <v>322</v>
       </c>
       <c r="J79" s="1">
-        <v>46387</v>
+        <v>46367</v>
       </c>
       <c r="K79" t="b">
         <v>0</v>
@@ -3875,34 +3947,34 @@
     </row>
     <row r="80" spans="1:11">
       <c r="A80" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B80">
-        <v>2728</v>
+        <v>2709</v>
       </c>
       <c r="C80" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="D80" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="E80" t="s">
-        <v>243</v>
+        <v>266</v>
       </c>
       <c r="F80" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
       <c r="G80" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="H80">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="I80" t="s">
-        <v>296</v>
+        <v>322</v>
       </c>
       <c r="J80" s="1">
-        <v>46388</v>
+        <v>46368</v>
       </c>
       <c r="K80" t="b">
         <v>0</v>
@@ -3910,34 +3982,34 @@
     </row>
     <row r="81" spans="1:11">
       <c r="A81" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B81">
-        <v>2704</v>
+        <v>2732</v>
       </c>
       <c r="C81" t="s">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="D81" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="E81" t="s">
-        <v>243</v>
+        <v>264</v>
       </c>
       <c r="F81" t="s">
         <v>278</v>
       </c>
       <c r="G81" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="H81">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="I81" t="s">
-        <v>296</v>
+        <v>322</v>
       </c>
       <c r="J81" s="1">
-        <v>46401</v>
+        <v>46375</v>
       </c>
       <c r="K81" t="b">
         <v>0</v>
@@ -3945,34 +4017,34 @@
     </row>
     <row r="82" spans="1:11">
       <c r="A82" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B82">
-        <v>2704</v>
+        <v>2730</v>
       </c>
       <c r="C82" t="s">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="D82" t="s">
-        <v>232</v>
+        <v>253</v>
       </c>
       <c r="E82" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="F82" t="s">
-        <v>274</v>
+        <v>301</v>
       </c>
       <c r="G82" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="H82">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="I82" t="s">
-        <v>296</v>
+        <v>322</v>
       </c>
       <c r="J82" s="1">
-        <v>46401</v>
+        <v>46387</v>
       </c>
       <c r="K82" t="b">
         <v>0</v>
@@ -3980,34 +4052,34 @@
     </row>
     <row r="83" spans="1:11">
       <c r="A83" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B83">
-        <v>2709</v>
+        <v>2732</v>
       </c>
       <c r="C83" t="s">
-        <v>197</v>
+        <v>219</v>
       </c>
       <c r="D83" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="E83" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="F83" t="s">
-        <v>275</v>
+        <v>301</v>
       </c>
       <c r="G83" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="H83">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="I83" t="s">
-        <v>296</v>
+        <v>322</v>
       </c>
       <c r="J83" s="1">
-        <v>46401</v>
+        <v>46387</v>
       </c>
       <c r="K83" t="b">
         <v>0</v>
@@ -4015,34 +4087,34 @@
     </row>
     <row r="84" spans="1:11">
       <c r="A84" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B84">
-        <v>2737</v>
+        <v>2736</v>
       </c>
       <c r="C84" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="D84" t="s">
-        <v>234</v>
+        <v>253</v>
       </c>
       <c r="E84" t="s">
-        <v>242</v>
+        <v>264</v>
       </c>
       <c r="F84" t="s">
-        <v>277</v>
+        <v>301</v>
       </c>
       <c r="G84" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="H84">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="I84" t="s">
-        <v>297</v>
+        <v>322</v>
       </c>
       <c r="J84" s="1">
-        <v>46412</v>
+        <v>46387</v>
       </c>
       <c r="K84" t="b">
         <v>0</v>
@@ -4050,34 +4122,34 @@
     </row>
     <row r="85" spans="1:11">
       <c r="A85" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B85">
-        <v>2740</v>
+        <v>2728</v>
       </c>
       <c r="C85" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="D85" t="s">
-        <v>234</v>
+        <v>250</v>
       </c>
       <c r="E85" t="s">
-        <v>242</v>
+        <v>261</v>
       </c>
       <c r="F85" t="s">
-        <v>277</v>
+        <v>296</v>
       </c>
       <c r="G85" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="H85">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="I85" t="s">
-        <v>297</v>
+        <v>322</v>
       </c>
       <c r="J85" s="1">
-        <v>46412</v>
+        <v>46388</v>
       </c>
       <c r="K85" t="b">
         <v>0</v>
@@ -4085,34 +4157,34 @@
     </row>
     <row r="86" spans="1:11">
       <c r="A86" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B86">
-        <v>2733</v>
+        <v>2704</v>
       </c>
       <c r="C86" t="s">
-        <v>197</v>
+        <v>221</v>
       </c>
       <c r="D86" t="s">
-        <v>229</v>
+        <v>255</v>
       </c>
       <c r="E86" t="s">
-        <v>246</v>
+        <v>261</v>
       </c>
       <c r="F86" t="s">
-        <v>275</v>
+        <v>303</v>
       </c>
       <c r="G86" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="H86">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="I86" t="s">
-        <v>297</v>
+        <v>323</v>
       </c>
       <c r="J86" s="1">
-        <v>46424</v>
+        <v>46401</v>
       </c>
       <c r="K86" t="b">
         <v>0</v>
@@ -4120,34 +4192,34 @@
     </row>
     <row r="87" spans="1:11">
       <c r="A87" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B87">
-        <v>2738</v>
+        <v>2704</v>
       </c>
       <c r="C87" t="s">
-        <v>203</v>
+        <v>217</v>
       </c>
       <c r="D87" t="s">
-        <v>234</v>
+        <v>249</v>
       </c>
       <c r="E87" t="s">
-        <v>242</v>
+        <v>261</v>
       </c>
       <c r="F87" t="s">
-        <v>277</v>
+        <v>298</v>
       </c>
       <c r="G87" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="H87">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="I87" t="s">
-        <v>297</v>
+        <v>323</v>
       </c>
       <c r="J87" s="1">
-        <v>46427</v>
+        <v>46401</v>
       </c>
       <c r="K87" t="b">
         <v>0</v>
@@ -4155,34 +4227,34 @@
     </row>
     <row r="88" spans="1:11">
       <c r="A88" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B88">
-        <v>2741</v>
+        <v>2709</v>
       </c>
       <c r="C88" t="s">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="D88" t="s">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="E88" t="s">
-        <v>242</v>
+        <v>266</v>
       </c>
       <c r="F88" t="s">
-        <v>277</v>
+        <v>299</v>
       </c>
       <c r="G88" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="H88">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="I88" t="s">
-        <v>297</v>
+        <v>323</v>
       </c>
       <c r="J88" s="1">
-        <v>46427</v>
+        <v>46401</v>
       </c>
       <c r="K88" t="b">
         <v>0</v>
@@ -4190,34 +4262,34 @@
     </row>
     <row r="89" spans="1:11">
       <c r="A89" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B89">
-        <v>2739</v>
+        <v>2731</v>
       </c>
       <c r="C89" t="s">
-        <v>197</v>
+        <v>218</v>
       </c>
       <c r="D89" t="s">
-        <v>229</v>
+        <v>252</v>
       </c>
       <c r="E89" t="s">
-        <v>246</v>
+        <v>265</v>
       </c>
       <c r="F89" t="s">
-        <v>275</v>
+        <v>299</v>
       </c>
       <c r="G89" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="H89">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="I89" t="s">
-        <v>298</v>
+        <v>323</v>
       </c>
       <c r="J89" s="1">
-        <v>46437</v>
+        <v>46403</v>
       </c>
       <c r="K89" t="b">
         <v>0</v>
@@ -4225,34 +4297,34 @@
     </row>
     <row r="90" spans="1:11">
       <c r="A90" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B90">
-        <v>2719</v>
+        <v>2737</v>
       </c>
       <c r="C90" t="s">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="D90" t="s">
-        <v>232</v>
+        <v>253</v>
       </c>
       <c r="E90" t="s">
-        <v>245</v>
+        <v>264</v>
       </c>
       <c r="F90" t="s">
-        <v>274</v>
+        <v>301</v>
       </c>
       <c r="G90" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="H90">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="I90" t="s">
-        <v>298</v>
+        <v>323</v>
       </c>
       <c r="J90" s="1">
-        <v>46451</v>
+        <v>46412</v>
       </c>
       <c r="K90" t="b">
         <v>0</v>
@@ -4260,34 +4332,34 @@
     </row>
     <row r="91" spans="1:11">
       <c r="A91" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B91">
-        <v>2741</v>
+        <v>2740</v>
       </c>
       <c r="C91" t="s">
-        <v>197</v>
+        <v>219</v>
       </c>
       <c r="D91" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="E91" t="s">
-        <v>242</v>
+        <v>264</v>
       </c>
       <c r="F91" t="s">
-        <v>275</v>
+        <v>301</v>
       </c>
       <c r="G91" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="H91">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="I91" t="s">
-        <v>298</v>
+        <v>323</v>
       </c>
       <c r="J91" s="1">
-        <v>46451</v>
+        <v>46412</v>
       </c>
       <c r="K91" t="b">
         <v>0</v>
@@ -4295,34 +4367,34 @@
     </row>
     <row r="92" spans="1:11">
       <c r="A92" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B92">
-        <v>2738</v>
+        <v>2733</v>
       </c>
       <c r="C92" t="s">
-        <v>197</v>
+        <v>218</v>
       </c>
       <c r="D92" t="s">
-        <v>229</v>
+        <v>252</v>
       </c>
       <c r="E92" t="s">
-        <v>242</v>
+        <v>265</v>
       </c>
       <c r="F92" t="s">
-        <v>275</v>
+        <v>299</v>
       </c>
       <c r="G92" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="H92">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="I92" t="s">
-        <v>298</v>
+        <v>323</v>
       </c>
       <c r="J92" s="1">
-        <v>46455</v>
+        <v>46424</v>
       </c>
       <c r="K92" t="b">
         <v>0</v>
@@ -4330,34 +4402,34 @@
     </row>
     <row r="93" spans="1:11">
       <c r="A93" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B93">
-        <v>2708</v>
+        <v>2738</v>
       </c>
       <c r="C93" t="s">
-        <v>183</v>
+        <v>219</v>
       </c>
       <c r="D93" t="s">
-        <v>222</v>
+        <v>253</v>
       </c>
       <c r="E93" t="s">
-        <v>244</v>
+        <v>264</v>
       </c>
       <c r="F93" t="s">
-        <v>276</v>
+        <v>301</v>
       </c>
       <c r="G93" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="H93">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="I93" t="s">
-        <v>298</v>
+        <v>324</v>
       </c>
       <c r="J93" s="1">
-        <v>46456</v>
+        <v>46427</v>
       </c>
       <c r="K93" t="b">
         <v>0</v>
@@ -4365,34 +4437,34 @@
     </row>
     <row r="94" spans="1:11">
       <c r="A94" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B94">
-        <v>2720</v>
+        <v>2741</v>
       </c>
       <c r="C94" t="s">
-        <v>197</v>
+        <v>219</v>
       </c>
       <c r="D94" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="E94" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="F94" t="s">
-        <v>275</v>
+        <v>301</v>
       </c>
       <c r="G94" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="H94">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="I94" t="s">
-        <v>298</v>
+        <v>324</v>
       </c>
       <c r="J94" s="1">
-        <v>46457</v>
+        <v>46427</v>
       </c>
       <c r="K94" t="b">
         <v>0</v>
@@ -4400,34 +4472,34 @@
     </row>
     <row r="95" spans="1:11">
       <c r="A95" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B95">
-        <v>2734</v>
+        <v>2739</v>
       </c>
       <c r="C95" t="s">
-        <v>197</v>
+        <v>218</v>
       </c>
       <c r="D95" t="s">
-        <v>229</v>
+        <v>252</v>
       </c>
       <c r="E95" t="s">
-        <v>243</v>
+        <v>265</v>
       </c>
       <c r="F95" t="s">
-        <v>275</v>
+        <v>299</v>
       </c>
       <c r="G95" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="H95">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="I95" t="s">
-        <v>298</v>
+        <v>324</v>
       </c>
       <c r="J95" s="1">
-        <v>46464</v>
+        <v>46437</v>
       </c>
       <c r="K95" t="b">
         <v>0</v>
@@ -4435,34 +4507,34 @@
     </row>
     <row r="96" spans="1:11">
       <c r="A96" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B96">
-        <v>2723</v>
+        <v>2719</v>
       </c>
       <c r="C96" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="D96" t="s">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="E96" t="s">
-        <v>250</v>
+        <v>263</v>
       </c>
       <c r="F96" t="s">
-        <v>271</v>
+        <v>298</v>
       </c>
       <c r="G96" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="H96">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="I96" t="s">
-        <v>299</v>
+        <v>324</v>
       </c>
       <c r="J96" s="1">
-        <v>46470</v>
+        <v>46451</v>
       </c>
       <c r="K96" t="b">
         <v>0</v>
@@ -4470,34 +4542,34 @@
     </row>
     <row r="97" spans="1:11">
       <c r="A97" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B97">
-        <v>2728</v>
+        <v>2741</v>
       </c>
       <c r="C97" t="s">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="D97" t="s">
-        <v>232</v>
+        <v>252</v>
       </c>
       <c r="E97" t="s">
-        <v>243</v>
+        <v>264</v>
       </c>
       <c r="F97" t="s">
-        <v>274</v>
+        <v>299</v>
       </c>
       <c r="G97" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="H97">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="I97" t="s">
-        <v>299</v>
+        <v>324</v>
       </c>
       <c r="J97" s="1">
-        <v>46485</v>
+        <v>46451</v>
       </c>
       <c r="K97" t="b">
         <v>0</v>
@@ -4505,34 +4577,34 @@
     </row>
     <row r="98" spans="1:11">
       <c r="A98" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B98">
-        <v>2741</v>
+        <v>2738</v>
       </c>
       <c r="C98" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="D98" t="s">
-        <v>237</v>
+        <v>252</v>
       </c>
       <c r="E98" t="s">
-        <v>242</v>
+        <v>264</v>
       </c>
       <c r="F98" t="s">
-        <v>258</v>
+        <v>299</v>
       </c>
       <c r="G98" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="H98">
-        <v>210</v>
+        <v>150</v>
       </c>
       <c r="I98" t="s">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="J98" s="1">
-        <v>46499</v>
+        <v>46455</v>
       </c>
       <c r="K98" t="b">
         <v>0</v>
@@ -4540,34 +4612,34 @@
     </row>
     <row r="99" spans="1:11">
       <c r="A99" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B99">
-        <v>2722</v>
+        <v>2708</v>
       </c>
       <c r="C99" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="D99" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="E99" t="s">
-        <v>245</v>
+        <v>262</v>
       </c>
       <c r="F99" t="s">
-        <v>274</v>
+        <v>300</v>
       </c>
       <c r="G99" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="H99">
-        <v>210</v>
+        <v>150</v>
       </c>
       <c r="I99" t="s">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="J99" s="1">
-        <v>46504</v>
+        <v>46456</v>
       </c>
       <c r="K99" t="b">
         <v>0</v>
@@ -4575,34 +4647,34 @@
     </row>
     <row r="100" spans="1:11">
       <c r="A100" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B100">
-        <v>2743</v>
+        <v>2720</v>
       </c>
       <c r="C100" t="s">
-        <v>197</v>
+        <v>218</v>
       </c>
       <c r="D100" t="s">
-        <v>229</v>
+        <v>252</v>
       </c>
       <c r="E100" t="s">
-        <v>248</v>
+        <v>266</v>
       </c>
       <c r="F100" t="s">
-        <v>279</v>
+        <v>299</v>
       </c>
       <c r="G100" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="H100">
-        <v>210</v>
+        <v>150</v>
       </c>
       <c r="I100" t="s">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="J100" s="1">
-        <v>46507</v>
+        <v>46457</v>
       </c>
       <c r="K100" t="b">
         <v>0</v>
@@ -4610,34 +4682,34 @@
     </row>
     <row r="101" spans="1:11">
       <c r="A101" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B101">
-        <v>2702</v>
+        <v>2740</v>
       </c>
       <c r="C101" t="s">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="D101" t="s">
-        <v>232</v>
+        <v>252</v>
       </c>
       <c r="E101" t="s">
-        <v>244</v>
+        <v>264</v>
       </c>
       <c r="F101" t="s">
-        <v>280</v>
+        <v>299</v>
       </c>
       <c r="G101" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="H101">
-        <v>210</v>
+        <v>150</v>
       </c>
       <c r="I101" t="s">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="J101" s="1">
-        <v>46508</v>
+        <v>46462</v>
       </c>
       <c r="K101" t="b">
         <v>0</v>
@@ -4645,34 +4717,34 @@
     </row>
     <row r="102" spans="1:11">
       <c r="A102" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B102">
-        <v>2728</v>
+        <v>2734</v>
       </c>
       <c r="C102" t="s">
-        <v>183</v>
+        <v>218</v>
       </c>
       <c r="D102" t="s">
-        <v>222</v>
+        <v>252</v>
       </c>
       <c r="E102" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="F102" t="s">
-        <v>276</v>
+        <v>299</v>
       </c>
       <c r="G102" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="H102">
-        <v>210</v>
+        <v>150</v>
       </c>
       <c r="I102" t="s">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="J102" s="1">
-        <v>46512</v>
+        <v>46464</v>
       </c>
       <c r="K102" t="b">
         <v>0</v>
@@ -4680,34 +4752,34 @@
     </row>
     <row r="103" spans="1:11">
       <c r="A103" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B103">
-        <v>2733</v>
+        <v>2723</v>
       </c>
       <c r="C103" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="D103" t="s">
-        <v>231</v>
+        <v>249</v>
       </c>
       <c r="E103" t="s">
-        <v>246</v>
+        <v>267</v>
       </c>
       <c r="F103" t="s">
-        <v>255</v>
+        <v>295</v>
       </c>
       <c r="G103" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="H103">
-        <v>210</v>
+        <v>150</v>
       </c>
       <c r="I103" t="s">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="J103" s="1">
-        <v>46512</v>
+        <v>46470</v>
       </c>
       <c r="K103" t="b">
         <v>0</v>
@@ -4715,34 +4787,34 @@
     </row>
     <row r="104" spans="1:11">
       <c r="A104" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B104">
-        <v>2703</v>
+        <v>2728</v>
       </c>
       <c r="C104" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="D104" t="s">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="E104" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="F104" t="s">
-        <v>274</v>
+        <v>298</v>
       </c>
       <c r="G104" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="H104">
-        <v>240</v>
+        <v>150</v>
       </c>
       <c r="I104" t="s">
-        <v>301</v>
+        <v>325</v>
       </c>
       <c r="J104" s="1">
-        <v>46528</v>
+        <v>46485</v>
       </c>
       <c r="K104" t="b">
         <v>0</v>
@@ -4750,34 +4822,34 @@
     </row>
     <row r="105" spans="1:11">
       <c r="A105" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B105">
-        <v>2704</v>
+        <v>2741</v>
       </c>
       <c r="C105" t="s">
-        <v>183</v>
+        <v>223</v>
       </c>
       <c r="D105" t="s">
-        <v>222</v>
+        <v>256</v>
       </c>
       <c r="E105" t="s">
-        <v>243</v>
+        <v>264</v>
       </c>
       <c r="F105" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="G105" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="H105">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="I105" t="s">
-        <v>301</v>
+        <v>326</v>
       </c>
       <c r="J105" s="1">
-        <v>46529</v>
+        <v>46499</v>
       </c>
       <c r="K105" t="b">
         <v>0</v>
@@ -4785,34 +4857,34 @@
     </row>
     <row r="106" spans="1:11">
       <c r="A106" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B106">
-        <v>2736</v>
+        <v>2722</v>
       </c>
       <c r="C106" t="s">
-        <v>197</v>
+        <v>217</v>
       </c>
       <c r="D106" t="s">
-        <v>229</v>
+        <v>249</v>
       </c>
       <c r="E106" t="s">
-        <v>242</v>
+        <v>263</v>
       </c>
       <c r="F106" t="s">
-        <v>275</v>
+        <v>298</v>
       </c>
       <c r="G106" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="H106">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="I106" t="s">
-        <v>301</v>
+        <v>326</v>
       </c>
       <c r="J106" s="1">
-        <v>46537</v>
+        <v>46504</v>
       </c>
       <c r="K106" t="b">
         <v>0</v>
@@ -4820,34 +4892,34 @@
     </row>
     <row r="107" spans="1:11">
       <c r="A107" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B107">
-        <v>2737</v>
+        <v>2743</v>
       </c>
       <c r="C107" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="D107" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="E107" t="s">
-        <v>242</v>
+        <v>269</v>
       </c>
       <c r="F107" t="s">
-        <v>258</v>
+        <v>304</v>
       </c>
       <c r="G107" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="H107">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="I107" t="s">
-        <v>301</v>
+        <v>326</v>
       </c>
       <c r="J107" s="1">
-        <v>46546</v>
+        <v>46507</v>
       </c>
       <c r="K107" t="b">
         <v>0</v>
@@ -4855,34 +4927,34 @@
     </row>
     <row r="108" spans="1:11">
       <c r="A108" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B108">
-        <v>2740</v>
+        <v>2702</v>
       </c>
       <c r="C108" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="D108" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="E108" t="s">
-        <v>242</v>
+        <v>262</v>
       </c>
       <c r="F108" t="s">
-        <v>258</v>
+        <v>305</v>
       </c>
       <c r="G108" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="H108">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="I108" t="s">
-        <v>301</v>
+        <v>326</v>
       </c>
       <c r="J108" s="1">
-        <v>46547</v>
+        <v>46508</v>
       </c>
       <c r="K108" t="b">
         <v>0</v>
@@ -4890,34 +4962,34 @@
     </row>
     <row r="109" spans="1:11">
       <c r="A109" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B109">
-        <v>2736</v>
+        <v>2728</v>
       </c>
       <c r="C109" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D109" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="E109" t="s">
-        <v>242</v>
+        <v>261</v>
       </c>
       <c r="F109" t="s">
-        <v>258</v>
+        <v>300</v>
       </c>
       <c r="G109" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="H109">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="I109" t="s">
-        <v>301</v>
+        <v>326</v>
       </c>
       <c r="J109" s="1">
-        <v>46547</v>
+        <v>46512</v>
       </c>
       <c r="K109" t="b">
         <v>0</v>
@@ -4925,34 +4997,34 @@
     </row>
     <row r="110" spans="1:11">
       <c r="A110" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B110">
-        <v>2708</v>
+        <v>2703</v>
       </c>
       <c r="C110" t="s">
-        <v>201</v>
+        <v>217</v>
       </c>
       <c r="D110" t="s">
-        <v>231</v>
+        <v>249</v>
       </c>
       <c r="E110" t="s">
-        <v>244</v>
+        <v>262</v>
       </c>
       <c r="F110" t="s">
-        <v>255</v>
+        <v>298</v>
       </c>
       <c r="G110" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="H110">
-        <v>240</v>
+        <v>210</v>
       </c>
       <c r="I110" t="s">
-        <v>301</v>
+        <v>327</v>
       </c>
       <c r="J110" s="1">
-        <v>46551</v>
+        <v>46528</v>
       </c>
       <c r="K110" t="b">
         <v>0</v>
@@ -4960,34 +5032,34 @@
     </row>
     <row r="111" spans="1:11">
       <c r="A111" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B111">
-        <v>2708</v>
+        <v>2704</v>
       </c>
       <c r="C111" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="D111" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="E111" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="F111" t="s">
-        <v>274</v>
+        <v>300</v>
       </c>
       <c r="G111" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="H111">
-        <v>270</v>
+        <v>210</v>
       </c>
       <c r="I111" t="s">
-        <v>302</v>
+        <v>327</v>
       </c>
       <c r="J111" s="1">
-        <v>46560</v>
+        <v>46529</v>
       </c>
       <c r="K111" t="b">
         <v>0</v>
@@ -4995,34 +5067,34 @@
     </row>
     <row r="112" spans="1:11">
       <c r="A112" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B112">
-        <v>2703</v>
+        <v>2736</v>
       </c>
       <c r="C112" t="s">
-        <v>183</v>
+        <v>218</v>
       </c>
       <c r="D112" t="s">
-        <v>222</v>
+        <v>252</v>
       </c>
       <c r="E112" t="s">
-        <v>244</v>
+        <v>264</v>
       </c>
       <c r="F112" t="s">
-        <v>276</v>
+        <v>299</v>
       </c>
       <c r="G112" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="H112">
-        <v>270</v>
+        <v>210</v>
       </c>
       <c r="I112" t="s">
-        <v>302</v>
+        <v>327</v>
       </c>
       <c r="J112" s="1">
-        <v>46567</v>
+        <v>46537</v>
       </c>
       <c r="K112" t="b">
         <v>0</v>
@@ -5030,34 +5102,34 @@
     </row>
     <row r="113" spans="1:11">
       <c r="A113" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B113">
-        <v>2742</v>
+        <v>2737</v>
       </c>
       <c r="C113" t="s">
-        <v>197</v>
+        <v>223</v>
       </c>
       <c r="D113" t="s">
-        <v>229</v>
+        <v>257</v>
       </c>
       <c r="E113" t="s">
-        <v>243</v>
+        <v>264</v>
       </c>
       <c r="F113" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="G113" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="H113">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="I113" t="s">
-        <v>302</v>
+        <v>328</v>
       </c>
       <c r="J113" s="1">
-        <v>46568</v>
+        <v>46546</v>
       </c>
       <c r="K113" t="b">
         <v>0</v>
@@ -5065,34 +5137,34 @@
     </row>
     <row r="114" spans="1:11">
       <c r="A114" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B114">
-        <v>2736</v>
+        <v>2740</v>
       </c>
       <c r="C114" t="s">
-        <v>198</v>
+        <v>223</v>
       </c>
       <c r="D114" t="s">
-        <v>232</v>
+        <v>256</v>
       </c>
       <c r="E114" t="s">
-        <v>242</v>
+        <v>264</v>
       </c>
       <c r="F114" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="G114" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="H114">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="I114" t="s">
-        <v>302</v>
+        <v>328</v>
       </c>
       <c r="J114" s="1">
-        <v>46578</v>
+        <v>46547</v>
       </c>
       <c r="K114" t="b">
         <v>0</v>
@@ -5100,34 +5172,34 @@
     </row>
     <row r="115" spans="1:11">
       <c r="A115" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B115">
-        <v>2737</v>
+        <v>2736</v>
       </c>
       <c r="C115" t="s">
-        <v>197</v>
+        <v>223</v>
       </c>
       <c r="D115" t="s">
-        <v>229</v>
+        <v>256</v>
       </c>
       <c r="E115" t="s">
-        <v>242</v>
+        <v>264</v>
       </c>
       <c r="F115" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="G115" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="H115">
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="I115" t="s">
-        <v>303</v>
+        <v>328</v>
       </c>
       <c r="J115" s="1">
-        <v>46592</v>
+        <v>46547</v>
       </c>
       <c r="K115" t="b">
         <v>0</v>
@@ -5135,34 +5207,34 @@
     </row>
     <row r="116" spans="1:11">
       <c r="A116" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B116">
-        <v>2737</v>
+        <v>2708</v>
       </c>
       <c r="C116" t="s">
-        <v>198</v>
+        <v>224</v>
       </c>
       <c r="D116" t="s">
-        <v>232</v>
+        <v>251</v>
       </c>
       <c r="E116" t="s">
-        <v>242</v>
+        <v>262</v>
       </c>
       <c r="F116" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="G116" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="H116">
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="I116" t="s">
-        <v>303</v>
+        <v>328</v>
       </c>
       <c r="J116" s="1">
-        <v>46592</v>
+        <v>46551</v>
       </c>
       <c r="K116" t="b">
         <v>0</v>
@@ -5170,34 +5242,34 @@
     </row>
     <row r="117" spans="1:11">
       <c r="A117" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B117">
-        <v>2731</v>
+        <v>2708</v>
       </c>
       <c r="C117" t="s">
-        <v>198</v>
+        <v>217</v>
       </c>
       <c r="D117" t="s">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="E117" t="s">
-        <v>246</v>
+        <v>262</v>
       </c>
       <c r="F117" t="s">
-        <v>281</v>
+        <v>298</v>
       </c>
       <c r="G117" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="H117">
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="I117" t="s">
-        <v>303</v>
+        <v>328</v>
       </c>
       <c r="J117" s="1">
-        <v>46603</v>
+        <v>46560</v>
       </c>
       <c r="K117" t="b">
         <v>0</v>
@@ -5205,34 +5277,34 @@
     </row>
     <row r="118" spans="1:11">
       <c r="A118" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B118">
-        <v>2738</v>
+        <v>2742</v>
       </c>
       <c r="C118" t="s">
-        <v>198</v>
+        <v>218</v>
       </c>
       <c r="D118" t="s">
-        <v>232</v>
+        <v>252</v>
       </c>
       <c r="E118" t="s">
-        <v>242</v>
+        <v>268</v>
       </c>
       <c r="F118" t="s">
-        <v>281</v>
+        <v>299</v>
       </c>
       <c r="G118" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="H118">
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="I118" t="s">
-        <v>303</v>
+        <v>328</v>
       </c>
       <c r="J118" s="1">
-        <v>46611</v>
+        <v>46568</v>
       </c>
       <c r="K118" t="b">
         <v>0</v>
@@ -5240,34 +5312,34 @@
     </row>
     <row r="119" spans="1:11">
       <c r="A119" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B119">
-        <v>2742</v>
+        <v>2737</v>
       </c>
       <c r="C119" t="s">
-        <v>198</v>
+        <v>218</v>
       </c>
       <c r="D119" t="s">
-        <v>230</v>
+        <v>252</v>
       </c>
       <c r="E119" t="s">
-        <v>243</v>
+        <v>264</v>
       </c>
       <c r="F119" t="s">
-        <v>272</v>
+        <v>299</v>
       </c>
       <c r="G119" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="H119">
-        <v>330</v>
+        <v>270</v>
       </c>
       <c r="I119" t="s">
-        <v>304</v>
+        <v>329</v>
       </c>
       <c r="J119" s="1">
-        <v>46631</v>
+        <v>46592</v>
       </c>
       <c r="K119" t="b">
         <v>0</v>
@@ -5275,34 +5347,34 @@
     </row>
     <row r="120" spans="1:11">
       <c r="A120" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B120">
-        <v>2727</v>
+        <v>2731</v>
       </c>
       <c r="C120" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="D120" t="s">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="E120" t="s">
-        <v>249</v>
+        <v>265</v>
       </c>
       <c r="F120" t="s">
-        <v>274</v>
+        <v>306</v>
       </c>
       <c r="G120" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="H120">
-        <v>330</v>
+        <v>270</v>
       </c>
       <c r="I120" t="s">
-        <v>304</v>
+        <v>329</v>
       </c>
       <c r="J120" s="1">
-        <v>46645</v>
+        <v>46603</v>
       </c>
       <c r="K120" t="b">
         <v>0</v>
@@ -5310,69 +5382,69 @@
     </row>
     <row r="121" spans="1:11">
       <c r="A121" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B121">
-        <v>2723</v>
+        <v>2738</v>
       </c>
       <c r="C121" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="D121" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="E121" t="s">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="F121" t="s">
-        <v>278</v>
+        <v>306</v>
       </c>
       <c r="G121" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="H121">
-        <v>-26</v>
+        <v>300</v>
       </c>
       <c r="I121" t="s">
-        <v>305</v>
+        <v>330</v>
       </c>
       <c r="J121" s="1">
-        <v>46254</v>
+        <v>46611</v>
       </c>
       <c r="K121" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:11">
       <c r="A122" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B122">
-        <v>2740</v>
+        <v>2742</v>
       </c>
       <c r="C122" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="D122" t="s">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="E122" t="s">
-        <v>242</v>
+        <v>268</v>
       </c>
       <c r="F122" t="s">
-        <v>272</v>
+        <v>296</v>
       </c>
       <c r="G122" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="H122">
-        <v>2</v>
+        <v>300</v>
       </c>
       <c r="I122" t="s">
-        <v>306</v>
+        <v>330</v>
       </c>
       <c r="J122" s="1">
-        <v>46284</v>
+        <v>46631</v>
       </c>
       <c r="K122" t="b">
         <v>0</v>
@@ -5380,34 +5452,34 @@
     </row>
     <row r="123" spans="1:11">
       <c r="A123" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B123">
         <v>2727</v>
       </c>
       <c r="C123" t="s">
-        <v>176</v>
+        <v>225</v>
       </c>
       <c r="D123" t="s">
-        <v>220</v>
+        <v>258</v>
       </c>
       <c r="E123" t="s">
-        <v>249</v>
+        <v>270</v>
       </c>
       <c r="F123" t="s">
-        <v>261</v>
+        <v>298</v>
       </c>
       <c r="G123" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="H123">
-        <v>12</v>
+        <v>330</v>
       </c>
       <c r="I123" t="s">
-        <v>307</v>
+        <v>331</v>
       </c>
       <c r="J123" s="1">
-        <v>46296</v>
+        <v>46645</v>
       </c>
       <c r="K123" t="b">
         <v>0</v>
@@ -5415,34 +5487,34 @@
     </row>
     <row r="124" spans="1:11">
       <c r="A124" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B124">
-        <v>2704</v>
+        <v>2703</v>
       </c>
       <c r="C124" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="D124" t="s">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="E124" t="s">
-        <v>243</v>
+        <v>262</v>
       </c>
       <c r="F124" t="s">
-        <v>251</v>
+        <v>300</v>
       </c>
       <c r="G124" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="H124">
-        <v>13</v>
+        <v>330</v>
       </c>
       <c r="I124" t="s">
-        <v>308</v>
+        <v>331</v>
       </c>
       <c r="J124" s="1">
-        <v>46293</v>
+        <v>46646</v>
       </c>
       <c r="K124" t="b">
         <v>0</v>
@@ -5450,34 +5522,34 @@
     </row>
     <row r="125" spans="1:11">
       <c r="A125" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B125">
-        <v>2733</v>
+        <v>2737</v>
       </c>
       <c r="C125" t="s">
-        <v>183</v>
+        <v>215</v>
       </c>
       <c r="D125" t="s">
-        <v>222</v>
+        <v>249</v>
       </c>
       <c r="E125" t="s">
-        <v>246</v>
+        <v>264</v>
       </c>
       <c r="F125" t="s">
-        <v>276</v>
+        <v>306</v>
       </c>
       <c r="G125" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="H125">
-        <v>23</v>
+        <v>330</v>
       </c>
       <c r="I125" t="s">
-        <v>309</v>
+        <v>331</v>
       </c>
       <c r="J125" s="1">
-        <v>46305</v>
+        <v>46652</v>
       </c>
       <c r="K125" t="b">
         <v>0</v>
@@ -5485,95 +5557,104 @@
     </row>
     <row r="126" spans="1:11">
       <c r="A126" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B126">
-        <v>2724</v>
+        <v>2736</v>
       </c>
       <c r="C126" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="D126" t="s">
-        <v>221</v>
+        <v>249</v>
       </c>
       <c r="E126" t="s">
-        <v>243</v>
+        <v>264</v>
       </c>
       <c r="F126" t="s">
-        <v>282</v>
+        <v>306</v>
       </c>
       <c r="G126" t="s">
-        <v>286</v>
+        <v>310</v>
       </c>
       <c r="H126">
-        <v>-1476</v>
+        <v>330</v>
+      </c>
+      <c r="I126" t="s">
+        <v>331</v>
       </c>
       <c r="J126" s="1">
-        <v>43773</v>
+        <v>46658</v>
       </c>
       <c r="K126" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:11">
       <c r="A127" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B127">
-        <v>2724</v>
+        <v>2738</v>
       </c>
       <c r="C127" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="D127" t="s">
-        <v>221</v>
+        <v>256</v>
       </c>
       <c r="E127" t="s">
-        <v>243</v>
+        <v>264</v>
       </c>
       <c r="F127" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="G127" t="s">
-        <v>286</v>
+        <v>310</v>
       </c>
       <c r="H127">
-        <v>-1469</v>
+        <v>330</v>
+      </c>
+      <c r="I127" t="s">
+        <v>331</v>
       </c>
       <c r="J127" s="1">
-        <v>43773</v>
+        <v>46659</v>
       </c>
       <c r="K127" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128" spans="1:11">
       <c r="A128" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B128">
-        <v>2736</v>
+        <v>2723</v>
       </c>
       <c r="C128" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="D128" t="s">
-        <v>221</v>
+        <v>247</v>
       </c>
       <c r="E128" t="s">
-        <v>242</v>
+        <v>267</v>
       </c>
       <c r="F128" t="s">
-        <v>283</v>
+        <v>303</v>
       </c>
       <c r="G128" t="s">
-        <v>286</v>
+        <v>310</v>
       </c>
       <c r="H128">
-        <v>-1250</v>
+        <v>-47</v>
+      </c>
+      <c r="I128" t="s">
+        <v>332</v>
       </c>
       <c r="J128" s="1">
-        <v>45295</v>
+        <v>46254</v>
       </c>
       <c r="K128" t="b">
         <v>1</v>
@@ -5581,31 +5662,34 @@
     </row>
     <row r="129" spans="1:11">
       <c r="A129" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B129">
-        <v>2740</v>
+        <v>2704</v>
       </c>
       <c r="C129" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="D129" t="s">
-        <v>221</v>
+        <v>251</v>
       </c>
       <c r="E129" t="s">
-        <v>242</v>
+        <v>261</v>
       </c>
       <c r="F129" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="G129" t="s">
-        <v>286</v>
+        <v>310</v>
       </c>
       <c r="H129">
-        <v>-1089</v>
+        <v>-8</v>
+      </c>
+      <c r="I129" t="s">
+        <v>333</v>
       </c>
       <c r="J129" s="1">
-        <v>45617</v>
+        <v>46293</v>
       </c>
       <c r="K129" t="b">
         <v>1</v>
@@ -5613,31 +5697,34 @@
     </row>
     <row r="130" spans="1:11">
       <c r="A130" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B130">
-        <v>2740</v>
+        <v>2727</v>
       </c>
       <c r="C130" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="D130" t="s">
-        <v>221</v>
+        <v>240</v>
       </c>
       <c r="E130" t="s">
-        <v>242</v>
+        <v>270</v>
       </c>
       <c r="F130" t="s">
-        <v>282</v>
+        <v>302</v>
       </c>
       <c r="G130" t="s">
-        <v>286</v>
+        <v>310</v>
       </c>
       <c r="H130">
-        <v>-1021</v>
+        <v>-8</v>
+      </c>
+      <c r="I130" t="s">
+        <v>333</v>
       </c>
       <c r="J130" s="1">
-        <v>45677</v>
+        <v>46296</v>
       </c>
       <c r="K130" t="b">
         <v>1</v>
@@ -5645,191 +5732,209 @@
     </row>
     <row r="131" spans="1:11">
       <c r="A131" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B131">
-        <v>2720</v>
+        <v>2733</v>
       </c>
       <c r="C131" t="s">
         <v>209</v>
       </c>
       <c r="D131" t="s">
-        <v>221</v>
+        <v>245</v>
       </c>
       <c r="E131" t="s">
-        <v>247</v>
+        <v>265</v>
       </c>
       <c r="F131" t="s">
-        <v>283</v>
+        <v>300</v>
       </c>
       <c r="G131" t="s">
-        <v>286</v>
+        <v>310</v>
       </c>
       <c r="H131">
-        <v>-1000</v>
+        <v>2</v>
+      </c>
+      <c r="I131" t="s">
+        <v>334</v>
       </c>
       <c r="J131" s="1">
-        <v>44944</v>
+        <v>46305</v>
       </c>
       <c r="K131" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132" spans="1:11">
       <c r="A132" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B132">
-        <v>2703</v>
+        <v>2739</v>
       </c>
       <c r="C132" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
       <c r="D132" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="E132" t="s">
-        <v>244</v>
+        <v>265</v>
       </c>
       <c r="F132" t="s">
-        <v>258</v>
+        <v>273</v>
       </c>
       <c r="G132" t="s">
-        <v>286</v>
+        <v>310</v>
       </c>
       <c r="H132">
-        <v>-296</v>
+        <v>18</v>
+      </c>
+      <c r="I132" t="s">
+        <v>335</v>
       </c>
       <c r="J132" s="1">
-        <v>46092</v>
+        <v>46317</v>
       </c>
       <c r="K132" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133" spans="1:11">
       <c r="A133" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B133">
-        <v>2703</v>
+        <v>2727</v>
       </c>
       <c r="C133" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="D133" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="E133" t="s">
-        <v>244</v>
+        <v>270</v>
       </c>
       <c r="F133" t="s">
-        <v>258</v>
+        <v>298</v>
       </c>
       <c r="G133" t="s">
-        <v>286</v>
+        <v>310</v>
       </c>
       <c r="H133">
-        <v>-51</v>
+        <v>30</v>
+      </c>
+      <c r="I133" t="s">
+        <v>321</v>
       </c>
       <c r="J133" s="1">
-        <v>46258</v>
+        <v>46333</v>
       </c>
       <c r="K133" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:11">
       <c r="A134" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B134">
-        <v>2702</v>
+        <v>2721</v>
       </c>
       <c r="C134" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="D134" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="E134" t="s">
-        <v>244</v>
+        <v>266</v>
       </c>
       <c r="F134" t="s">
-        <v>258</v>
+        <v>298</v>
       </c>
       <c r="G134" t="s">
-        <v>286</v>
+        <v>310</v>
       </c>
       <c r="H134">
-        <v>-49</v>
+        <v>35</v>
+      </c>
+      <c r="I134" t="s">
+        <v>336</v>
       </c>
       <c r="J134" s="1">
-        <v>46254</v>
+        <v>46338</v>
       </c>
       <c r="K134" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135" spans="1:11">
       <c r="A135" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B135">
-        <v>2702</v>
+        <v>2721</v>
       </c>
       <c r="C135" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D135" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="E135" t="s">
-        <v>244</v>
+        <v>266</v>
       </c>
       <c r="F135" t="s">
-        <v>258</v>
+        <v>306</v>
       </c>
       <c r="G135" t="s">
-        <v>286</v>
+        <v>310</v>
       </c>
       <c r="H135">
-        <v>-49</v>
+        <v>35</v>
+      </c>
+      <c r="I135" t="s">
+        <v>336</v>
       </c>
       <c r="J135" s="1">
-        <v>46254</v>
+        <v>46338</v>
       </c>
       <c r="K135" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136" spans="1:11">
       <c r="A136" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B136">
-        <v>2728</v>
+        <v>2722</v>
       </c>
       <c r="C136" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="D136" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="E136" t="s">
-        <v>243</v>
+        <v>263</v>
       </c>
       <c r="F136" t="s">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="G136" t="s">
-        <v>286</v>
+        <v>310</v>
       </c>
       <c r="H136">
-        <v>43</v>
+        <v>40</v>
+      </c>
+      <c r="I136" t="s">
+        <v>337</v>
       </c>
       <c r="J136" s="1">
-        <v>46440</v>
+        <v>46341</v>
       </c>
       <c r="K136" t="b">
         <v>0</v>
@@ -5837,31 +5942,34 @@
     </row>
     <row r="137" spans="1:11">
       <c r="A137" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B137">
-        <v>2728</v>
+        <v>2703</v>
       </c>
       <c r="C137" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="D137" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="E137" t="s">
-        <v>243</v>
+        <v>262</v>
       </c>
       <c r="F137" t="s">
-        <v>258</v>
+        <v>298</v>
       </c>
       <c r="G137" t="s">
-        <v>286</v>
+        <v>310</v>
       </c>
       <c r="H137">
-        <v>43</v>
+        <v>42</v>
+      </c>
+      <c r="I137" t="s">
+        <v>338</v>
       </c>
       <c r="J137" s="1">
-        <v>46440</v>
+        <v>46344</v>
       </c>
       <c r="K137" t="b">
         <v>0</v>
@@ -5869,319 +5977,319 @@
     </row>
     <row r="138" spans="1:11">
       <c r="A138" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B138">
-        <v>2732</v>
+        <v>2724</v>
       </c>
       <c r="C138" t="s">
-        <v>209</v>
+        <v>228</v>
       </c>
       <c r="D138" t="s">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="E138" t="s">
-        <v>242</v>
+        <v>261</v>
       </c>
       <c r="F138" t="s">
-        <v>282</v>
+        <v>307</v>
       </c>
       <c r="G138" t="s">
-        <v>286</v>
+        <v>311</v>
       </c>
       <c r="H138">
-        <v>102</v>
+        <v>-1476</v>
       </c>
       <c r="J138" s="1">
-        <v>46463</v>
+        <v>43773</v>
       </c>
       <c r="K138" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139" spans="1:11">
       <c r="A139" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B139">
-        <v>2741</v>
+        <v>2724</v>
       </c>
       <c r="C139" t="s">
-        <v>209</v>
+        <v>228</v>
       </c>
       <c r="D139" t="s">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="E139" t="s">
-        <v>242</v>
+        <v>261</v>
       </c>
       <c r="F139" t="s">
-        <v>282</v>
+        <v>307</v>
       </c>
       <c r="G139" t="s">
-        <v>286</v>
+        <v>311</v>
       </c>
       <c r="H139">
-        <v>106</v>
+        <v>-1469</v>
       </c>
       <c r="J139" s="1">
-        <v>46424</v>
+        <v>43773</v>
       </c>
       <c r="K139" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="140" spans="1:11">
       <c r="A140" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B140">
-        <v>2720</v>
+        <v>2736</v>
       </c>
       <c r="C140" t="s">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="D140" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E140" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="F140" t="s">
-        <v>258</v>
+        <v>308</v>
       </c>
       <c r="G140" t="s">
-        <v>286</v>
+        <v>311</v>
       </c>
       <c r="H140">
-        <v>119</v>
+        <v>-1280</v>
       </c>
       <c r="J140" s="1">
-        <v>46407</v>
+        <v>45295</v>
       </c>
       <c r="K140" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141" spans="1:11">
       <c r="A141" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B141">
-        <v>2720</v>
+        <v>2740</v>
       </c>
       <c r="C141" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="D141" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E141" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="F141" t="s">
-        <v>258</v>
+        <v>307</v>
       </c>
       <c r="G141" t="s">
-        <v>286</v>
+        <v>311</v>
       </c>
       <c r="H141">
-        <v>130</v>
+        <v>-1141</v>
       </c>
       <c r="J141" s="1">
-        <v>46416</v>
+        <v>45617</v>
       </c>
       <c r="K141" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="142" spans="1:11">
       <c r="A142" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B142">
-        <v>2723</v>
+        <v>2740</v>
       </c>
       <c r="C142" t="s">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="D142" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E142" t="s">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="F142" t="s">
-        <v>258</v>
+        <v>307</v>
       </c>
       <c r="G142" t="s">
-        <v>286</v>
+        <v>311</v>
       </c>
       <c r="H142">
-        <v>152</v>
+        <v>-1073</v>
       </c>
       <c r="J142" s="1">
-        <v>46295</v>
+        <v>45677</v>
       </c>
       <c r="K142" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="143" spans="1:11">
       <c r="A143" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B143">
-        <v>2723</v>
+        <v>2702</v>
       </c>
       <c r="C143" t="s">
-        <v>211</v>
+        <v>229</v>
       </c>
       <c r="D143" t="s">
-        <v>241</v>
+        <v>259</v>
       </c>
       <c r="E143" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="F143" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="G143" t="s">
-        <v>286</v>
+        <v>311</v>
       </c>
       <c r="H143">
-        <v>152</v>
+        <v>-78</v>
       </c>
       <c r="J143" s="1">
-        <v>46295</v>
+        <v>46254</v>
       </c>
       <c r="K143" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="144" spans="1:11">
       <c r="A144" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B144">
-        <v>2728</v>
+        <v>2702</v>
       </c>
       <c r="C144" t="s">
-        <v>209</v>
+        <v>230</v>
       </c>
       <c r="D144" t="s">
-        <v>221</v>
+        <v>259</v>
       </c>
       <c r="E144" t="s">
-        <v>243</v>
+        <v>262</v>
       </c>
       <c r="F144" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="G144" t="s">
-        <v>286</v>
+        <v>311</v>
       </c>
       <c r="H144">
-        <v>163</v>
+        <v>-78</v>
       </c>
       <c r="J144" s="1">
-        <v>46592</v>
+        <v>46254</v>
       </c>
       <c r="K144" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145" spans="1:11">
       <c r="A145" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B145">
-        <v>2709</v>
+        <v>2720</v>
       </c>
       <c r="C145" t="s">
-        <v>213</v>
+        <v>228</v>
       </c>
       <c r="D145" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E145" t="s">
-        <v>247</v>
+        <v>266</v>
       </c>
       <c r="F145" t="s">
-        <v>258</v>
+        <v>308</v>
       </c>
       <c r="G145" t="s">
-        <v>286</v>
+        <v>311</v>
       </c>
       <c r="H145">
-        <v>172</v>
+        <v>-40</v>
       </c>
       <c r="J145" s="1">
-        <v>46448</v>
+        <v>46092</v>
       </c>
       <c r="K145" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146" spans="1:11">
       <c r="A146" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B146">
-        <v>2709</v>
+        <v>2731</v>
       </c>
       <c r="C146" t="s">
-        <v>212</v>
+        <v>228</v>
       </c>
       <c r="D146" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E146" t="s">
-        <v>247</v>
+        <v>265</v>
       </c>
       <c r="F146" t="s">
-        <v>258</v>
+        <v>308</v>
       </c>
       <c r="G146" t="s">
-        <v>286</v>
+        <v>311</v>
       </c>
       <c r="H146">
-        <v>174</v>
+        <v>-4</v>
       </c>
       <c r="J146" s="1">
-        <v>46450</v>
+        <v>46298</v>
       </c>
       <c r="K146" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="147" spans="1:11">
       <c r="A147" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B147">
-        <v>2706</v>
+        <v>2728</v>
       </c>
       <c r="C147" t="s">
-        <v>214</v>
+        <v>229</v>
       </c>
       <c r="D147" t="s">
-        <v>221</v>
+        <v>259</v>
       </c>
       <c r="E147" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="F147" t="s">
-        <v>252</v>
+        <v>278</v>
       </c>
       <c r="G147" t="s">
-        <v>286</v>
+        <v>311</v>
       </c>
       <c r="H147">
-        <v>248</v>
+        <v>43</v>
       </c>
       <c r="J147" s="1">
-        <v>46571</v>
+        <v>46440</v>
       </c>
       <c r="K147" t="b">
         <v>0</v>
@@ -6189,31 +6297,31 @@
     </row>
     <row r="148" spans="1:11">
       <c r="A148" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B148">
-        <v>2742</v>
+        <v>2728</v>
       </c>
       <c r="C148" t="s">
-        <v>211</v>
+        <v>230</v>
       </c>
       <c r="D148" t="s">
-        <v>241</v>
+        <v>259</v>
       </c>
       <c r="E148" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="F148" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="G148" t="s">
-        <v>286</v>
+        <v>311</v>
       </c>
       <c r="H148">
-        <v>270</v>
+        <v>43</v>
       </c>
       <c r="J148" s="1">
-        <v>46524</v>
+        <v>46440</v>
       </c>
       <c r="K148" t="b">
         <v>0</v>
@@ -6221,31 +6329,31 @@
     </row>
     <row r="149" spans="1:11">
       <c r="A149" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B149">
-        <v>2733</v>
+        <v>2720</v>
       </c>
       <c r="C149" t="s">
-        <v>209</v>
+        <v>231</v>
       </c>
       <c r="D149" t="s">
-        <v>221</v>
+        <v>260</v>
       </c>
       <c r="E149" t="s">
-        <v>246</v>
+        <v>266</v>
       </c>
       <c r="F149" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="G149" t="s">
-        <v>286</v>
+        <v>311</v>
       </c>
       <c r="H149">
-        <v>281</v>
+        <v>72</v>
       </c>
       <c r="J149" s="1">
-        <v>46459</v>
+        <v>46386</v>
       </c>
       <c r="K149" t="b">
         <v>0</v>
@@ -6253,31 +6361,31 @@
     </row>
     <row r="150" spans="1:11">
       <c r="A150" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B150">
-        <v>2738</v>
+        <v>2723</v>
       </c>
       <c r="C150" t="s">
-        <v>209</v>
+        <v>231</v>
       </c>
       <c r="D150" t="s">
-        <v>221</v>
+        <v>260</v>
       </c>
       <c r="E150" t="s">
-        <v>242</v>
+        <v>267</v>
       </c>
       <c r="F150" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="G150" t="s">
-        <v>286</v>
+        <v>311</v>
       </c>
       <c r="H150">
-        <v>288</v>
+        <v>79</v>
       </c>
       <c r="J150" s="1">
-        <v>46531</v>
+        <v>46326</v>
       </c>
       <c r="K150" t="b">
         <v>0</v>
@@ -6285,31 +6393,31 @@
     </row>
     <row r="151" spans="1:11">
       <c r="A151" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B151">
-        <v>2738</v>
+        <v>2723</v>
       </c>
       <c r="C151" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="D151" t="s">
-        <v>221</v>
+        <v>259</v>
       </c>
       <c r="E151" t="s">
-        <v>242</v>
+        <v>267</v>
       </c>
       <c r="F151" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="G151" t="s">
-        <v>286</v>
+        <v>311</v>
       </c>
       <c r="H151">
-        <v>294</v>
+        <v>79</v>
       </c>
       <c r="J151" s="1">
-        <v>46535</v>
+        <v>46326</v>
       </c>
       <c r="K151" t="b">
         <v>0</v>
@@ -6317,31 +6425,31 @@
     </row>
     <row r="152" spans="1:11">
       <c r="A152" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B152">
-        <v>2739</v>
+        <v>2720</v>
       </c>
       <c r="C152" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="D152" t="s">
-        <v>221</v>
+        <v>259</v>
       </c>
       <c r="E152" t="s">
-        <v>246</v>
+        <v>266</v>
       </c>
       <c r="F152" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="G152" t="s">
-        <v>286</v>
+        <v>311</v>
       </c>
       <c r="H152">
-        <v>295</v>
+        <v>83</v>
       </c>
       <c r="J152" s="1">
-        <v>46468</v>
+        <v>46395</v>
       </c>
       <c r="K152" t="b">
         <v>0</v>
@@ -6349,31 +6457,31 @@
     </row>
     <row r="153" spans="1:11">
       <c r="A153" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B153">
-        <v>2739</v>
+        <v>2732</v>
       </c>
       <c r="C153" t="s">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="D153" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E153" t="s">
-        <v>246</v>
+        <v>264</v>
       </c>
       <c r="F153" t="s">
-        <v>258</v>
+        <v>307</v>
       </c>
       <c r="G153" t="s">
-        <v>286</v>
+        <v>311</v>
       </c>
       <c r="H153">
-        <v>318</v>
+        <v>102</v>
       </c>
       <c r="J153" s="1">
-        <v>46482</v>
+        <v>46463</v>
       </c>
       <c r="K153" t="b">
         <v>0</v>
@@ -6381,31 +6489,31 @@
     </row>
     <row r="154" spans="1:11">
       <c r="A154" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B154">
-        <v>2733</v>
+        <v>2741</v>
       </c>
       <c r="C154" t="s">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="D154" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E154" t="s">
-        <v>246</v>
+        <v>264</v>
       </c>
       <c r="F154" t="s">
-        <v>258</v>
+        <v>307</v>
       </c>
       <c r="G154" t="s">
-        <v>286</v>
+        <v>311</v>
       </c>
       <c r="H154">
-        <v>332</v>
+        <v>106</v>
       </c>
       <c r="J154" s="1">
-        <v>46490</v>
+        <v>46423</v>
       </c>
       <c r="K154" t="b">
         <v>0</v>
@@ -6413,31 +6521,31 @@
     </row>
     <row r="155" spans="1:11">
       <c r="A155" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B155">
-        <v>2733</v>
+        <v>2739</v>
       </c>
       <c r="C155" t="s">
-        <v>211</v>
+        <v>231</v>
       </c>
       <c r="D155" t="s">
-        <v>241</v>
+        <v>260</v>
       </c>
       <c r="E155" t="s">
-        <v>246</v>
+        <v>265</v>
       </c>
       <c r="F155" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="G155" t="s">
-        <v>286</v>
+        <v>311</v>
       </c>
       <c r="H155">
-        <v>332</v>
+        <v>107</v>
       </c>
       <c r="J155" s="1">
-        <v>46490</v>
+        <v>46376</v>
       </c>
       <c r="K155" t="b">
         <v>0</v>
@@ -6445,31 +6553,31 @@
     </row>
     <row r="156" spans="1:11">
       <c r="A156" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B156">
-        <v>2720</v>
+        <v>2728</v>
       </c>
       <c r="C156" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="D156" t="s">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="E156" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="F156" t="s">
-        <v>272</v>
+        <v>307</v>
       </c>
       <c r="G156" t="s">
-        <v>286</v>
+        <v>311</v>
       </c>
       <c r="H156">
-        <v>378</v>
+        <v>163</v>
       </c>
       <c r="J156" s="1">
-        <v>46603</v>
+        <v>46592</v>
       </c>
       <c r="K156" t="b">
         <v>0</v>
@@ -6477,31 +6585,31 @@
     </row>
     <row r="157" spans="1:11">
       <c r="A157" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B157">
-        <v>2731</v>
+        <v>2709</v>
       </c>
       <c r="C157" t="s">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="D157" t="s">
-        <v>221</v>
+        <v>259</v>
       </c>
       <c r="E157" t="s">
-        <v>246</v>
+        <v>266</v>
       </c>
       <c r="F157" t="s">
-        <v>252</v>
+        <v>278</v>
       </c>
       <c r="G157" t="s">
-        <v>286</v>
+        <v>311</v>
       </c>
       <c r="H157">
-        <v>385</v>
+        <v>168</v>
       </c>
       <c r="J157" s="1">
-        <v>46526</v>
+        <v>46456</v>
       </c>
       <c r="K157" t="b">
         <v>0</v>
@@ -6509,31 +6617,31 @@
     </row>
     <row r="158" spans="1:11">
       <c r="A158" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B158">
-        <v>2719</v>
+        <v>2709</v>
       </c>
       <c r="C158" t="s">
-        <v>210</v>
+        <v>229</v>
       </c>
       <c r="D158" t="s">
-        <v>240</v>
+        <v>259</v>
       </c>
       <c r="E158" t="s">
-        <v>245</v>
+        <v>266</v>
       </c>
       <c r="F158" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="G158" t="s">
-        <v>286</v>
+        <v>311</v>
       </c>
       <c r="H158">
-        <v>400</v>
+        <v>170</v>
       </c>
       <c r="J158" s="1">
-        <v>46643</v>
+        <v>46458</v>
       </c>
       <c r="K158" t="b">
         <v>0</v>
@@ -6541,31 +6649,31 @@
     </row>
     <row r="159" spans="1:11">
       <c r="A159" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B159">
-        <v>2739</v>
+        <v>2733</v>
       </c>
       <c r="C159" t="s">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="D159" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E159" t="s">
-        <v>246</v>
+        <v>265</v>
       </c>
       <c r="F159" t="s">
-        <v>258</v>
+        <v>308</v>
       </c>
       <c r="G159" t="s">
-        <v>286</v>
+        <v>311</v>
       </c>
       <c r="H159">
-        <v>459</v>
+        <v>188</v>
       </c>
       <c r="J159" s="1">
-        <v>46568</v>
+        <v>46416</v>
       </c>
       <c r="K159" t="b">
         <v>0</v>
@@ -6573,31 +6681,31 @@
     </row>
     <row r="160" spans="1:11">
       <c r="A160" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B160">
-        <v>2724</v>
+        <v>2738</v>
       </c>
       <c r="C160" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="D160" t="s">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="E160" t="s">
-        <v>243</v>
+        <v>264</v>
       </c>
       <c r="F160" t="s">
-        <v>272</v>
+        <v>308</v>
       </c>
       <c r="G160" t="s">
-        <v>286</v>
+        <v>311</v>
       </c>
       <c r="H160">
-        <v>488</v>
+        <v>232</v>
       </c>
       <c r="J160" s="1">
-        <v>46190</v>
+        <v>46509</v>
       </c>
       <c r="K160" t="b">
         <v>0</v>
@@ -6605,31 +6713,31 @@
     </row>
     <row r="161" spans="1:11">
       <c r="A161" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B161">
-        <v>2723</v>
+        <v>2738</v>
       </c>
       <c r="C161" t="s">
-        <v>209</v>
+        <v>228</v>
       </c>
       <c r="D161" t="s">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="E161" t="s">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="F161" t="s">
-        <v>283</v>
+        <v>308</v>
       </c>
       <c r="G161" t="s">
-        <v>286</v>
+        <v>311</v>
       </c>
       <c r="H161">
-        <v>721</v>
+        <v>238</v>
       </c>
       <c r="J161" s="1">
-        <v>46358</v>
+        <v>46513</v>
       </c>
       <c r="K161" t="b">
         <v>0</v>
@@ -6637,31 +6745,31 @@
     </row>
     <row r="162" spans="1:11">
       <c r="A162" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B162">
-        <v>2723</v>
+        <v>2733</v>
       </c>
       <c r="C162" t="s">
-        <v>209</v>
+        <v>231</v>
       </c>
       <c r="D162" t="s">
-        <v>221</v>
+        <v>260</v>
       </c>
       <c r="E162" t="s">
-        <v>250</v>
+        <v>265</v>
       </c>
       <c r="F162" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="G162" t="s">
-        <v>286</v>
+        <v>311</v>
       </c>
       <c r="H162">
-        <v>721</v>
+        <v>239</v>
       </c>
       <c r="J162" s="1">
-        <v>46358</v>
+        <v>46445</v>
       </c>
       <c r="K162" t="b">
         <v>0</v>
@@ -6669,31 +6777,31 @@
     </row>
     <row r="163" spans="1:11">
       <c r="A163" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B163">
-        <v>2723</v>
+        <v>2733</v>
       </c>
       <c r="C163" t="s">
-        <v>212</v>
+        <v>232</v>
       </c>
       <c r="D163" t="s">
-        <v>241</v>
+        <v>259</v>
       </c>
       <c r="E163" t="s">
-        <v>250</v>
+        <v>265</v>
       </c>
       <c r="F163" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="G163" t="s">
-        <v>286</v>
+        <v>311</v>
       </c>
       <c r="H163">
-        <v>850</v>
+        <v>239</v>
       </c>
       <c r="J163" s="1">
-        <v>46374</v>
+        <v>46445</v>
       </c>
       <c r="K163" t="b">
         <v>0</v>
@@ -6701,31 +6809,31 @@
     </row>
     <row r="164" spans="1:11">
       <c r="A164" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B164">
-        <v>2723</v>
+        <v>2706</v>
       </c>
       <c r="C164" t="s">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="D164" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E164" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="F164" t="s">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="G164" t="s">
-        <v>286</v>
+        <v>311</v>
       </c>
       <c r="H164">
-        <v>850</v>
+        <v>248</v>
       </c>
       <c r="J164" s="1">
-        <v>46374</v>
+        <v>46592</v>
       </c>
       <c r="K164" t="b">
         <v>0</v>
@@ -6733,31 +6841,31 @@
     </row>
     <row r="165" spans="1:11">
       <c r="A165" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B165">
-        <v>2723</v>
+        <v>2739</v>
       </c>
       <c r="C165" t="s">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="D165" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E165" t="s">
+        <v>265</v>
+      </c>
+      <c r="F165" t="s">
+        <v>308</v>
+      </c>
+      <c r="G165" t="s">
+        <v>311</v>
+      </c>
+      <c r="H165">
         <v>250</v>
       </c>
-      <c r="F165" t="s">
-        <v>258</v>
-      </c>
-      <c r="G165" t="s">
-        <v>286</v>
-      </c>
-      <c r="H165">
-        <v>1661</v>
-      </c>
       <c r="J165" s="1">
-        <v>46529</v>
+        <v>46461</v>
       </c>
       <c r="K165" t="b">
         <v>0</v>
@@ -6765,31 +6873,31 @@
     </row>
     <row r="166" spans="1:11">
       <c r="A166" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B166">
-        <v>2723</v>
+        <v>2742</v>
       </c>
       <c r="C166" t="s">
-        <v>211</v>
+        <v>232</v>
       </c>
       <c r="D166" t="s">
-        <v>241</v>
+        <v>259</v>
       </c>
       <c r="E166" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="F166" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="G166" t="s">
-        <v>286</v>
+        <v>311</v>
       </c>
       <c r="H166">
-        <v>1661</v>
+        <v>256</v>
       </c>
       <c r="J166" s="1">
-        <v>46529</v>
+        <v>46622</v>
       </c>
       <c r="K166" t="b">
         <v>0</v>
@@ -6797,31 +6905,31 @@
     </row>
     <row r="167" spans="1:11">
       <c r="A167" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B167">
-        <v>2724</v>
+        <v>2720</v>
       </c>
       <c r="C167" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="D167" t="s">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="E167" t="s">
-        <v>243</v>
+        <v>266</v>
       </c>
       <c r="F167" t="s">
-        <v>272</v>
+        <v>296</v>
       </c>
       <c r="G167" t="s">
-        <v>286</v>
+        <v>311</v>
       </c>
       <c r="H167">
-        <v>25565</v>
+        <v>331</v>
       </c>
       <c r="J167" s="1">
-        <v>46190</v>
+        <v>46582</v>
       </c>
       <c r="K167" t="b">
         <v>0</v>
@@ -6829,31 +6937,31 @@
     </row>
     <row r="168" spans="1:11">
       <c r="A168" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B168">
-        <v>2724</v>
+        <v>2739</v>
       </c>
       <c r="C168" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="D168" t="s">
-        <v>221</v>
+        <v>259</v>
       </c>
       <c r="E168" t="s">
-        <v>243</v>
+        <v>265</v>
       </c>
       <c r="F168" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="G168" t="s">
-        <v>286</v>
+        <v>311</v>
       </c>
       <c r="H168">
-        <v>25567</v>
+        <v>335</v>
       </c>
       <c r="J168" s="1">
-        <v>46190</v>
+        <v>46513</v>
       </c>
       <c r="K168" t="b">
         <v>0</v>
@@ -6861,33 +6969,513 @@
     </row>
     <row r="169" spans="1:11">
       <c r="A169" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B169">
+        <v>2719</v>
+      </c>
+      <c r="C169" t="s">
+        <v>231</v>
+      </c>
+      <c r="D169" t="s">
+        <v>260</v>
+      </c>
+      <c r="E169" t="s">
+        <v>263</v>
+      </c>
+      <c r="F169" t="s">
+        <v>278</v>
+      </c>
+      <c r="G169" t="s">
+        <v>311</v>
+      </c>
+      <c r="H169">
+        <v>363</v>
+      </c>
+      <c r="J169" s="1">
+        <v>46638</v>
+      </c>
+      <c r="K169" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:11">
+      <c r="A170" t="s">
+        <v>175</v>
+      </c>
+      <c r="B170">
+        <v>2731</v>
+      </c>
+      <c r="C170" t="s">
+        <v>235</v>
+      </c>
+      <c r="D170" t="s">
+        <v>239</v>
+      </c>
+      <c r="E170" t="s">
+        <v>265</v>
+      </c>
+      <c r="F170" t="s">
+        <v>271</v>
+      </c>
+      <c r="G170" t="s">
+        <v>311</v>
+      </c>
+      <c r="H170">
+        <v>380</v>
+      </c>
+      <c r="J170" s="1">
+        <v>46530</v>
+      </c>
+      <c r="K170" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:11">
+      <c r="A171" t="s">
+        <v>176</v>
+      </c>
+      <c r="B171">
+        <v>2737</v>
+      </c>
+      <c r="C171" t="s">
+        <v>229</v>
+      </c>
+      <c r="D171" t="s">
+        <v>259</v>
+      </c>
+      <c r="E171" t="s">
+        <v>264</v>
+      </c>
+      <c r="F171" t="s">
+        <v>278</v>
+      </c>
+      <c r="G171" t="s">
+        <v>311</v>
+      </c>
+      <c r="H171">
+        <v>403</v>
+      </c>
+      <c r="J171" s="1">
+        <v>46648</v>
+      </c>
+      <c r="K171" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:11">
+      <c r="A172" t="s">
+        <v>177</v>
+      </c>
+      <c r="B172">
+        <v>2737</v>
+      </c>
+      <c r="C172" t="s">
+        <v>230</v>
+      </c>
+      <c r="D172" t="s">
+        <v>259</v>
+      </c>
+      <c r="E172" t="s">
+        <v>264</v>
+      </c>
+      <c r="F172" t="s">
+        <v>278</v>
+      </c>
+      <c r="G172" t="s">
+        <v>311</v>
+      </c>
+      <c r="H172">
+        <v>403</v>
+      </c>
+      <c r="J172" s="1">
+        <v>46648</v>
+      </c>
+      <c r="K172" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="1:11">
+      <c r="A173" t="s">
+        <v>178</v>
+      </c>
+      <c r="B173">
+        <v>2731</v>
+      </c>
+      <c r="C173" t="s">
+        <v>231</v>
+      </c>
+      <c r="D173" t="s">
+        <v>260</v>
+      </c>
+      <c r="E173" t="s">
+        <v>265</v>
+      </c>
+      <c r="F173" t="s">
+        <v>278</v>
+      </c>
+      <c r="G173" t="s">
+        <v>311</v>
+      </c>
+      <c r="H173">
+        <v>409</v>
+      </c>
+      <c r="J173" s="1">
+        <v>46548</v>
+      </c>
+      <c r="K173" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:11">
+      <c r="A174" t="s">
+        <v>179</v>
+      </c>
+      <c r="B174">
         <v>2724</v>
       </c>
-      <c r="C169" t="s">
-        <v>219</v>
-      </c>
-      <c r="D169" t="s">
-        <v>221</v>
-      </c>
-      <c r="E169" t="s">
-        <v>243</v>
-      </c>
-      <c r="F169" t="s">
-        <v>272</v>
-      </c>
-      <c r="G169" t="s">
-        <v>286</v>
-      </c>
-      <c r="H169">
+      <c r="C174" t="s">
+        <v>236</v>
+      </c>
+      <c r="D174" t="s">
+        <v>239</v>
+      </c>
+      <c r="E174" t="s">
+        <v>261</v>
+      </c>
+      <c r="F174" t="s">
+        <v>296</v>
+      </c>
+      <c r="G174" t="s">
+        <v>311</v>
+      </c>
+      <c r="H174">
+        <v>488</v>
+      </c>
+      <c r="J174" s="1">
+        <v>46190</v>
+      </c>
+      <c r="K174" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:11">
+      <c r="A175" t="s">
+        <v>180</v>
+      </c>
+      <c r="B175">
+        <v>2739</v>
+      </c>
+      <c r="C175" t="s">
+        <v>231</v>
+      </c>
+      <c r="D175" t="s">
+        <v>260</v>
+      </c>
+      <c r="E175" t="s">
+        <v>265</v>
+      </c>
+      <c r="F175" t="s">
+        <v>278</v>
+      </c>
+      <c r="G175" t="s">
+        <v>311</v>
+      </c>
+      <c r="H175">
+        <v>533</v>
+      </c>
+      <c r="J175" s="1">
+        <v>46634</v>
+      </c>
+      <c r="K175" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:11">
+      <c r="A176" t="s">
+        <v>181</v>
+      </c>
+      <c r="B176">
+        <v>2723</v>
+      </c>
+      <c r="C176" t="s">
+        <v>228</v>
+      </c>
+      <c r="D176" t="s">
+        <v>239</v>
+      </c>
+      <c r="E176" t="s">
+        <v>267</v>
+      </c>
+      <c r="F176" t="s">
+        <v>308</v>
+      </c>
+      <c r="G176" t="s">
+        <v>311</v>
+      </c>
+      <c r="H176">
+        <v>648</v>
+      </c>
+      <c r="J176" s="1">
+        <v>46377</v>
+      </c>
+      <c r="K176" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="1:11">
+      <c r="A177" t="s">
+        <v>182</v>
+      </c>
+      <c r="B177">
+        <v>2723</v>
+      </c>
+      <c r="C177" t="s">
+        <v>228</v>
+      </c>
+      <c r="D177" t="s">
+        <v>239</v>
+      </c>
+      <c r="E177" t="s">
+        <v>267</v>
+      </c>
+      <c r="F177" t="s">
+        <v>308</v>
+      </c>
+      <c r="G177" t="s">
+        <v>311</v>
+      </c>
+      <c r="H177">
+        <v>648</v>
+      </c>
+      <c r="J177" s="1">
+        <v>46377</v>
+      </c>
+      <c r="K177" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:11">
+      <c r="A178" t="s">
+        <v>183</v>
+      </c>
+      <c r="B178">
+        <v>2723</v>
+      </c>
+      <c r="C178" t="s">
+        <v>229</v>
+      </c>
+      <c r="D178" t="s">
+        <v>259</v>
+      </c>
+      <c r="E178" t="s">
+        <v>267</v>
+      </c>
+      <c r="F178" t="s">
+        <v>278</v>
+      </c>
+      <c r="G178" t="s">
+        <v>311</v>
+      </c>
+      <c r="H178">
+        <v>777</v>
+      </c>
+      <c r="J178" s="1">
+        <v>46396</v>
+      </c>
+      <c r="K178" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="1:11">
+      <c r="A179" t="s">
+        <v>184</v>
+      </c>
+      <c r="B179">
+        <v>2723</v>
+      </c>
+      <c r="C179" t="s">
+        <v>230</v>
+      </c>
+      <c r="D179" t="s">
+        <v>259</v>
+      </c>
+      <c r="E179" t="s">
+        <v>267</v>
+      </c>
+      <c r="F179" t="s">
+        <v>278</v>
+      </c>
+      <c r="G179" t="s">
+        <v>311</v>
+      </c>
+      <c r="H179">
+        <v>777</v>
+      </c>
+      <c r="J179" s="1">
+        <v>46396</v>
+      </c>
+      <c r="K179" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="1:11">
+      <c r="A180" t="s">
+        <v>185</v>
+      </c>
+      <c r="B180">
+        <v>2723</v>
+      </c>
+      <c r="C180" t="s">
+        <v>232</v>
+      </c>
+      <c r="D180" t="s">
+        <v>259</v>
+      </c>
+      <c r="E180" t="s">
+        <v>267</v>
+      </c>
+      <c r="F180" t="s">
+        <v>278</v>
+      </c>
+      <c r="G180" t="s">
+        <v>311</v>
+      </c>
+      <c r="H180">
+        <v>1588</v>
+      </c>
+      <c r="J180" s="1">
+        <v>46559</v>
+      </c>
+      <c r="K180" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:11">
+      <c r="A181" t="s">
+        <v>186</v>
+      </c>
+      <c r="B181">
+        <v>2723</v>
+      </c>
+      <c r="C181" t="s">
+        <v>231</v>
+      </c>
+      <c r="D181" t="s">
+        <v>260</v>
+      </c>
+      <c r="E181" t="s">
+        <v>267</v>
+      </c>
+      <c r="F181" t="s">
+        <v>278</v>
+      </c>
+      <c r="G181" t="s">
+        <v>311</v>
+      </c>
+      <c r="H181">
+        <v>1588</v>
+      </c>
+      <c r="J181" s="1">
+        <v>46559</v>
+      </c>
+      <c r="K181" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="1:11">
+      <c r="A182" t="s">
+        <v>187</v>
+      </c>
+      <c r="B182">
+        <v>2724</v>
+      </c>
+      <c r="C182" t="s">
+        <v>233</v>
+      </c>
+      <c r="D182" t="s">
+        <v>239</v>
+      </c>
+      <c r="E182" t="s">
+        <v>261</v>
+      </c>
+      <c r="F182" t="s">
+        <v>296</v>
+      </c>
+      <c r="G182" t="s">
+        <v>311</v>
+      </c>
+      <c r="H182">
+        <v>25565</v>
+      </c>
+      <c r="J182" s="1">
+        <v>46190</v>
+      </c>
+      <c r="K182" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:11">
+      <c r="A183" t="s">
+        <v>188</v>
+      </c>
+      <c r="B183">
+        <v>2724</v>
+      </c>
+      <c r="C183" t="s">
+        <v>237</v>
+      </c>
+      <c r="D183" t="s">
+        <v>239</v>
+      </c>
+      <c r="E183" t="s">
+        <v>261</v>
+      </c>
+      <c r="F183" t="s">
+        <v>296</v>
+      </c>
+      <c r="G183" t="s">
+        <v>311</v>
+      </c>
+      <c r="H183">
+        <v>25567</v>
+      </c>
+      <c r="J183" s="1">
+        <v>46190</v>
+      </c>
+      <c r="K183" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:11">
+      <c r="A184" t="s">
+        <v>189</v>
+      </c>
+      <c r="B184">
+        <v>2724</v>
+      </c>
+      <c r="C184" t="s">
+        <v>238</v>
+      </c>
+      <c r="D184" t="s">
+        <v>239</v>
+      </c>
+      <c r="E184" t="s">
+        <v>261</v>
+      </c>
+      <c r="F184" t="s">
+        <v>296</v>
+      </c>
+      <c r="G184" t="s">
+        <v>311</v>
+      </c>
+      <c r="H184">
         <v>31293</v>
       </c>
-      <c r="J169" s="1">
+      <c r="J184" s="1">
         <v>46190</v>
       </c>
-      <c r="K169" t="b">
+      <c r="K184" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Coordenadoria/02_Dados_Tratados/base_vencimentos_tratada.xlsx
+++ b/Coordenadoria/02_Dados_Tratados/base_vencimentos_tratada.xlsx
@@ -1040,8 +1040,16 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1057,7 +1065,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1065,12 +1073,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1370,37 +1396,37 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1429,7 +1455,7 @@
       <c r="H2">
         <v>-2354.2</v>
       </c>
-      <c r="J2" s="1">
+      <c r="J2" s="2">
         <v>40669</v>
       </c>
       <c r="K2" t="b">
@@ -1461,7 +1487,7 @@
       <c r="H3">
         <v>-934.3</v>
       </c>
-      <c r="J3" s="1">
+      <c r="J3" s="2">
         <v>40669</v>
       </c>
       <c r="K3" t="b">
@@ -1493,7 +1519,7 @@
       <c r="H4">
         <v>-891.7</v>
       </c>
-      <c r="J4" s="1">
+      <c r="J4" s="2">
         <v>44884</v>
       </c>
       <c r="K4" t="b">
@@ -1525,7 +1551,7 @@
       <c r="H5">
         <v>-589.5</v>
       </c>
-      <c r="J5" s="1">
+      <c r="J5" s="2">
         <v>43855</v>
       </c>
       <c r="K5" t="b">
@@ -1557,7 +1583,7 @@
       <c r="H6">
         <v>-562</v>
       </c>
-      <c r="J6" s="1">
+      <c r="J6" s="2">
         <v>45804</v>
       </c>
       <c r="K6" t="b">
@@ -1589,7 +1615,7 @@
       <c r="H7">
         <v>-560.5</v>
       </c>
-      <c r="J7" s="1">
+      <c r="J7" s="2">
         <v>45804</v>
       </c>
       <c r="K7" t="b">
@@ -1621,7 +1647,7 @@
       <c r="H8">
         <v>-531.8</v>
       </c>
-      <c r="J8" s="1">
+      <c r="J8" s="2">
         <v>46014</v>
       </c>
       <c r="K8" t="b">
@@ -1653,7 +1679,7 @@
       <c r="H9">
         <v>-529.1</v>
       </c>
-      <c r="J9" s="1">
+      <c r="J9" s="2">
         <v>46014</v>
       </c>
       <c r="K9" t="b">
@@ -1685,7 +1711,7 @@
       <c r="H10">
         <v>-391.8</v>
       </c>
-      <c r="J10" s="1">
+      <c r="J10" s="2">
         <v>32786</v>
       </c>
       <c r="K10" t="b">
@@ -1717,7 +1743,7 @@
       <c r="H11">
         <v>-391.8</v>
       </c>
-      <c r="J11" s="1">
+      <c r="J11" s="2">
         <v>42769</v>
       </c>
       <c r="K11" t="b">
@@ -1749,7 +1775,7 @@
       <c r="H12">
         <v>-288.8</v>
       </c>
-      <c r="J12" s="1">
+      <c r="J12" s="2">
         <v>34700</v>
       </c>
       <c r="K12" t="b">
@@ -1781,7 +1807,7 @@
       <c r="H13">
         <v>-206</v>
       </c>
-      <c r="J13" s="1">
+      <c r="J13" s="2">
         <v>41204</v>
       </c>
       <c r="K13" t="b">
@@ -1813,7 +1839,7 @@
       <c r="H14">
         <v>-186.8</v>
       </c>
-      <c r="J14" s="1">
+      <c r="J14" s="2">
         <v>46111</v>
       </c>
       <c r="K14" t="b">
@@ -1845,7 +1871,7 @@
       <c r="H15">
         <v>-186.8</v>
       </c>
-      <c r="J15" s="1">
+      <c r="J15" s="2">
         <v>46111</v>
       </c>
       <c r="K15" t="b">
@@ -1877,7 +1903,7 @@
       <c r="H16">
         <v>-186.8</v>
       </c>
-      <c r="J16" s="1">
+      <c r="J16" s="2">
         <v>46111</v>
       </c>
       <c r="K16" t="b">
@@ -1909,7 +1935,7 @@
       <c r="H17">
         <v>-186.8</v>
       </c>
-      <c r="J17" s="1">
+      <c r="J17" s="2">
         <v>46111</v>
       </c>
       <c r="K17" t="b">
@@ -1941,7 +1967,7 @@
       <c r="H18">
         <v>-186.8</v>
       </c>
-      <c r="J18" s="1">
+      <c r="J18" s="2">
         <v>46111</v>
       </c>
       <c r="K18" t="b">
@@ -1973,7 +1999,7 @@
       <c r="H19">
         <v>-128.6</v>
       </c>
-      <c r="J19" s="1">
+      <c r="J19" s="2">
         <v>46161</v>
       </c>
       <c r="K19" t="b">
@@ -2005,7 +2031,7 @@
       <c r="H20">
         <v>-108.2</v>
       </c>
-      <c r="J20" s="1">
+      <c r="J20" s="2">
         <v>46242</v>
       </c>
       <c r="K20" t="b">
@@ -2037,7 +2063,7 @@
       <c r="H21">
         <v>-107</v>
       </c>
-      <c r="J21" s="1">
+      <c r="J21" s="2">
         <v>40979</v>
       </c>
       <c r="K21" t="b">
@@ -2069,7 +2095,7 @@
       <c r="H22">
         <v>-99.8</v>
       </c>
-      <c r="J22" s="1">
+      <c r="J22" s="2">
         <v>46255</v>
       </c>
       <c r="K22" t="b">
@@ -2101,7 +2127,7 @@
       <c r="H23">
         <v>-54.8</v>
       </c>
-      <c r="J23" s="1">
+      <c r="J23" s="2">
         <v>46285</v>
       </c>
       <c r="K23" t="b">
@@ -2133,7 +2159,7 @@
       <c r="H24">
         <v>-29.7</v>
       </c>
-      <c r="J24" s="1">
+      <c r="J24" s="2">
         <v>46269</v>
       </c>
       <c r="K24" t="b">
@@ -2165,7 +2191,7 @@
       <c r="H25">
         <v>-25.6</v>
       </c>
-      <c r="J25" s="1">
+      <c r="J25" s="2">
         <v>46282</v>
       </c>
       <c r="K25" t="b">
@@ -2197,7 +2223,7 @@
       <c r="H26">
         <v>-13.8</v>
       </c>
-      <c r="J26" s="1">
+      <c r="J26" s="2">
         <v>46236</v>
       </c>
       <c r="K26" t="b">
@@ -2229,7 +2255,7 @@
       <c r="H27">
         <v>9.9</v>
       </c>
-      <c r="J27" s="1">
+      <c r="J27" s="2">
         <v>46354</v>
       </c>
       <c r="K27" t="b">
@@ -2261,7 +2287,7 @@
       <c r="H28">
         <v>16.2</v>
       </c>
-      <c r="J28" s="1">
+      <c r="J28" s="2">
         <v>46326</v>
       </c>
       <c r="K28" t="b">
@@ -2293,7 +2319,7 @@
       <c r="H29">
         <v>30.4</v>
       </c>
-      <c r="J29" s="1">
+      <c r="J29" s="2">
         <v>46335</v>
       </c>
       <c r="K29" t="b">
@@ -2325,7 +2351,7 @@
       <c r="H30">
         <v>33.6</v>
       </c>
-      <c r="J30" s="1">
+      <c r="J30" s="2">
         <v>46326</v>
       </c>
       <c r="K30" t="b">
@@ -2357,7 +2383,7 @@
       <c r="H31">
         <v>36.7</v>
       </c>
-      <c r="J31" s="1">
+      <c r="J31" s="2">
         <v>46326</v>
       </c>
       <c r="K31" t="b">
@@ -2389,7 +2415,7 @@
       <c r="H32">
         <v>41.4</v>
       </c>
-      <c r="J32" s="1">
+      <c r="J32" s="2">
         <v>46335</v>
       </c>
       <c r="K32" t="b">
@@ -2421,7 +2447,7 @@
       <c r="H33">
         <v>42.8</v>
       </c>
-      <c r="J33" s="1">
+      <c r="J33" s="2">
         <v>46389</v>
       </c>
       <c r="K33" t="b">
@@ -2453,7 +2479,7 @@
       <c r="H34">
         <v>45.6</v>
       </c>
-      <c r="J34" s="1">
+      <c r="J34" s="2">
         <v>46475</v>
       </c>
       <c r="K34" t="b">
@@ -2485,7 +2511,7 @@
       <c r="H35">
         <v>47.2</v>
       </c>
-      <c r="J35" s="1">
+      <c r="J35" s="2">
         <v>46391</v>
       </c>
       <c r="K35" t="b">
@@ -2517,7 +2543,7 @@
       <c r="H36">
         <v>59.1</v>
       </c>
-      <c r="J36" s="1">
+      <c r="J36" s="2">
         <v>46509</v>
       </c>
       <c r="K36" t="b">
@@ -2549,7 +2575,7 @@
       <c r="H37">
         <v>61.1</v>
       </c>
-      <c r="J37" s="1">
+      <c r="J37" s="2">
         <v>46514</v>
       </c>
       <c r="K37" t="b">
@@ -2581,7 +2607,7 @@
       <c r="H38">
         <v>67</v>
       </c>
-      <c r="J38" s="1">
+      <c r="J38" s="2">
         <v>46336</v>
       </c>
       <c r="K38" t="b">
@@ -2613,7 +2639,7 @@
       <c r="H39">
         <v>72.5</v>
       </c>
-      <c r="J39" s="1">
+      <c r="J39" s="2">
         <v>46343</v>
       </c>
       <c r="K39" t="b">
@@ -2645,7 +2671,7 @@
       <c r="H40">
         <v>74.09999999999999</v>
       </c>
-      <c r="J40" s="1">
+      <c r="J40" s="2">
         <v>46326</v>
       </c>
       <c r="K40" t="b">
@@ -2677,7 +2703,7 @@
       <c r="H41">
         <v>74.09999999999999</v>
       </c>
-      <c r="J41" s="1">
+      <c r="J41" s="2">
         <v>46326</v>
       </c>
       <c r="K41" t="b">
@@ -2709,7 +2735,7 @@
       <c r="H42">
         <v>77.5</v>
       </c>
-      <c r="J42" s="1">
+      <c r="J42" s="2">
         <v>46346</v>
       </c>
       <c r="K42" t="b">
@@ -2741,7 +2767,7 @@
       <c r="H43">
         <v>95.2</v>
       </c>
-      <c r="J43" s="1">
+      <c r="J43" s="2">
         <v>46392</v>
       </c>
       <c r="K43" t="b">
@@ -2773,7 +2799,7 @@
       <c r="H44">
         <v>100</v>
       </c>
-      <c r="J44" s="1">
+      <c r="J44" s="2">
         <v>46375</v>
       </c>
       <c r="K44" t="b">
@@ -2805,7 +2831,7 @@
       <c r="H45">
         <v>100</v>
       </c>
-      <c r="J45" s="1">
+      <c r="J45" s="2">
         <v>46375</v>
       </c>
       <c r="K45" t="b">
@@ -2837,7 +2863,7 @@
       <c r="H46">
         <v>100.3</v>
       </c>
-      <c r="J46" s="1">
+      <c r="J46" s="2">
         <v>46345</v>
       </c>
       <c r="K46" t="b">
@@ -2869,7 +2895,7 @@
       <c r="H47">
         <v>104.1</v>
       </c>
-      <c r="J47" s="1">
+      <c r="J47" s="2">
         <v>46418</v>
       </c>
       <c r="K47" t="b">
@@ -2901,7 +2927,7 @@
       <c r="H48">
         <v>106.4</v>
       </c>
-      <c r="J48" s="1">
+      <c r="J48" s="2">
         <v>46347</v>
       </c>
       <c r="K48" t="b">
@@ -2933,7 +2959,7 @@
       <c r="H49">
         <v>114.3</v>
       </c>
-      <c r="J49" s="1">
+      <c r="J49" s="2">
         <v>46418</v>
       </c>
       <c r="K49" t="b">
@@ -2965,7 +2991,7 @@
       <c r="H50">
         <v>114.8</v>
       </c>
-      <c r="J50" s="1">
+      <c r="J50" s="2">
         <v>46400</v>
       </c>
       <c r="K50" t="b">
@@ -2997,7 +3023,7 @@
       <c r="H51">
         <v>133.6</v>
       </c>
-      <c r="J51" s="1">
+      <c r="J51" s="2">
         <v>46424</v>
       </c>
       <c r="K51" t="b">
@@ -3029,7 +3055,7 @@
       <c r="H52">
         <v>135.2</v>
       </c>
-      <c r="J52" s="1">
+      <c r="J52" s="2">
         <v>46384</v>
       </c>
       <c r="K52" t="b">
@@ -3061,7 +3087,7 @@
       <c r="H53">
         <v>141.4</v>
       </c>
-      <c r="J53" s="1">
+      <c r="J53" s="2">
         <v>46395</v>
       </c>
       <c r="K53" t="b">
@@ -3093,7 +3119,7 @@
       <c r="H54">
         <v>144.2</v>
       </c>
-      <c r="J54" s="1">
+      <c r="J54" s="2">
         <v>46388</v>
       </c>
       <c r="K54" t="b">
@@ -3125,7 +3151,7 @@
       <c r="H55">
         <v>160.3</v>
       </c>
-      <c r="J55" s="1">
+      <c r="J55" s="2">
         <v>46433</v>
       </c>
       <c r="K55" t="b">
@@ -3157,7 +3183,7 @@
       <c r="H56">
         <v>177</v>
       </c>
-      <c r="J56" s="1">
+      <c r="J56" s="2">
         <v>46397</v>
       </c>
       <c r="K56" t="b">
@@ -3189,7 +3215,7 @@
       <c r="H57">
         <v>177.2</v>
       </c>
-      <c r="J57" s="1">
+      <c r="J57" s="2">
         <v>46423</v>
       </c>
       <c r="K57" t="b">
@@ -3221,7 +3247,7 @@
       <c r="H58">
         <v>177.4</v>
       </c>
-      <c r="J58" s="1">
+      <c r="J58" s="2">
         <v>46490</v>
       </c>
       <c r="K58" t="b">
@@ -3253,7 +3279,7 @@
       <c r="H59">
         <v>178.8</v>
       </c>
-      <c r="J59" s="1">
+      <c r="J59" s="2">
         <v>46384</v>
       </c>
       <c r="K59" t="b">
@@ -3285,7 +3311,7 @@
       <c r="H60">
         <v>196.2</v>
       </c>
-      <c r="J60" s="1">
+      <c r="J60" s="2">
         <v>46392</v>
       </c>
       <c r="K60" t="b">
@@ -3317,7 +3343,7 @@
       <c r="H61">
         <v>202.9</v>
       </c>
-      <c r="J61" s="1">
+      <c r="J61" s="2">
         <v>46394</v>
       </c>
       <c r="K61" t="b">
@@ -3349,7 +3375,7 @@
       <c r="H62">
         <v>211.2</v>
       </c>
-      <c r="J62" s="1">
+      <c r="J62" s="2">
         <v>46451</v>
       </c>
       <c r="K62" t="b">
@@ -3381,7 +3407,7 @@
       <c r="H63">
         <v>275.6</v>
       </c>
-      <c r="J63" s="1">
+      <c r="J63" s="2">
         <v>46459</v>
       </c>
       <c r="K63" t="b">
@@ -3413,7 +3439,7 @@
       <c r="H64">
         <v>293.4</v>
       </c>
-      <c r="J64" s="1">
+      <c r="J64" s="2">
         <v>46473</v>
       </c>
       <c r="K64" t="b">
@@ -3448,7 +3474,7 @@
       <c r="I65" t="s">
         <v>312</v>
       </c>
-      <c r="J65" s="1">
+      <c r="J65" s="2">
         <v>36557</v>
       </c>
       <c r="K65" t="b">
@@ -3483,7 +3509,7 @@
       <c r="I66" t="s">
         <v>313</v>
       </c>
-      <c r="J66" s="1">
+      <c r="J66" s="2">
         <v>38353</v>
       </c>
       <c r="K66" t="b">
@@ -3518,7 +3544,7 @@
       <c r="I67" t="s">
         <v>314</v>
       </c>
-      <c r="J67" s="1">
+      <c r="J67" s="2">
         <v>45380</v>
       </c>
       <c r="K67" t="b">
@@ -3553,7 +3579,7 @@
       <c r="I68" t="s">
         <v>315</v>
       </c>
-      <c r="J68" s="1">
+      <c r="J68" s="2">
         <v>45421</v>
       </c>
       <c r="K68" t="b">
@@ -3588,7 +3614,7 @@
       <c r="I69" t="s">
         <v>315</v>
       </c>
-      <c r="J69" s="1">
+      <c r="J69" s="2">
         <v>45428</v>
       </c>
       <c r="K69" t="b">
@@ -3623,7 +3649,7 @@
       <c r="I70" t="s">
         <v>316</v>
       </c>
-      <c r="J70" s="1">
+      <c r="J70" s="2">
         <v>45490</v>
       </c>
       <c r="K70" t="b">
@@ -3658,7 +3684,7 @@
       <c r="I71" t="s">
         <v>317</v>
       </c>
-      <c r="J71" s="1">
+      <c r="J71" s="2">
         <v>45566</v>
       </c>
       <c r="K71" t="b">
@@ -3693,7 +3719,7 @@
       <c r="I72" t="s">
         <v>318</v>
       </c>
-      <c r="J72" s="1">
+      <c r="J72" s="2">
         <v>45986</v>
       </c>
       <c r="K72" t="b">
@@ -3728,7 +3754,7 @@
       <c r="I73" t="s">
         <v>319</v>
       </c>
-      <c r="J73" s="1">
+      <c r="J73" s="2">
         <v>46197</v>
       </c>
       <c r="K73" t="b">
@@ -3763,7 +3789,7 @@
       <c r="I74" t="s">
         <v>320</v>
       </c>
-      <c r="J74" s="1">
+      <c r="J74" s="2">
         <v>46212</v>
       </c>
       <c r="K74" t="b">
@@ -3798,7 +3824,7 @@
       <c r="I75" t="s">
         <v>320</v>
       </c>
-      <c r="J75" s="1">
+      <c r="J75" s="2">
         <v>46225</v>
       </c>
       <c r="K75" t="b">
@@ -3833,7 +3859,7 @@
       <c r="I76" t="s">
         <v>320</v>
       </c>
-      <c r="J76" s="1">
+      <c r="J76" s="2">
         <v>46235</v>
       </c>
       <c r="K76" t="b">
@@ -3868,7 +3894,7 @@
       <c r="I77" t="s">
         <v>321</v>
       </c>
-      <c r="J77" s="1">
+      <c r="J77" s="2">
         <v>46345</v>
       </c>
       <c r="K77" t="b">
@@ -3903,7 +3929,7 @@
       <c r="I78" t="s">
         <v>321</v>
       </c>
-      <c r="J78" s="1">
+      <c r="J78" s="2">
         <v>46360</v>
       </c>
       <c r="K78" t="b">
@@ -3938,7 +3964,7 @@
       <c r="I79" t="s">
         <v>322</v>
       </c>
-      <c r="J79" s="1">
+      <c r="J79" s="2">
         <v>46367</v>
       </c>
       <c r="K79" t="b">
@@ -3973,7 +3999,7 @@
       <c r="I80" t="s">
         <v>322</v>
       </c>
-      <c r="J80" s="1">
+      <c r="J80" s="2">
         <v>46368</v>
       </c>
       <c r="K80" t="b">
@@ -4008,7 +4034,7 @@
       <c r="I81" t="s">
         <v>322</v>
       </c>
-      <c r="J81" s="1">
+      <c r="J81" s="2">
         <v>46375</v>
       </c>
       <c r="K81" t="b">
@@ -4043,7 +4069,7 @@
       <c r="I82" t="s">
         <v>322</v>
       </c>
-      <c r="J82" s="1">
+      <c r="J82" s="2">
         <v>46387</v>
       </c>
       <c r="K82" t="b">
@@ -4078,7 +4104,7 @@
       <c r="I83" t="s">
         <v>322</v>
       </c>
-      <c r="J83" s="1">
+      <c r="J83" s="2">
         <v>46387</v>
       </c>
       <c r="K83" t="b">
@@ -4113,7 +4139,7 @@
       <c r="I84" t="s">
         <v>322</v>
       </c>
-      <c r="J84" s="1">
+      <c r="J84" s="2">
         <v>46387</v>
       </c>
       <c r="K84" t="b">
@@ -4148,7 +4174,7 @@
       <c r="I85" t="s">
         <v>322</v>
       </c>
-      <c r="J85" s="1">
+      <c r="J85" s="2">
         <v>46388</v>
       </c>
       <c r="K85" t="b">
@@ -4183,7 +4209,7 @@
       <c r="I86" t="s">
         <v>323</v>
       </c>
-      <c r="J86" s="1">
+      <c r="J86" s="2">
         <v>46401</v>
       </c>
       <c r="K86" t="b">
@@ -4218,7 +4244,7 @@
       <c r="I87" t="s">
         <v>323</v>
       </c>
-      <c r="J87" s="1">
+      <c r="J87" s="2">
         <v>46401</v>
       </c>
       <c r="K87" t="b">
@@ -4253,7 +4279,7 @@
       <c r="I88" t="s">
         <v>323</v>
       </c>
-      <c r="J88" s="1">
+      <c r="J88" s="2">
         <v>46401</v>
       </c>
       <c r="K88" t="b">
@@ -4288,7 +4314,7 @@
       <c r="I89" t="s">
         <v>323</v>
       </c>
-      <c r="J89" s="1">
+      <c r="J89" s="2">
         <v>46403</v>
       </c>
       <c r="K89" t="b">
@@ -4323,7 +4349,7 @@
       <c r="I90" t="s">
         <v>323</v>
       </c>
-      <c r="J90" s="1">
+      <c r="J90" s="2">
         <v>46412</v>
       </c>
       <c r="K90" t="b">
@@ -4358,7 +4384,7 @@
       <c r="I91" t="s">
         <v>323</v>
       </c>
-      <c r="J91" s="1">
+      <c r="J91" s="2">
         <v>46412</v>
       </c>
       <c r="K91" t="b">
@@ -4393,7 +4419,7 @@
       <c r="I92" t="s">
         <v>323</v>
       </c>
-      <c r="J92" s="1">
+      <c r="J92" s="2">
         <v>46424</v>
       </c>
       <c r="K92" t="b">
@@ -4428,7 +4454,7 @@
       <c r="I93" t="s">
         <v>324</v>
       </c>
-      <c r="J93" s="1">
+      <c r="J93" s="2">
         <v>46427</v>
       </c>
       <c r="K93" t="b">
@@ -4463,7 +4489,7 @@
       <c r="I94" t="s">
         <v>324</v>
       </c>
-      <c r="J94" s="1">
+      <c r="J94" s="2">
         <v>46427</v>
       </c>
       <c r="K94" t="b">
@@ -4498,7 +4524,7 @@
       <c r="I95" t="s">
         <v>324</v>
       </c>
-      <c r="J95" s="1">
+      <c r="J95" s="2">
         <v>46437</v>
       </c>
       <c r="K95" t="b">
@@ -4533,7 +4559,7 @@
       <c r="I96" t="s">
         <v>324</v>
       </c>
-      <c r="J96" s="1">
+      <c r="J96" s="2">
         <v>46451</v>
       </c>
       <c r="K96" t="b">
@@ -4568,7 +4594,7 @@
       <c r="I97" t="s">
         <v>324</v>
       </c>
-      <c r="J97" s="1">
+      <c r="J97" s="2">
         <v>46451</v>
       </c>
       <c r="K97" t="b">
@@ -4603,7 +4629,7 @@
       <c r="I98" t="s">
         <v>325</v>
       </c>
-      <c r="J98" s="1">
+      <c r="J98" s="2">
         <v>46455</v>
       </c>
       <c r="K98" t="b">
@@ -4638,7 +4664,7 @@
       <c r="I99" t="s">
         <v>325</v>
       </c>
-      <c r="J99" s="1">
+      <c r="J99" s="2">
         <v>46456</v>
       </c>
       <c r="K99" t="b">
@@ -4673,7 +4699,7 @@
       <c r="I100" t="s">
         <v>325</v>
       </c>
-      <c r="J100" s="1">
+      <c r="J100" s="2">
         <v>46457</v>
       </c>
       <c r="K100" t="b">
@@ -4708,7 +4734,7 @@
       <c r="I101" t="s">
         <v>325</v>
       </c>
-      <c r="J101" s="1">
+      <c r="J101" s="2">
         <v>46462</v>
       </c>
       <c r="K101" t="b">
@@ -4743,7 +4769,7 @@
       <c r="I102" t="s">
         <v>325</v>
       </c>
-      <c r="J102" s="1">
+      <c r="J102" s="2">
         <v>46464</v>
       </c>
       <c r="K102" t="b">
@@ -4778,7 +4804,7 @@
       <c r="I103" t="s">
         <v>325</v>
       </c>
-      <c r="J103" s="1">
+      <c r="J103" s="2">
         <v>46470</v>
       </c>
       <c r="K103" t="b">
@@ -4813,7 +4839,7 @@
       <c r="I104" t="s">
         <v>325</v>
       </c>
-      <c r="J104" s="1">
+      <c r="J104" s="2">
         <v>46485</v>
       </c>
       <c r="K104" t="b">
@@ -4848,7 +4874,7 @@
       <c r="I105" t="s">
         <v>326</v>
       </c>
-      <c r="J105" s="1">
+      <c r="J105" s="2">
         <v>46499</v>
       </c>
       <c r="K105" t="b">
@@ -4883,7 +4909,7 @@
       <c r="I106" t="s">
         <v>326</v>
       </c>
-      <c r="J106" s="1">
+      <c r="J106" s="2">
         <v>46504</v>
       </c>
       <c r="K106" t="b">
@@ -4918,7 +4944,7 @@
       <c r="I107" t="s">
         <v>326</v>
       </c>
-      <c r="J107" s="1">
+      <c r="J107" s="2">
         <v>46507</v>
       </c>
       <c r="K107" t="b">
@@ -4953,7 +4979,7 @@
       <c r="I108" t="s">
         <v>326</v>
       </c>
-      <c r="J108" s="1">
+      <c r="J108" s="2">
         <v>46508</v>
       </c>
       <c r="K108" t="b">
@@ -4988,7 +5014,7 @@
       <c r="I109" t="s">
         <v>326</v>
       </c>
-      <c r="J109" s="1">
+      <c r="J109" s="2">
         <v>46512</v>
       </c>
       <c r="K109" t="b">
@@ -5023,7 +5049,7 @@
       <c r="I110" t="s">
         <v>327</v>
       </c>
-      <c r="J110" s="1">
+      <c r="J110" s="2">
         <v>46528</v>
       </c>
       <c r="K110" t="b">
@@ -5058,7 +5084,7 @@
       <c r="I111" t="s">
         <v>327</v>
       </c>
-      <c r="J111" s="1">
+      <c r="J111" s="2">
         <v>46529</v>
       </c>
       <c r="K111" t="b">
@@ -5093,7 +5119,7 @@
       <c r="I112" t="s">
         <v>327</v>
       </c>
-      <c r="J112" s="1">
+      <c r="J112" s="2">
         <v>46537</v>
       </c>
       <c r="K112" t="b">
@@ -5128,7 +5154,7 @@
       <c r="I113" t="s">
         <v>328</v>
       </c>
-      <c r="J113" s="1">
+      <c r="J113" s="2">
         <v>46546</v>
       </c>
       <c r="K113" t="b">
@@ -5163,7 +5189,7 @@
       <c r="I114" t="s">
         <v>328</v>
       </c>
-      <c r="J114" s="1">
+      <c r="J114" s="2">
         <v>46547</v>
       </c>
       <c r="K114" t="b">
@@ -5198,7 +5224,7 @@
       <c r="I115" t="s">
         <v>328</v>
       </c>
-      <c r="J115" s="1">
+      <c r="J115" s="2">
         <v>46547</v>
       </c>
       <c r="K115" t="b">
@@ -5233,7 +5259,7 @@
       <c r="I116" t="s">
         <v>328</v>
       </c>
-      <c r="J116" s="1">
+      <c r="J116" s="2">
         <v>46551</v>
       </c>
       <c r="K116" t="b">
@@ -5268,7 +5294,7 @@
       <c r="I117" t="s">
         <v>328</v>
       </c>
-      <c r="J117" s="1">
+      <c r="J117" s="2">
         <v>46560</v>
       </c>
       <c r="K117" t="b">
@@ -5303,7 +5329,7 @@
       <c r="I118" t="s">
         <v>328</v>
       </c>
-      <c r="J118" s="1">
+      <c r="J118" s="2">
         <v>46568</v>
       </c>
       <c r="K118" t="b">
@@ -5338,7 +5364,7 @@
       <c r="I119" t="s">
         <v>329</v>
       </c>
-      <c r="J119" s="1">
+      <c r="J119" s="2">
         <v>46592</v>
       </c>
       <c r="K119" t="b">
@@ -5373,7 +5399,7 @@
       <c r="I120" t="s">
         <v>329</v>
       </c>
-      <c r="J120" s="1">
+      <c r="J120" s="2">
         <v>46603</v>
       </c>
       <c r="K120" t="b">
@@ -5408,7 +5434,7 @@
       <c r="I121" t="s">
         <v>330</v>
       </c>
-      <c r="J121" s="1">
+      <c r="J121" s="2">
         <v>46611</v>
       </c>
       <c r="K121" t="b">
@@ -5443,7 +5469,7 @@
       <c r="I122" t="s">
         <v>330</v>
       </c>
-      <c r="J122" s="1">
+      <c r="J122" s="2">
         <v>46631</v>
       </c>
       <c r="K122" t="b">
@@ -5478,7 +5504,7 @@
       <c r="I123" t="s">
         <v>331</v>
       </c>
-      <c r="J123" s="1">
+      <c r="J123" s="2">
         <v>46645</v>
       </c>
       <c r="K123" t="b">
@@ -5513,7 +5539,7 @@
       <c r="I124" t="s">
         <v>331</v>
       </c>
-      <c r="J124" s="1">
+      <c r="J124" s="2">
         <v>46646</v>
       </c>
       <c r="K124" t="b">
@@ -5548,7 +5574,7 @@
       <c r="I125" t="s">
         <v>331</v>
       </c>
-      <c r="J125" s="1">
+      <c r="J125" s="2">
         <v>46652</v>
       </c>
       <c r="K125" t="b">
@@ -5583,7 +5609,7 @@
       <c r="I126" t="s">
         <v>331</v>
       </c>
-      <c r="J126" s="1">
+      <c r="J126" s="2">
         <v>46658</v>
       </c>
       <c r="K126" t="b">
@@ -5618,7 +5644,7 @@
       <c r="I127" t="s">
         <v>331</v>
       </c>
-      <c r="J127" s="1">
+      <c r="J127" s="2">
         <v>46659</v>
       </c>
       <c r="K127" t="b">
@@ -5653,7 +5679,7 @@
       <c r="I128" t="s">
         <v>332</v>
       </c>
-      <c r="J128" s="1">
+      <c r="J128" s="2">
         <v>46254</v>
       </c>
       <c r="K128" t="b">
@@ -5688,7 +5714,7 @@
       <c r="I129" t="s">
         <v>333</v>
       </c>
-      <c r="J129" s="1">
+      <c r="J129" s="2">
         <v>46293</v>
       </c>
       <c r="K129" t="b">
@@ -5723,7 +5749,7 @@
       <c r="I130" t="s">
         <v>333</v>
       </c>
-      <c r="J130" s="1">
+      <c r="J130" s="2">
         <v>46296</v>
       </c>
       <c r="K130" t="b">
@@ -5758,7 +5784,7 @@
       <c r="I131" t="s">
         <v>334</v>
       </c>
-      <c r="J131" s="1">
+      <c r="J131" s="2">
         <v>46305</v>
       </c>
       <c r="K131" t="b">
@@ -5793,7 +5819,7 @@
       <c r="I132" t="s">
         <v>335</v>
       </c>
-      <c r="J132" s="1">
+      <c r="J132" s="2">
         <v>46317</v>
       </c>
       <c r="K132" t="b">
@@ -5828,7 +5854,7 @@
       <c r="I133" t="s">
         <v>321</v>
       </c>
-      <c r="J133" s="1">
+      <c r="J133" s="2">
         <v>46333</v>
       </c>
       <c r="K133" t="b">
@@ -5863,7 +5889,7 @@
       <c r="I134" t="s">
         <v>336</v>
       </c>
-      <c r="J134" s="1">
+      <c r="J134" s="2">
         <v>46338</v>
       </c>
       <c r="K134" t="b">
@@ -5898,7 +5924,7 @@
       <c r="I135" t="s">
         <v>336</v>
       </c>
-      <c r="J135" s="1">
+      <c r="J135" s="2">
         <v>46338</v>
       </c>
       <c r="K135" t="b">
@@ -5933,7 +5959,7 @@
       <c r="I136" t="s">
         <v>337</v>
       </c>
-      <c r="J136" s="1">
+      <c r="J136" s="2">
         <v>46341</v>
       </c>
       <c r="K136" t="b">
@@ -5968,7 +5994,7 @@
       <c r="I137" t="s">
         <v>338</v>
       </c>
-      <c r="J137" s="1">
+      <c r="J137" s="2">
         <v>46344</v>
       </c>
       <c r="K137" t="b">
@@ -6000,7 +6026,7 @@
       <c r="H138">
         <v>-1476</v>
       </c>
-      <c r="J138" s="1">
+      <c r="J138" s="2">
         <v>43773</v>
       </c>
       <c r="K138" t="b">
@@ -6032,7 +6058,7 @@
       <c r="H139">
         <v>-1469</v>
       </c>
-      <c r="J139" s="1">
+      <c r="J139" s="2">
         <v>43773</v>
       </c>
       <c r="K139" t="b">
@@ -6064,7 +6090,7 @@
       <c r="H140">
         <v>-1280</v>
       </c>
-      <c r="J140" s="1">
+      <c r="J140" s="2">
         <v>45295</v>
       </c>
       <c r="K140" t="b">
@@ -6096,7 +6122,7 @@
       <c r="H141">
         <v>-1141</v>
       </c>
-      <c r="J141" s="1">
+      <c r="J141" s="2">
         <v>45617</v>
       </c>
       <c r="K141" t="b">
@@ -6128,7 +6154,7 @@
       <c r="H142">
         <v>-1073</v>
       </c>
-      <c r="J142" s="1">
+      <c r="J142" s="2">
         <v>45677</v>
       </c>
       <c r="K142" t="b">
@@ -6160,7 +6186,7 @@
       <c r="H143">
         <v>-78</v>
       </c>
-      <c r="J143" s="1">
+      <c r="J143" s="2">
         <v>46254</v>
       </c>
       <c r="K143" t="b">
@@ -6192,7 +6218,7 @@
       <c r="H144">
         <v>-78</v>
       </c>
-      <c r="J144" s="1">
+      <c r="J144" s="2">
         <v>46254</v>
       </c>
       <c r="K144" t="b">
@@ -6224,7 +6250,7 @@
       <c r="H145">
         <v>-40</v>
       </c>
-      <c r="J145" s="1">
+      <c r="J145" s="2">
         <v>46092</v>
       </c>
       <c r="K145" t="b">
@@ -6256,7 +6282,7 @@
       <c r="H146">
         <v>-4</v>
       </c>
-      <c r="J146" s="1">
+      <c r="J146" s="2">
         <v>46298</v>
       </c>
       <c r="K146" t="b">
@@ -6288,7 +6314,7 @@
       <c r="H147">
         <v>43</v>
       </c>
-      <c r="J147" s="1">
+      <c r="J147" s="2">
         <v>46440</v>
       </c>
       <c r="K147" t="b">
@@ -6320,7 +6346,7 @@
       <c r="H148">
         <v>43</v>
       </c>
-      <c r="J148" s="1">
+      <c r="J148" s="2">
         <v>46440</v>
       </c>
       <c r="K148" t="b">
@@ -6352,7 +6378,7 @@
       <c r="H149">
         <v>72</v>
       </c>
-      <c r="J149" s="1">
+      <c r="J149" s="2">
         <v>46386</v>
       </c>
       <c r="K149" t="b">
@@ -6384,7 +6410,7 @@
       <c r="H150">
         <v>79</v>
       </c>
-      <c r="J150" s="1">
+      <c r="J150" s="2">
         <v>46326</v>
       </c>
       <c r="K150" t="b">
@@ -6416,7 +6442,7 @@
       <c r="H151">
         <v>79</v>
       </c>
-      <c r="J151" s="1">
+      <c r="J151" s="2">
         <v>46326</v>
       </c>
       <c r="K151" t="b">
@@ -6448,7 +6474,7 @@
       <c r="H152">
         <v>83</v>
       </c>
-      <c r="J152" s="1">
+      <c r="J152" s="2">
         <v>46395</v>
       </c>
       <c r="K152" t="b">
@@ -6480,7 +6506,7 @@
       <c r="H153">
         <v>102</v>
       </c>
-      <c r="J153" s="1">
+      <c r="J153" s="2">
         <v>46463</v>
       </c>
       <c r="K153" t="b">
@@ -6512,7 +6538,7 @@
       <c r="H154">
         <v>106</v>
       </c>
-      <c r="J154" s="1">
+      <c r="J154" s="2">
         <v>46423</v>
       </c>
       <c r="K154" t="b">
@@ -6544,7 +6570,7 @@
       <c r="H155">
         <v>107</v>
       </c>
-      <c r="J155" s="1">
+      <c r="J155" s="2">
         <v>46376</v>
       </c>
       <c r="K155" t="b">
@@ -6576,7 +6602,7 @@
       <c r="H156">
         <v>163</v>
       </c>
-      <c r="J156" s="1">
+      <c r="J156" s="2">
         <v>46592</v>
       </c>
       <c r="K156" t="b">
@@ -6608,7 +6634,7 @@
       <c r="H157">
         <v>168</v>
       </c>
-      <c r="J157" s="1">
+      <c r="J157" s="2">
         <v>46456</v>
       </c>
       <c r="K157" t="b">
@@ -6640,7 +6666,7 @@
       <c r="H158">
         <v>170</v>
       </c>
-      <c r="J158" s="1">
+      <c r="J158" s="2">
         <v>46458</v>
       </c>
       <c r="K158" t="b">
@@ -6672,7 +6698,7 @@
       <c r="H159">
         <v>188</v>
       </c>
-      <c r="J159" s="1">
+      <c r="J159" s="2">
         <v>46416</v>
       </c>
       <c r="K159" t="b">
@@ -6704,7 +6730,7 @@
       <c r="H160">
         <v>232</v>
       </c>
-      <c r="J160" s="1">
+      <c r="J160" s="2">
         <v>46509</v>
       </c>
       <c r="K160" t="b">
@@ -6736,7 +6762,7 @@
       <c r="H161">
         <v>238</v>
       </c>
-      <c r="J161" s="1">
+      <c r="J161" s="2">
         <v>46513</v>
       </c>
       <c r="K161" t="b">
@@ -6768,7 +6794,7 @@
       <c r="H162">
         <v>239</v>
       </c>
-      <c r="J162" s="1">
+      <c r="J162" s="2">
         <v>46445</v>
       </c>
       <c r="K162" t="b">
@@ -6800,7 +6826,7 @@
       <c r="H163">
         <v>239</v>
       </c>
-      <c r="J163" s="1">
+      <c r="J163" s="2">
         <v>46445</v>
       </c>
       <c r="K163" t="b">
@@ -6832,7 +6858,7 @@
       <c r="H164">
         <v>248</v>
       </c>
-      <c r="J164" s="1">
+      <c r="J164" s="2">
         <v>46592</v>
       </c>
       <c r="K164" t="b">
@@ -6864,7 +6890,7 @@
       <c r="H165">
         <v>250</v>
       </c>
-      <c r="J165" s="1">
+      <c r="J165" s="2">
         <v>46461</v>
       </c>
       <c r="K165" t="b">
@@ -6896,7 +6922,7 @@
       <c r="H166">
         <v>256</v>
       </c>
-      <c r="J166" s="1">
+      <c r="J166" s="2">
         <v>46622</v>
       </c>
       <c r="K166" t="b">
@@ -6928,7 +6954,7 @@
       <c r="H167">
         <v>331</v>
       </c>
-      <c r="J167" s="1">
+      <c r="J167" s="2">
         <v>46582</v>
       </c>
       <c r="K167" t="b">
@@ -6960,7 +6986,7 @@
       <c r="H168">
         <v>335</v>
       </c>
-      <c r="J168" s="1">
+      <c r="J168" s="2">
         <v>46513</v>
       </c>
       <c r="K168" t="b">
@@ -6992,7 +7018,7 @@
       <c r="H169">
         <v>363</v>
       </c>
-      <c r="J169" s="1">
+      <c r="J169" s="2">
         <v>46638</v>
       </c>
       <c r="K169" t="b">
@@ -7024,7 +7050,7 @@
       <c r="H170">
         <v>380</v>
       </c>
-      <c r="J170" s="1">
+      <c r="J170" s="2">
         <v>46530</v>
       </c>
       <c r="K170" t="b">
@@ -7056,7 +7082,7 @@
       <c r="H171">
         <v>403</v>
       </c>
-      <c r="J171" s="1">
+      <c r="J171" s="2">
         <v>46648</v>
       </c>
       <c r="K171" t="b">
@@ -7088,7 +7114,7 @@
       <c r="H172">
         <v>403</v>
       </c>
-      <c r="J172" s="1">
+      <c r="J172" s="2">
         <v>46648</v>
       </c>
       <c r="K172" t="b">
@@ -7120,7 +7146,7 @@
       <c r="H173">
         <v>409</v>
       </c>
-      <c r="J173" s="1">
+      <c r="J173" s="2">
         <v>46548</v>
       </c>
       <c r="K173" t="b">
@@ -7152,7 +7178,7 @@
       <c r="H174">
         <v>488</v>
       </c>
-      <c r="J174" s="1">
+      <c r="J174" s="2">
         <v>46190</v>
       </c>
       <c r="K174" t="b">
@@ -7184,7 +7210,7 @@
       <c r="H175">
         <v>533</v>
       </c>
-      <c r="J175" s="1">
+      <c r="J175" s="2">
         <v>46634</v>
       </c>
       <c r="K175" t="b">
@@ -7216,7 +7242,7 @@
       <c r="H176">
         <v>648</v>
       </c>
-      <c r="J176" s="1">
+      <c r="J176" s="2">
         <v>46377</v>
       </c>
       <c r="K176" t="b">
@@ -7248,7 +7274,7 @@
       <c r="H177">
         <v>648</v>
       </c>
-      <c r="J177" s="1">
+      <c r="J177" s="2">
         <v>46377</v>
       </c>
       <c r="K177" t="b">
@@ -7280,7 +7306,7 @@
       <c r="H178">
         <v>777</v>
       </c>
-      <c r="J178" s="1">
+      <c r="J178" s="2">
         <v>46396</v>
       </c>
       <c r="K178" t="b">
@@ -7312,7 +7338,7 @@
       <c r="H179">
         <v>777</v>
       </c>
-      <c r="J179" s="1">
+      <c r="J179" s="2">
         <v>46396</v>
       </c>
       <c r="K179" t="b">
@@ -7344,7 +7370,7 @@
       <c r="H180">
         <v>1588</v>
       </c>
-      <c r="J180" s="1">
+      <c r="J180" s="2">
         <v>46559</v>
       </c>
       <c r="K180" t="b">
@@ -7376,7 +7402,7 @@
       <c r="H181">
         <v>1588</v>
       </c>
-      <c r="J181" s="1">
+      <c r="J181" s="2">
         <v>46559</v>
       </c>
       <c r="K181" t="b">
@@ -7408,7 +7434,7 @@
       <c r="H182">
         <v>25565</v>
       </c>
-      <c r="J182" s="1">
+      <c r="J182" s="2">
         <v>46190</v>
       </c>
       <c r="K182" t="b">
@@ -7440,7 +7466,7 @@
       <c r="H183">
         <v>25567</v>
       </c>
-      <c r="J183" s="1">
+      <c r="J183" s="2">
         <v>46190</v>
       </c>
       <c r="K183" t="b">
@@ -7472,7 +7498,7 @@
       <c r="H184">
         <v>31293</v>
       </c>
-      <c r="J184" s="1">
+      <c r="J184" s="2">
         <v>46190</v>
       </c>
       <c r="K184" t="b">

--- a/Coordenadoria/02_Dados_Tratados/base_vencimentos_tratada.xlsx
+++ b/Coordenadoria/02_Dados_Tratados/base_vencimentos_tratada.xlsx
@@ -1040,16 +1040,8 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1065,7 +1057,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1073,30 +1065,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1396,37 +1370,37 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1455,7 +1429,7 @@
       <c r="H2">
         <v>-2354.2</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J2" s="1">
         <v>40669</v>
       </c>
       <c r="K2" t="b">
@@ -1487,7 +1461,7 @@
       <c r="H3">
         <v>-934.3</v>
       </c>
-      <c r="J3" s="2">
+      <c r="J3" s="1">
         <v>40669</v>
       </c>
       <c r="K3" t="b">
@@ -1519,7 +1493,7 @@
       <c r="H4">
         <v>-891.7</v>
       </c>
-      <c r="J4" s="2">
+      <c r="J4" s="1">
         <v>44884</v>
       </c>
       <c r="K4" t="b">
@@ -1551,7 +1525,7 @@
       <c r="H5">
         <v>-589.5</v>
       </c>
-      <c r="J5" s="2">
+      <c r="J5" s="1">
         <v>43855</v>
       </c>
       <c r="K5" t="b">
@@ -1583,7 +1557,7 @@
       <c r="H6">
         <v>-562</v>
       </c>
-      <c r="J6" s="2">
+      <c r="J6" s="1">
         <v>45804</v>
       </c>
       <c r="K6" t="b">
@@ -1615,7 +1589,7 @@
       <c r="H7">
         <v>-560.5</v>
       </c>
-      <c r="J7" s="2">
+      <c r="J7" s="1">
         <v>45804</v>
       </c>
       <c r="K7" t="b">
@@ -1647,7 +1621,7 @@
       <c r="H8">
         <v>-531.8</v>
       </c>
-      <c r="J8" s="2">
+      <c r="J8" s="1">
         <v>46014</v>
       </c>
       <c r="K8" t="b">
@@ -1679,7 +1653,7 @@
       <c r="H9">
         <v>-529.1</v>
       </c>
-      <c r="J9" s="2">
+      <c r="J9" s="1">
         <v>46014</v>
       </c>
       <c r="K9" t="b">
@@ -1711,7 +1685,7 @@
       <c r="H10">
         <v>-391.8</v>
       </c>
-      <c r="J10" s="2">
+      <c r="J10" s="1">
         <v>32786</v>
       </c>
       <c r="K10" t="b">
@@ -1743,7 +1717,7 @@
       <c r="H11">
         <v>-391.8</v>
       </c>
-      <c r="J11" s="2">
+      <c r="J11" s="1">
         <v>42769</v>
       </c>
       <c r="K11" t="b">
@@ -1775,7 +1749,7 @@
       <c r="H12">
         <v>-288.8</v>
       </c>
-      <c r="J12" s="2">
+      <c r="J12" s="1">
         <v>34700</v>
       </c>
       <c r="K12" t="b">
@@ -1807,7 +1781,7 @@
       <c r="H13">
         <v>-206</v>
       </c>
-      <c r="J13" s="2">
+      <c r="J13" s="1">
         <v>41204</v>
       </c>
       <c r="K13" t="b">
@@ -1839,7 +1813,7 @@
       <c r="H14">
         <v>-186.8</v>
       </c>
-      <c r="J14" s="2">
+      <c r="J14" s="1">
         <v>46111</v>
       </c>
       <c r="K14" t="b">
@@ -1871,7 +1845,7 @@
       <c r="H15">
         <v>-186.8</v>
       </c>
-      <c r="J15" s="2">
+      <c r="J15" s="1">
         <v>46111</v>
       </c>
       <c r="K15" t="b">
@@ -1903,7 +1877,7 @@
       <c r="H16">
         <v>-186.8</v>
       </c>
-      <c r="J16" s="2">
+      <c r="J16" s="1">
         <v>46111</v>
       </c>
       <c r="K16" t="b">
@@ -1935,7 +1909,7 @@
       <c r="H17">
         <v>-186.8</v>
       </c>
-      <c r="J17" s="2">
+      <c r="J17" s="1">
         <v>46111</v>
       </c>
       <c r="K17" t="b">
@@ -1967,7 +1941,7 @@
       <c r="H18">
         <v>-186.8</v>
       </c>
-      <c r="J18" s="2">
+      <c r="J18" s="1">
         <v>46111</v>
       </c>
       <c r="K18" t="b">
@@ -1999,7 +1973,7 @@
       <c r="H19">
         <v>-128.6</v>
       </c>
-      <c r="J19" s="2">
+      <c r="J19" s="1">
         <v>46161</v>
       </c>
       <c r="K19" t="b">
@@ -2031,7 +2005,7 @@
       <c r="H20">
         <v>-108.2</v>
       </c>
-      <c r="J20" s="2">
+      <c r="J20" s="1">
         <v>46242</v>
       </c>
       <c r="K20" t="b">
@@ -2063,7 +2037,7 @@
       <c r="H21">
         <v>-107</v>
       </c>
-      <c r="J21" s="2">
+      <c r="J21" s="1">
         <v>40979</v>
       </c>
       <c r="K21" t="b">
@@ -2095,7 +2069,7 @@
       <c r="H22">
         <v>-99.8</v>
       </c>
-      <c r="J22" s="2">
+      <c r="J22" s="1">
         <v>46255</v>
       </c>
       <c r="K22" t="b">
@@ -2127,7 +2101,7 @@
       <c r="H23">
         <v>-54.8</v>
       </c>
-      <c r="J23" s="2">
+      <c r="J23" s="1">
         <v>46285</v>
       </c>
       <c r="K23" t="b">
@@ -2159,7 +2133,7 @@
       <c r="H24">
         <v>-29.7</v>
       </c>
-      <c r="J24" s="2">
+      <c r="J24" s="1">
         <v>46269</v>
       </c>
       <c r="K24" t="b">
@@ -2191,7 +2165,7 @@
       <c r="H25">
         <v>-25.6</v>
       </c>
-      <c r="J25" s="2">
+      <c r="J25" s="1">
         <v>46282</v>
       </c>
       <c r="K25" t="b">
@@ -2223,7 +2197,7 @@
       <c r="H26">
         <v>-13.8</v>
       </c>
-      <c r="J26" s="2">
+      <c r="J26" s="1">
         <v>46236</v>
       </c>
       <c r="K26" t="b">
@@ -2255,7 +2229,7 @@
       <c r="H27">
         <v>9.9</v>
       </c>
-      <c r="J27" s="2">
+      <c r="J27" s="1">
         <v>46354</v>
       </c>
       <c r="K27" t="b">
@@ -2287,7 +2261,7 @@
       <c r="H28">
         <v>16.2</v>
       </c>
-      <c r="J28" s="2">
+      <c r="J28" s="1">
         <v>46326</v>
       </c>
       <c r="K28" t="b">
@@ -2319,7 +2293,7 @@
       <c r="H29">
         <v>30.4</v>
       </c>
-      <c r="J29" s="2">
+      <c r="J29" s="1">
         <v>46335</v>
       </c>
       <c r="K29" t="b">
@@ -2351,7 +2325,7 @@
       <c r="H30">
         <v>33.6</v>
       </c>
-      <c r="J30" s="2">
+      <c r="J30" s="1">
         <v>46326</v>
       </c>
       <c r="K30" t="b">
@@ -2383,7 +2357,7 @@
       <c r="H31">
         <v>36.7</v>
       </c>
-      <c r="J31" s="2">
+      <c r="J31" s="1">
         <v>46326</v>
       </c>
       <c r="K31" t="b">
@@ -2415,7 +2389,7 @@
       <c r="H32">
         <v>41.4</v>
       </c>
-      <c r="J32" s="2">
+      <c r="J32" s="1">
         <v>46335</v>
       </c>
       <c r="K32" t="b">
@@ -2447,7 +2421,7 @@
       <c r="H33">
         <v>42.8</v>
       </c>
-      <c r="J33" s="2">
+      <c r="J33" s="1">
         <v>46389</v>
       </c>
       <c r="K33" t="b">
@@ -2479,7 +2453,7 @@
       <c r="H34">
         <v>45.6</v>
       </c>
-      <c r="J34" s="2">
+      <c r="J34" s="1">
         <v>46475</v>
       </c>
       <c r="K34" t="b">
@@ -2511,7 +2485,7 @@
       <c r="H35">
         <v>47.2</v>
       </c>
-      <c r="J35" s="2">
+      <c r="J35" s="1">
         <v>46391</v>
       </c>
       <c r="K35" t="b">
@@ -2543,7 +2517,7 @@
       <c r="H36">
         <v>59.1</v>
       </c>
-      <c r="J36" s="2">
+      <c r="J36" s="1">
         <v>46509</v>
       </c>
       <c r="K36" t="b">
@@ -2575,7 +2549,7 @@
       <c r="H37">
         <v>61.1</v>
       </c>
-      <c r="J37" s="2">
+      <c r="J37" s="1">
         <v>46514</v>
       </c>
       <c r="K37" t="b">
@@ -2607,7 +2581,7 @@
       <c r="H38">
         <v>67</v>
       </c>
-      <c r="J38" s="2">
+      <c r="J38" s="1">
         <v>46336</v>
       </c>
       <c r="K38" t="b">
@@ -2639,7 +2613,7 @@
       <c r="H39">
         <v>72.5</v>
       </c>
-      <c r="J39" s="2">
+      <c r="J39" s="1">
         <v>46343</v>
       </c>
       <c r="K39" t="b">
@@ -2671,7 +2645,7 @@
       <c r="H40">
         <v>74.09999999999999</v>
       </c>
-      <c r="J40" s="2">
+      <c r="J40" s="1">
         <v>46326</v>
       </c>
       <c r="K40" t="b">
@@ -2703,7 +2677,7 @@
       <c r="H41">
         <v>74.09999999999999</v>
       </c>
-      <c r="J41" s="2">
+      <c r="J41" s="1">
         <v>46326</v>
       </c>
       <c r="K41" t="b">
@@ -2735,7 +2709,7 @@
       <c r="H42">
         <v>77.5</v>
       </c>
-      <c r="J42" s="2">
+      <c r="J42" s="1">
         <v>46346</v>
       </c>
       <c r="K42" t="b">
@@ -2767,7 +2741,7 @@
       <c r="H43">
         <v>95.2</v>
       </c>
-      <c r="J43" s="2">
+      <c r="J43" s="1">
         <v>46392</v>
       </c>
       <c r="K43" t="b">
@@ -2799,7 +2773,7 @@
       <c r="H44">
         <v>100</v>
       </c>
-      <c r="J44" s="2">
+      <c r="J44" s="1">
         <v>46375</v>
       </c>
       <c r="K44" t="b">
@@ -2831,7 +2805,7 @@
       <c r="H45">
         <v>100</v>
       </c>
-      <c r="J45" s="2">
+      <c r="J45" s="1">
         <v>46375</v>
       </c>
       <c r="K45" t="b">
@@ -2863,7 +2837,7 @@
       <c r="H46">
         <v>100.3</v>
       </c>
-      <c r="J46" s="2">
+      <c r="J46" s="1">
         <v>46345</v>
       </c>
       <c r="K46" t="b">
@@ -2895,7 +2869,7 @@
       <c r="H47">
         <v>104.1</v>
       </c>
-      <c r="J47" s="2">
+      <c r="J47" s="1">
         <v>46418</v>
       </c>
       <c r="K47" t="b">
@@ -2927,7 +2901,7 @@
       <c r="H48">
         <v>106.4</v>
       </c>
-      <c r="J48" s="2">
+      <c r="J48" s="1">
         <v>46347</v>
       </c>
       <c r="K48" t="b">
@@ -2959,7 +2933,7 @@
       <c r="H49">
         <v>114.3</v>
       </c>
-      <c r="J49" s="2">
+      <c r="J49" s="1">
         <v>46418</v>
       </c>
       <c r="K49" t="b">
@@ -2991,7 +2965,7 @@
       <c r="H50">
         <v>114.8</v>
       </c>
-      <c r="J50" s="2">
+      <c r="J50" s="1">
         <v>46400</v>
       </c>
       <c r="K50" t="b">
@@ -3023,7 +2997,7 @@
       <c r="H51">
         <v>133.6</v>
       </c>
-      <c r="J51" s="2">
+      <c r="J51" s="1">
         <v>46424</v>
       </c>
       <c r="K51" t="b">
@@ -3055,7 +3029,7 @@
       <c r="H52">
         <v>135.2</v>
       </c>
-      <c r="J52" s="2">
+      <c r="J52" s="1">
         <v>46384</v>
       </c>
       <c r="K52" t="b">
@@ -3087,7 +3061,7 @@
       <c r="H53">
         <v>141.4</v>
       </c>
-      <c r="J53" s="2">
+      <c r="J53" s="1">
         <v>46395</v>
       </c>
       <c r="K53" t="b">
@@ -3119,7 +3093,7 @@
       <c r="H54">
         <v>144.2</v>
       </c>
-      <c r="J54" s="2">
+      <c r="J54" s="1">
         <v>46388</v>
       </c>
       <c r="K54" t="b">
@@ -3151,7 +3125,7 @@
       <c r="H55">
         <v>160.3</v>
       </c>
-      <c r="J55" s="2">
+      <c r="J55" s="1">
         <v>46433</v>
       </c>
       <c r="K55" t="b">
@@ -3183,7 +3157,7 @@
       <c r="H56">
         <v>177</v>
       </c>
-      <c r="J56" s="2">
+      <c r="J56" s="1">
         <v>46397</v>
       </c>
       <c r="K56" t="b">
@@ -3215,7 +3189,7 @@
       <c r="H57">
         <v>177.2</v>
       </c>
-      <c r="J57" s="2">
+      <c r="J57" s="1">
         <v>46423</v>
       </c>
       <c r="K57" t="b">
@@ -3247,7 +3221,7 @@
       <c r="H58">
         <v>177.4</v>
       </c>
-      <c r="J58" s="2">
+      <c r="J58" s="1">
         <v>46490</v>
       </c>
       <c r="K58" t="b">
@@ -3279,7 +3253,7 @@
       <c r="H59">
         <v>178.8</v>
       </c>
-      <c r="J59" s="2">
+      <c r="J59" s="1">
         <v>46384</v>
       </c>
       <c r="K59" t="b">
@@ -3311,7 +3285,7 @@
       <c r="H60">
         <v>196.2</v>
       </c>
-      <c r="J60" s="2">
+      <c r="J60" s="1">
         <v>46392</v>
       </c>
       <c r="K60" t="b">
@@ -3343,7 +3317,7 @@
       <c r="H61">
         <v>202.9</v>
       </c>
-      <c r="J61" s="2">
+      <c r="J61" s="1">
         <v>46394</v>
       </c>
       <c r="K61" t="b">
@@ -3375,7 +3349,7 @@
       <c r="H62">
         <v>211.2</v>
       </c>
-      <c r="J62" s="2">
+      <c r="J62" s="1">
         <v>46451</v>
       </c>
       <c r="K62" t="b">
@@ -3407,7 +3381,7 @@
       <c r="H63">
         <v>275.6</v>
       </c>
-      <c r="J63" s="2">
+      <c r="J63" s="1">
         <v>46459</v>
       </c>
       <c r="K63" t="b">
@@ -3439,7 +3413,7 @@
       <c r="H64">
         <v>293.4</v>
       </c>
-      <c r="J64" s="2">
+      <c r="J64" s="1">
         <v>46473</v>
       </c>
       <c r="K64" t="b">
@@ -3474,7 +3448,7 @@
       <c r="I65" t="s">
         <v>312</v>
       </c>
-      <c r="J65" s="2">
+      <c r="J65" s="1">
         <v>36557</v>
       </c>
       <c r="K65" t="b">
@@ -3509,7 +3483,7 @@
       <c r="I66" t="s">
         <v>313</v>
       </c>
-      <c r="J66" s="2">
+      <c r="J66" s="1">
         <v>38353</v>
       </c>
       <c r="K66" t="b">
@@ -3544,7 +3518,7 @@
       <c r="I67" t="s">
         <v>314</v>
       </c>
-      <c r="J67" s="2">
+      <c r="J67" s="1">
         <v>45380</v>
       </c>
       <c r="K67" t="b">
@@ -3579,7 +3553,7 @@
       <c r="I68" t="s">
         <v>315</v>
       </c>
-      <c r="J68" s="2">
+      <c r="J68" s="1">
         <v>45421</v>
       </c>
       <c r="K68" t="b">
@@ -3614,7 +3588,7 @@
       <c r="I69" t="s">
         <v>315</v>
       </c>
-      <c r="J69" s="2">
+      <c r="J69" s="1">
         <v>45428</v>
       </c>
       <c r="K69" t="b">
@@ -3649,7 +3623,7 @@
       <c r="I70" t="s">
         <v>316</v>
       </c>
-      <c r="J70" s="2">
+      <c r="J70" s="1">
         <v>45490</v>
       </c>
       <c r="K70" t="b">
@@ -3684,7 +3658,7 @@
       <c r="I71" t="s">
         <v>317</v>
       </c>
-      <c r="J71" s="2">
+      <c r="J71" s="1">
         <v>45566</v>
       </c>
       <c r="K71" t="b">
@@ -3719,7 +3693,7 @@
       <c r="I72" t="s">
         <v>318</v>
       </c>
-      <c r="J72" s="2">
+      <c r="J72" s="1">
         <v>45986</v>
       </c>
       <c r="K72" t="b">
@@ -3754,7 +3728,7 @@
       <c r="I73" t="s">
         <v>319</v>
       </c>
-      <c r="J73" s="2">
+      <c r="J73" s="1">
         <v>46197</v>
       </c>
       <c r="K73" t="b">
@@ -3789,7 +3763,7 @@
       <c r="I74" t="s">
         <v>320</v>
       </c>
-      <c r="J74" s="2">
+      <c r="J74" s="1">
         <v>46212</v>
       </c>
       <c r="K74" t="b">
@@ -3824,7 +3798,7 @@
       <c r="I75" t="s">
         <v>320</v>
       </c>
-      <c r="J75" s="2">
+      <c r="J75" s="1">
         <v>46225</v>
       </c>
       <c r="K75" t="b">
@@ -3859,7 +3833,7 @@
       <c r="I76" t="s">
         <v>320</v>
       </c>
-      <c r="J76" s="2">
+      <c r="J76" s="1">
         <v>46235</v>
       </c>
       <c r="K76" t="b">
@@ -3894,7 +3868,7 @@
       <c r="I77" t="s">
         <v>321</v>
       </c>
-      <c r="J77" s="2">
+      <c r="J77" s="1">
         <v>46345</v>
       </c>
       <c r="K77" t="b">
@@ -3929,7 +3903,7 @@
       <c r="I78" t="s">
         <v>321</v>
       </c>
-      <c r="J78" s="2">
+      <c r="J78" s="1">
         <v>46360</v>
       </c>
       <c r="K78" t="b">
@@ -3964,7 +3938,7 @@
       <c r="I79" t="s">
         <v>322</v>
       </c>
-      <c r="J79" s="2">
+      <c r="J79" s="1">
         <v>46367</v>
       </c>
       <c r="K79" t="b">
@@ -3999,7 +3973,7 @@
       <c r="I80" t="s">
         <v>322</v>
       </c>
-      <c r="J80" s="2">
+      <c r="J80" s="1">
         <v>46368</v>
       </c>
       <c r="K80" t="b">
@@ -4034,7 +4008,7 @@
       <c r="I81" t="s">
         <v>322</v>
       </c>
-      <c r="J81" s="2">
+      <c r="J81" s="1">
         <v>46375</v>
       </c>
       <c r="K81" t="b">
@@ -4069,7 +4043,7 @@
       <c r="I82" t="s">
         <v>322</v>
       </c>
-      <c r="J82" s="2">
+      <c r="J82" s="1">
         <v>46387</v>
       </c>
       <c r="K82" t="b">
@@ -4104,7 +4078,7 @@
       <c r="I83" t="s">
         <v>322</v>
       </c>
-      <c r="J83" s="2">
+      <c r="J83" s="1">
         <v>46387</v>
       </c>
       <c r="K83" t="b">
@@ -4139,7 +4113,7 @@
       <c r="I84" t="s">
         <v>322</v>
       </c>
-      <c r="J84" s="2">
+      <c r="J84" s="1">
         <v>46387</v>
       </c>
       <c r="K84" t="b">
@@ -4174,7 +4148,7 @@
       <c r="I85" t="s">
         <v>322</v>
       </c>
-      <c r="J85" s="2">
+      <c r="J85" s="1">
         <v>46388</v>
       </c>
       <c r="K85" t="b">
@@ -4209,7 +4183,7 @@
       <c r="I86" t="s">
         <v>323</v>
       </c>
-      <c r="J86" s="2">
+      <c r="J86" s="1">
         <v>46401</v>
       </c>
       <c r="K86" t="b">
@@ -4244,7 +4218,7 @@
       <c r="I87" t="s">
         <v>323</v>
       </c>
-      <c r="J87" s="2">
+      <c r="J87" s="1">
         <v>46401</v>
       </c>
       <c r="K87" t="b">
@@ -4279,7 +4253,7 @@
       <c r="I88" t="s">
         <v>323</v>
       </c>
-      <c r="J88" s="2">
+      <c r="J88" s="1">
         <v>46401</v>
       </c>
       <c r="K88" t="b">
@@ -4314,7 +4288,7 @@
       <c r="I89" t="s">
         <v>323</v>
       </c>
-      <c r="J89" s="2">
+      <c r="J89" s="1">
         <v>46403</v>
       </c>
       <c r="K89" t="b">
@@ -4349,7 +4323,7 @@
       <c r="I90" t="s">
         <v>323</v>
       </c>
-      <c r="J90" s="2">
+      <c r="J90" s="1">
         <v>46412</v>
       </c>
       <c r="K90" t="b">
@@ -4384,7 +4358,7 @@
       <c r="I91" t="s">
         <v>323</v>
       </c>
-      <c r="J91" s="2">
+      <c r="J91" s="1">
         <v>46412</v>
       </c>
       <c r="K91" t="b">
@@ -4419,7 +4393,7 @@
       <c r="I92" t="s">
         <v>323</v>
       </c>
-      <c r="J92" s="2">
+      <c r="J92" s="1">
         <v>46424</v>
       </c>
       <c r="K92" t="b">
@@ -4454,7 +4428,7 @@
       <c r="I93" t="s">
         <v>324</v>
       </c>
-      <c r="J93" s="2">
+      <c r="J93" s="1">
         <v>46427</v>
       </c>
       <c r="K93" t="b">
@@ -4489,7 +4463,7 @@
       <c r="I94" t="s">
         <v>324</v>
       </c>
-      <c r="J94" s="2">
+      <c r="J94" s="1">
         <v>46427</v>
       </c>
       <c r="K94" t="b">
@@ -4524,7 +4498,7 @@
       <c r="I95" t="s">
         <v>324</v>
       </c>
-      <c r="J95" s="2">
+      <c r="J95" s="1">
         <v>46437</v>
       </c>
       <c r="K95" t="b">
@@ -4559,7 +4533,7 @@
       <c r="I96" t="s">
         <v>324</v>
       </c>
-      <c r="J96" s="2">
+      <c r="J96" s="1">
         <v>46451</v>
       </c>
       <c r="K96" t="b">
@@ -4594,7 +4568,7 @@
       <c r="I97" t="s">
         <v>324</v>
       </c>
-      <c r="J97" s="2">
+      <c r="J97" s="1">
         <v>46451</v>
       </c>
       <c r="K97" t="b">
@@ -4629,7 +4603,7 @@
       <c r="I98" t="s">
         <v>325</v>
       </c>
-      <c r="J98" s="2">
+      <c r="J98" s="1">
         <v>46455</v>
       </c>
       <c r="K98" t="b">
@@ -4664,7 +4638,7 @@
       <c r="I99" t="s">
         <v>325</v>
       </c>
-      <c r="J99" s="2">
+      <c r="J99" s="1">
         <v>46456</v>
       </c>
       <c r="K99" t="b">
@@ -4699,7 +4673,7 @@
       <c r="I100" t="s">
         <v>325</v>
       </c>
-      <c r="J100" s="2">
+      <c r="J100" s="1">
         <v>46457</v>
       </c>
       <c r="K100" t="b">
@@ -4734,7 +4708,7 @@
       <c r="I101" t="s">
         <v>325</v>
       </c>
-      <c r="J101" s="2">
+      <c r="J101" s="1">
         <v>46462</v>
       </c>
       <c r="K101" t="b">
@@ -4769,7 +4743,7 @@
       <c r="I102" t="s">
         <v>325</v>
       </c>
-      <c r="J102" s="2">
+      <c r="J102" s="1">
         <v>46464</v>
       </c>
       <c r="K102" t="b">
@@ -4804,7 +4778,7 @@
       <c r="I103" t="s">
         <v>325</v>
       </c>
-      <c r="J103" s="2">
+      <c r="J103" s="1">
         <v>46470</v>
       </c>
       <c r="K103" t="b">
@@ -4839,7 +4813,7 @@
       <c r="I104" t="s">
         <v>325</v>
       </c>
-      <c r="J104" s="2">
+      <c r="J104" s="1">
         <v>46485</v>
       </c>
       <c r="K104" t="b">
@@ -4874,7 +4848,7 @@
       <c r="I105" t="s">
         <v>326</v>
       </c>
-      <c r="J105" s="2">
+      <c r="J105" s="1">
         <v>46499</v>
       </c>
       <c r="K105" t="b">
@@ -4909,7 +4883,7 @@
       <c r="I106" t="s">
         <v>326</v>
       </c>
-      <c r="J106" s="2">
+      <c r="J106" s="1">
         <v>46504</v>
       </c>
       <c r="K106" t="b">
@@ -4944,7 +4918,7 @@
       <c r="I107" t="s">
         <v>326</v>
       </c>
-      <c r="J107" s="2">
+      <c r="J107" s="1">
         <v>46507</v>
       </c>
       <c r="K107" t="b">
@@ -4979,7 +4953,7 @@
       <c r="I108" t="s">
         <v>326</v>
       </c>
-      <c r="J108" s="2">
+      <c r="J108" s="1">
         <v>46508</v>
       </c>
       <c r="K108" t="b">
@@ -5014,7 +4988,7 @@
       <c r="I109" t="s">
         <v>326</v>
       </c>
-      <c r="J109" s="2">
+      <c r="J109" s="1">
         <v>46512</v>
       </c>
       <c r="K109" t="b">
@@ -5049,7 +5023,7 @@
       <c r="I110" t="s">
         <v>327</v>
       </c>
-      <c r="J110" s="2">
+      <c r="J110" s="1">
         <v>46528</v>
       </c>
       <c r="K110" t="b">
@@ -5084,7 +5058,7 @@
       <c r="I111" t="s">
         <v>327</v>
       </c>
-      <c r="J111" s="2">
+      <c r="J111" s="1">
         <v>46529</v>
       </c>
       <c r="K111" t="b">
@@ -5119,7 +5093,7 @@
       <c r="I112" t="s">
         <v>327</v>
       </c>
-      <c r="J112" s="2">
+      <c r="J112" s="1">
         <v>46537</v>
       </c>
       <c r="K112" t="b">
@@ -5154,7 +5128,7 @@
       <c r="I113" t="s">
         <v>328</v>
       </c>
-      <c r="J113" s="2">
+      <c r="J113" s="1">
         <v>46546</v>
       </c>
       <c r="K113" t="b">
@@ -5189,7 +5163,7 @@
       <c r="I114" t="s">
         <v>328</v>
       </c>
-      <c r="J114" s="2">
+      <c r="J114" s="1">
         <v>46547</v>
       </c>
       <c r="K114" t="b">
@@ -5224,7 +5198,7 @@
       <c r="I115" t="s">
         <v>328</v>
       </c>
-      <c r="J115" s="2">
+      <c r="J115" s="1">
         <v>46547</v>
       </c>
       <c r="K115" t="b">
@@ -5259,7 +5233,7 @@
       <c r="I116" t="s">
         <v>328</v>
       </c>
-      <c r="J116" s="2">
+      <c r="J116" s="1">
         <v>46551</v>
       </c>
       <c r="K116" t="b">
@@ -5294,7 +5268,7 @@
       <c r="I117" t="s">
         <v>328</v>
       </c>
-      <c r="J117" s="2">
+      <c r="J117" s="1">
         <v>46560</v>
       </c>
       <c r="K117" t="b">
@@ -5329,7 +5303,7 @@
       <c r="I118" t="s">
         <v>328</v>
       </c>
-      <c r="J118" s="2">
+      <c r="J118" s="1">
         <v>46568</v>
       </c>
       <c r="K118" t="b">
@@ -5364,7 +5338,7 @@
       <c r="I119" t="s">
         <v>329</v>
       </c>
-      <c r="J119" s="2">
+      <c r="J119" s="1">
         <v>46592</v>
       </c>
       <c r="K119" t="b">
@@ -5399,7 +5373,7 @@
       <c r="I120" t="s">
         <v>329</v>
       </c>
-      <c r="J120" s="2">
+      <c r="J120" s="1">
         <v>46603</v>
       </c>
       <c r="K120" t="b">
@@ -5434,7 +5408,7 @@
       <c r="I121" t="s">
         <v>330</v>
       </c>
-      <c r="J121" s="2">
+      <c r="J121" s="1">
         <v>46611</v>
       </c>
       <c r="K121" t="b">
@@ -5469,7 +5443,7 @@
       <c r="I122" t="s">
         <v>330</v>
       </c>
-      <c r="J122" s="2">
+      <c r="J122" s="1">
         <v>46631</v>
       </c>
       <c r="K122" t="b">
@@ -5504,7 +5478,7 @@
       <c r="I123" t="s">
         <v>331</v>
       </c>
-      <c r="J123" s="2">
+      <c r="J123" s="1">
         <v>46645</v>
       </c>
       <c r="K123" t="b">
@@ -5539,7 +5513,7 @@
       <c r="I124" t="s">
         <v>331</v>
       </c>
-      <c r="J124" s="2">
+      <c r="J124" s="1">
         <v>46646</v>
       </c>
       <c r="K124" t="b">
@@ -5574,7 +5548,7 @@
       <c r="I125" t="s">
         <v>331</v>
       </c>
-      <c r="J125" s="2">
+      <c r="J125" s="1">
         <v>46652</v>
       </c>
       <c r="K125" t="b">
@@ -5609,7 +5583,7 @@
       <c r="I126" t="s">
         <v>331</v>
       </c>
-      <c r="J126" s="2">
+      <c r="J126" s="1">
         <v>46658</v>
       </c>
       <c r="K126" t="b">
@@ -5644,7 +5618,7 @@
       <c r="I127" t="s">
         <v>331</v>
       </c>
-      <c r="J127" s="2">
+      <c r="J127" s="1">
         <v>46659</v>
       </c>
       <c r="K127" t="b">
@@ -5679,7 +5653,7 @@
       <c r="I128" t="s">
         <v>332</v>
       </c>
-      <c r="J128" s="2">
+      <c r="J128" s="1">
         <v>46254</v>
       </c>
       <c r="K128" t="b">
@@ -5714,7 +5688,7 @@
       <c r="I129" t="s">
         <v>333</v>
       </c>
-      <c r="J129" s="2">
+      <c r="J129" s="1">
         <v>46293</v>
       </c>
       <c r="K129" t="b">
@@ -5749,7 +5723,7 @@
       <c r="I130" t="s">
         <v>333</v>
       </c>
-      <c r="J130" s="2">
+      <c r="J130" s="1">
         <v>46296</v>
       </c>
       <c r="K130" t="b">
@@ -5784,7 +5758,7 @@
       <c r="I131" t="s">
         <v>334</v>
       </c>
-      <c r="J131" s="2">
+      <c r="J131" s="1">
         <v>46305</v>
       </c>
       <c r="K131" t="b">
@@ -5819,7 +5793,7 @@
       <c r="I132" t="s">
         <v>335</v>
       </c>
-      <c r="J132" s="2">
+      <c r="J132" s="1">
         <v>46317</v>
       </c>
       <c r="K132" t="b">
@@ -5854,7 +5828,7 @@
       <c r="I133" t="s">
         <v>321</v>
       </c>
-      <c r="J133" s="2">
+      <c r="J133" s="1">
         <v>46333</v>
       </c>
       <c r="K133" t="b">
@@ -5889,7 +5863,7 @@
       <c r="I134" t="s">
         <v>336</v>
       </c>
-      <c r="J134" s="2">
+      <c r="J134" s="1">
         <v>46338</v>
       </c>
       <c r="K134" t="b">
@@ -5924,7 +5898,7 @@
       <c r="I135" t="s">
         <v>336</v>
       </c>
-      <c r="J135" s="2">
+      <c r="J135" s="1">
         <v>46338</v>
       </c>
       <c r="K135" t="b">
@@ -5959,7 +5933,7 @@
       <c r="I136" t="s">
         <v>337</v>
       </c>
-      <c r="J136" s="2">
+      <c r="J136" s="1">
         <v>46341</v>
       </c>
       <c r="K136" t="b">
@@ -5994,7 +5968,7 @@
       <c r="I137" t="s">
         <v>338</v>
       </c>
-      <c r="J137" s="2">
+      <c r="J137" s="1">
         <v>46344</v>
       </c>
       <c r="K137" t="b">
@@ -6026,7 +6000,7 @@
       <c r="H138">
         <v>-1476</v>
       </c>
-      <c r="J138" s="2">
+      <c r="J138" s="1">
         <v>43773</v>
       </c>
       <c r="K138" t="b">
@@ -6058,7 +6032,7 @@
       <c r="H139">
         <v>-1469</v>
       </c>
-      <c r="J139" s="2">
+      <c r="J139" s="1">
         <v>43773</v>
       </c>
       <c r="K139" t="b">
@@ -6090,7 +6064,7 @@
       <c r="H140">
         <v>-1280</v>
       </c>
-      <c r="J140" s="2">
+      <c r="J140" s="1">
         <v>45295</v>
       </c>
       <c r="K140" t="b">
@@ -6122,7 +6096,7 @@
       <c r="H141">
         <v>-1141</v>
       </c>
-      <c r="J141" s="2">
+      <c r="J141" s="1">
         <v>45617</v>
       </c>
       <c r="K141" t="b">
@@ -6154,7 +6128,7 @@
       <c r="H142">
         <v>-1073</v>
       </c>
-      <c r="J142" s="2">
+      <c r="J142" s="1">
         <v>45677</v>
       </c>
       <c r="K142" t="b">
@@ -6186,7 +6160,7 @@
       <c r="H143">
         <v>-78</v>
       </c>
-      <c r="J143" s="2">
+      <c r="J143" s="1">
         <v>46254</v>
       </c>
       <c r="K143" t="b">
@@ -6218,7 +6192,7 @@
       <c r="H144">
         <v>-78</v>
       </c>
-      <c r="J144" s="2">
+      <c r="J144" s="1">
         <v>46254</v>
       </c>
       <c r="K144" t="b">
@@ -6250,7 +6224,7 @@
       <c r="H145">
         <v>-40</v>
       </c>
-      <c r="J145" s="2">
+      <c r="J145" s="1">
         <v>46092</v>
       </c>
       <c r="K145" t="b">
@@ -6282,7 +6256,7 @@
       <c r="H146">
         <v>-4</v>
       </c>
-      <c r="J146" s="2">
+      <c r="J146" s="1">
         <v>46298</v>
       </c>
       <c r="K146" t="b">
@@ -6314,7 +6288,7 @@
       <c r="H147">
         <v>43</v>
       </c>
-      <c r="J147" s="2">
+      <c r="J147" s="1">
         <v>46440</v>
       </c>
       <c r="K147" t="b">
@@ -6346,7 +6320,7 @@
       <c r="H148">
         <v>43</v>
       </c>
-      <c r="J148" s="2">
+      <c r="J148" s="1">
         <v>46440</v>
       </c>
       <c r="K148" t="b">
@@ -6378,7 +6352,7 @@
       <c r="H149">
         <v>72</v>
       </c>
-      <c r="J149" s="2">
+      <c r="J149" s="1">
         <v>46386</v>
       </c>
       <c r="K149" t="b">
@@ -6410,7 +6384,7 @@
       <c r="H150">
         <v>79</v>
       </c>
-      <c r="J150" s="2">
+      <c r="J150" s="1">
         <v>46326</v>
       </c>
       <c r="K150" t="b">
@@ -6442,7 +6416,7 @@
       <c r="H151">
         <v>79</v>
       </c>
-      <c r="J151" s="2">
+      <c r="J151" s="1">
         <v>46326</v>
       </c>
       <c r="K151" t="b">
@@ -6474,7 +6448,7 @@
       <c r="H152">
         <v>83</v>
       </c>
-      <c r="J152" s="2">
+      <c r="J152" s="1">
         <v>46395</v>
       </c>
       <c r="K152" t="b">
@@ -6506,7 +6480,7 @@
       <c r="H153">
         <v>102</v>
       </c>
-      <c r="J153" s="2">
+      <c r="J153" s="1">
         <v>46463</v>
       </c>
       <c r="K153" t="b">
@@ -6538,7 +6512,7 @@
       <c r="H154">
         <v>106</v>
       </c>
-      <c r="J154" s="2">
+      <c r="J154" s="1">
         <v>46423</v>
       </c>
       <c r="K154" t="b">
@@ -6570,7 +6544,7 @@
       <c r="H155">
         <v>107</v>
       </c>
-      <c r="J155" s="2">
+      <c r="J155" s="1">
         <v>46376</v>
       </c>
       <c r="K155" t="b">
@@ -6602,7 +6576,7 @@
       <c r="H156">
         <v>163</v>
       </c>
-      <c r="J156" s="2">
+      <c r="J156" s="1">
         <v>46592</v>
       </c>
       <c r="K156" t="b">
@@ -6634,7 +6608,7 @@
       <c r="H157">
         <v>168</v>
       </c>
-      <c r="J157" s="2">
+      <c r="J157" s="1">
         <v>46456</v>
       </c>
       <c r="K157" t="b">
@@ -6666,7 +6640,7 @@
       <c r="H158">
         <v>170</v>
       </c>
-      <c r="J158" s="2">
+      <c r="J158" s="1">
         <v>46458</v>
       </c>
       <c r="K158" t="b">
@@ -6698,7 +6672,7 @@
       <c r="H159">
         <v>188</v>
       </c>
-      <c r="J159" s="2">
+      <c r="J159" s="1">
         <v>46416</v>
       </c>
       <c r="K159" t="b">
@@ -6730,7 +6704,7 @@
       <c r="H160">
         <v>232</v>
       </c>
-      <c r="J160" s="2">
+      <c r="J160" s="1">
         <v>46509</v>
       </c>
       <c r="K160" t="b">
@@ -6762,7 +6736,7 @@
       <c r="H161">
         <v>238</v>
       </c>
-      <c r="J161" s="2">
+      <c r="J161" s="1">
         <v>46513</v>
       </c>
       <c r="K161" t="b">
@@ -6794,7 +6768,7 @@
       <c r="H162">
         <v>239</v>
       </c>
-      <c r="J162" s="2">
+      <c r="J162" s="1">
         <v>46445</v>
       </c>
       <c r="K162" t="b">
@@ -6826,7 +6800,7 @@
       <c r="H163">
         <v>239</v>
       </c>
-      <c r="J163" s="2">
+      <c r="J163" s="1">
         <v>46445</v>
       </c>
       <c r="K163" t="b">
@@ -6858,7 +6832,7 @@
       <c r="H164">
         <v>248</v>
       </c>
-      <c r="J164" s="2">
+      <c r="J164" s="1">
         <v>46592</v>
       </c>
       <c r="K164" t="b">
@@ -6890,7 +6864,7 @@
       <c r="H165">
         <v>250</v>
       </c>
-      <c r="J165" s="2">
+      <c r="J165" s="1">
         <v>46461</v>
       </c>
       <c r="K165" t="b">
@@ -6922,7 +6896,7 @@
       <c r="H166">
         <v>256</v>
       </c>
-      <c r="J166" s="2">
+      <c r="J166" s="1">
         <v>46622</v>
       </c>
       <c r="K166" t="b">
@@ -6954,7 +6928,7 @@
       <c r="H167">
         <v>331</v>
       </c>
-      <c r="J167" s="2">
+      <c r="J167" s="1">
         <v>46582</v>
       </c>
       <c r="K167" t="b">
@@ -6986,7 +6960,7 @@
       <c r="H168">
         <v>335</v>
       </c>
-      <c r="J168" s="2">
+      <c r="J168" s="1">
         <v>46513</v>
       </c>
       <c r="K168" t="b">
@@ -7018,7 +6992,7 @@
       <c r="H169">
         <v>363</v>
       </c>
-      <c r="J169" s="2">
+      <c r="J169" s="1">
         <v>46638</v>
       </c>
       <c r="K169" t="b">
@@ -7050,7 +7024,7 @@
       <c r="H170">
         <v>380</v>
       </c>
-      <c r="J170" s="2">
+      <c r="J170" s="1">
         <v>46530</v>
       </c>
       <c r="K170" t="b">
@@ -7082,7 +7056,7 @@
       <c r="H171">
         <v>403</v>
       </c>
-      <c r="J171" s="2">
+      <c r="J171" s="1">
         <v>46648</v>
       </c>
       <c r="K171" t="b">
@@ -7114,7 +7088,7 @@
       <c r="H172">
         <v>403</v>
       </c>
-      <c r="J172" s="2">
+      <c r="J172" s="1">
         <v>46648</v>
       </c>
       <c r="K172" t="b">
@@ -7146,7 +7120,7 @@
       <c r="H173">
         <v>409</v>
       </c>
-      <c r="J173" s="2">
+      <c r="J173" s="1">
         <v>46548</v>
       </c>
       <c r="K173" t="b">
@@ -7178,7 +7152,7 @@
       <c r="H174">
         <v>488</v>
       </c>
-      <c r="J174" s="2">
+      <c r="J174" s="1">
         <v>46190</v>
       </c>
       <c r="K174" t="b">
@@ -7210,7 +7184,7 @@
       <c r="H175">
         <v>533</v>
       </c>
-      <c r="J175" s="2">
+      <c r="J175" s="1">
         <v>46634</v>
       </c>
       <c r="K175" t="b">
@@ -7242,7 +7216,7 @@
       <c r="H176">
         <v>648</v>
       </c>
-      <c r="J176" s="2">
+      <c r="J176" s="1">
         <v>46377</v>
       </c>
       <c r="K176" t="b">
@@ -7274,7 +7248,7 @@
       <c r="H177">
         <v>648</v>
       </c>
-      <c r="J177" s="2">
+      <c r="J177" s="1">
         <v>46377</v>
       </c>
       <c r="K177" t="b">
@@ -7306,7 +7280,7 @@
       <c r="H178">
         <v>777</v>
       </c>
-      <c r="J178" s="2">
+      <c r="J178" s="1">
         <v>46396</v>
       </c>
       <c r="K178" t="b">
@@ -7338,7 +7312,7 @@
       <c r="H179">
         <v>777</v>
       </c>
-      <c r="J179" s="2">
+      <c r="J179" s="1">
         <v>46396</v>
       </c>
       <c r="K179" t="b">
@@ -7370,7 +7344,7 @@
       <c r="H180">
         <v>1588</v>
       </c>
-      <c r="J180" s="2">
+      <c r="J180" s="1">
         <v>46559</v>
       </c>
       <c r="K180" t="b">
@@ -7402,7 +7376,7 @@
       <c r="H181">
         <v>1588</v>
       </c>
-      <c r="J181" s="2">
+      <c r="J181" s="1">
         <v>46559</v>
       </c>
       <c r="K181" t="b">
@@ -7434,7 +7408,7 @@
       <c r="H182">
         <v>25565</v>
       </c>
-      <c r="J182" s="2">
+      <c r="J182" s="1">
         <v>46190</v>
       </c>
       <c r="K182" t="b">
@@ -7466,7 +7440,7 @@
       <c r="H183">
         <v>25567</v>
       </c>
-      <c r="J183" s="2">
+      <c r="J183" s="1">
         <v>46190</v>
       </c>
       <c r="K183" t="b">
@@ -7498,7 +7472,7 @@
       <c r="H184">
         <v>31293</v>
       </c>
-      <c r="J184" s="2">
+      <c r="J184" s="1">
         <v>46190</v>
       </c>
       <c r="K184" t="b">
